--- a/docs/As-Is調査_未回答リスク一覧.xlsx
+++ b/docs/As-Is調査_未回答リスク一覧.xlsx
@@ -79,7 +79,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -99,6 +99,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFE699"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DDEBF7"/>
       </patternFill>
     </fill>
     <fill>
@@ -138,7 +143,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -167,10 +172,13 @@
     <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -538,7 +546,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A18"/>
+  <dimension ref="A1:A23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="140" customWidth="1" min="1" max="1"/>
@@ -650,7 +658,38 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>D列: 未回答だとシステム要件で何が起きるか（リスク） ／ E列: 影響する成果物・機能 ／ F列: 影響度 ／ G列: 未回答時に事務局が採用するデフォルト前提（＝帰責の基準線）</t>
+          <t>D列: 回答形式（薄青＝選択のみ・すぐ答えられる設問） ／ E列: 所要時間の保守的目安（分） ／ F列: 未回答だとシステム要件で何が起きるか ／ G列: 影響する成果物・機能 ／ H列: 影響度 ／ I列: 未回答時に事務局が採用するデフォルト前提（＝帰責の基準線）</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>【所要時間の考え方（保守的＝上振れ側）】</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>選択のみ=2分／選択+補足=5分／記述=10分／工数集計=30分／データ項目インベントリ=90分。読む時間を含む多めの想定。</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>設問数は多く見えるが、全拠点に記入いただくシートのうちコア設問37問中35問は「選択のみ」。記述が必要なのは工数集計と自由記述のみで、拠点の負担の実体はインベントリ（棚卸し）に集中している。</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>シート3〜9（手順〜海外固有）は選抜拠点のみを対象とした事務局ヒアリングの台本であり、拠点側での記入は不要。</t>
         </is>
       </c>
     </row>
@@ -665,16 +704,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G159"/>
+  <dimension ref="A1:I164"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="46" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="6" customWidth="1" min="6" max="6"/>
-    <col width="44" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="7" customWidth="1" min="5" max="5"/>
+    <col width="42" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="6" customWidth="1" min="8" max="8"/>
+    <col width="40" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -702,20 +743,31 @@
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
+          <t>回答形式</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>所要目安
+(分)</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
           <t>未回答時のシステム要件リスク</t>
         </is>
       </c>
-      <c r="E2" s="5" t="inlineStr">
+      <c r="G2" s="5" t="inlineStr">
         <is>
           <t>影響する成果物・機能</t>
         </is>
       </c>
-      <c r="F2" s="5" t="inlineStr">
+      <c r="H2" s="5" t="inlineStr">
         <is>
           <t>影響度</t>
         </is>
       </c>
-      <c r="G2" s="5" t="inlineStr">
+      <c r="I2" s="5" t="inlineStr">
         <is>
           <t>未回答時のデフォルト前提（帰責の基準線）</t>
         </is>
@@ -733,6 +785,8 @@
       <c r="E3" s="7" t="n"/>
       <c r="F3" s="7" t="n"/>
       <c r="G3" s="7" t="n"/>
+      <c r="H3" s="7" t="n"/>
+      <c r="I3" s="7" t="n"/>
     </row>
     <row r="4" ht="52" customHeight="1">
       <c r="A4" s="8" t="inlineStr">
@@ -750,22 +804,30 @@
           <t>会社名・拠点名・回答者・担当領域等</t>
         </is>
       </c>
-      <c r="D4" s="10" t="inlineStr">
+      <c r="D4" s="9" t="inlineStr">
+        <is>
+          <t>記入</t>
+        </is>
+      </c>
+      <c r="E4" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="F4" s="10" t="inlineStr">
         <is>
           <t>回答者・担当領域が不明だと、後続ヒアリングの宛先も、要件への異議申立ての窓口も特定できない。未回答拠点は「要件定義に参加しなかった拠点」として扱わざるを得ない。</t>
         </is>
       </c>
-      <c r="E4" s="10" t="inlineStr">
+      <c r="G4" s="10" t="inlineStr">
         <is>
           <t>ヒアリング計画・展開計画（拠点マスタ）</t>
         </is>
       </c>
-      <c r="F4" s="11" t="inlineStr">
+      <c r="H4" s="11" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="G4" s="10" t="inlineStr">
+      <c r="I4" s="10" t="inlineStr">
         <is>
           <t>未回答拠点は「標準要件をそのまま適用する拠点」とみなし、拠点固有要件は一切考慮しない。</t>
         </is>
@@ -783,6 +845,8 @@
       <c r="E5" s="7" t="n"/>
       <c r="F5" s="7" t="n"/>
       <c r="G5" s="7" t="n"/>
+      <c r="H5" s="7" t="n"/>
+      <c r="I5" s="7" t="n"/>
     </row>
     <row r="6" ht="52" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
@@ -800,22 +864,30 @@
           <t>手順書・マニュアルの有無</t>
         </is>
       </c>
-      <c r="D6" s="10" t="inlineStr">
+      <c r="D6" s="12" t="inlineStr">
+        <is>
+          <t>選択のみ</t>
+        </is>
+      </c>
+      <c r="E6" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="F6" s="10" t="inlineStr">
         <is>
           <t>現行業務を要件定義の出発点として文書化できず、To-Be業務フロー・画面設計の根拠が失われる。ヒアリングをゼロからやり直す工数増。</t>
         </is>
       </c>
-      <c r="E6" s="10" t="inlineStr">
+      <c r="G6" s="10" t="inlineStr">
         <is>
           <t>業務要件定義書・To-Beフロー</t>
         </is>
       </c>
-      <c r="F6" s="11" t="inlineStr">
+      <c r="H6" s="11" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="G6" s="10" t="inlineStr">
+      <c r="I6" s="10" t="inlineStr">
         <is>
           <t>「手順書なし・完全属人」とみなし、追加ヒアリング工数を当該拠点に割り当てる。</t>
         </is>
@@ -837,22 +909,30 @@
           <t>月次報告の締切余裕</t>
         </is>
       </c>
-      <c r="D7" s="10" t="inlineStr">
+      <c r="D7" s="12" t="inlineStr">
+        <is>
+          <t>選択のみ</t>
+        </is>
+      </c>
+      <c r="E7" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="F7" s="10" t="inlineStr">
         <is>
           <t>締切逼迫度が不明のままでは、入力期限設定・リマインド・督促機能の要件（強度・頻度）が決められない。</t>
         </is>
       </c>
-      <c r="E7" s="10" t="inlineStr">
+      <c r="G7" s="10" t="inlineStr">
         <is>
           <t>ワークフロー要件・督促自動化</t>
         </is>
       </c>
-      <c r="F7" s="11" t="inlineStr">
+      <c r="H7" s="11" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="G7" s="10" t="inlineStr">
+      <c r="I7" s="10" t="inlineStr">
         <is>
           <t>「毎回ぎりぎり」とみなし督促自動化・早期警報を必須要件化（過剰なら費用増）。</t>
         </is>
@@ -874,22 +954,30 @@
           <t>期ズレ（使用期間と請求期間のズレ）の処理方法</t>
         </is>
       </c>
-      <c r="D8" s="10" t="inlineStr">
+      <c r="D8" s="12" t="inlineStr">
+        <is>
+          <t>選択のみ</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="F8" s="10" t="inlineStr">
         <is>
           <t>按分機能（日割・翌月計上等）の要否・仕様が確定できず、算定エンジン要件が曖昧になり、ベンダー見積りに高値バッファが乗る。</t>
         </is>
       </c>
-      <c r="E8" s="10" t="inlineStr">
+      <c r="G8" s="10" t="inlineStr">
         <is>
           <t>算定ロジック要件・データモデル（期間属性）</t>
         </is>
       </c>
-      <c r="F8" s="12" t="inlineStr">
+      <c r="H8" s="13" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="G8" s="10" t="inlineStr">
+      <c r="I8" s="10" t="inlineStr">
         <is>
           <t>「拠点ごとに処理方法がバラバラ」とみなし、複数方式対応の按分機能を必須化（過剰スペック＝コスト増）。</t>
         </is>
@@ -911,22 +999,30 @@
           <t>報告後のデータ修正頻度</t>
         </is>
       </c>
-      <c r="D9" s="10" t="inlineStr">
+      <c r="D9" s="12" t="inlineStr">
+        <is>
+          <t>選択のみ</t>
+        </is>
+      </c>
+      <c r="E9" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="F9" s="10" t="inlineStr">
         <is>
           <t>修正申請ワークフロー・再承認・再計算の負荷設計（同時実行・性能）が決められない。</t>
         </is>
       </c>
-      <c r="E9" s="10" t="inlineStr">
+      <c r="G9" s="10" t="inlineStr">
         <is>
           <t>修正WF要件・性能要件</t>
         </is>
       </c>
-      <c r="F9" s="11" t="inlineStr">
+      <c r="H9" s="11" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="G9" s="10" t="inlineStr">
+      <c r="I9" s="10" t="inlineStr">
         <is>
           <t>「ほぼ毎月修正あり」とみなし修正WFをフル装備で設計。</t>
         </is>
@@ -948,22 +1044,30 @@
           <t>主担当1ヶ月不在時の影響</t>
         </is>
       </c>
-      <c r="D10" s="10" t="inlineStr">
+      <c r="D10" s="12" t="inlineStr">
+        <is>
+          <t>選択のみ</t>
+        </is>
+      </c>
+      <c r="E10" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="F10" s="10" t="inlineStr">
         <is>
           <t>代行権限・委任機能の要否が決まらず、承認が止まるリスクを設計で防げない。</t>
         </is>
       </c>
-      <c r="E10" s="10" t="inlineStr">
+      <c r="G10" s="10" t="inlineStr">
         <is>
           <t>権限設計・代行承認機能</t>
         </is>
       </c>
-      <c r="F10" s="11" t="inlineStr">
+      <c r="H10" s="11" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="G10" s="10" t="inlineStr">
+      <c r="I10" s="10" t="inlineStr">
         <is>
           <t>「報告が止まる」とみなし代行承認・不在アラートを必須化。</t>
         </is>
@@ -985,22 +1089,30 @@
           <t>排出量計算をどこまで拠点側で実施しているか</t>
         </is>
       </c>
-      <c r="D11" s="10" t="inlineStr">
+      <c r="D11" s="12" t="inlineStr">
+        <is>
+          <t>選択のみ</t>
+        </is>
+      </c>
+      <c r="E11" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="F11" s="10" t="inlineStr">
         <is>
           <t>算定エンジンの機能配置（中央集約か拠点計算容認か）というアーキテクチャの根幹が決められない。拠点独自計算が後から発覚すると数値の連続性が切れる。</t>
         </is>
       </c>
-      <c r="E11" s="10" t="inlineStr">
+      <c r="G11" s="10" t="inlineStr">
         <is>
           <t>算定エンジン・アーキテクチャ</t>
         </is>
       </c>
-      <c r="F11" s="12" t="inlineStr">
+      <c r="H11" s="13" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="G11" s="10" t="inlineStr">
+      <c r="I11" s="10" t="inlineStr">
         <is>
           <t>「拠点独自計算あり」とみなし、既存ロジックの棚卸し・移植検証を要件化（追加工数は当該拠点起因）。</t>
         </is>
@@ -1022,22 +1134,30 @@
           <t>本社標準と異なる独自係数・ルールの使用</t>
         </is>
       </c>
-      <c r="D12" s="10" t="inlineStr">
+      <c r="D12" s="12" t="inlineStr">
+        <is>
+          <t>選択のみ</t>
+        </is>
+      </c>
+      <c r="E12" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="F12" s="10" t="inlineStr">
         <is>
           <t>係数マスタの拠点別上書き管理の要否が不明。未申告の独自係数は移行後に数値差異として顕在化し、保証で説明不能になる。</t>
         </is>
       </c>
-      <c r="E12" s="10" t="inlineStr">
+      <c r="G12" s="10" t="inlineStr">
         <is>
           <t>係数マスタ設計・監査対応</t>
         </is>
       </c>
-      <c r="F12" s="12" t="inlineStr">
+      <c r="H12" s="13" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="G12" s="10" t="inlineStr">
+      <c r="I12" s="10" t="inlineStr">
         <is>
           <t>「独自係数あり」とみなし拠点別係数設定を実装。移行後に発覚した未申告係数による数値差異は当該拠点起因として記録。</t>
         </is>
@@ -1059,22 +1179,30 @@
           <t>計算Excel・マクロを説明・修正できる人数</t>
         </is>
       </c>
-      <c r="D13" s="10" t="inlineStr">
+      <c r="D13" s="12" t="inlineStr">
+        <is>
+          <t>選択のみ</t>
+        </is>
+      </c>
+      <c r="E13" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="F13" s="10" t="inlineStr">
         <is>
           <t>ロジック移植の可否・工数が見積れず、RFPでベンダーが高値バッファを乗せる。作成者退職済みなら再現不能＝過年度との連続性が切れる。</t>
         </is>
       </c>
-      <c r="E13" s="10" t="inlineStr">
+      <c r="G13" s="10" t="inlineStr">
         <is>
           <t>ロジック移植計画・RFP見積り前提</t>
         </is>
       </c>
-      <c r="F13" s="12" t="inlineStr">
+      <c r="H13" s="13" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="G13" s="10" t="inlineStr">
+      <c r="I13" s="10" t="inlineStr">
         <is>
           <t>「作成者頼み・ブラックボックス」とみなしリバースエンジニアリング工数を計上（費用増）。</t>
         </is>
@@ -1096,22 +1224,30 @@
           <t>証憑の形式（紙／電子の比率）</t>
         </is>
       </c>
-      <c r="D14" s="10" t="inlineStr">
+      <c r="D14" s="12" t="inlineStr">
+        <is>
+          <t>選択のみ</t>
+        </is>
+      </c>
+      <c r="E14" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="F14" s="10" t="inlineStr">
         <is>
           <t>スキャン運用・ストレージ容量・アップロードUIの要件規模が決められない。</t>
         </is>
       </c>
-      <c r="E14" s="10" t="inlineStr">
+      <c r="G14" s="10" t="inlineStr">
         <is>
           <t>証憑管理機能・ストレージ設計</t>
         </is>
       </c>
-      <c r="F14" s="11" t="inlineStr">
+      <c r="H14" s="11" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="G14" s="10" t="inlineStr">
+      <c r="I14" s="10" t="inlineStr">
         <is>
           <t>「ほぼ紙」とみなしスキャン運用＋容量大きめで設計（費用増）。</t>
         </is>
@@ -1133,22 +1269,30 @@
           <t>報告数値から証憑まで遡れるか</t>
         </is>
       </c>
-      <c r="D15" s="10" t="inlineStr">
+      <c r="D15" s="12" t="inlineStr">
+        <is>
+          <t>選択のみ</t>
+        </is>
+      </c>
+      <c r="E15" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="F15" s="10" t="inlineStr">
         <is>
           <t>数値⇔証憑の紐付けデータモデルと移行時の証憑再収集range が設計できない。保証対応の根幹要件が確定しない。</t>
         </is>
       </c>
-      <c r="E15" s="10" t="inlineStr">
+      <c r="G15" s="10" t="inlineStr">
         <is>
           <t>証憑紐付けデータモデル・移行計画</t>
         </is>
       </c>
-      <c r="F15" s="12" t="inlineStr">
+      <c r="H15" s="13" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="G15" s="10" t="inlineStr">
+      <c r="I15" s="10" t="inlineStr">
         <is>
           <t>「一部遡れない」とみなし移行時の証憑再収集タスクを計画化（工数は当該拠点負担）。</t>
         </is>
@@ -1170,22 +1314,30 @@
           <t>証憑添付必須化への対応可否</t>
         </is>
       </c>
-      <c r="D16" s="10" t="inlineStr">
+      <c r="D16" s="12" t="inlineStr">
+        <is>
+          <t>選択のみ</t>
+        </is>
+      </c>
+      <c r="E16" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="F16" s="10" t="inlineStr">
         <is>
           <t>証憑必須制御の例外ルール（欠測時の代替手続き）が設計できず、稼働後に現場の入力が止まる。</t>
         </is>
       </c>
-      <c r="E16" s="10" t="inlineStr">
+      <c r="G16" s="10" t="inlineStr">
         <is>
           <t>入力制御・例外申請フロー</t>
         </is>
       </c>
-      <c r="F16" s="12" t="inlineStr">
+      <c r="H16" s="13" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="G16" s="10" t="inlineStr">
+      <c r="I16" s="10" t="inlineStr">
         <is>
           <t>「一部困難」とみなし例外申請フローを実装。稼働後の「添付できない」申告は当該拠点起因の運用課題として扱う。</t>
         </is>
@@ -1207,22 +1359,30 @@
           <t>データ報告への承認行為の有無</t>
         </is>
       </c>
-      <c r="D17" s="10" t="inlineStr">
+      <c r="D17" s="12" t="inlineStr">
+        <is>
+          <t>選択のみ</t>
+        </is>
+      </c>
+      <c r="E17" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="F17" s="10" t="inlineStr">
         <is>
           <t>承認階層の現状が不明だと多段階WFの段数・承認者マスタが設計できない。</t>
         </is>
       </c>
-      <c r="E17" s="10" t="inlineStr">
+      <c r="G17" s="10" t="inlineStr">
         <is>
           <t>承認ワークフロー設計</t>
         </is>
       </c>
-      <c r="F17" s="12" t="inlineStr">
+      <c r="H17" s="13" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="G17" s="10" t="inlineStr">
+      <c r="I17" s="10" t="inlineStr">
         <is>
           <t>「承認なし」とみなしゼロから承認体制を設計（当該拠点の業務変更負荷が最大化）。</t>
         </is>
@@ -1244,22 +1404,30 @@
           <t>データ変更履歴が残るか</t>
         </is>
       </c>
-      <c r="D18" s="10" t="inlineStr">
+      <c r="D18" s="12" t="inlineStr">
+        <is>
+          <t>選択のみ</t>
+        </is>
+      </c>
+      <c r="E18" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="F18" s="10" t="inlineStr">
         <is>
           <t>監査ログ要件（全項目履歴の要否）が決められない。保証の必須要件。</t>
         </is>
       </c>
-      <c r="E18" s="10" t="inlineStr">
+      <c r="G18" s="10" t="inlineStr">
         <is>
           <t>監査ログ・証跡要件</t>
         </is>
       </c>
-      <c r="F18" s="12" t="inlineStr">
+      <c r="H18" s="13" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="G18" s="10" t="inlineStr">
+      <c r="I18" s="10" t="inlineStr">
         <is>
           <t>「残らない（上書き）」とみなし全項目監査ログを必須化。</t>
         </is>
@@ -1281,22 +1449,30 @@
           <t>業務システムからのデータ出力（CSV/API）可否</t>
         </is>
       </c>
-      <c r="D19" s="10" t="inlineStr">
+      <c r="D19" s="12" t="inlineStr">
+        <is>
+          <t>選択のみ</t>
+        </is>
+      </c>
+      <c r="E19" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="F19" s="10" t="inlineStr">
         <is>
           <t>自動連携の対象範囲が確定できず、RFPの連携要件が「全件手入力」ベースになる。自動化によるROIも算定不能。</t>
         </is>
       </c>
-      <c r="E19" s="10" t="inlineStr">
+      <c r="G19" s="10" t="inlineStr">
         <is>
           <t>外部IF一覧・RFP連携要件・ROI</t>
         </is>
       </c>
-      <c r="F19" s="12" t="inlineStr">
+      <c r="H19" s="13" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="G19" s="10" t="inlineStr">
+      <c r="I19" s="10" t="inlineStr">
         <is>
           <t>「ほぼ不可」とみなし手入力ベースで設計。後日「出力可能」と判明した場合の連携追加費用は当該拠点起因。</t>
         </is>
@@ -1318,22 +1494,30 @@
           <t>電力・ガス会社のWeb明細サービス利用状況</t>
         </is>
       </c>
-      <c r="D20" s="10" t="inlineStr">
+      <c r="D20" s="12" t="inlineStr">
+        <is>
+          <t>選択のみ</t>
+        </is>
+      </c>
+      <c r="E20" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="F20" s="10" t="inlineStr">
         <is>
           <t>検針データ自動取込の対象から外れ、転記工数の削減効果を放棄することになる。</t>
         </is>
       </c>
-      <c r="E20" s="10" t="inlineStr">
+      <c r="G20" s="10" t="inlineStr">
         <is>
           <t>自動取込設計・ROI</t>
         </is>
       </c>
-      <c r="F20" s="11" t="inlineStr">
+      <c r="H20" s="11" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="G20" s="10" t="inlineStr">
+      <c r="I20" s="10" t="inlineStr">
         <is>
           <t>「利用不可」とみなす（自動化効果の逸失は当該拠点起因として記録）。</t>
         </is>
@@ -1355,22 +1539,30 @@
           <t>社外クラウド（SaaS）へのアクセス制限</t>
         </is>
       </c>
-      <c r="D21" s="10" t="inlineStr">
+      <c r="D21" s="12" t="inlineStr">
+        <is>
+          <t>選択のみ</t>
+        </is>
+      </c>
+      <c r="E21" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="F21" s="10" t="inlineStr">
         <is>
           <t>クラウドSaaS前提のアーキテクチャが成立するかという根本条件が未確認のままになる。稼働直前に「接続できない拠点」が発覚すると構成変更＝最大級の手戻り。</t>
         </is>
       </c>
-      <c r="E21" s="10" t="inlineStr">
+      <c r="G21" s="10" t="inlineStr">
         <is>
           <t>アーキテクチャ成立性・ネットワーク要件</t>
         </is>
       </c>
-      <c r="F21" s="12" t="inlineStr">
+      <c r="H21" s="13" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="G21" s="10" t="inlineStr">
+      <c r="I21" s="10" t="inlineStr">
         <is>
           <t>「原則不可の拠点あり」とみなしプロキシ/ホワイトリスト申請工程を計画化。稼働後の接続不可発覚は当該拠点起因。</t>
         </is>
@@ -1392,22 +1584,30 @@
           <t>非財務データ業務の月間工数</t>
         </is>
       </c>
-      <c r="D22" s="10" t="inlineStr">
+      <c r="D22" s="9" t="inlineStr">
+        <is>
+          <t>数値記入（工数集計）</t>
+        </is>
+      </c>
+      <c r="E22" s="9" t="n">
+        <v>30</v>
+      </c>
+      <c r="F22" s="10" t="inlineStr">
         <is>
           <t>ROI試算（工数削減効果）の分母が作れず、経営上申の定量根拠が失われる。投資判断が定性論に退化する。</t>
         </is>
       </c>
-      <c r="E22" s="10" t="inlineStr">
+      <c r="G22" s="10" t="inlineStr">
         <is>
           <t>ROI試算・経営上申資料</t>
         </is>
       </c>
-      <c r="F22" s="12" t="inlineStr">
+      <c r="H22" s="13" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="G22" s="10" t="inlineStr">
+      <c r="I22" s="10" t="inlineStr">
         <is>
           <t>当該拠点の工数削減効果をROIから除外（効果の過小計上は当該拠点起因として記録）。</t>
         </is>
@@ -1429,22 +1629,30 @@
           <t>統制強化導入時の最大の懸念（任意）</t>
         </is>
       </c>
-      <c r="D23" s="10" t="inlineStr">
+      <c r="D23" s="9" t="inlineStr">
+        <is>
+          <t>短記述（任意）</t>
+        </is>
+      </c>
+      <c r="E23" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="F23" s="10" t="inlineStr">
         <is>
           <t>チェンジマネジメント設計の材料を失うが、要件の根幹には影響しない。</t>
         </is>
       </c>
-      <c r="E23" s="10" t="inlineStr">
+      <c r="G23" s="10" t="inlineStr">
         <is>
           <t>定着計画</t>
         </is>
       </c>
-      <c r="F23" s="13" t="inlineStr">
+      <c r="H23" s="14" t="inlineStr">
         <is>
           <t>低</t>
         </is>
       </c>
-      <c r="G23" s="10" t="inlineStr">
+      <c r="I23" s="10" t="inlineStr">
         <is>
           <t>「重大な懸念なし」とみなす。</t>
         </is>
@@ -1466,22 +1674,30 @@
           <t>現地語UI・現地サポートなしでの運用可否</t>
         </is>
       </c>
-      <c r="D24" s="10" t="inlineStr">
+      <c r="D24" s="12" t="inlineStr">
+        <is>
+          <t>選択のみ</t>
+        </is>
+      </c>
+      <c r="E24" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="F24" s="10" t="inlineStr">
         <is>
           <t>多言語要件の要否＝ベンダー選定の足切り条件が決められない。過剰なら対応ベンダーが絞られ価格上昇、過少なら現地が使えないシステムになる。</t>
         </is>
       </c>
-      <c r="E24" s="10" t="inlineStr">
+      <c r="G24" s="10" t="inlineStr">
         <is>
           <t>多言語要件・RFP必須要件</t>
         </is>
       </c>
-      <c r="F24" s="12" t="inlineStr">
+      <c r="H24" s="13" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="G24" s="10" t="inlineStr">
+      <c r="I24" s="10" t="inlineStr">
         <is>
           <t>「現地語UI必須」とみなしRFPに多言語要件を必須化（ベンダー絞り込み・価格上昇は未回答拠点起因）。</t>
         </is>
@@ -1503,22 +1719,30 @@
           <t>月次で最も時間がかかるステップ</t>
         </is>
       </c>
-      <c r="D25" s="10" t="inlineStr">
+      <c r="D25" s="12" t="inlineStr">
+        <is>
+          <t>選択のみ</t>
+        </is>
+      </c>
+      <c r="E25" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="F25" s="10" t="inlineStr">
         <is>
           <t>自動化投資の優先順位（Must/Should分類）が現場実態でなく推測ベースになる。</t>
         </is>
       </c>
-      <c r="E25" s="10" t="inlineStr">
+      <c r="G25" s="10" t="inlineStr">
         <is>
           <t>機能優先度・Must/Should分類</t>
         </is>
       </c>
-      <c r="F25" s="11" t="inlineStr">
+      <c r="H25" s="11" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="G25" s="10" t="inlineStr">
+      <c r="I25" s="10" t="inlineStr">
         <is>
           <t>全ステップ均等として設計（優先順位最適化を放棄）。</t>
         </is>
@@ -1540,22 +1764,30 @@
           <t>データ修正の方法（上書きか履歴付きか）</t>
         </is>
       </c>
-      <c r="D26" s="10" t="inlineStr">
+      <c r="D26" s="12" t="inlineStr">
+        <is>
+          <t>選択のみ</t>
+        </is>
+      </c>
+      <c r="E26" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="F26" s="10" t="inlineStr">
         <is>
           <t>上書き運用の拠点は過去データの信頼性に疑義。移行時のデータクレンジング要否が判断できない。</t>
         </is>
       </c>
-      <c r="E26" s="10" t="inlineStr">
+      <c r="G26" s="10" t="inlineStr">
         <is>
           <t>移行設計・修正WF</t>
         </is>
       </c>
-      <c r="F26" s="11" t="inlineStr">
+      <c r="H26" s="11" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="G26" s="10" t="inlineStr">
+      <c r="I26" s="10" t="inlineStr">
         <is>
           <t>「上書き（履歴なし）」とみなし移行データの検証タスクを追加。</t>
         </is>
@@ -1577,22 +1809,30 @@
           <t>年間で最も負荷が高い月</t>
         </is>
       </c>
-      <c r="D27" s="10" t="inlineStr">
+      <c r="D27" s="12" t="inlineStr">
+        <is>
+          <t>選択のみ</t>
+        </is>
+      </c>
+      <c r="E27" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="F27" s="10" t="inlineStr">
         <is>
           <t>ピーク時の同時アクセス・処理性能の要件根拠と、締切カレンダー設計ができない。</t>
         </is>
       </c>
-      <c r="E27" s="10" t="inlineStr">
+      <c r="G27" s="10" t="inlineStr">
         <is>
           <t>性能要件・年間スケジュール設計</t>
         </is>
       </c>
-      <c r="F27" s="11" t="inlineStr">
+      <c r="H27" s="11" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="G27" s="10" t="inlineStr">
+      <c r="I27" s="10" t="inlineStr">
         <is>
           <t>「1〜3月ピーク」とみなして設計。</t>
         </is>
@@ -1614,22 +1854,30 @@
           <t>抜け漏れ・遅延の主な原因</t>
         </is>
       </c>
-      <c r="D28" s="10" t="inlineStr">
+      <c r="D28" s="12" t="inlineStr">
+        <is>
+          <t>選択のみ</t>
+        </is>
+      </c>
+      <c r="E28" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="F28" s="10" t="inlineStr">
         <is>
           <t>督促・エスカレーション設計が原因に即さない汎用設計になる。</t>
         </is>
       </c>
-      <c r="E28" s="10" t="inlineStr">
+      <c r="G28" s="10" t="inlineStr">
         <is>
           <t>督促・エスカレーション設計</t>
         </is>
       </c>
-      <c r="F28" s="11" t="inlineStr">
+      <c r="H28" s="11" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="G28" s="10" t="inlineStr">
+      <c r="I28" s="10" t="inlineStr">
         <is>
           <t>「担当者不在＋請求書遅延」の複合とみなす。</t>
         </is>
@@ -1651,22 +1899,30 @@
           <t>過年度データの遡及修正経験</t>
         </is>
       </c>
-      <c r="D29" s="10" t="inlineStr">
+      <c r="D29" s="12" t="inlineStr">
+        <is>
+          <t>選択のみ</t>
+        </is>
+      </c>
+      <c r="E29" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="F29" s="10" t="inlineStr">
         <is>
           <t>遡及再計算機能（過年度ロック解除・再計算・再承認・訂正開示連携）の要否が決められない。</t>
         </is>
       </c>
-      <c r="E29" s="10" t="inlineStr">
+      <c r="G29" s="10" t="inlineStr">
         <is>
           <t>遡及再計算機能・訂正フロー</t>
         </is>
       </c>
-      <c r="F29" s="12" t="inlineStr">
+      <c r="H29" s="13" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="G29" s="10" t="inlineStr">
+      <c r="I29" s="10" t="inlineStr">
         <is>
           <t>「経験あり」とみなし遡及再計算を要件化（機能費用増）。</t>
         </is>
@@ -1688,22 +1944,30 @@
           <t>単位換算・按分計算の実施有無</t>
         </is>
       </c>
-      <c r="D30" s="10" t="inlineStr">
+      <c r="D30" s="12" t="inlineStr">
+        <is>
+          <t>選択のみ</t>
+        </is>
+      </c>
+      <c r="E30" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="F30" s="10" t="inlineStr">
         <is>
           <t>換算・按分エンジンの対象範囲が確定できない。</t>
         </is>
       </c>
-      <c r="E30" s="10" t="inlineStr">
+      <c r="G30" s="10" t="inlineStr">
         <is>
           <t>算定エンジン要件</t>
         </is>
       </c>
-      <c r="F30" s="12" t="inlineStr">
+      <c r="H30" s="13" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="G30" s="10" t="inlineStr">
+      <c r="I30" s="10" t="inlineStr">
         <is>
           <t>「両方実施」とみなしフル機能で設計（過剰なら費用増）。</t>
         </is>
@@ -1725,22 +1989,30 @@
           <t>推計・概算データの割合</t>
         </is>
       </c>
-      <c r="D31" s="10" t="inlineStr">
+      <c r="D31" s="12" t="inlineStr">
+        <is>
+          <t>選択のみ</t>
+        </is>
+      </c>
+      <c r="E31" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="F31" s="10" t="inlineStr">
         <is>
           <t>推計値管理機能（実測/推計フラグ・後日置換・遡及）の要否と、保証上の説明範囲が確定しない。推計割合が高いと保証で重点検証対象になる。</t>
         </is>
       </c>
-      <c r="E31" s="10" t="inlineStr">
+      <c r="G31" s="10" t="inlineStr">
         <is>
           <t>推計管理機能・保証対応</t>
         </is>
       </c>
-      <c r="F31" s="12" t="inlineStr">
+      <c r="H31" s="13" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="G31" s="10" t="inlineStr">
+      <c r="I31" s="10" t="inlineStr">
         <is>
           <t>「25%以上が推計」とみなし推計管理を必須化。保証時の指摘は当該拠点起因。</t>
         </is>
@@ -1762,22 +2034,30 @@
           <t>計算結果の妥当性チェック方法</t>
         </is>
       </c>
-      <c r="D32" s="10" t="inlineStr">
+      <c r="D32" s="12" t="inlineStr">
+        <is>
+          <t>選択のみ</t>
+        </is>
+      </c>
+      <c r="E32" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="F32" s="10" t="inlineStr">
         <is>
           <t>異常値検知ルール（前年比・原単位の閾値）の初期値が現場実態でなく机上設定になる。</t>
         </is>
       </c>
-      <c r="E32" s="10" t="inlineStr">
+      <c r="G32" s="10" t="inlineStr">
         <is>
           <t>異常値検知ルール</t>
         </is>
       </c>
-      <c r="F32" s="11" t="inlineStr">
+      <c r="H32" s="11" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="G32" s="10" t="inlineStr">
+      <c r="I32" s="10" t="inlineStr">
         <is>
           <t>「チェックなし」とみなし標準閾値から設計。</t>
         </is>
@@ -1799,22 +2079,30 @@
           <t>個人PC・個人メールにしかない証憑の有無</t>
         </is>
       </c>
-      <c r="D33" s="10" t="inlineStr">
+      <c r="D33" s="12" t="inlineStr">
+        <is>
+          <t>選択のみ</t>
+        </is>
+      </c>
+      <c r="E33" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="F33" s="10" t="inlineStr">
         <is>
           <t>証憑消失リスクが放置される。移行前に退避しないと保証で証憑を提示できず、意見不能・重大指摘になり得る。</t>
         </is>
       </c>
-      <c r="E33" s="10" t="inlineStr">
+      <c r="G33" s="10" t="inlineStr">
         <is>
           <t>証憑救済・移行計画・保証対応</t>
         </is>
       </c>
-      <c r="F33" s="12" t="inlineStr">
+      <c r="H33" s="13" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="G33" s="10" t="inlineStr">
+      <c r="I33" s="10" t="inlineStr">
         <is>
           <t>「あり」とみなし移行前の証憑退避タスクを計画化。消失した証憑の責任は当該拠点起因。</t>
         </is>
@@ -1836,22 +2124,30 @@
           <t>過去の監査・検証で証憑を探すのに要した時間</t>
         </is>
       </c>
-      <c r="D34" s="10" t="inlineStr">
+      <c r="D34" s="12" t="inlineStr">
+        <is>
+          <t>選択のみ</t>
+        </is>
+      </c>
+      <c r="E34" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="F34" s="10" t="inlineStr">
         <is>
           <t>検索性要件の根拠とROI（保証対応工数削減）の現状値が欠落する。</t>
         </is>
       </c>
-      <c r="E34" s="10" t="inlineStr">
+      <c r="G34" s="10" t="inlineStr">
         <is>
           <t>検索性要件・ROI</t>
         </is>
       </c>
-      <c r="F34" s="11" t="inlineStr">
+      <c r="H34" s="11" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="G34" s="10" t="inlineStr">
+      <c r="I34" s="10" t="inlineStr">
         <is>
           <t>「数日かかった」とみなす。</t>
         </is>
@@ -1873,22 +2169,30 @@
           <t>入力データのチェック実施者</t>
         </is>
       </c>
-      <c r="D35" s="10" t="inlineStr">
+      <c r="D35" s="12" t="inlineStr">
+        <is>
+          <t>選択のみ</t>
+        </is>
+      </c>
+      <c r="E35" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="F35" s="10" t="inlineStr">
         <is>
           <t>人的統制のどこをシステム統制に置換するかの設計根拠がない。統制過剰・過少の両リスク。</t>
         </is>
       </c>
-      <c r="E35" s="10" t="inlineStr">
+      <c r="G35" s="10" t="inlineStr">
         <is>
           <t>統制設計（キーコントロール配置）</t>
         </is>
       </c>
-      <c r="F35" s="12" t="inlineStr">
+      <c r="H35" s="13" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="G35" s="10" t="inlineStr">
+      <c r="I35" s="10" t="inlineStr">
         <is>
           <t>「自己チェックのみ」とみなし統制を厚めに設計（現場負荷増は当該拠点起因）。</t>
         </is>
@@ -1910,22 +2214,30 @@
           <t>確定・ロックの概念の有無</t>
         </is>
       </c>
-      <c r="D36" s="10" t="inlineStr">
+      <c r="D36" s="12" t="inlineStr">
+        <is>
+          <t>選択のみ</t>
+        </is>
+      </c>
+      <c r="E36" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="F36" s="10" t="inlineStr">
         <is>
           <t>ロック機能導入時の業務変更の大きさ（教育・移行負荷）が見積れない。</t>
         </is>
       </c>
-      <c r="E36" s="10" t="inlineStr">
+      <c r="G36" s="10" t="inlineStr">
         <is>
           <t>確定ロック機能・定着計画</t>
         </is>
       </c>
-      <c r="F36" s="11" t="inlineStr">
+      <c r="H36" s="11" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="G36" s="10" t="inlineStr">
+      <c r="I36" s="10" t="inlineStr">
         <is>
           <t>「概念なし」とみなし導入教育を計画化。</t>
         </is>
@@ -1947,22 +2259,30 @@
           <t>入力ファイル・システムのアクセス権</t>
         </is>
       </c>
-      <c r="D37" s="10" t="inlineStr">
+      <c r="D37" s="12" t="inlineStr">
+        <is>
+          <t>選択のみ</t>
+        </is>
+      </c>
+      <c r="E37" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="F37" s="10" t="inlineStr">
         <is>
           <t>権限マトリクスの現状が不明。「誰でも編集可」の拠点は改ざんリスクとして保証で指摘される。</t>
         </is>
       </c>
-      <c r="E37" s="10" t="inlineStr">
+      <c r="G37" s="10" t="inlineStr">
         <is>
           <t>権限設計・統制指摘リスク</t>
         </is>
       </c>
-      <c r="F37" s="12" t="inlineStr">
+      <c r="H37" s="13" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="G37" s="10" t="inlineStr">
+      <c r="I37" s="10" t="inlineStr">
         <is>
           <t>「誰でも編集可」とみなし統制上のリスク拠点として記録（指摘時の帰責明確化）。</t>
         </is>
@@ -1984,22 +2304,30 @@
           <t>拠点でのSAP利用状況</t>
         </is>
       </c>
-      <c r="D38" s="10" t="inlineStr">
+      <c r="D38" s="12" t="inlineStr">
+        <is>
+          <t>選択のみ</t>
+        </is>
+      </c>
+      <c r="E38" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="F38" s="10" t="inlineStr">
         <is>
           <t>SAP連携（直接連携の対象拠点range）が確定できず、連携設計から漏れる。後日判明時は連携追加＝追加費用。</t>
         </is>
       </c>
-      <c r="E38" s="10" t="inlineStr">
+      <c r="G38" s="10" t="inlineStr">
         <is>
           <t>SAP連携要件・外部IF設計</t>
         </is>
       </c>
-      <c r="F38" s="12" t="inlineStr">
+      <c r="H38" s="13" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="G38" s="10" t="inlineStr">
+      <c r="I38" s="10" t="inlineStr">
         <is>
           <t>「使っていない」とみなし連携対象外とする。後日の連携追加費用は当該拠点起因。</t>
         </is>
@@ -2021,22 +2349,30 @@
           <t>スマートメーター・BEMSの有無</t>
         </is>
       </c>
-      <c r="D39" s="10" t="inlineStr">
+      <c r="D39" s="12" t="inlineStr">
+        <is>
+          <t>選択のみ</t>
+        </is>
+      </c>
+      <c r="E39" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="F39" s="10" t="inlineStr">
         <is>
           <t>自動計測データ取込の対象から漏れ、手入力前提の設計になる。</t>
         </is>
       </c>
-      <c r="E39" s="10" t="inlineStr">
+      <c r="G39" s="10" t="inlineStr">
         <is>
           <t>自動取込設計</t>
         </is>
       </c>
-      <c r="F39" s="11" t="inlineStr">
+      <c r="H39" s="11" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="G39" s="10" t="inlineStr">
+      <c r="I39" s="10" t="inlineStr">
         <is>
           <t>「なし」とみなす（自動化機会の逸失は当該拠点起因）。</t>
         </is>
@@ -2058,22 +2394,30 @@
           <t>工場・現場のPC・ネットワーク環境</t>
         </is>
       </c>
-      <c r="D40" s="10" t="inlineStr">
+      <c r="D40" s="12" t="inlineStr">
+        <is>
+          <t>選択のみ</t>
+        </is>
+      </c>
+      <c r="E40" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="F40" s="10" t="inlineStr">
         <is>
           <t>入力UI要件（モバイル対応・オフライン入力）の要否が決められず、現場で使えないUIになるリスク。</t>
         </is>
       </c>
-      <c r="E40" s="10" t="inlineStr">
+      <c r="G40" s="10" t="inlineStr">
         <is>
           <t>入力UI要件・デバイス要件</t>
         </is>
       </c>
-      <c r="F40" s="11" t="inlineStr">
+      <c r="H40" s="11" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="G40" s="10" t="inlineStr">
+      <c r="I40" s="10" t="inlineStr">
         <is>
           <t>「PC利用可だがネットワーク制限あり」とみなす。</t>
         </is>
@@ -2095,22 +2439,30 @@
           <t>電子承認・ワークフローシステムの導入状況</t>
         </is>
       </c>
-      <c r="D41" s="10" t="inlineStr">
+      <c r="D41" s="12" t="inlineStr">
+        <is>
+          <t>選択のみ</t>
+        </is>
+      </c>
+      <c r="E41" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="F41" s="10" t="inlineStr">
         <is>
           <t>既存WFの流用可否が不明のまま新規実装し、二重投資になるリスク。</t>
         </is>
       </c>
-      <c r="E41" s="10" t="inlineStr">
+      <c r="G41" s="10" t="inlineStr">
         <is>
           <t>WF実装方式・投資効率</t>
         </is>
       </c>
-      <c r="F41" s="11" t="inlineStr">
+      <c r="H41" s="11" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="G41" s="10" t="inlineStr">
+      <c r="I41" s="10" t="inlineStr">
         <is>
           <t>「非財務には不向き」とみなし新規実装（二重投資リスクは未回答起因として記録）。</t>
         </is>
@@ -2132,22 +2484,30 @@
           <t>業務の属人化状況</t>
         </is>
       </c>
-      <c r="D42" s="10" t="inlineStr">
+      <c r="D42" s="12" t="inlineStr">
+        <is>
+          <t>選択のみ</t>
+        </is>
+      </c>
+      <c r="E42" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="F42" s="10" t="inlineStr">
         <is>
           <t>マニュアル・教育・機能化（フールプルーフ）の要件規模が決められない。</t>
         </is>
       </c>
-      <c r="E42" s="10" t="inlineStr">
+      <c r="G42" s="10" t="inlineStr">
         <is>
           <t>教育・マニュアル要件</t>
         </is>
       </c>
-      <c r="F42" s="11" t="inlineStr">
+      <c r="H42" s="11" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="G42" s="10" t="inlineStr">
+      <c r="I42" s="10" t="inlineStr">
         <is>
           <t>「一部属人化」とみなす。</t>
         </is>
@@ -2165,6 +2525,8 @@
       <c r="E43" s="7" t="n"/>
       <c r="F43" s="7" t="n"/>
       <c r="G43" s="7" t="n"/>
+      <c r="H43" s="7" t="n"/>
+      <c r="I43" s="7" t="n"/>
     </row>
     <row r="44" ht="52" customHeight="1">
       <c r="A44" s="8" t="inlineStr">
@@ -2182,22 +2544,30 @@
           <t>報告データ項目の一覧（項目名・頻度・発生源・取得方法）</t>
         </is>
       </c>
-      <c r="D44" s="10" t="inlineStr">
+      <c r="D44" s="9" t="inlineStr">
+        <is>
+          <t>一覧記入（棚卸し）</t>
+        </is>
+      </c>
+      <c r="E44" s="9" t="n">
+        <v>90</v>
+      </c>
+      <c r="F44" s="10" t="inlineStr">
         <is>
           <t>収集項目マスタ・データモデル（項目・単位・頻度・発生源）が設計できず、RFPの規模前提（データ量・画面数・連携数）が示せない。ベンダー見積りが全面的に概算化し高値バッファが乗る。本調査の中で最も要件に直結するシート。</t>
         </is>
       </c>
-      <c r="E44" s="10" t="inlineStr">
+      <c r="G44" s="10" t="inlineStr">
         <is>
           <t>収集項目マスタ・データモデル・RFP規模前提</t>
         </is>
       </c>
-      <c r="F44" s="12" t="inlineStr">
+      <c r="H44" s="13" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="G44" s="10" t="inlineStr">
+      <c r="I44" s="10" t="inlineStr">
         <is>
           <t>事務局が既存報告様式（エコアシスト等）から項目を推定して確定する。拠点固有項目・ローカル報告項目の漏れが後日判明した場合の項目追加・改修費用は当該拠点起因。</t>
         </is>
@@ -2215,6 +2585,8 @@
       <c r="E45" s="7" t="n"/>
       <c r="F45" s="7" t="n"/>
       <c r="G45" s="7" t="n"/>
+      <c r="H45" s="7" t="n"/>
+      <c r="I45" s="7" t="n"/>
     </row>
     <row r="46" ht="52" customHeight="1">
       <c r="A46" s="8" t="inlineStr">
@@ -2232,22 +2604,30 @@
           <t>手順書の形式・保管場所・更新時期</t>
         </is>
       </c>
-      <c r="D46" s="10" t="inlineStr">
+      <c r="D46" s="9" t="inlineStr">
+        <is>
+          <t>選択+補足〔ヒアリング〕</t>
+        </is>
+      </c>
+      <c r="E46" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="F46" s="10" t="inlineStr">
         <is>
           <t>C-01の詳細検証ができず、業務要件の文書化根拠が推測のままになる。</t>
         </is>
       </c>
-      <c r="E46" s="10" t="inlineStr">
+      <c r="G46" s="10" t="inlineStr">
         <is>
           <t>業務要件定義書</t>
         </is>
       </c>
-      <c r="F46" s="11" t="inlineStr">
+      <c r="H46" s="11" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="G46" s="10" t="inlineStr">
+      <c r="I46" s="10" t="inlineStr">
         <is>
           <t>「手順書なし」とみなす。</t>
         </is>
@@ -2269,22 +2649,30 @@
           <t>手順書と実運用の乖離・独自の工夫</t>
         </is>
       </c>
-      <c r="D47" s="10" t="inlineStr">
+      <c r="D47" s="9" t="inlineStr">
+        <is>
+          <t>記述〔ヒアリング〕</t>
+        </is>
+      </c>
+      <c r="E47" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="F47" s="10" t="inlineStr">
         <is>
           <t>実運用に埋まった暗黙ルールを要件に反映できず、稼働後に「システムが実態と合わない」となる定着リスク。</t>
         </is>
       </c>
-      <c r="E47" s="10" t="inlineStr">
+      <c r="G47" s="10" t="inlineStr">
         <is>
           <t>To-Be業務フロー・定着計画</t>
         </is>
       </c>
-      <c r="F47" s="11" t="inlineStr">
+      <c r="H47" s="11" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="G47" s="10" t="inlineStr">
+      <c r="I47" s="10" t="inlineStr">
         <is>
           <t>「乖離あり」とみなし移行時の業務調査を追加。</t>
         </is>
@@ -2306,22 +2694,30 @@
           <t>月次報告の作業ステップ（着手→完了）</t>
         </is>
       </c>
-      <c r="D48" s="10" t="inlineStr">
+      <c r="D48" s="9" t="inlineStr">
+        <is>
+          <t>記述〔ヒアリング〕</t>
+        </is>
+      </c>
+      <c r="E48" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="F48" s="10" t="inlineStr">
         <is>
           <t>To-Be業務フロー・画面遷移・入力ステップ設計の土台がなく、UI設計が机上になる。</t>
         </is>
       </c>
-      <c r="E48" s="10" t="inlineStr">
+      <c r="G48" s="10" t="inlineStr">
         <is>
           <t>To-Beフロー・画面設計</t>
         </is>
       </c>
-      <c r="F48" s="12" t="inlineStr">
+      <c r="H48" s="13" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="G48" s="10" t="inlineStr">
+      <c r="I48" s="10" t="inlineStr">
         <is>
           <t>標準テンプレートのフローを当該拠点に適用（適合しない場合の改修は当該拠点起因）。</t>
         </is>
@@ -2343,22 +2739,30 @@
           <t>最も時間がかかる／神経を使うステップ</t>
         </is>
       </c>
-      <c r="D49" s="10" t="inlineStr">
+      <c r="D49" s="9" t="inlineStr">
+        <is>
+          <t>記述〔ヒアリング〕</t>
+        </is>
+      </c>
+      <c r="E49" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="F49" s="10" t="inlineStr">
         <is>
           <t>自動化・チェック機能の優先順位の根拠を失う。</t>
         </is>
       </c>
-      <c r="E49" s="10" t="inlineStr">
+      <c r="G49" s="10" t="inlineStr">
         <is>
           <t>機能優先度</t>
         </is>
       </c>
-      <c r="F49" s="11" t="inlineStr">
+      <c r="H49" s="11" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="G49" s="10" t="inlineStr">
+      <c r="I49" s="10" t="inlineStr">
         <is>
           <t>「転記・入力」が最重とみなす。</t>
         </is>
@@ -2380,22 +2784,30 @@
           <t>月次入力の実施タイミング</t>
         </is>
       </c>
-      <c r="D50" s="10" t="inlineStr">
+      <c r="D50" s="9" t="inlineStr">
+        <is>
+          <t>記述〔ヒアリング〕</t>
+        </is>
+      </c>
+      <c r="E50" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="F50" s="10" t="inlineStr">
         <is>
           <t>締め処理・リマインダーのカレンダー設計ができない。</t>
         </is>
       </c>
-      <c r="E50" s="10" t="inlineStr">
+      <c r="G50" s="10" t="inlineStr">
         <is>
           <t>締めスケジュール設計</t>
         </is>
       </c>
-      <c r="F50" s="11" t="inlineStr">
+      <c r="H50" s="11" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="G50" s="10" t="inlineStr">
+      <c r="I50" s="10" t="inlineStr">
         <is>
           <t>「月初5営業日以内」とみなす。</t>
         </is>
@@ -2417,22 +2829,30 @@
           <t>検針日・請求書到着と締切の時間差</t>
         </is>
       </c>
-      <c r="D51" s="10" t="inlineStr">
+      <c r="D51" s="9" t="inlineStr">
+        <is>
+          <t>記述〔ヒアリング〕</t>
+        </is>
+      </c>
+      <c r="E51" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="F51" s="10" t="inlineStr">
         <is>
           <t>締切設定が物理的に実現可能かが検証できず、実現不能な締切を要件化するリスク。</t>
         </is>
       </c>
-      <c r="E51" s="10" t="inlineStr">
+      <c r="G51" s="10" t="inlineStr">
         <is>
           <t>締切設計・推計値運用</t>
         </is>
       </c>
-      <c r="F51" s="12" t="inlineStr">
+      <c r="H51" s="13" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="G51" s="10" t="inlineStr">
+      <c r="I51" s="10" t="inlineStr">
         <is>
           <t>「間に合わない月あり」とみなし推計値入力→実績置換の機能を要件化。</t>
         </is>
@@ -2454,22 +2874,30 @@
           <t>期ズレの処理方法（詳細）</t>
         </is>
       </c>
-      <c r="D52" s="10" t="inlineStr">
+      <c r="D52" s="9" t="inlineStr">
+        <is>
+          <t>選択+補足〔ヒアリング〕</t>
+        </is>
+      </c>
+      <c r="E52" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="F52" s="10" t="inlineStr">
         <is>
           <t>C-03の詳細。按分エンジンの仕様（方式・端数処理）が確定できない。</t>
         </is>
       </c>
-      <c r="E52" s="10" t="inlineStr">
+      <c r="G52" s="10" t="inlineStr">
         <is>
           <t>算定エンジン仕様</t>
         </is>
       </c>
-      <c r="F52" s="12" t="inlineStr">
+      <c r="H52" s="13" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="G52" s="10" t="inlineStr">
+      <c r="I52" s="10" t="inlineStr">
         <is>
           <t>複数方式対応で設計（費用増）。</t>
         </is>
@@ -2491,22 +2919,30 @@
           <t>年間繁忙月と理由</t>
         </is>
       </c>
-      <c r="D53" s="10" t="inlineStr">
+      <c r="D53" s="9" t="inlineStr">
+        <is>
+          <t>記述〔ヒアリング〕</t>
+        </is>
+      </c>
+      <c r="E53" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="F53" s="10" t="inlineStr">
         <is>
           <t>C-22と同。性能・スケジュール設計の精度が下がる。</t>
         </is>
       </c>
-      <c r="E53" s="10" t="inlineStr">
+      <c r="G53" s="10" t="inlineStr">
         <is>
           <t>性能要件</t>
         </is>
       </c>
-      <c r="F53" s="13" t="inlineStr">
+      <c r="H53" s="14" t="inlineStr">
         <is>
           <t>低</t>
         </is>
       </c>
-      <c r="G53" s="10" t="inlineStr">
+      <c r="I53" s="10" t="inlineStr">
         <is>
           <t>「1〜3月」とみなす。</t>
         </is>
@@ -2528,22 +2964,30 @@
           <t>修正頻度と主な理由</t>
         </is>
       </c>
-      <c r="D54" s="10" t="inlineStr">
+      <c r="D54" s="9" t="inlineStr">
+        <is>
+          <t>選択+補足〔ヒアリング〕</t>
+        </is>
+      </c>
+      <c r="E54" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="F54" s="10" t="inlineStr">
         <is>
           <t>修正WFの分岐（理由別の承認レベル）が設計できない。</t>
         </is>
       </c>
-      <c r="E54" s="10" t="inlineStr">
+      <c r="G54" s="10" t="inlineStr">
         <is>
           <t>修正WF設計</t>
         </is>
       </c>
-      <c r="F54" s="11" t="inlineStr">
+      <c r="H54" s="11" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="G54" s="10" t="inlineStr">
+      <c r="I54" s="10" t="inlineStr">
         <is>
           <t>「毎月・理由多様」とみなす。</t>
         </is>
@@ -2565,22 +3009,30 @@
           <t>修正方法と連絡経路</t>
         </is>
       </c>
-      <c r="D55" s="10" t="inlineStr">
+      <c r="D55" s="9" t="inlineStr">
+        <is>
+          <t>記述〔ヒアリング〕</t>
+        </is>
+      </c>
+      <c r="E55" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="F55" s="10" t="inlineStr">
         <is>
           <t>差戻し・通知設計が実態と乖離するリスク。</t>
         </is>
       </c>
-      <c r="E55" s="10" t="inlineStr">
+      <c r="G55" s="10" t="inlineStr">
         <is>
           <t>差戻しフロー・通知設計</t>
         </is>
       </c>
-      <c r="F55" s="11" t="inlineStr">
+      <c r="H55" s="11" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="G55" s="10" t="inlineStr">
+      <c r="I55" s="10" t="inlineStr">
         <is>
           <t>「上書き・連絡なし」とみなす。</t>
         </is>
@@ -2602,22 +3054,30 @@
           <t>過年度遡及修正の作業実態</t>
         </is>
       </c>
-      <c r="D56" s="10" t="inlineStr">
+      <c r="D56" s="9" t="inlineStr">
+        <is>
+          <t>記述〔ヒアリング〕</t>
+        </is>
+      </c>
+      <c r="E56" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="F56" s="10" t="inlineStr">
         <is>
           <t>遡及再計算機能の深度（何年分・何を再計算するか）が決められない。</t>
         </is>
       </c>
-      <c r="E56" s="10" t="inlineStr">
+      <c r="G56" s="10" t="inlineStr">
         <is>
           <t>遡及再計算仕様</t>
         </is>
       </c>
-      <c r="F56" s="11" t="inlineStr">
+      <c r="H56" s="11" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="G56" s="10" t="inlineStr">
+      <c r="I56" s="10" t="inlineStr">
         <is>
           <t>「過去3年分の遡及が必要」とみなす。</t>
         </is>
@@ -2639,22 +3099,30 @@
           <t>欠測の典型パターンと穴埋め方法</t>
         </is>
       </c>
-      <c r="D57" s="10" t="inlineStr">
+      <c r="D57" s="9" t="inlineStr">
+        <is>
+          <t>記述〔ヒアリング〕</t>
+        </is>
+      </c>
+      <c r="E57" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="F57" s="10" t="inlineStr">
         <is>
           <t>欠測時の推計・代替ルール（例外設計）が現場実態と乖離し、稼働後に入力が止まる。</t>
         </is>
       </c>
-      <c r="E57" s="10" t="inlineStr">
+      <c r="G57" s="10" t="inlineStr">
         <is>
           <t>例外設計・推計ルール</t>
         </is>
       </c>
-      <c r="F57" s="12" t="inlineStr">
+      <c r="H57" s="13" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="G57" s="10" t="inlineStr">
+      <c r="I57" s="10" t="inlineStr">
         <is>
           <t>「メーター故障・請求遅延・担当不在の3パターンあり」とみなし例外フローを実装。</t>
         </is>
@@ -2676,22 +3144,30 @@
           <t>督促を受ける頻度と根本原因</t>
         </is>
       </c>
-      <c r="D58" s="10" t="inlineStr">
+      <c r="D58" s="9" t="inlineStr">
+        <is>
+          <t>記述〔ヒアリング〕</t>
+        </is>
+      </c>
+      <c r="E58" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="F58" s="10" t="inlineStr">
         <is>
           <t>督促自動化の設計根拠を失うが根幹には影響しない。</t>
         </is>
       </c>
-      <c r="E58" s="10" t="inlineStr">
+      <c r="G58" s="10" t="inlineStr">
         <is>
           <t>督促設計</t>
         </is>
       </c>
-      <c r="F58" s="13" t="inlineStr">
+      <c r="H58" s="14" t="inlineStr">
         <is>
           <t>低</t>
         </is>
       </c>
-      <c r="G58" s="10" t="inlineStr">
+      <c r="I58" s="10" t="inlineStr">
         <is>
           <t>「月1回以上」とみなす。</t>
         </is>
@@ -2713,22 +3189,30 @@
           <t>メーター交換・契約変更時の処理手順</t>
         </is>
       </c>
-      <c r="D59" s="10" t="inlineStr">
+      <c r="D59" s="9" t="inlineStr">
+        <is>
+          <t>選択+補足〔ヒアリング〕</t>
+        </is>
+      </c>
+      <c r="E59" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="F59" s="10" t="inlineStr">
         <is>
           <t>設備・契約マスタの変更イベント処理（計測連続性の担保）が設計できない。</t>
         </is>
       </c>
-      <c r="E59" s="10" t="inlineStr">
+      <c r="G59" s="10" t="inlineStr">
         <is>
           <t>マスタ変更イベント処理</t>
         </is>
       </c>
-      <c r="F59" s="11" t="inlineStr">
+      <c r="H59" s="11" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="G59" s="10" t="inlineStr">
+      <c r="I59" s="10" t="inlineStr">
         <is>
           <t>「手順なし」とみなしシステム側でガイドを実装。</t>
         </is>
@@ -2750,22 +3234,30 @@
           <t>組織変更・拠点統廃合時のデータ連続性</t>
         </is>
       </c>
-      <c r="D60" s="10" t="inlineStr">
+      <c r="D60" s="9" t="inlineStr">
+        <is>
+          <t>記述〔ヒアリング〕</t>
+        </is>
+      </c>
+      <c r="E60" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="F60" s="10" t="inlineStr">
         <is>
           <t>組織マスタの世代管理（比較可能性の担保）が設計できない。SSBJの過年度比較の根幹。</t>
         </is>
       </c>
-      <c r="E60" s="10" t="inlineStr">
+      <c r="G60" s="10" t="inlineStr">
         <is>
           <t>組織マスタ世代管理・比較可能性</t>
         </is>
       </c>
-      <c r="F60" s="12" t="inlineStr">
+      <c r="H60" s="13" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="G60" s="10" t="inlineStr">
+      <c r="I60" s="10" t="inlineStr">
         <is>
           <t>「連続性の担保なし」とみなし組織改編対応機能を必須化。</t>
         </is>
@@ -2787,22 +3279,30 @@
           <t>複数報告間の数値不一致の有無と原因</t>
         </is>
       </c>
-      <c r="D61" s="10" t="inlineStr">
+      <c r="D61" s="9" t="inlineStr">
+        <is>
+          <t>選択+補足〔ヒアリング〕</t>
+        </is>
+      </c>
+      <c r="E61" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="F61" s="10" t="inlineStr">
         <is>
           <t>ワンソース・マルチユース要件の根拠を失い、開示数値の不整合リスク（最悪、訂正開示）が残置される。</t>
         </is>
       </c>
-      <c r="E61" s="10" t="inlineStr">
+      <c r="G61" s="10" t="inlineStr">
         <is>
           <t>一元データ管理・開示整合性</t>
         </is>
       </c>
-      <c r="F61" s="12" t="inlineStr">
+      <c r="H61" s="13" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="G61" s="10" t="inlineStr">
+      <c r="I61" s="10" t="inlineStr">
         <is>
           <t>「不一致あり」とみなし単一ソースからの多目的出力を必須要件化。</t>
         </is>
@@ -2824,22 +3324,30 @@
           <t>担当者不在時の代替可否</t>
         </is>
       </c>
-      <c r="D62" s="10" t="inlineStr">
+      <c r="D62" s="9" t="inlineStr">
+        <is>
+          <t>選択+補足〔ヒアリング〕</t>
+        </is>
+      </c>
+      <c r="E62" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="F62" s="10" t="inlineStr">
         <is>
           <t>C-05と同。</t>
         </is>
       </c>
-      <c r="E62" s="10" t="inlineStr">
+      <c r="G62" s="10" t="inlineStr">
         <is>
           <t>代行設計</t>
         </is>
       </c>
-      <c r="F62" s="13" t="inlineStr">
+      <c r="H62" s="14" t="inlineStr">
         <is>
           <t>低</t>
         </is>
       </c>
-      <c r="G62" s="10" t="inlineStr">
+      <c r="I62" s="10" t="inlineStr">
         <is>
           <t>「止まる」とみなす。</t>
         </is>
@@ -2861,22 +3369,30 @@
           <t>後任の独り立ちに要する期間</t>
         </is>
       </c>
-      <c r="D63" s="10" t="inlineStr">
+      <c r="D63" s="12" t="inlineStr">
+        <is>
+          <t>選択のみ〔ヒアリング〕</t>
+        </is>
+      </c>
+      <c r="E63" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="F63" s="10" t="inlineStr">
         <is>
           <t>教育・研修要件の規模が決められない。</t>
         </is>
       </c>
-      <c r="E63" s="10" t="inlineStr">
+      <c r="G63" s="10" t="inlineStr">
         <is>
           <t>教育要件</t>
         </is>
       </c>
-      <c r="F63" s="13" t="inlineStr">
+      <c r="H63" s="14" t="inlineStr">
         <is>
           <t>低</t>
         </is>
       </c>
-      <c r="G63" s="10" t="inlineStr">
+      <c r="I63" s="10" t="inlineStr">
         <is>
           <t>「3ヶ月」とみなす。</t>
         </is>
@@ -2894,6 +3410,8 @@
       <c r="E64" s="7" t="n"/>
       <c r="F64" s="7" t="n"/>
       <c r="G64" s="7" t="n"/>
+      <c r="H64" s="7" t="n"/>
+      <c r="I64" s="7" t="n"/>
     </row>
     <row r="65" ht="52" customHeight="1">
       <c r="A65" s="8" t="inlineStr">
@@ -2911,22 +3429,30 @@
           <t>拠点側の計算範囲（詳細）</t>
         </is>
       </c>
-      <c r="D65" s="10" t="inlineStr">
+      <c r="D65" s="9" t="inlineStr">
+        <is>
+          <t>選択+補足〔ヒアリング〕</t>
+        </is>
+      </c>
+      <c r="E65" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="F65" s="10" t="inlineStr">
         <is>
           <t>C-06の詳細。算定エンジンの機能配置が確定できない。</t>
         </is>
       </c>
-      <c r="E65" s="10" t="inlineStr">
+      <c r="G65" s="10" t="inlineStr">
         <is>
           <t>算定エンジン配置</t>
         </is>
       </c>
-      <c r="F65" s="12" t="inlineStr">
+      <c r="H65" s="13" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="G65" s="10" t="inlineStr">
+      <c r="I65" s="10" t="inlineStr">
         <is>
           <t>「拠点独自計算あり」とみなす。</t>
         </is>
@@ -2948,22 +3474,30 @@
           <t>使用係数の名称・出典・年度版の全量</t>
         </is>
       </c>
-      <c r="D66" s="10" t="inlineStr">
+      <c r="D66" s="9" t="inlineStr">
+        <is>
+          <t>記述〔ヒアリング〕</t>
+        </is>
+      </c>
+      <c r="E66" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="F66" s="10" t="inlineStr">
         <is>
           <t>係数マスタの初期データ（出典・版）が作れない。監査で「この数値の係数の出典は」と問われ回答不能＝保証の重大指摘。</t>
         </is>
       </c>
-      <c r="E66" s="10" t="inlineStr">
+      <c r="G66" s="10" t="inlineStr">
         <is>
           <t>係数マスタ初期整備・保証対応</t>
         </is>
       </c>
-      <c r="F66" s="12" t="inlineStr">
+      <c r="H66" s="13" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="G66" s="10" t="inlineStr">
+      <c r="I66" s="10" t="inlineStr">
         <is>
           <t>「出典不明の係数あり」とみなし、全係数を本社標準に強制置換（過年度との数値断絶は当該拠点起因）。</t>
         </is>
@@ -2985,22 +3519,30 @@
           <t>係数更新の連絡経路・適用時期・再計算有無</t>
         </is>
       </c>
-      <c r="D67" s="10" t="inlineStr">
+      <c r="D67" s="9" t="inlineStr">
+        <is>
+          <t>記述〔ヒアリング〕</t>
+        </is>
+      </c>
+      <c r="E67" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="F67" s="10" t="inlineStr">
         <is>
           <t>係数版管理・遡及再計算のトリガー設計ができず、係数改定のたびに手作業対応が残る。</t>
         </is>
       </c>
-      <c r="E67" s="10" t="inlineStr">
+      <c r="G67" s="10" t="inlineStr">
         <is>
           <t>係数版管理・自動再計算</t>
         </is>
       </c>
-      <c r="F67" s="12" t="inlineStr">
+      <c r="H67" s="13" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="G67" s="10" t="inlineStr">
+      <c r="I67" s="10" t="inlineStr">
         <is>
           <t>「連絡なし・再計算なし」とみなし自動再計算を必須化。</t>
         </is>
@@ -3022,22 +3564,30 @@
           <t>独自係数・独自ルールの内容と理由</t>
         </is>
       </c>
-      <c r="D68" s="10" t="inlineStr">
+      <c r="D68" s="9" t="inlineStr">
+        <is>
+          <t>選択+補足〔ヒアリング〕</t>
+        </is>
+      </c>
+      <c r="E68" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="F68" s="10" t="inlineStr">
         <is>
           <t>C-07の詳細。未申告の独自ルールは移行後の数値差異として顕在化。</t>
         </is>
       </c>
-      <c r="E68" s="10" t="inlineStr">
+      <c r="G68" s="10" t="inlineStr">
         <is>
           <t>係数マスタ・数値連続性</t>
         </is>
       </c>
-      <c r="F68" s="12" t="inlineStr">
+      <c r="H68" s="13" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="G68" s="10" t="inlineStr">
+      <c r="I68" s="10" t="inlineStr">
         <is>
           <t>「独自ルールあり・内容不明」とみなし本社標準に強制統一（差異発生は当該拠点起因）。</t>
         </is>
@@ -3059,22 +3609,30 @@
           <t>単位換算の場面と換算表の管理者</t>
         </is>
       </c>
-      <c r="D69" s="10" t="inlineStr">
+      <c r="D69" s="9" t="inlineStr">
+        <is>
+          <t>記述〔ヒアリング〕</t>
+        </is>
+      </c>
+      <c r="E69" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="F69" s="10" t="inlineStr">
         <is>
           <t>換算マスタ（換算係数・管理責任）が設計できない。</t>
         </is>
       </c>
-      <c r="E69" s="10" t="inlineStr">
+      <c r="G69" s="10" t="inlineStr">
         <is>
           <t>換算マスタ設計</t>
         </is>
       </c>
-      <c r="F69" s="11" t="inlineStr">
+      <c r="H69" s="11" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="G69" s="10" t="inlineStr">
+      <c r="I69" s="10" t="inlineStr">
         <is>
           <t>「管理者不在・Excel内に散在」とみなす。</t>
         </is>
@@ -3096,22 +3654,30 @@
           <t>按分計算の項目と按分基準の根拠</t>
         </is>
       </c>
-      <c r="D70" s="10" t="inlineStr">
+      <c r="D70" s="9" t="inlineStr">
+        <is>
+          <t>記述〔ヒアリング〕</t>
+        </is>
+      </c>
+      <c r="E70" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="F70" s="10" t="inlineStr">
         <is>
           <t>按分エンジンの仕様（基準マスタ）と、監査での按分根拠の説明可能性が確保できない。</t>
         </is>
       </c>
-      <c r="E70" s="10" t="inlineStr">
+      <c r="G70" s="10" t="inlineStr">
         <is>
           <t>按分エンジン・按分基準マスタ</t>
         </is>
       </c>
-      <c r="F70" s="12" t="inlineStr">
+      <c r="H70" s="13" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="G70" s="10" t="inlineStr">
+      <c r="I70" s="10" t="inlineStr">
         <is>
           <t>「根拠文書なし」とみなし按分基準の再整備タスクを計画化（工数は当該拠点負担）。</t>
         </is>
@@ -3133,22 +3699,30 @@
           <t>按分基準の見直し頻度・根拠資料</t>
         </is>
       </c>
-      <c r="D71" s="10" t="inlineStr">
+      <c r="D71" s="9" t="inlineStr">
+        <is>
+          <t>記述〔ヒアリング〕</t>
+        </is>
+      </c>
+      <c r="E71" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="F71" s="10" t="inlineStr">
         <is>
           <t>按分根拠の証跡化要件（版管理）が設計できない。</t>
         </is>
       </c>
-      <c r="E71" s="10" t="inlineStr">
+      <c r="G71" s="10" t="inlineStr">
         <is>
           <t>按分証跡要件</t>
         </is>
       </c>
-      <c r="F71" s="11" t="inlineStr">
+      <c r="H71" s="11" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="G71" s="10" t="inlineStr">
+      <c r="I71" s="10" t="inlineStr">
         <is>
           <t>「見直しなし・資料なし」とみなす。</t>
         </is>
@@ -3170,22 +3744,30 @@
           <t>推計項目・推計方法・割合</t>
         </is>
       </c>
-      <c r="D72" s="10" t="inlineStr">
+      <c r="D72" s="9" t="inlineStr">
+        <is>
+          <t>記述〔ヒアリング〕</t>
+        </is>
+      </c>
+      <c r="E72" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="F72" s="10" t="inlineStr">
         <is>
           <t>C-26の詳細。推計ロジックの標準化範囲が確定しない。</t>
         </is>
       </c>
-      <c r="E72" s="10" t="inlineStr">
+      <c r="G72" s="10" t="inlineStr">
         <is>
           <t>推計ロジック標準化</t>
         </is>
       </c>
-      <c r="F72" s="12" t="inlineStr">
+      <c r="H72" s="13" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="G72" s="10" t="inlineStr">
+      <c r="I72" s="10" t="inlineStr">
         <is>
           <t>「推計方法バラバラ」とみなし標準推計式を強制適用。</t>
         </is>
@@ -3207,22 +3789,30 @@
           <t>計算Excelの作成者・在籍状況・説明可能者数</t>
         </is>
       </c>
-      <c r="D73" s="10" t="inlineStr">
+      <c r="D73" s="9" t="inlineStr">
+        <is>
+          <t>記述〔ヒアリング〕</t>
+        </is>
+      </c>
+      <c r="E73" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="F73" s="10" t="inlineStr">
         <is>
           <t>C-08の詳細。ロジック資産の仕分け（残す/移植/作り直す/捨てる）が不能になり、移植工数が確定しない。</t>
         </is>
       </c>
-      <c r="E73" s="10" t="inlineStr">
+      <c r="G73" s="10" t="inlineStr">
         <is>
           <t>ロジック移植計画</t>
         </is>
       </c>
-      <c r="F73" s="12" t="inlineStr">
+      <c r="H73" s="13" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="G73" s="10" t="inlineStr">
+      <c r="I73" s="10" t="inlineStr">
         <is>
           <t>「作成者退職・説明者ゼロ」とみなしロジック再構築（作り直し）費用を計上。</t>
         </is>
@@ -3244,22 +3834,30 @@
           <t>計算Excelの修正対応可否</t>
         </is>
       </c>
-      <c r="D74" s="10" t="inlineStr">
+      <c r="D74" s="12" t="inlineStr">
+        <is>
+          <t>選択のみ〔ヒアリング〕</t>
+        </is>
+      </c>
+      <c r="E74" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="F74" s="10" t="inlineStr">
         <is>
           <t>同上の補完。要件定義中にロジック検証へ協力できる人がいるかの確認。</t>
         </is>
       </c>
-      <c r="E74" s="10" t="inlineStr">
+      <c r="G74" s="10" t="inlineStr">
         <is>
           <t>ロジック検証体制</t>
         </is>
       </c>
-      <c r="F74" s="11" t="inlineStr">
+      <c r="H74" s="11" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="G74" s="10" t="inlineStr">
+      <c r="I74" s="10" t="inlineStr">
         <is>
           <t>「できない」とみなす。</t>
         </is>
@@ -3281,22 +3879,30 @@
           <t>計算結果の妥当性判断方法</t>
         </is>
       </c>
-      <c r="D75" s="10" t="inlineStr">
+      <c r="D75" s="9" t="inlineStr">
+        <is>
+          <t>記述〔ヒアリング〕</t>
+        </is>
+      </c>
+      <c r="E75" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="F75" s="10" t="inlineStr">
         <is>
           <t>異常値検知の閾値・確認手順の初期値が机上設定になる。</t>
         </is>
       </c>
-      <c r="E75" s="10" t="inlineStr">
+      <c r="G75" s="10" t="inlineStr">
         <is>
           <t>異常値検知設計</t>
         </is>
       </c>
-      <c r="F75" s="11" t="inlineStr">
+      <c r="H75" s="11" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="G75" s="10" t="inlineStr">
+      <c r="I75" s="10" t="inlineStr">
         <is>
           <t>「目視・感覚のみ」とみなす。</t>
         </is>
@@ -3318,22 +3924,30 @@
           <t>計算ファイルのバージョン管理</t>
         </is>
       </c>
-      <c r="D76" s="10" t="inlineStr">
+      <c r="D76" s="9" t="inlineStr">
+        <is>
+          <t>記述〔ヒアリング〕</t>
+        </is>
+      </c>
+      <c r="E76" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="F76" s="10" t="inlineStr">
         <is>
           <t>移行時に「正版」を特定できず、誤った版のロジックをシステム化するリスク。過年度数値の再現もできない。</t>
         </is>
       </c>
-      <c r="E76" s="10" t="inlineStr">
+      <c r="G76" s="10" t="inlineStr">
         <is>
           <t>移行時の正版特定・数値再現性</t>
         </is>
       </c>
-      <c r="F76" s="12" t="inlineStr">
+      <c r="H76" s="13" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="G76" s="10" t="inlineStr">
+      <c r="I76" s="10" t="inlineStr">
         <is>
           <t>「版管理なし」とみなし移行時のロジック検証（正版特定）タスクを計画化。</t>
         </is>
@@ -3355,22 +3969,30 @@
           <t>小口排出源（社有車・非常用発電機等）の網羅状況</t>
         </is>
       </c>
-      <c r="D77" s="10" t="inlineStr">
+      <c r="D77" s="9" t="inlineStr">
+        <is>
+          <t>選択+補足〔ヒアリング〕</t>
+        </is>
+      </c>
+      <c r="E77" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="F77" s="10" t="inlineStr">
         <is>
           <t>排出源の網羅性＝保証の完全性要件が確認できない。バウンダリの漏れは保証の指摘対象。</t>
         </is>
       </c>
-      <c r="E77" s="10" t="inlineStr">
+      <c r="G77" s="10" t="inlineStr">
         <is>
           <t>バウンダリ設計・完全性</t>
         </is>
       </c>
-      <c r="F77" s="12" t="inlineStr">
+      <c r="H77" s="13" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="G77" s="10" t="inlineStr">
+      <c r="I77" s="10" t="inlineStr">
         <is>
           <t>「漏れあり」とみなし網羅性再調査タスクを計画化（工数は当該拠点負担）。</t>
         </is>
@@ -3392,22 +4014,30 @@
           <t>冷媒（フロン類）の把握方法</t>
         </is>
       </c>
-      <c r="D78" s="10" t="inlineStr">
+      <c r="D78" s="9" t="inlineStr">
+        <is>
+          <t>記述〔ヒアリング〕</t>
+        </is>
+      </c>
+      <c r="E78" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="F78" s="10" t="inlineStr">
         <is>
           <t>冷媒管理機能（充填・漏えい記録）の要否とデータ源が決められない。</t>
         </is>
       </c>
-      <c r="E78" s="10" t="inlineStr">
+      <c r="G78" s="10" t="inlineStr">
         <is>
           <t>冷媒管理機能</t>
         </is>
       </c>
-      <c r="F78" s="11" t="inlineStr">
+      <c r="H78" s="11" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="G78" s="10" t="inlineStr">
+      <c r="I78" s="10" t="inlineStr">
         <is>
           <t>「点検記録から手動転記」とみなす。</t>
         </is>
@@ -3429,22 +4059,30 @@
           <t>水の取水源別計測・排水把握</t>
         </is>
       </c>
-      <c r="D79" s="10" t="inlineStr">
+      <c r="D79" s="9" t="inlineStr">
+        <is>
+          <t>記述〔ヒアリング〕</t>
+        </is>
+      </c>
+      <c r="E79" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="F79" s="10" t="inlineStr">
         <is>
           <t>水関連のデータモデル（実測/推計区分）が設計できない。</t>
         </is>
       </c>
-      <c r="E79" s="10" t="inlineStr">
+      <c r="G79" s="10" t="inlineStr">
         <is>
           <t>水データモデル</t>
         </is>
       </c>
-      <c r="F79" s="11" t="inlineStr">
+      <c r="H79" s="11" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="G79" s="10" t="inlineStr">
+      <c r="I79" s="10" t="inlineStr">
         <is>
           <t>「上水以外は推計」とみなす。</t>
         </is>
@@ -3466,22 +4104,30 @@
           <t>廃棄物のマニフェスト照合有無</t>
         </is>
       </c>
-      <c r="D80" s="10" t="inlineStr">
+      <c r="D80" s="9" t="inlineStr">
+        <is>
+          <t>選択+補足〔ヒアリング〕</t>
+        </is>
+      </c>
+      <c r="E80" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="F80" s="10" t="inlineStr">
         <is>
           <t>マニフェスト連携・照合機能の要否が決められない。</t>
         </is>
       </c>
-      <c r="E80" s="10" t="inlineStr">
+      <c r="G80" s="10" t="inlineStr">
         <is>
           <t>廃棄物照合機能</t>
         </is>
       </c>
-      <c r="F80" s="11" t="inlineStr">
+      <c r="H80" s="11" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="G80" s="10" t="inlineStr">
+      <c r="I80" s="10" t="inlineStr">
         <is>
           <t>「照合なし」とみなす。</t>
         </is>
@@ -3503,22 +4149,30 @@
           <t>Scope3関連データの提供可能範囲</t>
         </is>
       </c>
-      <c r="D81" s="10" t="inlineStr">
+      <c r="D81" s="9" t="inlineStr">
+        <is>
+          <t>記述〔ヒアリング〕</t>
+        </is>
+      </c>
+      <c r="E81" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="F81" s="10" t="inlineStr">
         <is>
           <t>Scope3一次データ化（攻めの柱）の実現可能性が検証できず、拡張性要件が机上になる。</t>
         </is>
       </c>
-      <c r="E81" s="10" t="inlineStr">
+      <c r="G81" s="10" t="inlineStr">
         <is>
           <t>Scope3拡張要件（攻め）</t>
         </is>
       </c>
-      <c r="F81" s="12" t="inlineStr">
+      <c r="H81" s="13" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="G81" s="10" t="inlineStr">
+      <c r="I81" s="10" t="inlineStr">
         <is>
           <t>「提供不可」とみなしScope3拡張は将来要件へ後退（攻めの効果縮小は当該拠点起因として記録）。</t>
         </is>
@@ -3540,22 +4194,30 @@
           <t>製品LCA用データの関与・粒度</t>
         </is>
       </c>
-      <c r="D82" s="10" t="inlineStr">
+      <c r="D82" s="9" t="inlineStr">
+        <is>
+          <t>記述〔ヒアリング〕</t>
+        </is>
+      </c>
+      <c r="E82" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="F82" s="10" t="inlineStr">
         <is>
           <t>CFP即応（攻めユースケース第1候補）に必要な製品別データ構造（生産量×組成×包材）の実現可能性が確認できない。</t>
         </is>
       </c>
-      <c r="E82" s="10" t="inlineStr">
+      <c r="G82" s="10" t="inlineStr">
         <is>
           <t>CFP対応データ構造（攻め）</t>
         </is>
       </c>
-      <c r="F82" s="12" t="inlineStr">
+      <c r="H82" s="13" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="G82" s="10" t="inlineStr">
+      <c r="I82" s="10" t="inlineStr">
         <is>
           <t>「提供不可」とみなしCFP即応要件を縮小（受注対応力の逸失として記録）。</t>
         </is>
@@ -3577,22 +4239,30 @@
           <t>人事・労安データの定義の揺れ</t>
         </is>
       </c>
-      <c r="D83" s="10" t="inlineStr">
+      <c r="D83" s="9" t="inlineStr">
+        <is>
+          <t>記述〔ヒアリング〕</t>
+        </is>
+      </c>
+      <c r="E83" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="F83" s="10" t="inlineStr">
         <is>
           <t>S（社会）系データの定義標準化の対象が特定できず、拠点解釈のまま要件が固まる。</t>
         </is>
       </c>
-      <c r="E83" s="10" t="inlineStr">
+      <c r="G83" s="10" t="inlineStr">
         <is>
           <t>S系データ定義標準化</t>
         </is>
       </c>
-      <c r="F83" s="11" t="inlineStr">
+      <c r="H83" s="11" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="G83" s="10" t="inlineStr">
+      <c r="I83" s="10" t="inlineStr">
         <is>
           <t>「定義揺れあり」とみなし本社定義を強制適用。</t>
         </is>
@@ -3614,22 +4284,30 @@
           <t>本社算定ルールで曖昧・矛盾と感じる点</t>
         </is>
       </c>
-      <c r="D84" s="10" t="inlineStr">
+      <c r="D84" s="9" t="inlineStr">
+        <is>
+          <t>記述〔ヒアリング〕</t>
+        </is>
+      </c>
+      <c r="E84" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="F84" s="10" t="inlineStr">
         <is>
           <t>ルール標準化のバックログ（難所①の検討リスト）が作れず、曖昧なルールがそのままシステム要件に転写される。</t>
         </is>
       </c>
-      <c r="E84" s="10" t="inlineStr">
+      <c r="G84" s="10" t="inlineStr">
         <is>
           <t>算定ルール標準化・難所①</t>
         </is>
       </c>
-      <c r="F84" s="12" t="inlineStr">
+      <c r="H84" s="13" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="G84" s="10" t="inlineStr">
+      <c r="I84" s="10" t="inlineStr">
         <is>
           <t>「曖昧箇所なし」とみなしルールを現行のまま確定（後日の解釈揺れによる改修は未回答拠点起因）。</t>
         </is>
@@ -3647,6 +4325,8 @@
       <c r="E85" s="7" t="n"/>
       <c r="F85" s="7" t="n"/>
       <c r="G85" s="7" t="n"/>
+      <c r="H85" s="7" t="n"/>
+      <c r="I85" s="7" t="n"/>
     </row>
     <row r="86" ht="52" customHeight="1">
       <c r="A86" s="8" t="inlineStr">
@@ -3664,22 +4344,30 @@
           <t>証憑の種類の全量</t>
         </is>
       </c>
-      <c r="D86" s="10" t="inlineStr">
+      <c r="D86" s="9" t="inlineStr">
+        <is>
+          <t>記述〔ヒアリング〕</t>
+        </is>
+      </c>
+      <c r="E86" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="F86" s="10" t="inlineStr">
         <is>
           <t>証憑管理機能の対象（添付形式・種類マスタ）が設計できない。</t>
         </is>
       </c>
-      <c r="E86" s="10" t="inlineStr">
+      <c r="G86" s="10" t="inlineStr">
         <is>
           <t>証憑種類マスタ</t>
         </is>
       </c>
-      <c r="F86" s="11" t="inlineStr">
+      <c r="H86" s="11" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="G86" s="10" t="inlineStr">
+      <c r="I86" s="10" t="inlineStr">
         <is>
           <t>「請求書・検針票・マニフェスト」の標準3種とみなす。</t>
         </is>
@@ -3701,22 +4389,30 @@
           <t>証憑形式の内訳（紙/PDF/システム内）</t>
         </is>
       </c>
-      <c r="D87" s="10" t="inlineStr">
+      <c r="D87" s="9" t="inlineStr">
+        <is>
+          <t>記述〔ヒアリング〕</t>
+        </is>
+      </c>
+      <c r="E87" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="F87" s="10" t="inlineStr">
         <is>
           <t>C-09の詳細。スキャン運用・容量設計の精度が下がる。</t>
         </is>
       </c>
-      <c r="E87" s="10" t="inlineStr">
+      <c r="G87" s="10" t="inlineStr">
         <is>
           <t>ストレージ・スキャン運用</t>
         </is>
       </c>
-      <c r="F87" s="11" t="inlineStr">
+      <c r="H87" s="11" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="G87" s="10" t="inlineStr">
+      <c r="I87" s="10" t="inlineStr">
         <is>
           <t>「紙半分」とみなす。</t>
         </is>
@@ -3738,22 +4434,30 @@
           <t>証憑の保管場所の全量</t>
         </is>
       </c>
-      <c r="D88" s="10" t="inlineStr">
+      <c r="D88" s="9" t="inlineStr">
+        <is>
+          <t>記述〔ヒアリング〕</t>
+        </is>
+      </c>
+      <c r="E88" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="F88" s="10" t="inlineStr">
         <is>
           <t>移行対象証憑の所在が特定できず、移行計画から漏れる。個人PC保管分は消失リスク。</t>
         </is>
       </c>
-      <c r="E88" s="10" t="inlineStr">
+      <c r="G88" s="10" t="inlineStr">
         <is>
           <t>証憑移行計画</t>
         </is>
       </c>
-      <c r="F88" s="12" t="inlineStr">
+      <c r="H88" s="13" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="G88" s="10" t="inlineStr">
+      <c r="I88" s="10" t="inlineStr">
         <is>
           <t>「個人PC・メール保管あり」とみなし全拠点に退避指示（未実施拠点の証憑消失は当該拠点起因）。</t>
         </is>
@@ -3775,22 +4479,30 @@
           <t>ファイル・フォルダの命名ルール</t>
         </is>
       </c>
-      <c r="D89" s="10" t="inlineStr">
+      <c r="D89" s="9" t="inlineStr">
+        <is>
+          <t>選択+補足〔ヒアリング〕</t>
+        </is>
+      </c>
+      <c r="E89" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="F89" s="10" t="inlineStr">
         <is>
           <t>証憑メタデータ（検索キー）設計の参考情報を失う。</t>
         </is>
       </c>
-      <c r="E89" s="10" t="inlineStr">
+      <c r="G89" s="10" t="inlineStr">
         <is>
           <t>検索性設計</t>
         </is>
       </c>
-      <c r="F89" s="13" t="inlineStr">
+      <c r="H89" s="14" t="inlineStr">
         <is>
           <t>低</t>
         </is>
       </c>
-      <c r="G89" s="10" t="inlineStr">
+      <c r="I89" s="10" t="inlineStr">
         <is>
           <t>「ルールなし」とみなす。</t>
         </is>
@@ -3812,22 +4524,30 @@
           <t>保存年限のルールと実態</t>
         </is>
       </c>
-      <c r="D90" s="10" t="inlineStr">
+      <c r="D90" s="9" t="inlineStr">
+        <is>
+          <t>記述〔ヒアリング〕</t>
+        </is>
+      </c>
+      <c r="E90" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="F90" s="10" t="inlineStr">
         <is>
           <t>保存期間要件（法定年数・保証対応年数）とストレージ容量が確定できない。</t>
         </is>
       </c>
-      <c r="E90" s="10" t="inlineStr">
+      <c r="G90" s="10" t="inlineStr">
         <is>
           <t>保存期間要件</t>
         </is>
       </c>
-      <c r="F90" s="11" t="inlineStr">
+      <c r="H90" s="11" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="G90" s="10" t="inlineStr">
+      <c r="I90" s="10" t="inlineStr">
         <is>
           <t>「実態は3年分のみ」とみなし過年度分の欠落リスクを記録。</t>
         </is>
@@ -3849,22 +4569,30 @@
           <t>数値→証憑のトレーサビリティ</t>
         </is>
       </c>
-      <c r="D91" s="10" t="inlineStr">
+      <c r="D91" s="9" t="inlineStr">
+        <is>
+          <t>選択+補足〔ヒアリング〕</t>
+        </is>
+      </c>
+      <c r="E91" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="F91" s="10" t="inlineStr">
         <is>
           <t>C-10の詳細。紐付けデータモデルと移行時の対応表整備範囲が確定しない。</t>
         </is>
       </c>
-      <c r="E91" s="10" t="inlineStr">
+      <c r="G91" s="10" t="inlineStr">
         <is>
           <t>紐付けモデル・移行対応表</t>
         </is>
       </c>
-      <c r="F91" s="12" t="inlineStr">
+      <c r="H91" s="13" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="G91" s="10" t="inlineStr">
+      <c r="I91" s="10" t="inlineStr">
         <is>
           <t>「対応表なし」とみなし移行時の紐付け再構築タスクを計画化。</t>
         </is>
@@ -3886,22 +4614,30 @@
           <t>監査時の証憑提示所要時間</t>
         </is>
       </c>
-      <c r="D92" s="10" t="inlineStr">
+      <c r="D92" s="9" t="inlineStr">
+        <is>
+          <t>記述〔ヒアリング〕</t>
+        </is>
+      </c>
+      <c r="E92" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="F92" s="10" t="inlineStr">
         <is>
           <t>検索性要件・ROIの根拠精度が下がる。</t>
         </is>
       </c>
-      <c r="E92" s="10" t="inlineStr">
+      <c r="G92" s="10" t="inlineStr">
         <is>
           <t>検索性・ROI</t>
         </is>
       </c>
-      <c r="F92" s="13" t="inlineStr">
+      <c r="H92" s="14" t="inlineStr">
         <is>
           <t>低</t>
         </is>
       </c>
-      <c r="G92" s="10" t="inlineStr">
+      <c r="I92" s="10" t="inlineStr">
         <is>
           <t>「半日/件」とみなす。</t>
         </is>
@@ -3923,22 +4659,30 @@
           <t>証憑が存在しない・再入手困難な項目</t>
         </is>
       </c>
-      <c r="D93" s="10" t="inlineStr">
+      <c r="D93" s="9" t="inlineStr">
+        <is>
+          <t>選択+補足〔ヒアリング〕</t>
+        </is>
+      </c>
+      <c r="E93" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="F93" s="10" t="inlineStr">
         <is>
           <t>保証で意見不能になり得る項目を事前に特定できず、検証本番で発覚する（最悪のタイミング）。代替証憑ルールも設計できない。</t>
         </is>
       </c>
-      <c r="E93" s="10" t="inlineStr">
+      <c r="G93" s="10" t="inlineStr">
         <is>
           <t>代替証憑ルール・保証リスク</t>
         </is>
       </c>
-      <c r="F93" s="12" t="inlineStr">
+      <c r="H93" s="13" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="G93" s="10" t="inlineStr">
+      <c r="I93" s="10" t="inlineStr">
         <is>
           <t>「存在しない項目あり」とみなし代替手続き（推計根拠文書化）を要件化。検証時の指摘は当該拠点起因。</t>
         </is>
@@ -3960,22 +4704,30 @@
           <t>第三者（ビル管理・テナント等）保有証憑の入手性</t>
         </is>
       </c>
-      <c r="D94" s="10" t="inlineStr">
+      <c r="D94" s="9" t="inlineStr">
+        <is>
+          <t>記述〔ヒアリング〕</t>
+        </is>
+      </c>
+      <c r="E94" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="F94" s="10" t="inlineStr">
         <is>
           <t>外部証憑の取得フロー（契約上の提供義務の有無）が設計できない。</t>
         </is>
       </c>
-      <c r="E94" s="10" t="inlineStr">
+      <c r="G94" s="10" t="inlineStr">
         <is>
           <t>外部証憑取得フロー</t>
         </is>
       </c>
-      <c r="F94" s="11" t="inlineStr">
+      <c r="H94" s="11" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="G94" s="10" t="inlineStr">
+      <c r="I94" s="10" t="inlineStr">
         <is>
           <t>「入手困難」とみなし契約整備タスクを追加。</t>
         </is>
@@ -3997,22 +4749,30 @@
           <t>担当交代時の記録引継ぎ・消失経験</t>
         </is>
       </c>
-      <c r="D95" s="10" t="inlineStr">
+      <c r="D95" s="9" t="inlineStr">
+        <is>
+          <t>記述〔ヒアリング〕</t>
+        </is>
+      </c>
+      <c r="E95" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="F95" s="10" t="inlineStr">
         <is>
           <t>記録保全の弱点が特定できず、システム化後も同じ消失が再発する。</t>
         </is>
       </c>
-      <c r="E95" s="10" t="inlineStr">
+      <c r="G95" s="10" t="inlineStr">
         <is>
           <t>記録保全設計</t>
         </is>
       </c>
-      <c r="F95" s="11" t="inlineStr">
+      <c r="H95" s="11" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="G95" s="10" t="inlineStr">
+      <c r="I95" s="10" t="inlineStr">
         <is>
           <t>「消失経験あり」とみなす。</t>
         </is>
@@ -4034,22 +4794,30 @@
           <t>個人メール・PCのみの重要記録</t>
         </is>
       </c>
-      <c r="D96" s="10" t="inlineStr">
+      <c r="D96" s="9" t="inlineStr">
+        <is>
+          <t>選択+補足〔ヒアリング〕</t>
+        </is>
+      </c>
+      <c r="E96" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="F96" s="10" t="inlineStr">
         <is>
           <t>C-28の詳細。</t>
         </is>
       </c>
-      <c r="E96" s="10" t="inlineStr">
+      <c r="G96" s="10" t="inlineStr">
         <is>
           <t>証憑退避</t>
         </is>
       </c>
-      <c r="F96" s="12" t="inlineStr">
+      <c r="H96" s="13" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="G96" s="10" t="inlineStr">
+      <c r="I96" s="10" t="inlineStr">
         <is>
           <t>「あり」とみなし退避タスクを計画化。</t>
         </is>
@@ -4071,22 +4839,30 @@
           <t>過去の検証指摘と対応の記録所在</t>
         </is>
       </c>
-      <c r="D97" s="10" t="inlineStr">
+      <c r="D97" s="9" t="inlineStr">
+        <is>
+          <t>記述〔ヒアリング〕</t>
+        </is>
+      </c>
+      <c r="E97" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="F97" s="10" t="inlineStr">
         <is>
           <t>過去指摘の要件反映（保証人協議のインプット）ができず、「後出しNG」予防の前提が崩れる。同じ指摘を再度受ける。</t>
         </is>
       </c>
-      <c r="E97" s="10" t="inlineStr">
+      <c r="G97" s="10" t="inlineStr">
         <is>
           <t>過去指摘反映・保証人協議</t>
         </is>
       </c>
-      <c r="F97" s="12" t="inlineStr">
+      <c r="H97" s="13" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="G97" s="10" t="inlineStr">
+      <c r="I97" s="10" t="inlineStr">
         <is>
           <t>「記録なし」とみなし保証人への指摘事項再照会を計画化（追加協議工数は当該部門起因）。</t>
         </is>
@@ -4108,22 +4884,30 @@
           <t>改ざん防止の仕組み</t>
         </is>
       </c>
-      <c r="D98" s="10" t="inlineStr">
+      <c r="D98" s="9" t="inlineStr">
+        <is>
+          <t>選択+補足〔ヒアリング〕</t>
+        </is>
+      </c>
+      <c r="E98" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="F98" s="10" t="inlineStr">
         <is>
           <t>統制設計の現状値が欠落し、改ざんリスク評価ができない。</t>
         </is>
       </c>
-      <c r="E98" s="10" t="inlineStr">
+      <c r="G98" s="10" t="inlineStr">
         <is>
           <t>改ざん防止要件</t>
         </is>
       </c>
-      <c r="F98" s="11" t="inlineStr">
+      <c r="H98" s="11" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="G98" s="10" t="inlineStr">
+      <c r="I98" s="10" t="inlineStr">
         <is>
           <t>「仕組みなし」とみなす。</t>
         </is>
@@ -4145,22 +4929,30 @@
           <t>証憑添付必須化の障害</t>
         </is>
       </c>
-      <c r="D99" s="10" t="inlineStr">
+      <c r="D99" s="9" t="inlineStr">
+        <is>
+          <t>記述〔ヒアリング〕</t>
+        </is>
+      </c>
+      <c r="E99" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="F99" s="10" t="inlineStr">
         <is>
           <t>C-11の詳細。例外設計が現場実態と乖離。</t>
         </is>
       </c>
-      <c r="E99" s="10" t="inlineStr">
+      <c r="G99" s="10" t="inlineStr">
         <is>
           <t>例外設計</t>
         </is>
       </c>
-      <c r="F99" s="12" t="inlineStr">
+      <c r="H99" s="13" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="G99" s="10" t="inlineStr">
+      <c r="I99" s="10" t="inlineStr">
         <is>
           <t>「障害あり」とみなし例外フロー実装。</t>
         </is>
@@ -4178,6 +4970,8 @@
       <c r="E100" s="7" t="n"/>
       <c r="F100" s="7" t="n"/>
       <c r="G100" s="7" t="n"/>
+      <c r="H100" s="7" t="n"/>
+      <c r="I100" s="7" t="n"/>
     </row>
     <row r="101" ht="52" customHeight="1">
       <c r="A101" s="8" t="inlineStr">
@@ -4195,22 +4989,30 @@
           <t>チェックの実施者・方法</t>
         </is>
       </c>
-      <c r="D101" s="10" t="inlineStr">
+      <c r="D101" s="9" t="inlineStr">
+        <is>
+          <t>記述〔ヒアリング〕</t>
+        </is>
+      </c>
+      <c r="E101" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="F101" s="10" t="inlineStr">
         <is>
           <t>人的統制→システム統制の置換設計の根拠がない。統制の過剰／過少の両リスク。</t>
         </is>
       </c>
-      <c r="E101" s="10" t="inlineStr">
+      <c r="G101" s="10" t="inlineStr">
         <is>
           <t>キーコントロール配置</t>
         </is>
       </c>
-      <c r="F101" s="12" t="inlineStr">
+      <c r="H101" s="13" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="G101" s="10" t="inlineStr">
+      <c r="I101" s="10" t="inlineStr">
         <is>
           <t>「自己チェックのみ」とみなし統制を厚めに設計。</t>
         </is>
@@ -4232,22 +5034,30 @@
           <t>チェック実施の記録有無</t>
         </is>
       </c>
-      <c r="D102" s="10" t="inlineStr">
+      <c r="D102" s="9" t="inlineStr">
+        <is>
+          <t>選択+補足〔ヒアリング〕</t>
+        </is>
+      </c>
+      <c r="E102" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="F102" s="10" t="inlineStr">
         <is>
           <t>統制の証跡化（チェック記録の保存）要件が決められない。保証で「チェックの証拠」を求められ提示不能。</t>
         </is>
       </c>
-      <c r="E102" s="10" t="inlineStr">
+      <c r="G102" s="10" t="inlineStr">
         <is>
           <t>統制証跡要件</t>
         </is>
       </c>
-      <c r="F102" s="11" t="inlineStr">
+      <c r="H102" s="11" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="G102" s="10" t="inlineStr">
+      <c r="I102" s="10" t="inlineStr">
         <is>
           <t>「残らない」とみなしシステムでのチェック記録を必須化。</t>
         </is>
@@ -4269,22 +5079,30 @@
           <t>異常値の定義・閾値・対応者</t>
         </is>
       </c>
-      <c r="D103" s="10" t="inlineStr">
+      <c r="D103" s="9" t="inlineStr">
+        <is>
+          <t>選択+補足〔ヒアリング〕</t>
+        </is>
+      </c>
+      <c r="E103" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="F103" s="10" t="inlineStr">
         <is>
           <t>異常値検知ルールの初期値と対応フローが机上設定になる。</t>
         </is>
       </c>
-      <c r="E103" s="10" t="inlineStr">
+      <c r="G103" s="10" t="inlineStr">
         <is>
           <t>異常値検知・対応フロー</t>
         </is>
       </c>
-      <c r="F103" s="11" t="inlineStr">
+      <c r="H103" s="11" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="G103" s="10" t="inlineStr">
+      <c r="I103" s="10" t="inlineStr">
         <is>
           <t>「定義なし」とみなし標準閾値で設計。</t>
         </is>
@@ -4306,22 +5124,30 @@
           <t>入力ミスが開示まで流れた経験</t>
         </is>
       </c>
-      <c r="D104" s="10" t="inlineStr">
+      <c r="D104" s="9" t="inlineStr">
+        <is>
+          <t>記述〔ヒアリング〕</t>
+        </is>
+      </c>
+      <c r="E104" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="F104" s="10" t="inlineStr">
         <is>
           <t>統制の穴の実例＝キーコントロール配置の最重要根拠を失う。同じ経路のミスが再発する。</t>
         </is>
       </c>
-      <c r="E104" s="10" t="inlineStr">
+      <c r="G104" s="10" t="inlineStr">
         <is>
           <t>キーコントロール設計</t>
         </is>
       </c>
-      <c r="F104" s="12" t="inlineStr">
+      <c r="H104" s="13" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="G104" s="10" t="inlineStr">
+      <c r="I104" s="10" t="inlineStr">
         <is>
           <t>「経験あり・経路不明」とみなし全経路に統制を配置（過剰統制コスト増）。</t>
         </is>
@@ -4343,22 +5169,30 @@
           <t>承認の実施者・形式</t>
         </is>
       </c>
-      <c r="D105" s="10" t="inlineStr">
+      <c r="D105" s="9" t="inlineStr">
+        <is>
+          <t>選択+補足〔ヒアリング〕</t>
+        </is>
+      </c>
+      <c r="E105" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="F105" s="10" t="inlineStr">
         <is>
           <t>C-12の詳細。承認者マスタ・承認形式が設計できない。</t>
         </is>
       </c>
-      <c r="E105" s="10" t="inlineStr">
+      <c r="G105" s="10" t="inlineStr">
         <is>
           <t>承認WF設計</t>
         </is>
       </c>
-      <c r="F105" s="12" t="inlineStr">
+      <c r="H105" s="13" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="G105" s="10" t="inlineStr">
+      <c r="I105" s="10" t="inlineStr">
         <is>
           <t>「承認なし」とみなす。</t>
         </is>
@@ -4380,22 +5214,30 @@
           <t>拠点長のデータ関与機会</t>
         </is>
       </c>
-      <c r="D106" s="10" t="inlineStr">
+      <c r="D106" s="9" t="inlineStr">
+        <is>
+          <t>選択+補足〔ヒアリング〕</t>
+        </is>
+      </c>
+      <c r="E106" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="F106" s="10" t="inlineStr">
         <is>
           <t>承認階層に拠点長を含めるかの判断材料を失う。</t>
         </is>
       </c>
-      <c r="E106" s="10" t="inlineStr">
+      <c r="G106" s="10" t="inlineStr">
         <is>
           <t>承認階層設計</t>
         </is>
       </c>
-      <c r="F106" s="11" t="inlineStr">
+      <c r="H106" s="11" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="G106" s="10" t="inlineStr">
+      <c r="I106" s="10" t="inlineStr">
         <is>
           <t>「関与なし」とみなし拠点長承認を新設（負荷増は当該拠点調整事項）。</t>
         </is>
@@ -4417,22 +5259,30 @@
           <t>承認者不在時の代行ルール</t>
         </is>
       </c>
-      <c r="D107" s="10" t="inlineStr">
+      <c r="D107" s="9" t="inlineStr">
+        <is>
+          <t>選択+補足〔ヒアリング〕</t>
+        </is>
+      </c>
+      <c r="E107" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="F107" s="10" t="inlineStr">
         <is>
           <t>代行承認・委任機能の仕様が決められない。</t>
         </is>
       </c>
-      <c r="E107" s="10" t="inlineStr">
+      <c r="G107" s="10" t="inlineStr">
         <is>
           <t>代行機能</t>
         </is>
       </c>
-      <c r="F107" s="11" t="inlineStr">
+      <c r="H107" s="11" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="G107" s="10" t="inlineStr">
+      <c r="I107" s="10" t="inlineStr">
         <is>
           <t>「ルールなし」とみなし代行機能を実装。</t>
         </is>
@@ -4454,22 +5304,30 @@
           <t>確定（ロック）の概念とタイミング・変更権限</t>
         </is>
       </c>
-      <c r="D108" s="10" t="inlineStr">
+      <c r="D108" s="9" t="inlineStr">
+        <is>
+          <t>記述〔ヒアリング〕</t>
+        </is>
+      </c>
+      <c r="E108" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="F108" s="10" t="inlineStr">
         <is>
           <t>確定ロック機能の仕様（誰がいつロック・解除権限）が設計できない。保証の前提となる「数値の確定」概念が定まらない。</t>
         </is>
       </c>
-      <c r="E108" s="10" t="inlineStr">
+      <c r="G108" s="10" t="inlineStr">
         <is>
           <t>確定ロック仕様</t>
         </is>
       </c>
-      <c r="F108" s="12" t="inlineStr">
+      <c r="H108" s="13" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="G108" s="10" t="inlineStr">
+      <c r="I108" s="10" t="inlineStr">
         <is>
           <t>「概念なし」とみなし本社一括ロック方式で設計。</t>
         </is>
@@ -4491,22 +5349,30 @@
           <t>ファイル・システムの編集権限</t>
         </is>
       </c>
-      <c r="D109" s="10" t="inlineStr">
+      <c r="D109" s="9" t="inlineStr">
+        <is>
+          <t>選択+補足〔ヒアリング〕</t>
+        </is>
+      </c>
+      <c r="E109" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="F109" s="10" t="inlineStr">
         <is>
           <t>C-32の詳細。</t>
         </is>
       </c>
-      <c r="E109" s="10" t="inlineStr">
+      <c r="G109" s="10" t="inlineStr">
         <is>
           <t>権限マトリクス</t>
         </is>
       </c>
-      <c r="F109" s="12" t="inlineStr">
+      <c r="H109" s="13" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="G109" s="10" t="inlineStr">
+      <c r="I109" s="10" t="inlineStr">
         <is>
           <t>「誰でも編集可」とみなす。</t>
         </is>
@@ -4528,22 +5394,30 @@
           <t>変更履歴の記録有無</t>
         </is>
       </c>
-      <c r="D110" s="10" t="inlineStr">
+      <c r="D110" s="9" t="inlineStr">
+        <is>
+          <t>選択+補足〔ヒアリング〕</t>
+        </is>
+      </c>
+      <c r="E110" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="F110" s="10" t="inlineStr">
         <is>
           <t>C-13の詳細。</t>
         </is>
       </c>
-      <c r="E110" s="10" t="inlineStr">
+      <c r="G110" s="10" t="inlineStr">
         <is>
           <t>監査ログ</t>
         </is>
       </c>
-      <c r="F110" s="12" t="inlineStr">
+      <c r="H110" s="13" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="G110" s="10" t="inlineStr">
+      <c r="I110" s="10" t="inlineStr">
         <is>
           <t>「残らない」とみなす。</t>
         </is>
@@ -4565,22 +5439,30 @@
           <t>共有ID・パスワードの使い回し</t>
         </is>
       </c>
-      <c r="D111" s="10" t="inlineStr">
+      <c r="D111" s="9" t="inlineStr">
+        <is>
+          <t>選択+補足〔ヒアリング〕</t>
+        </is>
+      </c>
+      <c r="E111" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="F111" s="10" t="inlineStr">
         <is>
           <t>個人ID必須化の移行負荷（アカウント発行数）が見積れない。共有IDは保証・監査で確実に指摘される。</t>
         </is>
       </c>
-      <c r="E111" s="10" t="inlineStr">
+      <c r="G111" s="10" t="inlineStr">
         <is>
           <t>認証設計・監査指摘リスク</t>
         </is>
       </c>
-      <c r="F111" s="12" t="inlineStr">
+      <c r="H111" s="13" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="G111" s="10" t="inlineStr">
+      <c r="I111" s="10" t="inlineStr">
         <is>
           <t>「共有IDあり」とみなし個人ID移行を必須化（移行負荷は当該拠点起因）。</t>
         </is>
@@ -4602,22 +5484,30 @@
           <t>内部監査・J-SOX・ISO審査の対象経験と指摘</t>
         </is>
       </c>
-      <c r="D112" s="10" t="inlineStr">
+      <c r="D112" s="9" t="inlineStr">
+        <is>
+          <t>選択+補足〔ヒアリング〕</t>
+        </is>
+      </c>
+      <c r="E112" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="F112" s="10" t="inlineStr">
         <is>
           <t>過去指摘を要件に反映できず、既知の弱点を放置した設計になる。</t>
         </is>
       </c>
-      <c r="E112" s="10" t="inlineStr">
+      <c r="G112" s="10" t="inlineStr">
         <is>
           <t>過去指摘反映</t>
         </is>
       </c>
-      <c r="F112" s="12" t="inlineStr">
+      <c r="H112" s="13" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="G112" s="10" t="inlineStr">
+      <c r="I112" s="10" t="inlineStr">
         <is>
           <t>「指摘あり・内容不明」とみなし内部監査室への照会を実施（回答遅延は当該部門起因）。</t>
         </is>
@@ -4639,22 +5529,30 @@
           <t>データ信頼性のヒヤリ経験</t>
         </is>
       </c>
-      <c r="D113" s="10" t="inlineStr">
+      <c r="D113" s="9" t="inlineStr">
+        <is>
+          <t>記述〔ヒアリング〕</t>
+        </is>
+      </c>
+      <c r="E113" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="F113" s="10" t="inlineStr">
         <is>
           <t>リスクシナリオの実例を失い、統制の優先順位が机上になる。</t>
         </is>
       </c>
-      <c r="E113" s="10" t="inlineStr">
+      <c r="G113" s="10" t="inlineStr">
         <is>
           <t>統制優先順位</t>
         </is>
       </c>
-      <c r="F113" s="11" t="inlineStr">
+      <c r="H113" s="11" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="G113" s="10" t="inlineStr">
+      <c r="I113" s="10" t="inlineStr">
         <is>
           <t>「ヒヤリ経験あり」とみなす。</t>
         </is>
@@ -4676,22 +5574,30 @@
           <t>統制強化で業務が回らなくなる懸念</t>
         </is>
       </c>
-      <c r="D114" s="10" t="inlineStr">
+      <c r="D114" s="9" t="inlineStr">
+        <is>
+          <t>記述〔ヒアリング〕</t>
+        </is>
+      </c>
+      <c r="E114" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="F114" s="10" t="inlineStr">
         <is>
           <t>例外設計・チェンジマネジメントの重点が特定できず、稼働後に現場が停止する統制を設計するリスク。</t>
         </is>
       </c>
-      <c r="E114" s="10" t="inlineStr">
+      <c r="G114" s="10" t="inlineStr">
         <is>
           <t>例外設計・定着計画</t>
         </is>
       </c>
-      <c r="F114" s="11" t="inlineStr">
+      <c r="H114" s="11" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="G114" s="10" t="inlineStr">
+      <c r="I114" s="10" t="inlineStr">
         <is>
           <t>「懸念あり・内容不明」とみなし統制は段階導入方式で設計。</t>
         </is>
@@ -4709,6 +5615,8 @@
       <c r="E115" s="7" t="n"/>
       <c r="F115" s="7" t="n"/>
       <c r="G115" s="7" t="n"/>
+      <c r="H115" s="7" t="n"/>
+      <c r="I115" s="7" t="n"/>
     </row>
     <row r="116" ht="52" customHeight="1">
       <c r="A116" s="8" t="inlineStr">
@@ -4726,22 +5634,30 @@
           <t>拠点の業務システム全量</t>
         </is>
       </c>
-      <c r="D116" s="10" t="inlineStr">
+      <c r="D116" s="9" t="inlineStr">
+        <is>
+          <t>記述〔ヒアリング〕</t>
+        </is>
+      </c>
+      <c r="E116" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="F116" s="10" t="inlineStr">
         <is>
           <t>連携対象の全量が不明＝アーキテクチャ（外部IF一覧）が設計できず、RFPの連携要件が欠落。ベンダー見積りに高値バッファ。</t>
         </is>
       </c>
-      <c r="E116" s="10" t="inlineStr">
+      <c r="G116" s="10" t="inlineStr">
         <is>
           <t>外部IF一覧・アーキテクチャ</t>
         </is>
       </c>
-      <c r="F116" s="12" t="inlineStr">
+      <c r="H116" s="13" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="G116" s="10" t="inlineStr">
+      <c r="I116" s="10" t="inlineStr">
         <is>
           <t>「連携対象なし（全て手入力）」とみなす。後日の連携追加費用は当該拠点起因。</t>
         </is>
@@ -4763,22 +5679,30 @@
           <t>各システムのデータ出力可否</t>
         </is>
       </c>
-      <c r="D117" s="10" t="inlineStr">
+      <c r="D117" s="9" t="inlineStr">
+        <is>
+          <t>記述〔ヒアリング〕</t>
+        </is>
+      </c>
+      <c r="E117" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="F117" s="10" t="inlineStr">
         <is>
           <t>連携方式（API/CSV/手入力）が確定できない。</t>
         </is>
       </c>
-      <c r="E117" s="10" t="inlineStr">
+      <c r="G117" s="10" t="inlineStr">
         <is>
           <t>連携方式設計</t>
         </is>
       </c>
-      <c r="F117" s="12" t="inlineStr">
+      <c r="H117" s="13" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="G117" s="10" t="inlineStr">
+      <c r="I117" s="10" t="inlineStr">
         <is>
           <t>「出力不可」とみなす。</t>
         </is>
@@ -4800,22 +5724,30 @@
           <t>SAPとの関係・ユーティリティ費用の計上コード</t>
         </is>
       </c>
-      <c r="D118" s="10" t="inlineStr">
+      <c r="D118" s="9" t="inlineStr">
+        <is>
+          <t>記述〔ヒアリング〕</t>
+        </is>
+      </c>
+      <c r="E118" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="F118" s="10" t="inlineStr">
         <is>
           <t>SAP連携仕様（費用データからの活動量推計・勘定科目粒度）が設計できない。</t>
         </is>
       </c>
-      <c r="E118" s="10" t="inlineStr">
+      <c r="G118" s="10" t="inlineStr">
         <is>
           <t>SAP連携仕様</t>
         </is>
       </c>
-      <c r="F118" s="12" t="inlineStr">
+      <c r="H118" s="13" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="G118" s="10" t="inlineStr">
+      <c r="I118" s="10" t="inlineStr">
         <is>
           <t>「連携不可」とみなしSAP連携を対象外化。</t>
         </is>
@@ -4837,22 +5769,30 @@
           <t>会計システムからの費用データ抽出可否</t>
         </is>
       </c>
-      <c r="D119" s="10" t="inlineStr">
+      <c r="D119" s="9" t="inlineStr">
+        <is>
+          <t>選択+補足〔ヒアリング〕</t>
+        </is>
+      </c>
+      <c r="E119" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="F119" s="10" t="inlineStr">
         <is>
           <t>金額ベース推計（支出ベース算定）のフォールバック経路が使えるか不明。</t>
         </is>
       </c>
-      <c r="E119" s="10" t="inlineStr">
+      <c r="G119" s="10" t="inlineStr">
         <is>
           <t>支出ベース算定</t>
         </is>
       </c>
-      <c r="F119" s="11" t="inlineStr">
+      <c r="H119" s="11" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="G119" s="10" t="inlineStr">
+      <c r="I119" s="10" t="inlineStr">
         <is>
           <t>「抽出不可」とみなす。</t>
         </is>
@@ -4874,22 +5814,30 @@
           <t>BEMS/FEMS・スマートメーターの有無とデータ取出</t>
         </is>
       </c>
-      <c r="D120" s="10" t="inlineStr">
+      <c r="D120" s="9" t="inlineStr">
+        <is>
+          <t>選択+補足〔ヒアリング〕</t>
+        </is>
+      </c>
+      <c r="E120" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="F120" s="10" t="inlineStr">
         <is>
           <t>自動計測連携の対象が確定できない。</t>
         </is>
       </c>
-      <c r="E120" s="10" t="inlineStr">
+      <c r="G120" s="10" t="inlineStr">
         <is>
           <t>計測データ連携</t>
         </is>
       </c>
-      <c r="F120" s="11" t="inlineStr">
+      <c r="H120" s="11" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="G120" s="10" t="inlineStr">
+      <c r="I120" s="10" t="inlineStr">
         <is>
           <t>「なし」とみなす。</t>
         </is>
@@ -4911,22 +5859,30 @@
           <t>電力会社Web明細等の利用状況</t>
         </is>
       </c>
-      <c r="D121" s="10" t="inlineStr">
+      <c r="D121" s="9" t="inlineStr">
+        <is>
+          <t>選択+補足〔ヒアリング〕</t>
+        </is>
+      </c>
+      <c r="E121" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="F121" s="10" t="inlineStr">
         <is>
           <t>C-15の詳細。</t>
         </is>
       </c>
-      <c r="E121" s="10" t="inlineStr">
+      <c r="G121" s="10" t="inlineStr">
         <is>
           <t>自動取込</t>
         </is>
       </c>
-      <c r="F121" s="11" t="inlineStr">
+      <c r="H121" s="11" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="G121" s="10" t="inlineStr">
+      <c r="I121" s="10" t="inlineStr">
         <is>
           <t>「利用不可」とみなす。</t>
         </is>
@@ -4948,22 +5904,30 @@
           <t>子メーターの設置状況・検針方法</t>
         </is>
       </c>
-      <c r="D122" s="10" t="inlineStr">
+      <c r="D122" s="9" t="inlineStr">
+        <is>
+          <t>記述〔ヒアリング〕</t>
+        </is>
+      </c>
+      <c r="E122" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="F122" s="10" t="inlineStr">
         <is>
           <t>データ粒度（建屋別・部門別）の実現可能性が不明。細かい粒度の開示・按分要件が物理的に満たせない可能性。</t>
         </is>
       </c>
-      <c r="E122" s="10" t="inlineStr">
+      <c r="G122" s="10" t="inlineStr">
         <is>
           <t>データ粒度設計</t>
         </is>
       </c>
-      <c r="F122" s="11" t="inlineStr">
+      <c r="H122" s="11" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="G122" s="10" t="inlineStr">
+      <c r="I122" s="10" t="inlineStr">
         <is>
           <t>「拠点全体計のみ」とみなし細粒度要件を断念（粒度不足は当該拠点起因）。</t>
         </is>
@@ -4985,22 +5949,30 @@
           <t>SaaSアクセス制限の詳細</t>
         </is>
       </c>
-      <c r="D123" s="10" t="inlineStr">
+      <c r="D123" s="9" t="inlineStr">
+        <is>
+          <t>選択+補足〔ヒアリング〕</t>
+        </is>
+      </c>
+      <c r="E123" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="F123" s="10" t="inlineStr">
         <is>
           <t>C-16の詳細。アーキテクチャ成立性。</t>
         </is>
       </c>
-      <c r="E123" s="10" t="inlineStr">
+      <c r="G123" s="10" t="inlineStr">
         <is>
           <t>ネットワーク要件</t>
         </is>
       </c>
-      <c r="F123" s="12" t="inlineStr">
+      <c r="H123" s="13" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="G123" s="10" t="inlineStr">
+      <c r="I123" s="10" t="inlineStr">
         <is>
           <t>「制限あり」とみなす。</t>
         </is>
@@ -5022,22 +5994,30 @@
           <t>現場のネットワーク・デバイス環境</t>
         </is>
       </c>
-      <c r="D124" s="10" t="inlineStr">
+      <c r="D124" s="9" t="inlineStr">
+        <is>
+          <t>記述〔ヒアリング〕</t>
+        </is>
+      </c>
+      <c r="E124" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="F124" s="10" t="inlineStr">
         <is>
           <t>入力UI（モバイル・オフライン）要件が決められない。</t>
         </is>
       </c>
-      <c r="E124" s="10" t="inlineStr">
+      <c r="G124" s="10" t="inlineStr">
         <is>
           <t>デバイス・UI要件</t>
         </is>
       </c>
-      <c r="F124" s="11" t="inlineStr">
+      <c r="H124" s="11" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="G124" s="10" t="inlineStr">
+      <c r="I124" s="10" t="inlineStr">
         <is>
           <t>「制約あり」とみなす。</t>
         </is>
@@ -5059,22 +6039,30 @@
           <t>電子承認WFの導入状況（製品名）</t>
         </is>
       </c>
-      <c r="D125" s="10" t="inlineStr">
+      <c r="D125" s="9" t="inlineStr">
+        <is>
+          <t>選択+補足〔ヒアリング〕</t>
+        </is>
+      </c>
+      <c r="E125" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="F125" s="10" t="inlineStr">
         <is>
           <t>既存WF流用可否が不明のまま新規実装＝二重投資リスク。</t>
         </is>
       </c>
-      <c r="E125" s="10" t="inlineStr">
+      <c r="G125" s="10" t="inlineStr">
         <is>
           <t>WF実装方式</t>
         </is>
       </c>
-      <c r="F125" s="11" t="inlineStr">
+      <c r="H125" s="11" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="G125" s="10" t="inlineStr">
+      <c r="I125" s="10" t="inlineStr">
         <is>
           <t>「流用不可」とみなし新規実装。</t>
         </is>
@@ -5096,22 +6084,30 @@
           <t>OS・Office・マクロ実行可否</t>
         </is>
       </c>
-      <c r="D126" s="10" t="inlineStr">
+      <c r="D126" s="9" t="inlineStr">
+        <is>
+          <t>記述〔ヒアリング〕</t>
+        </is>
+      </c>
+      <c r="E126" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="F126" s="10" t="inlineStr">
         <is>
           <t>クライアント要件・移行制約の確認漏れ。</t>
         </is>
       </c>
-      <c r="E126" s="10" t="inlineStr">
+      <c r="G126" s="10" t="inlineStr">
         <is>
           <t>クライアント要件</t>
         </is>
       </c>
-      <c r="F126" s="13" t="inlineStr">
+      <c r="H126" s="14" t="inlineStr">
         <is>
           <t>低</t>
         </is>
       </c>
-      <c r="G126" s="10" t="inlineStr">
+      <c r="I126" s="10" t="inlineStr">
         <is>
           <t>「標準環境」とみなす。</t>
         </is>
@@ -5133,22 +6129,30 @@
           <t>ITサポート体制</t>
         </is>
       </c>
-      <c r="D127" s="10" t="inlineStr">
+      <c r="D127" s="9" t="inlineStr">
+        <is>
+          <t>記述〔ヒアリング〕</t>
+        </is>
+      </c>
+      <c r="E127" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="F127" s="10" t="inlineStr">
         <is>
           <t>導入・展開時の現地IT支援の有無が不明で、展開計画の実現性が検証できない。</t>
         </is>
       </c>
-      <c r="E127" s="10" t="inlineStr">
+      <c r="G127" s="10" t="inlineStr">
         <is>
           <t>展開計画</t>
         </is>
       </c>
-      <c r="F127" s="11" t="inlineStr">
+      <c r="H127" s="11" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="G127" s="10" t="inlineStr">
+      <c r="I127" s="10" t="inlineStr">
         <is>
           <t>「支援なし」とみなし本社リモート支援を計画化。</t>
         </is>
@@ -5170,22 +6174,30 @@
           <t>定着しなかったシステムとその理由</t>
         </is>
       </c>
-      <c r="D128" s="10" t="inlineStr">
+      <c r="D128" s="9" t="inlineStr">
+        <is>
+          <t>記述〔ヒアリング〕</t>
+        </is>
+      </c>
+      <c r="E128" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="F128" s="10" t="inlineStr">
         <is>
           <t>失敗要因（操作性・言語・負荷）を要件に反映できず、同じ失敗を繰り返す。難所⑦（定着）の最重要インプット。</t>
         </is>
       </c>
-      <c r="E128" s="10" t="inlineStr">
+      <c r="G128" s="10" t="inlineStr">
         <is>
           <t>定着要件・難所⑦</t>
         </is>
       </c>
-      <c r="F128" s="12" t="inlineStr">
+      <c r="H128" s="13" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="G128" s="10" t="inlineStr">
+      <c r="I128" s="10" t="inlineStr">
         <is>
           <t>「失敗経験あり・要因不明」とみなしUI・研修要件を厚めに設計。</t>
         </is>
@@ -5207,22 +6219,30 @@
           <t>エコアシスト等の改善要望</t>
         </is>
       </c>
-      <c r="D129" s="10" t="inlineStr">
+      <c r="D129" s="9" t="inlineStr">
+        <is>
+          <t>記述〔ヒアリング〕</t>
+        </is>
+      </c>
+      <c r="E129" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="F129" s="10" t="inlineStr">
         <is>
           <t>UI要件のバックログを失うが根幹には影響しない。</t>
         </is>
       </c>
-      <c r="E129" s="10" t="inlineStr">
+      <c r="G129" s="10" t="inlineStr">
         <is>
           <t>UI改善バックログ</t>
         </is>
       </c>
-      <c r="F129" s="13" t="inlineStr">
+      <c r="H129" s="14" t="inlineStr">
         <is>
           <t>低</t>
         </is>
       </c>
-      <c r="G129" s="10" t="inlineStr">
+      <c r="I129" s="10" t="inlineStr">
         <is>
           <t>「要望なし」とみなす。</t>
         </is>
@@ -5240,6 +6260,8 @@
       <c r="E130" s="7" t="n"/>
       <c r="F130" s="7" t="n"/>
       <c r="G130" s="7" t="n"/>
+      <c r="H130" s="7" t="n"/>
+      <c r="I130" s="7" t="n"/>
     </row>
     <row r="131" ht="52" customHeight="1">
       <c r="A131" s="8" t="inlineStr">
@@ -5257,22 +6279,30 @@
           <t>月間工数の作業別内訳</t>
         </is>
       </c>
-      <c r="D131" s="10" t="inlineStr">
+      <c r="D131" s="9" t="inlineStr">
+        <is>
+          <t>記述〔ヒアリング〕</t>
+        </is>
+      </c>
+      <c r="E131" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="F131" s="10" t="inlineStr">
         <is>
           <t>C-17の詳細。ROI試算の分母が作れず投資対効果の定量説明が不能。</t>
         </is>
       </c>
-      <c r="E131" s="10" t="inlineStr">
+      <c r="G131" s="10" t="inlineStr">
         <is>
           <t>ROI試算</t>
         </is>
       </c>
-      <c r="F131" s="12" t="inlineStr">
+      <c r="H131" s="13" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="G131" s="10" t="inlineStr">
+      <c r="I131" s="10" t="inlineStr">
         <is>
           <t>当該拠点をROI算定から除外。</t>
         </is>
@@ -5294,22 +6324,30 @@
           <t>年次イベントの追加工数</t>
         </is>
       </c>
-      <c r="D132" s="10" t="inlineStr">
+      <c r="D132" s="9" t="inlineStr">
+        <is>
+          <t>記述〔ヒアリング〕</t>
+        </is>
+      </c>
+      <c r="E132" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="F132" s="10" t="inlineStr">
         <is>
           <t>繁忙期のピーク設計とROIの年次効果が欠落。</t>
         </is>
       </c>
-      <c r="E132" s="10" t="inlineStr">
+      <c r="G132" s="10" t="inlineStr">
         <is>
           <t>性能設計・ROI</t>
         </is>
       </c>
-      <c r="F132" s="11" t="inlineStr">
+      <c r="H132" s="11" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="G132" s="10" t="inlineStr">
+      <c r="I132" s="10" t="inlineStr">
         <is>
           <t>「年200時間」とみなす。</t>
         </is>
@@ -5331,22 +6369,30 @@
           <t>本社照会・差し戻しの件数・時間</t>
         </is>
       </c>
-      <c r="D133" s="10" t="inlineStr">
+      <c r="D133" s="9" t="inlineStr">
+        <is>
+          <t>記述〔ヒアリング〕</t>
+        </is>
+      </c>
+      <c r="E133" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="F133" s="10" t="inlineStr">
         <is>
           <t>データ品質の現状値（差戻し率）が不明で、品質改善効果が測定できない。</t>
         </is>
       </c>
-      <c r="E133" s="10" t="inlineStr">
+      <c r="G133" s="10" t="inlineStr">
         <is>
           <t>品質KPI・差戻しフロー</t>
         </is>
       </c>
-      <c r="F133" s="11" t="inlineStr">
+      <c r="H133" s="11" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="G133" s="10" t="inlineStr">
+      <c r="I133" s="10" t="inlineStr">
         <is>
           <t>「月5件・10時間」とみなす。</t>
         </is>
@@ -5368,22 +6414,30 @@
           <t>関与人数（主担当・副担当・承認者）と兼務状況</t>
         </is>
       </c>
-      <c r="D134" s="10" t="inlineStr">
+      <c r="D134" s="9" t="inlineStr">
+        <is>
+          <t>記述〔ヒアリング〕</t>
+        </is>
+      </c>
+      <c r="E134" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="F134" s="10" t="inlineStr">
         <is>
           <t>ユーザー数＝ライセンス数・アカウント数が見積れず、RFPのコスト前提が狂う。ベンダー見積りの重要変数。</t>
         </is>
       </c>
-      <c r="E134" s="10" t="inlineStr">
+      <c r="G134" s="10" t="inlineStr">
         <is>
           <t>ライセンス数・RFPコスト前提</t>
         </is>
       </c>
-      <c r="F134" s="12" t="inlineStr">
+      <c r="H134" s="13" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="G134" s="10" t="inlineStr">
+      <c r="I134" s="10" t="inlineStr">
         <is>
           <t>「1拠点3ユーザー」とみなす。超過分のライセンス追加費用は当該拠点起因。</t>
         </is>
@@ -5405,22 +6459,30 @@
           <t>主担当の在籍年数・交代回数</t>
         </is>
       </c>
-      <c r="D135" s="10" t="inlineStr">
+      <c r="D135" s="9" t="inlineStr">
+        <is>
+          <t>記述〔ヒアリング〕</t>
+        </is>
+      </c>
+      <c r="E135" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="F135" s="10" t="inlineStr">
         <is>
           <t>教育要件の規模感が不明。</t>
         </is>
       </c>
-      <c r="E135" s="10" t="inlineStr">
+      <c r="G135" s="10" t="inlineStr">
         <is>
           <t>教育要件</t>
         </is>
       </c>
-      <c r="F135" s="13" t="inlineStr">
+      <c r="H135" s="14" t="inlineStr">
         <is>
           <t>低</t>
         </is>
       </c>
-      <c r="G135" s="10" t="inlineStr">
+      <c r="I135" s="10" t="inlineStr">
         <is>
           <t>「交代頻繁」とみなす。</t>
         </is>
@@ -5442,22 +6504,30 @@
           <t>「この人がいないと回らない」業務・知識</t>
         </is>
       </c>
-      <c r="D136" s="10" t="inlineStr">
+      <c r="D136" s="9" t="inlineStr">
+        <is>
+          <t>記述〔ヒアリング〕</t>
+        </is>
+      </c>
+      <c r="E136" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="F136" s="10" t="inlineStr">
         <is>
           <t>属人知識の機能化（システムに埋め込むべきガイド・チェック）対象が特定できない。</t>
         </is>
       </c>
-      <c r="E136" s="10" t="inlineStr">
+      <c r="G136" s="10" t="inlineStr">
         <is>
           <t>フールプルーフ設計</t>
         </is>
       </c>
-      <c r="F136" s="11" t="inlineStr">
+      <c r="H136" s="11" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="G136" s="10" t="inlineStr">
+      <c r="I136" s="10" t="inlineStr">
         <is>
           <t>「属人知識あり・内容不明」とみなす。</t>
         </is>
@@ -5479,22 +6549,30 @@
           <t>引継ぎ資料の有無と質</t>
         </is>
       </c>
-      <c r="D137" s="10" t="inlineStr">
+      <c r="D137" s="9" t="inlineStr">
+        <is>
+          <t>選択+補足〔ヒアリング〕</t>
+        </is>
+      </c>
+      <c r="E137" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="F137" s="10" t="inlineStr">
         <is>
           <t>同上。</t>
         </is>
       </c>
-      <c r="E137" s="10" t="inlineStr">
+      <c r="G137" s="10" t="inlineStr">
         <is>
           <t>教育・マニュアル要件</t>
         </is>
       </c>
-      <c r="F137" s="13" t="inlineStr">
+      <c r="H137" s="14" t="inlineStr">
         <is>
           <t>低</t>
         </is>
       </c>
-      <c r="G137" s="10" t="inlineStr">
+      <c r="I137" s="10" t="inlineStr">
         <is>
           <t>「実質なし」とみなす。</t>
         </is>
@@ -5516,22 +6594,30 @@
           <t>担当者のスキル自己評価</t>
         </is>
       </c>
-      <c r="D138" s="10" t="inlineStr">
+      <c r="D138" s="9" t="inlineStr">
+        <is>
+          <t>記述〔ヒアリング〕</t>
+        </is>
+      </c>
+      <c r="E138" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="F138" s="10" t="inlineStr">
         <is>
           <t>UI複雑度・研修設計の前提が不明。高機能UIを設計しても使いこなせないリスク。</t>
         </is>
       </c>
-      <c r="E138" s="10" t="inlineStr">
+      <c r="G138" s="10" t="inlineStr">
         <is>
           <t>UI要件・研修設計</t>
         </is>
       </c>
-      <c r="F138" s="11" t="inlineStr">
+      <c r="H138" s="11" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="G138" s="10" t="inlineStr">
+      <c r="I138" s="10" t="inlineStr">
         <is>
           <t>「Excel基本操作レベル」とみなしシンプルUI必須。</t>
         </is>
@@ -5553,22 +6639,30 @@
           <t>新システムへの期待と不安</t>
         </is>
       </c>
-      <c r="D139" s="10" t="inlineStr">
+      <c r="D139" s="9" t="inlineStr">
+        <is>
+          <t>記述〔ヒアリング〕</t>
+        </is>
+      </c>
+      <c r="E139" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="F139" s="10" t="inlineStr">
         <is>
           <t>チェンジマネジメントの材料。</t>
         </is>
       </c>
-      <c r="E139" s="10" t="inlineStr">
+      <c r="G139" s="10" t="inlineStr">
         <is>
           <t>定着計画</t>
         </is>
       </c>
-      <c r="F139" s="13" t="inlineStr">
+      <c r="H139" s="14" t="inlineStr">
         <is>
           <t>低</t>
         </is>
       </c>
-      <c r="G139" s="10" t="inlineStr">
+      <c r="I139" s="10" t="inlineStr">
         <is>
           <t>「不安あり」とみなす。</t>
         </is>
@@ -5590,22 +6684,30 @@
           <t>業務の拠点内での位置づけ</t>
         </is>
       </c>
-      <c r="D140" s="10" t="inlineStr">
+      <c r="D140" s="9" t="inlineStr">
+        <is>
+          <t>記述〔ヒアリング〕</t>
+        </is>
+      </c>
+      <c r="E140" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="F140" s="10" t="inlineStr">
         <is>
           <t>「片手間仕事」扱いの拠点は入力遅延の高リスク拠点。督促設計・経営巻き込みの対象特定ができない。</t>
         </is>
       </c>
-      <c r="E140" s="10" t="inlineStr">
+      <c r="G140" s="10" t="inlineStr">
         <is>
           <t>定着リスク評価</t>
         </is>
       </c>
-      <c r="F140" s="11" t="inlineStr">
+      <c r="H140" s="11" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="G140" s="10" t="inlineStr">
+      <c r="I140" s="10" t="inlineStr">
         <is>
           <t>「片手間扱い」とみなし高リスク拠点として督促を強化。</t>
         </is>
@@ -5627,22 +6729,30 @@
           <t>自動化で浮いた時間でやりたい業務</t>
         </is>
       </c>
-      <c r="D141" s="10" t="inlineStr">
+      <c r="D141" s="9" t="inlineStr">
+        <is>
+          <t>記述〔ヒアリング〕</t>
+        </is>
+      </c>
+      <c r="E141" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="F141" s="10" t="inlineStr">
         <is>
           <t>効果の定性ストーリー（攻めの説明材料）を失うが根幹には影響しない。</t>
         </is>
       </c>
-      <c r="E141" s="10" t="inlineStr">
+      <c r="G141" s="10" t="inlineStr">
         <is>
           <t>効果ストーリー</t>
         </is>
       </c>
-      <c r="F141" s="13" t="inlineStr">
+      <c r="H141" s="14" t="inlineStr">
         <is>
           <t>低</t>
         </is>
       </c>
-      <c r="G141" s="10" t="inlineStr">
+      <c r="I141" s="10" t="inlineStr">
         <is>
           <t>記載なしで進める。</t>
         </is>
@@ -5660,6 +6770,8 @@
       <c r="E142" s="7" t="n"/>
       <c r="F142" s="7" t="n"/>
       <c r="G142" s="7" t="n"/>
+      <c r="H142" s="7" t="n"/>
+      <c r="I142" s="7" t="n"/>
     </row>
     <row r="143" ht="52" customHeight="1">
       <c r="A143" s="8" t="inlineStr">
@@ -5677,22 +6789,30 @@
           <t>業務・帳票・システムの言語と翻訳体制</t>
         </is>
       </c>
-      <c r="D143" s="10" t="inlineStr">
+      <c r="D143" s="9" t="inlineStr">
+        <is>
+          <t>記述〔ヒアリング〕</t>
+        </is>
+      </c>
+      <c r="E143" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="F143" s="10" t="inlineStr">
         <is>
           <t>多言語UI・翻訳運用の要件（対象言語・翻訳責任）が決められない。RFPの必須要件が確定しない。</t>
         </is>
       </c>
-      <c r="E143" s="10" t="inlineStr">
+      <c r="G143" s="10" t="inlineStr">
         <is>
           <t>多言語要件・RFP必須要件</t>
         </is>
       </c>
-      <c r="F143" s="12" t="inlineStr">
+      <c r="H143" s="13" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="G143" s="10" t="inlineStr">
+      <c r="I143" s="10" t="inlineStr">
         <is>
           <t>「現地語のみ・翻訳者なし」とみなし多言語UI＋翻訳運用を必須化（費用増）。</t>
         </is>
@@ -5714,22 +6834,30 @@
           <t>使用単位系（ガロン・ポンド等）</t>
         </is>
       </c>
-      <c r="D144" s="10" t="inlineStr">
+      <c r="D144" s="9" t="inlineStr">
+        <is>
+          <t>記述〔ヒアリング〕</t>
+        </is>
+      </c>
+      <c r="E144" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="F144" s="10" t="inlineStr">
         <is>
           <t>単位換算エンジンの対象（ヤードポンド法対応）が漏れる。換算ミス＝数値誤りの温床。</t>
         </is>
       </c>
-      <c r="E144" s="10" t="inlineStr">
+      <c r="G144" s="10" t="inlineStr">
         <is>
           <t>単位換算エンジン</t>
         </is>
       </c>
-      <c r="F144" s="11" t="inlineStr">
+      <c r="H144" s="11" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="G144" s="10" t="inlineStr">
+      <c r="I144" s="10" t="inlineStr">
         <is>
           <t>「非メートル法あり」とみなし換算機能を実装。</t>
         </is>
@@ -5751,22 +6879,30 @@
           <t>現地会計年度と暦年報告のズレ</t>
         </is>
       </c>
-      <c r="D145" s="10" t="inlineStr">
+      <c r="D145" s="9" t="inlineStr">
+        <is>
+          <t>記述〔ヒアリング〕</t>
+        </is>
+      </c>
+      <c r="E145" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="F145" s="10" t="inlineStr">
         <is>
           <t>レポーティング期間変換（FY/CY変換）機能の要否が決められない。</t>
         </is>
       </c>
-      <c r="E145" s="10" t="inlineStr">
+      <c r="G145" s="10" t="inlineStr">
         <is>
           <t>期間変換機能</t>
         </is>
       </c>
-      <c r="F145" s="11" t="inlineStr">
+      <c r="H145" s="11" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="G145" s="10" t="inlineStr">
+      <c r="I145" s="10" t="inlineStr">
         <is>
           <t>「ズレあり」とみなし変換機能を実装。</t>
         </is>
@@ -5788,22 +6924,30 @@
           <t>通貨換算のレートと実施者</t>
         </is>
       </c>
-      <c r="D146" s="10" t="inlineStr">
+      <c r="D146" s="9" t="inlineStr">
+        <is>
+          <t>記述〔ヒアリング〕</t>
+        </is>
+      </c>
+      <c r="E146" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="F146" s="10" t="inlineStr">
         <is>
           <t>為替レートマスタ（レート種別・時点・責任者）が設計できない。</t>
         </is>
       </c>
-      <c r="E146" s="10" t="inlineStr">
+      <c r="G146" s="10" t="inlineStr">
         <is>
           <t>為替レートマスタ</t>
         </is>
       </c>
-      <c r="F146" s="11" t="inlineStr">
+      <c r="H146" s="11" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="G146" s="10" t="inlineStr">
+      <c r="I146" s="10" t="inlineStr">
         <is>
           <t>「レート不統一」とみなし本社一元管理で設計。</t>
         </is>
@@ -5825,22 +6969,30 @@
           <t>現地排出係数の種類と入手元</t>
         </is>
       </c>
-      <c r="D147" s="10" t="inlineStr">
+      <c r="D147" s="9" t="inlineStr">
+        <is>
+          <t>記述〔ヒアリング〕</t>
+        </is>
+      </c>
+      <c r="E147" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="F147" s="10" t="inlineStr">
         <is>
           <t>係数マスタの国別整備（出典・更新経路）ができず、海外分の算定が保証で説明不能。</t>
         </is>
       </c>
-      <c r="E147" s="10" t="inlineStr">
+      <c r="G147" s="10" t="inlineStr">
         <is>
           <t>国別係数マスタ</t>
         </is>
       </c>
-      <c r="F147" s="12" t="inlineStr">
+      <c r="H147" s="13" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="G147" s="10" t="inlineStr">
+      <c r="I147" s="10" t="inlineStr">
         <is>
           <t>「出典不明」とみなしIEA標準係数へ強制統一（現地当局報告との不整合リスクは当該拠点起因）。</t>
         </is>
@@ -5862,22 +7014,30 @@
           <t>現地の報告義務と本社報告との重複</t>
         </is>
       </c>
-      <c r="D148" s="10" t="inlineStr">
+      <c r="D148" s="9" t="inlineStr">
+        <is>
+          <t>記述〔ヒアリング〕</t>
+        </is>
+      </c>
+      <c r="E148" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="F148" s="10" t="inlineStr">
         <is>
           <t>ワンソース・マルチユースの対象（現地当局レポート）が漏れ、二重入力が温存される。</t>
         </is>
       </c>
-      <c r="E148" s="10" t="inlineStr">
+      <c r="G148" s="10" t="inlineStr">
         <is>
           <t>マルチユース出力設計</t>
         </is>
       </c>
-      <c r="F148" s="11" t="inlineStr">
+      <c r="H148" s="11" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="G148" s="10" t="inlineStr">
+      <c r="I148" s="10" t="inlineStr">
         <is>
           <t>「重複なし」とみなし現地レポート出力を対象外化。</t>
         </is>
@@ -5899,22 +7059,30 @@
           <t>CSRD・現地開示・顧客ESG要請の有無</t>
         </is>
       </c>
-      <c r="D149" s="10" t="inlineStr">
+      <c r="D149" s="9" t="inlineStr">
+        <is>
+          <t>選択+補足〔ヒアリング〕</t>
+        </is>
+      </c>
+      <c r="E149" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="F149" s="10" t="inlineStr">
         <is>
           <t>マルチ基準対応（CSRD等）の拡張性要件が漏れ、将来の追加開発費用が増大。</t>
         </is>
       </c>
-      <c r="E149" s="10" t="inlineStr">
+      <c r="G149" s="10" t="inlineStr">
         <is>
           <t>拡張性要件</t>
         </is>
       </c>
-      <c r="F149" s="11" t="inlineStr">
+      <c r="H149" s="11" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="G149" s="10" t="inlineStr">
+      <c r="I149" s="10" t="inlineStr">
         <is>
           <t>「追加要求なし」とみなす（後日判明時の追加開発は当該拠点起因）。</t>
         </is>
@@ -5936,22 +7104,30 @@
           <t>データ越境移転の制約（中国データ安全法等）</t>
         </is>
       </c>
-      <c r="D150" s="10" t="inlineStr">
+      <c r="D150" s="9" t="inlineStr">
+        <is>
+          <t>選択+補足〔ヒアリング〕</t>
+        </is>
+      </c>
+      <c r="E150" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="F150" s="10" t="inlineStr">
         <is>
           <t>アーキテクチャの根幹（リージョン設計・データ保管場所）とベンダー足切り条件が確定できない。稼働後に発覚すると構成変更＝最大級の手戻り＋法令違反リスク。</t>
         </is>
       </c>
-      <c r="E150" s="10" t="inlineStr">
+      <c r="G150" s="10" t="inlineStr">
         <is>
           <t>リージョン設計・法令対応・ベンダー要件</t>
         </is>
       </c>
-      <c r="F150" s="12" t="inlineStr">
+      <c r="H150" s="13" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="G150" s="10" t="inlineStr">
+      <c r="I150" s="10" t="inlineStr">
         <is>
           <t>「制約あり」とみなしリージョン分離可能な構成を必須化（費用増）。法令違反リスクの帰責は明確化必須。</t>
         </is>
@@ -5973,22 +7149,30 @@
           <t>現地事情による欠測・遅延の頻度</t>
         </is>
       </c>
-      <c r="D151" s="10" t="inlineStr">
+      <c r="D151" s="9" t="inlineStr">
+        <is>
+          <t>記述〔ヒアリング〕</t>
+        </is>
+      </c>
+      <c r="E151" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="F151" s="10" t="inlineStr">
         <is>
           <t>欠測例外設計（現地固有パターン）が漏れる。</t>
         </is>
       </c>
-      <c r="E151" s="10" t="inlineStr">
+      <c r="G151" s="10" t="inlineStr">
         <is>
           <t>例外設計</t>
         </is>
       </c>
-      <c r="F151" s="11" t="inlineStr">
+      <c r="H151" s="11" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="G151" s="10" t="inlineStr">
+      <c r="I151" s="10" t="inlineStr">
         <is>
           <t>「頻発」とみなす。</t>
         </is>
@@ -6010,22 +7194,30 @@
           <t>現地委託先からのデータ・証憑の入手性</t>
         </is>
       </c>
-      <c r="D152" s="10" t="inlineStr">
+      <c r="D152" s="9" t="inlineStr">
+        <is>
+          <t>記述〔ヒアリング〕</t>
+        </is>
+      </c>
+      <c r="E152" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="F152" s="10" t="inlineStr">
         <is>
           <t>第三者データの取得可能性と契約整備の要否が不明。</t>
         </is>
       </c>
-      <c r="E152" s="10" t="inlineStr">
+      <c r="G152" s="10" t="inlineStr">
         <is>
           <t>外部データ取得・契約整備</t>
         </is>
       </c>
-      <c r="F152" s="11" t="inlineStr">
+      <c r="H152" s="11" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="G152" s="10" t="inlineStr">
+      <c r="I152" s="10" t="inlineStr">
         <is>
           <t>「入手困難」とみなし契約整備タスクを追加。</t>
         </is>
@@ -6047,22 +7239,30 @@
           <t>現地経営層の関与度と承認の実現性</t>
         </is>
       </c>
-      <c r="D153" s="10" t="inlineStr">
+      <c r="D153" s="9" t="inlineStr">
+        <is>
+          <t>記述〔ヒアリング〕</t>
+        </is>
+      </c>
+      <c r="E153" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="F153" s="10" t="inlineStr">
         <is>
           <t>承認階層に現地社長を組み込めるかが不明で、グローバル統制設計が机上になる。</t>
         </is>
       </c>
-      <c r="E153" s="10" t="inlineStr">
+      <c r="G153" s="10" t="inlineStr">
         <is>
           <t>グローバル承認設計</t>
         </is>
       </c>
-      <c r="F153" s="11" t="inlineStr">
+      <c r="H153" s="11" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="G153" s="10" t="inlineStr">
+      <c r="I153" s="10" t="inlineStr">
         <is>
           <t>「関与なし」とみなし本社側承認で代替。</t>
         </is>
@@ -6084,22 +7284,30 @@
           <t>時差・現地祝日の締切影響</t>
         </is>
       </c>
-      <c r="D154" s="10" t="inlineStr">
+      <c r="D154" s="9" t="inlineStr">
+        <is>
+          <t>記述〔ヒアリング〕</t>
+        </is>
+      </c>
+      <c r="E154" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="F154" s="10" t="inlineStr">
         <is>
           <t>締切カレンダー（タイムゾーン・祝日）設計の精度が下がる。</t>
         </is>
       </c>
-      <c r="E154" s="10" t="inlineStr">
+      <c r="G154" s="10" t="inlineStr">
         <is>
           <t>締切カレンダー</t>
         </is>
       </c>
-      <c r="F154" s="13" t="inlineStr">
+      <c r="H154" s="14" t="inlineStr">
         <is>
           <t>低</t>
         </is>
       </c>
-      <c r="G154" s="10" t="inlineStr">
+      <c r="I154" s="10" t="inlineStr">
         <is>
           <t>「影響あり」とみなし現地優先で設計。</t>
         </is>
@@ -6121,22 +7329,30 @@
           <t>本社未報告の現地環境・安全データ</t>
         </is>
       </c>
-      <c r="D155" s="10" t="inlineStr">
+      <c r="D155" s="9" t="inlineStr">
+        <is>
+          <t>選択+補足〔ヒアリング〕</t>
+        </is>
+      </c>
+      <c r="E155" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="F155" s="10" t="inlineStr">
         <is>
           <t>バウンダリ漏れ＝保証の完全性違反の火種が残る。後日発覚すると開示訂正リスク。</t>
         </is>
       </c>
-      <c r="E155" s="10" t="inlineStr">
+      <c r="G155" s="10" t="inlineStr">
         <is>
           <t>バウンダリ完全性</t>
         </is>
       </c>
-      <c r="F155" s="12" t="inlineStr">
+      <c r="H155" s="13" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="G155" s="10" t="inlineStr">
+      <c r="I155" s="10" t="inlineStr">
         <is>
           <t>「未報告データあり」とみなし全量調査を指示（未申告分の後日発覚は当該拠点起因）。</t>
         </is>
@@ -6158,22 +7374,30 @@
           <t>現地語UI・サポートなしでの運用可否</t>
         </is>
       </c>
-      <c r="D156" s="10" t="inlineStr">
+      <c r="D156" s="9" t="inlineStr">
+        <is>
+          <t>選択+補足〔ヒアリング〕</t>
+        </is>
+      </c>
+      <c r="E156" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="F156" s="10" t="inlineStr">
         <is>
           <t>C-19の詳細。</t>
         </is>
       </c>
-      <c r="E156" s="10" t="inlineStr">
+      <c r="G156" s="10" t="inlineStr">
         <is>
           <t>多言語要件</t>
         </is>
       </c>
-      <c r="F156" s="12" t="inlineStr">
+      <c r="H156" s="13" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="G156" s="10" t="inlineStr">
+      <c r="I156" s="10" t="inlineStr">
         <is>
           <t>「困難」とみなし多言語要件を必須化。</t>
         </is>
@@ -6191,6 +7415,8 @@
       <c r="E157" s="7" t="n"/>
       <c r="F157" s="7" t="n"/>
       <c r="G157" s="7" t="n"/>
+      <c r="H157" s="7" t="n"/>
+      <c r="I157" s="7" t="n"/>
     </row>
     <row r="158" ht="52" customHeight="1">
       <c r="A158" s="8" t="inlineStr">
@@ -6208,22 +7434,30 @@
           <t>5つの難所への当てはまり度（14症状）</t>
         </is>
       </c>
-      <c r="D158" s="10" t="inlineStr">
+      <c r="D158" s="12" t="inlineStr">
+        <is>
+          <t>選択のみ（14問合計）</t>
+        </is>
+      </c>
+      <c r="E158" s="9" t="n">
+        <v>30</v>
+      </c>
+      <c r="F158" s="10" t="inlineStr">
         <is>
           <t>難所別の症状マップ（どの拠点がどの難所で苦しんでいるか）が作れず、機能要件の優先順位・拠点Tier設計・重点統制拠点の選定がすべて推測になる。</t>
         </is>
       </c>
-      <c r="E158" s="10" t="inlineStr">
+      <c r="G158" s="10" t="inlineStr">
         <is>
           <t>機能優先度・拠点Tier設計・統制重点化</t>
         </is>
       </c>
-      <c r="F158" s="11" t="inlineStr">
+      <c r="H158" s="11" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="G158" s="10" t="inlineStr">
+      <c r="I158" s="10" t="inlineStr">
         <is>
           <t>全症状「3（中程度）」とみなし平均的な設計とする（当該拠点の実態が重い場合の対応漏れは当該拠点起因）。</t>
         </is>
@@ -6245,41 +7479,89 @@
           <t>最大のペイン・要望トップ3・残してほしい点</t>
         </is>
       </c>
-      <c r="D159" s="10" t="inlineStr">
+      <c r="D159" s="9" t="inlineStr">
+        <is>
+          <t>自由記述（3問合計）</t>
+        </is>
+      </c>
+      <c r="E159" s="9" t="n">
+        <v>15</v>
+      </c>
+      <c r="F159" s="10" t="inlineStr">
         <is>
           <t>現場の受容性設計（何を残し何を変えるか）の材料を失い、定着リスクが高まる。</t>
         </is>
       </c>
-      <c r="E159" s="10" t="inlineStr">
+      <c r="G159" s="10" t="inlineStr">
         <is>
           <t>定着計画・UI設計</t>
         </is>
       </c>
-      <c r="F159" s="13" t="inlineStr">
+      <c r="H159" s="14" t="inlineStr">
         <is>
           <t>低</t>
         </is>
       </c>
-      <c r="G159" s="10" t="inlineStr">
+      <c r="I159" s="10" t="inlineStr">
         <is>
           <t>「特記なし」とみなす。</t>
         </is>
       </c>
     </row>
+    <row r="161">
+      <c r="A161" s="6" t="inlineStr">
+        <is>
+          <t>【所要時間の集計（保守的見積り）】</t>
+        </is>
+      </c>
+      <c r="B161" s="7" t="n"/>
+      <c r="C161" s="7" t="n"/>
+      <c r="D161" s="7" t="n"/>
+      <c r="E161" s="7" t="n"/>
+      <c r="F161" s="7" t="n"/>
+      <c r="G161" s="7" t="n"/>
+      <c r="H161" s="7" t="n"/>
+      <c r="I161" s="7" t="n"/>
+    </row>
+    <row r="162" ht="46" customHeight="1">
+      <c r="A162" s="2" t="inlineStr">
+        <is>
+          <t>■ 全拠点が記入するシート（プロファイル＋コア設問＋インベントリ＋難所チェック）: 合計 約245分 ≒ 約4.1時間／拠点。うちコア設問37問の大半（35問）は選択のみ・1問2分想定であり、時間の大半はインベントリ（棚卸し90分）と工数集計（30分）が占める。『設問数は多く見えるが、記述が必要なのはごく一部』という点を回答依頼時に明記すると回収率が上がる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="163" ht="46" customHeight="1">
+      <c r="A163" s="2" t="inlineStr">
+        <is>
+          <t>■ 選抜拠点ヒアリング（シート3〜9・拠点での記入不要）: 台本全量で約864分 ≒ 約14.4時間。ただし実際は該当領域のみに絞って実施するため、1拠点あたり2〜3時間×2回程度（合計4〜6時間）を想定。事務局が聞き取り・記録するため拠点側の事前準備は原則不要。</t>
+        </is>
+      </c>
+    </row>
+    <row r="164" ht="46" customHeight="1">
+      <c r="A164" s="2" t="inlineStr">
+        <is>
+          <t>■ 保守的見積りの前提: 選択のみ=2分／選択+補足=5分／記述=10分／工数集計=30分／インベントリ=90分。読む時間・確認時間を含む上振れ側の想定であり、実際はこれより短く終わる拠点が多い見込み。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="16">
+    <mergeCell ref="A64:I64"/>
+    <mergeCell ref="A43:I43"/>
+    <mergeCell ref="A142:I142"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A115:G115"/>
-    <mergeCell ref="A5:G5"/>
-    <mergeCell ref="A100:G100"/>
-    <mergeCell ref="A130:G130"/>
-    <mergeCell ref="A157:G157"/>
-    <mergeCell ref="A64:G64"/>
-    <mergeCell ref="A43:G43"/>
-    <mergeCell ref="A142:G142"/>
-    <mergeCell ref="A85:G85"/>
-    <mergeCell ref="A45:G45"/>
+    <mergeCell ref="A85:I85"/>
+    <mergeCell ref="A5:I5"/>
+    <mergeCell ref="A115:I115"/>
+    <mergeCell ref="A161:I161"/>
+    <mergeCell ref="A164:I164"/>
+    <mergeCell ref="A45:I45"/>
+    <mergeCell ref="A3:I3"/>
+    <mergeCell ref="A162:I162"/>
+    <mergeCell ref="A163:I163"/>
+    <mergeCell ref="A100:I100"/>
+    <mergeCell ref="A130:I130"/>
+    <mergeCell ref="A157:I157"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/As-Is調査_未回答リスク一覧.xlsx
+++ b/docs/As-Is調査_未回答リスク一覧.xlsx
@@ -668,14 +668,14 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>【所要時間の考え方（保守的＝上振れ側）】</t>
+          <t>【所要時間の考え方（適正目安）】</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>選択のみ=2分／選択+補足=5分／記述=10分／工数集計=30分／データ項目インベントリ=90分。読む時間を含む多めの想定。</t>
+          <t>選択のみ=1分／選択+補足=3分／記述=5分／工数集計=15分／データ項目インベントリ=60分。標準的な回答速度での想定。</t>
         </is>
       </c>
     </row>
@@ -810,7 +810,7 @@
         </is>
       </c>
       <c r="E4" s="9" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F4" s="10" t="inlineStr">
         <is>
@@ -870,7 +870,7 @@
         </is>
       </c>
       <c r="E6" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F6" s="10" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="E7" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F7" s="10" t="inlineStr">
         <is>
@@ -960,7 +960,7 @@
         </is>
       </c>
       <c r="E8" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F8" s="10" t="inlineStr">
         <is>
@@ -1005,7 +1005,7 @@
         </is>
       </c>
       <c r="E9" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F9" s="10" t="inlineStr">
         <is>
@@ -1050,7 +1050,7 @@
         </is>
       </c>
       <c r="E10" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F10" s="10" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
         </is>
       </c>
       <c r="E11" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F11" s="10" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
         </is>
       </c>
       <c r="E12" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F12" s="10" t="inlineStr">
         <is>
@@ -1185,7 +1185,7 @@
         </is>
       </c>
       <c r="E13" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F13" s="10" t="inlineStr">
         <is>
@@ -1230,7 +1230,7 @@
         </is>
       </c>
       <c r="E14" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F14" s="10" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
         </is>
       </c>
       <c r="E15" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F15" s="10" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         </is>
       </c>
       <c r="E16" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F16" s="10" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         </is>
       </c>
       <c r="E17" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F17" s="10" t="inlineStr">
         <is>
@@ -1410,7 +1410,7 @@
         </is>
       </c>
       <c r="E18" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F18" s="10" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
         </is>
       </c>
       <c r="E19" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F19" s="10" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         </is>
       </c>
       <c r="E20" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F20" s="10" t="inlineStr">
         <is>
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="E21" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F21" s="10" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         </is>
       </c>
       <c r="E22" s="9" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="F22" s="10" t="inlineStr">
         <is>
@@ -1635,7 +1635,7 @@
         </is>
       </c>
       <c r="E23" s="9" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F23" s="10" t="inlineStr">
         <is>
@@ -1680,7 +1680,7 @@
         </is>
       </c>
       <c r="E24" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F24" s="10" t="inlineStr">
         <is>
@@ -1725,7 +1725,7 @@
         </is>
       </c>
       <c r="E25" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F25" s="10" t="inlineStr">
         <is>
@@ -1770,7 +1770,7 @@
         </is>
       </c>
       <c r="E26" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F26" s="10" t="inlineStr">
         <is>
@@ -1815,7 +1815,7 @@
         </is>
       </c>
       <c r="E27" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F27" s="10" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
         </is>
       </c>
       <c r="E28" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F28" s="10" t="inlineStr">
         <is>
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="E29" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F29" s="10" t="inlineStr">
         <is>
@@ -1950,7 +1950,7 @@
         </is>
       </c>
       <c r="E30" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F30" s="10" t="inlineStr">
         <is>
@@ -1995,7 +1995,7 @@
         </is>
       </c>
       <c r="E31" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F31" s="10" t="inlineStr">
         <is>
@@ -2040,7 +2040,7 @@
         </is>
       </c>
       <c r="E32" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F32" s="10" t="inlineStr">
         <is>
@@ -2085,7 +2085,7 @@
         </is>
       </c>
       <c r="E33" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F33" s="10" t="inlineStr">
         <is>
@@ -2130,7 +2130,7 @@
         </is>
       </c>
       <c r="E34" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F34" s="10" t="inlineStr">
         <is>
@@ -2175,7 +2175,7 @@
         </is>
       </c>
       <c r="E35" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F35" s="10" t="inlineStr">
         <is>
@@ -2220,7 +2220,7 @@
         </is>
       </c>
       <c r="E36" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F36" s="10" t="inlineStr">
         <is>
@@ -2265,7 +2265,7 @@
         </is>
       </c>
       <c r="E37" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F37" s="10" t="inlineStr">
         <is>
@@ -2310,7 +2310,7 @@
         </is>
       </c>
       <c r="E38" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F38" s="10" t="inlineStr">
         <is>
@@ -2355,7 +2355,7 @@
         </is>
       </c>
       <c r="E39" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F39" s="10" t="inlineStr">
         <is>
@@ -2400,7 +2400,7 @@
         </is>
       </c>
       <c r="E40" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F40" s="10" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
         </is>
       </c>
       <c r="E41" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F41" s="10" t="inlineStr">
         <is>
@@ -2490,7 +2490,7 @@
         </is>
       </c>
       <c r="E42" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F42" s="10" t="inlineStr">
         <is>
@@ -2550,7 +2550,7 @@
         </is>
       </c>
       <c r="E44" s="9" t="n">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="F44" s="10" t="inlineStr">
         <is>
@@ -2610,7 +2610,7 @@
         </is>
       </c>
       <c r="E46" s="9" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F46" s="10" t="inlineStr">
         <is>
@@ -2655,7 +2655,7 @@
         </is>
       </c>
       <c r="E47" s="9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F47" s="10" t="inlineStr">
         <is>
@@ -2700,7 +2700,7 @@
         </is>
       </c>
       <c r="E48" s="9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F48" s="10" t="inlineStr">
         <is>
@@ -2745,7 +2745,7 @@
         </is>
       </c>
       <c r="E49" s="9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F49" s="10" t="inlineStr">
         <is>
@@ -2790,7 +2790,7 @@
         </is>
       </c>
       <c r="E50" s="9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F50" s="10" t="inlineStr">
         <is>
@@ -2835,7 +2835,7 @@
         </is>
       </c>
       <c r="E51" s="9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F51" s="10" t="inlineStr">
         <is>
@@ -2880,7 +2880,7 @@
         </is>
       </c>
       <c r="E52" s="9" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F52" s="10" t="inlineStr">
         <is>
@@ -2925,7 +2925,7 @@
         </is>
       </c>
       <c r="E53" s="9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F53" s="10" t="inlineStr">
         <is>
@@ -2970,7 +2970,7 @@
         </is>
       </c>
       <c r="E54" s="9" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F54" s="10" t="inlineStr">
         <is>
@@ -3015,7 +3015,7 @@
         </is>
       </c>
       <c r="E55" s="9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F55" s="10" t="inlineStr">
         <is>
@@ -3060,7 +3060,7 @@
         </is>
       </c>
       <c r="E56" s="9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F56" s="10" t="inlineStr">
         <is>
@@ -3105,7 +3105,7 @@
         </is>
       </c>
       <c r="E57" s="9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F57" s="10" t="inlineStr">
         <is>
@@ -3150,7 +3150,7 @@
         </is>
       </c>
       <c r="E58" s="9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F58" s="10" t="inlineStr">
         <is>
@@ -3195,7 +3195,7 @@
         </is>
       </c>
       <c r="E59" s="9" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F59" s="10" t="inlineStr">
         <is>
@@ -3240,7 +3240,7 @@
         </is>
       </c>
       <c r="E60" s="9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F60" s="10" t="inlineStr">
         <is>
@@ -3285,7 +3285,7 @@
         </is>
       </c>
       <c r="E61" s="9" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F61" s="10" t="inlineStr">
         <is>
@@ -3330,7 +3330,7 @@
         </is>
       </c>
       <c r="E62" s="9" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F62" s="10" t="inlineStr">
         <is>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="E63" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F63" s="10" t="inlineStr">
         <is>
@@ -3435,7 +3435,7 @@
         </is>
       </c>
       <c r="E65" s="9" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F65" s="10" t="inlineStr">
         <is>
@@ -3480,7 +3480,7 @@
         </is>
       </c>
       <c r="E66" s="9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F66" s="10" t="inlineStr">
         <is>
@@ -3525,7 +3525,7 @@
         </is>
       </c>
       <c r="E67" s="9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F67" s="10" t="inlineStr">
         <is>
@@ -3570,7 +3570,7 @@
         </is>
       </c>
       <c r="E68" s="9" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F68" s="10" t="inlineStr">
         <is>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="E69" s="9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F69" s="10" t="inlineStr">
         <is>
@@ -3660,7 +3660,7 @@
         </is>
       </c>
       <c r="E70" s="9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F70" s="10" t="inlineStr">
         <is>
@@ -3705,7 +3705,7 @@
         </is>
       </c>
       <c r="E71" s="9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F71" s="10" t="inlineStr">
         <is>
@@ -3750,7 +3750,7 @@
         </is>
       </c>
       <c r="E72" s="9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F72" s="10" t="inlineStr">
         <is>
@@ -3795,7 +3795,7 @@
         </is>
       </c>
       <c r="E73" s="9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F73" s="10" t="inlineStr">
         <is>
@@ -3840,7 +3840,7 @@
         </is>
       </c>
       <c r="E74" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F74" s="10" t="inlineStr">
         <is>
@@ -3885,7 +3885,7 @@
         </is>
       </c>
       <c r="E75" s="9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F75" s="10" t="inlineStr">
         <is>
@@ -3930,7 +3930,7 @@
         </is>
       </c>
       <c r="E76" s="9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F76" s="10" t="inlineStr">
         <is>
@@ -3975,7 +3975,7 @@
         </is>
       </c>
       <c r="E77" s="9" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F77" s="10" t="inlineStr">
         <is>
@@ -4020,7 +4020,7 @@
         </is>
       </c>
       <c r="E78" s="9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F78" s="10" t="inlineStr">
         <is>
@@ -4065,7 +4065,7 @@
         </is>
       </c>
       <c r="E79" s="9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F79" s="10" t="inlineStr">
         <is>
@@ -4110,7 +4110,7 @@
         </is>
       </c>
       <c r="E80" s="9" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F80" s="10" t="inlineStr">
         <is>
@@ -4155,7 +4155,7 @@
         </is>
       </c>
       <c r="E81" s="9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F81" s="10" t="inlineStr">
         <is>
@@ -4200,7 +4200,7 @@
         </is>
       </c>
       <c r="E82" s="9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F82" s="10" t="inlineStr">
         <is>
@@ -4245,7 +4245,7 @@
         </is>
       </c>
       <c r="E83" s="9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F83" s="10" t="inlineStr">
         <is>
@@ -4290,7 +4290,7 @@
         </is>
       </c>
       <c r="E84" s="9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F84" s="10" t="inlineStr">
         <is>
@@ -4350,7 +4350,7 @@
         </is>
       </c>
       <c r="E86" s="9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F86" s="10" t="inlineStr">
         <is>
@@ -4395,7 +4395,7 @@
         </is>
       </c>
       <c r="E87" s="9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F87" s="10" t="inlineStr">
         <is>
@@ -4440,7 +4440,7 @@
         </is>
       </c>
       <c r="E88" s="9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F88" s="10" t="inlineStr">
         <is>
@@ -4485,7 +4485,7 @@
         </is>
       </c>
       <c r="E89" s="9" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F89" s="10" t="inlineStr">
         <is>
@@ -4530,7 +4530,7 @@
         </is>
       </c>
       <c r="E90" s="9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F90" s="10" t="inlineStr">
         <is>
@@ -4575,7 +4575,7 @@
         </is>
       </c>
       <c r="E91" s="9" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F91" s="10" t="inlineStr">
         <is>
@@ -4620,7 +4620,7 @@
         </is>
       </c>
       <c r="E92" s="9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F92" s="10" t="inlineStr">
         <is>
@@ -4665,7 +4665,7 @@
         </is>
       </c>
       <c r="E93" s="9" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F93" s="10" t="inlineStr">
         <is>
@@ -4710,7 +4710,7 @@
         </is>
       </c>
       <c r="E94" s="9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F94" s="10" t="inlineStr">
         <is>
@@ -4755,7 +4755,7 @@
         </is>
       </c>
       <c r="E95" s="9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F95" s="10" t="inlineStr">
         <is>
@@ -4800,7 +4800,7 @@
         </is>
       </c>
       <c r="E96" s="9" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F96" s="10" t="inlineStr">
         <is>
@@ -4845,7 +4845,7 @@
         </is>
       </c>
       <c r="E97" s="9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F97" s="10" t="inlineStr">
         <is>
@@ -4890,7 +4890,7 @@
         </is>
       </c>
       <c r="E98" s="9" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F98" s="10" t="inlineStr">
         <is>
@@ -4935,7 +4935,7 @@
         </is>
       </c>
       <c r="E99" s="9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F99" s="10" t="inlineStr">
         <is>
@@ -4995,7 +4995,7 @@
         </is>
       </c>
       <c r="E101" s="9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F101" s="10" t="inlineStr">
         <is>
@@ -5040,7 +5040,7 @@
         </is>
       </c>
       <c r="E102" s="9" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F102" s="10" t="inlineStr">
         <is>
@@ -5085,7 +5085,7 @@
         </is>
       </c>
       <c r="E103" s="9" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F103" s="10" t="inlineStr">
         <is>
@@ -5130,7 +5130,7 @@
         </is>
       </c>
       <c r="E104" s="9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F104" s="10" t="inlineStr">
         <is>
@@ -5175,7 +5175,7 @@
         </is>
       </c>
       <c r="E105" s="9" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F105" s="10" t="inlineStr">
         <is>
@@ -5220,7 +5220,7 @@
         </is>
       </c>
       <c r="E106" s="9" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F106" s="10" t="inlineStr">
         <is>
@@ -5265,7 +5265,7 @@
         </is>
       </c>
       <c r="E107" s="9" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F107" s="10" t="inlineStr">
         <is>
@@ -5310,7 +5310,7 @@
         </is>
       </c>
       <c r="E108" s="9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F108" s="10" t="inlineStr">
         <is>
@@ -5355,7 +5355,7 @@
         </is>
       </c>
       <c r="E109" s="9" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F109" s="10" t="inlineStr">
         <is>
@@ -5400,7 +5400,7 @@
         </is>
       </c>
       <c r="E110" s="9" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F110" s="10" t="inlineStr">
         <is>
@@ -5445,7 +5445,7 @@
         </is>
       </c>
       <c r="E111" s="9" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F111" s="10" t="inlineStr">
         <is>
@@ -5490,7 +5490,7 @@
         </is>
       </c>
       <c r="E112" s="9" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F112" s="10" t="inlineStr">
         <is>
@@ -5535,7 +5535,7 @@
         </is>
       </c>
       <c r="E113" s="9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F113" s="10" t="inlineStr">
         <is>
@@ -5580,7 +5580,7 @@
         </is>
       </c>
       <c r="E114" s="9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F114" s="10" t="inlineStr">
         <is>
@@ -5640,7 +5640,7 @@
         </is>
       </c>
       <c r="E116" s="9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F116" s="10" t="inlineStr">
         <is>
@@ -5685,7 +5685,7 @@
         </is>
       </c>
       <c r="E117" s="9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F117" s="10" t="inlineStr">
         <is>
@@ -5730,7 +5730,7 @@
         </is>
       </c>
       <c r="E118" s="9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F118" s="10" t="inlineStr">
         <is>
@@ -5775,7 +5775,7 @@
         </is>
       </c>
       <c r="E119" s="9" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F119" s="10" t="inlineStr">
         <is>
@@ -5820,7 +5820,7 @@
         </is>
       </c>
       <c r="E120" s="9" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F120" s="10" t="inlineStr">
         <is>
@@ -5865,7 +5865,7 @@
         </is>
       </c>
       <c r="E121" s="9" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F121" s="10" t="inlineStr">
         <is>
@@ -5910,7 +5910,7 @@
         </is>
       </c>
       <c r="E122" s="9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F122" s="10" t="inlineStr">
         <is>
@@ -5955,7 +5955,7 @@
         </is>
       </c>
       <c r="E123" s="9" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F123" s="10" t="inlineStr">
         <is>
@@ -6000,7 +6000,7 @@
         </is>
       </c>
       <c r="E124" s="9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F124" s="10" t="inlineStr">
         <is>
@@ -6045,7 +6045,7 @@
         </is>
       </c>
       <c r="E125" s="9" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F125" s="10" t="inlineStr">
         <is>
@@ -6090,7 +6090,7 @@
         </is>
       </c>
       <c r="E126" s="9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F126" s="10" t="inlineStr">
         <is>
@@ -6135,7 +6135,7 @@
         </is>
       </c>
       <c r="E127" s="9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F127" s="10" t="inlineStr">
         <is>
@@ -6180,7 +6180,7 @@
         </is>
       </c>
       <c r="E128" s="9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F128" s="10" t="inlineStr">
         <is>
@@ -6225,7 +6225,7 @@
         </is>
       </c>
       <c r="E129" s="9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F129" s="10" t="inlineStr">
         <is>
@@ -6285,7 +6285,7 @@
         </is>
       </c>
       <c r="E131" s="9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F131" s="10" t="inlineStr">
         <is>
@@ -6330,7 +6330,7 @@
         </is>
       </c>
       <c r="E132" s="9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F132" s="10" t="inlineStr">
         <is>
@@ -6375,7 +6375,7 @@
         </is>
       </c>
       <c r="E133" s="9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F133" s="10" t="inlineStr">
         <is>
@@ -6420,7 +6420,7 @@
         </is>
       </c>
       <c r="E134" s="9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F134" s="10" t="inlineStr">
         <is>
@@ -6465,7 +6465,7 @@
         </is>
       </c>
       <c r="E135" s="9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F135" s="10" t="inlineStr">
         <is>
@@ -6510,7 +6510,7 @@
         </is>
       </c>
       <c r="E136" s="9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F136" s="10" t="inlineStr">
         <is>
@@ -6555,7 +6555,7 @@
         </is>
       </c>
       <c r="E137" s="9" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F137" s="10" t="inlineStr">
         <is>
@@ -6600,7 +6600,7 @@
         </is>
       </c>
       <c r="E138" s="9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F138" s="10" t="inlineStr">
         <is>
@@ -6645,7 +6645,7 @@
         </is>
       </c>
       <c r="E139" s="9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F139" s="10" t="inlineStr">
         <is>
@@ -6690,7 +6690,7 @@
         </is>
       </c>
       <c r="E140" s="9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F140" s="10" t="inlineStr">
         <is>
@@ -6735,7 +6735,7 @@
         </is>
       </c>
       <c r="E141" s="9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F141" s="10" t="inlineStr">
         <is>
@@ -6795,7 +6795,7 @@
         </is>
       </c>
       <c r="E143" s="9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F143" s="10" t="inlineStr">
         <is>
@@ -6840,7 +6840,7 @@
         </is>
       </c>
       <c r="E144" s="9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F144" s="10" t="inlineStr">
         <is>
@@ -6885,7 +6885,7 @@
         </is>
       </c>
       <c r="E145" s="9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F145" s="10" t="inlineStr">
         <is>
@@ -6930,7 +6930,7 @@
         </is>
       </c>
       <c r="E146" s="9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F146" s="10" t="inlineStr">
         <is>
@@ -6975,7 +6975,7 @@
         </is>
       </c>
       <c r="E147" s="9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F147" s="10" t="inlineStr">
         <is>
@@ -7020,7 +7020,7 @@
         </is>
       </c>
       <c r="E148" s="9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F148" s="10" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="E149" s="9" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F149" s="10" t="inlineStr">
         <is>
@@ -7110,7 +7110,7 @@
         </is>
       </c>
       <c r="E150" s="9" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F150" s="10" t="inlineStr">
         <is>
@@ -7155,7 +7155,7 @@
         </is>
       </c>
       <c r="E151" s="9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F151" s="10" t="inlineStr">
         <is>
@@ -7200,7 +7200,7 @@
         </is>
       </c>
       <c r="E152" s="9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F152" s="10" t="inlineStr">
         <is>
@@ -7245,7 +7245,7 @@
         </is>
       </c>
       <c r="E153" s="9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F153" s="10" t="inlineStr">
         <is>
@@ -7290,7 +7290,7 @@
         </is>
       </c>
       <c r="E154" s="9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F154" s="10" t="inlineStr">
         <is>
@@ -7335,7 +7335,7 @@
         </is>
       </c>
       <c r="E155" s="9" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F155" s="10" t="inlineStr">
         <is>
@@ -7380,7 +7380,7 @@
         </is>
       </c>
       <c r="E156" s="9" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F156" s="10" t="inlineStr">
         <is>
@@ -7440,7 +7440,7 @@
         </is>
       </c>
       <c r="E158" s="9" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="F158" s="10" t="inlineStr">
         <is>
@@ -7485,7 +7485,7 @@
         </is>
       </c>
       <c r="E159" s="9" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F159" s="10" t="inlineStr">
         <is>
@@ -7511,7 +7511,7 @@
     <row r="161">
       <c r="A161" s="6" t="inlineStr">
         <is>
-          <t>【所要時間の集計（保守的見積り）】</t>
+          <t>【所要時間の集計（適正目安）】</t>
         </is>
       </c>
       <c r="B161" s="7" t="n"/>
@@ -7526,21 +7526,21 @@
     <row r="162" ht="46" customHeight="1">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>■ 全拠点が記入するシート（プロファイル＋コア設問＋インベントリ＋難所チェック）: 合計 約245分 ≒ 約4.1時間／拠点。うちコア設問37問の大半（35問）は選択のみ・1問2分想定であり、時間の大半はインベントリ（棚卸し90分）と工数集計（30分）が占める。『設問数は多く見えるが、記述が必要なのはごく一部』という点を回答依頼時に明記すると回収率が上がる。</t>
+          <t>■ 全拠点が記入するシート（プロファイル＋コア設問＋インベントリ＋難所チェック）: 合計 約141分 ≒ 約2.4時間／拠点。うちコア設問37問の大半（35問）は選択のみ・1問1分想定であり、時間の半分近くはインベントリ（棚卸し60分）が占める。『設問数は多く見えるが、記述が必要なのはごく一部』という点を回答依頼時に明記すると回収率が上がる。</t>
         </is>
       </c>
     </row>
     <row r="163" ht="46" customHeight="1">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>■ 選抜拠点ヒアリング（シート3〜9・拠点での記入不要）: 台本全量で約864分 ≒ 約14.4時間。ただし実際は該当領域のみに絞って実施するため、1拠点あたり2〜3時間×2回程度（合計4〜6時間）を想定。事務局が聞き取り・記録するため拠点側の事前準備は原則不要。</t>
+          <t>■ 選抜拠点ヒアリング（シート3〜9・拠点での記入不要）: 台本全量で約449分 ≒ 約7.5時間。ただし実際は該当領域のみに絞って実施するため、1拠点あたり2時間×1〜2回を想定。事務局が聞き取り・記録するため拠点側の事前準備は原則不要。</t>
         </is>
       </c>
     </row>
     <row r="164" ht="46" customHeight="1">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>■ 保守的見積りの前提: 選択のみ=2分／選択+補足=5分／記述=10分／工数集計=30分／インベントリ=90分。読む時間・確認時間を含む上振れ側の想定であり、実際はこれより短く終わる拠点が多い見込み。</t>
+          <t>■ 適正見積りの前提: 選択のみ=1分／選択+補足=3分／記述=5分／工数集計=15分／インベントリ=60分。標準的な回答速度での想定（インベントリは既存報告様式を参照しながらの転記を前提）。</t>
         </is>
       </c>
     </row>

--- a/docs/As-Is調査_未回答リスク一覧.xlsx
+++ b/docs/As-Is調査_未回答リスク一覧.xlsx
@@ -46,6 +46,12 @@
     <font>
       <name val="Meiryo"/>
       <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Meiryo"/>
+      <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="13"/>
     </font>
@@ -71,12 +77,6 @@
       <name val="Meiryo"/>
       <color rgb="00000000"/>
       <sz val="8"/>
-    </font>
-    <font>
-      <name val="Meiryo"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="9"/>
     </font>
   </fonts>
   <fills count="8">
@@ -143,7 +143,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -154,31 +154,34 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -546,7 +549,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A23"/>
+  <dimension ref="A1:A24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="140" customWidth="1" min="1" max="1"/>
@@ -687,9 +690,16 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>シート3〜9（手順〜海外固有）は選抜拠点のみを対象とした事務局ヒアリングの台本であり、拠点側での記入は不要。</t>
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>シート3〜9（手順〜海外固有）は選抜拠点のみを対象とした事務局ヒアリングの台本であり、拠点側での記入は不要。ただし台本101問を全問実施すると約7.5時間かかり、全拠点記入分（約2.4時間）と合わせて選抜拠点は合計約10時間規模になる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>選抜拠点ヒアリングは全問実施を前提にせず、影響度「高」の設問と、コア設問で要注意回答（『一部ある・古い』『わからない』『困難』等）があったカテゴリに絞って実施する。絞り込み後の目安は1拠点2時間×1〜2回（計2〜4時間）、選抜拠点の総所要は約4.4〜6.4時間。</t>
         </is>
       </c>
     </row>
@@ -704,7 +714,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I164"/>
+  <dimension ref="A1:I165"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -719,6809 +729,6809 @@
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>As-Is調査 設問別｜未回答時のシステム要件リスク一覧</t>
         </is>
       </c>
     </row>
     <row r="2" ht="28" customHeight="1">
-      <c r="A2" s="5" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B2" s="5" t="inlineStr">
+      <c r="B2" s="6" t="inlineStr">
         <is>
           <t>カテゴリ</t>
         </is>
       </c>
-      <c r="C2" s="5" t="inlineStr">
+      <c r="C2" s="6" t="inlineStr">
         <is>
           <t>設問（要約）</t>
         </is>
       </c>
-      <c r="D2" s="5" t="inlineStr">
+      <c r="D2" s="6" t="inlineStr">
         <is>
           <t>回答形式</t>
         </is>
       </c>
-      <c r="E2" s="5" t="inlineStr">
+      <c r="E2" s="6" t="inlineStr">
         <is>
           <t>所要目安
 (分)</t>
         </is>
       </c>
-      <c r="F2" s="5" t="inlineStr">
+      <c r="F2" s="6" t="inlineStr">
         <is>
           <t>未回答時のシステム要件リスク</t>
         </is>
       </c>
-      <c r="G2" s="5" t="inlineStr">
+      <c r="G2" s="6" t="inlineStr">
         <is>
           <t>影響する成果物・機能</t>
         </is>
       </c>
-      <c r="H2" s="5" t="inlineStr">
+      <c r="H2" s="6" t="inlineStr">
         <is>
           <t>影響度</t>
         </is>
       </c>
-      <c r="I2" s="5" t="inlineStr">
+      <c r="I2" s="6" t="inlineStr">
         <is>
           <t>未回答時のデフォルト前提（帰責の基準線）</t>
         </is>
       </c>
     </row>
     <row r="3" ht="17" customHeight="1">
-      <c r="A3" s="6" t="inlineStr">
+      <c r="A3" s="7" t="inlineStr">
         <is>
           <t>1. 拠点プロファイル（全拠点）</t>
         </is>
       </c>
-      <c r="B3" s="7" t="n"/>
-      <c r="C3" s="7" t="n"/>
-      <c r="D3" s="7" t="n"/>
-      <c r="E3" s="7" t="n"/>
-      <c r="F3" s="7" t="n"/>
-      <c r="G3" s="7" t="n"/>
-      <c r="H3" s="7" t="n"/>
-      <c r="I3" s="7" t="n"/>
+      <c r="B3" s="8" t="n"/>
+      <c r="C3" s="8" t="n"/>
+      <c r="D3" s="8" t="n"/>
+      <c r="E3" s="8" t="n"/>
+      <c r="F3" s="8" t="n"/>
+      <c r="G3" s="8" t="n"/>
+      <c r="H3" s="8" t="n"/>
+      <c r="I3" s="8" t="n"/>
     </row>
     <row r="4" ht="52" customHeight="1">
-      <c r="A4" s="8" t="inlineStr">
+      <c r="A4" s="9" t="inlineStr">
         <is>
           <t>P-1〜7</t>
         </is>
       </c>
-      <c r="B4" s="9" t="inlineStr">
+      <c r="B4" s="10" t="inlineStr">
         <is>
           <t>プロファイル</t>
         </is>
       </c>
-      <c r="C4" s="10" t="inlineStr">
+      <c r="C4" s="11" t="inlineStr">
         <is>
           <t>会社名・拠点名・回答者・担当領域等</t>
         </is>
       </c>
-      <c r="D4" s="9" t="inlineStr">
+      <c r="D4" s="10" t="inlineStr">
         <is>
           <t>記入</t>
         </is>
       </c>
-      <c r="E4" s="9" t="n">
+      <c r="E4" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="F4" s="10" t="inlineStr">
+      <c r="F4" s="11" t="inlineStr">
         <is>
           <t>回答者・担当領域が不明だと、後続ヒアリングの宛先も、要件への異議申立ての窓口も特定できない。未回答拠点は「要件定義に参加しなかった拠点」として扱わざるを得ない。</t>
         </is>
       </c>
-      <c r="G4" s="10" t="inlineStr">
+      <c r="G4" s="11" t="inlineStr">
         <is>
           <t>ヒアリング計画・展開計画（拠点マスタ）</t>
         </is>
       </c>
-      <c r="H4" s="11" t="inlineStr">
+      <c r="H4" s="12" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="I4" s="10" t="inlineStr">
+      <c r="I4" s="11" t="inlineStr">
         <is>
           <t>未回答拠点は「標準要件をそのまま適用する拠点」とみなし、拠点固有要件は一切考慮しない。</t>
         </is>
       </c>
     </row>
     <row r="5" ht="17" customHeight="1">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>3C. コア設問（全拠点・C-01〜C-37）</t>
         </is>
       </c>
-      <c r="B5" s="7" t="n"/>
-      <c r="C5" s="7" t="n"/>
-      <c r="D5" s="7" t="n"/>
-      <c r="E5" s="7" t="n"/>
-      <c r="F5" s="7" t="n"/>
-      <c r="G5" s="7" t="n"/>
-      <c r="H5" s="7" t="n"/>
-      <c r="I5" s="7" t="n"/>
+      <c r="B5" s="8" t="n"/>
+      <c r="C5" s="8" t="n"/>
+      <c r="D5" s="8" t="n"/>
+      <c r="E5" s="8" t="n"/>
+      <c r="F5" s="8" t="n"/>
+      <c r="G5" s="8" t="n"/>
+      <c r="H5" s="8" t="n"/>
+      <c r="I5" s="8" t="n"/>
     </row>
     <row r="6" ht="52" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
+      <c r="A6" s="9" t="inlineStr">
         <is>
           <t>C-01</t>
         </is>
       </c>
-      <c r="B6" s="9" t="inlineStr">
+      <c r="B6" s="10" t="inlineStr">
         <is>
           <t>手順</t>
         </is>
       </c>
-      <c r="C6" s="10" t="inlineStr">
+      <c r="C6" s="11" t="inlineStr">
         <is>
           <t>手順書・マニュアルの有無</t>
         </is>
       </c>
-      <c r="D6" s="12" t="inlineStr">
+      <c r="D6" s="13" t="inlineStr">
         <is>
           <t>選択のみ</t>
         </is>
       </c>
-      <c r="E6" s="9" t="n">
+      <c r="E6" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="F6" s="10" t="inlineStr">
+      <c r="F6" s="11" t="inlineStr">
         <is>
           <t>現行業務を要件定義の出発点として文書化できず、To-Be業務フロー・画面設計の根拠が失われる。ヒアリングをゼロからやり直す工数増。</t>
         </is>
       </c>
-      <c r="G6" s="10" t="inlineStr">
+      <c r="G6" s="11" t="inlineStr">
         <is>
           <t>業務要件定義書・To-Beフロー</t>
         </is>
       </c>
-      <c r="H6" s="11" t="inlineStr">
+      <c r="H6" s="12" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="I6" s="10" t="inlineStr">
+      <c r="I6" s="11" t="inlineStr">
         <is>
           <t>「手順書なし・完全属人」とみなし、追加ヒアリング工数を当該拠点に割り当てる。</t>
         </is>
       </c>
     </row>
     <row r="7" ht="52" customHeight="1">
-      <c r="A7" s="8" t="inlineStr">
+      <c r="A7" s="9" t="inlineStr">
         <is>
           <t>C-02</t>
         </is>
       </c>
-      <c r="B7" s="9" t="inlineStr">
+      <c r="B7" s="10" t="inlineStr">
         <is>
           <t>手順</t>
         </is>
       </c>
-      <c r="C7" s="10" t="inlineStr">
+      <c r="C7" s="11" t="inlineStr">
         <is>
           <t>月次報告の締切余裕</t>
         </is>
       </c>
-      <c r="D7" s="12" t="inlineStr">
+      <c r="D7" s="13" t="inlineStr">
         <is>
           <t>選択のみ</t>
         </is>
       </c>
-      <c r="E7" s="9" t="n">
+      <c r="E7" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="F7" s="10" t="inlineStr">
+      <c r="F7" s="11" t="inlineStr">
         <is>
           <t>締切逼迫度が不明のままでは、入力期限設定・リマインド・督促機能の要件（強度・頻度）が決められない。</t>
         </is>
       </c>
-      <c r="G7" s="10" t="inlineStr">
+      <c r="G7" s="11" t="inlineStr">
         <is>
           <t>ワークフロー要件・督促自動化</t>
         </is>
       </c>
-      <c r="H7" s="11" t="inlineStr">
+      <c r="H7" s="12" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="I7" s="10" t="inlineStr">
+      <c r="I7" s="11" t="inlineStr">
         <is>
           <t>「毎回ぎりぎり」とみなし督促自動化・早期警報を必須要件化（過剰なら費用増）。</t>
         </is>
       </c>
     </row>
     <row r="8" ht="52" customHeight="1">
-      <c r="A8" s="8" t="inlineStr">
+      <c r="A8" s="9" t="inlineStr">
         <is>
           <t>C-03</t>
         </is>
       </c>
-      <c r="B8" s="9" t="inlineStr">
+      <c r="B8" s="10" t="inlineStr">
         <is>
           <t>手順</t>
         </is>
       </c>
-      <c r="C8" s="10" t="inlineStr">
+      <c r="C8" s="11" t="inlineStr">
         <is>
           <t>期ズレ（使用期間と請求期間のズレ）の処理方法</t>
         </is>
       </c>
-      <c r="D8" s="12" t="inlineStr">
+      <c r="D8" s="13" t="inlineStr">
         <is>
           <t>選択のみ</t>
         </is>
       </c>
-      <c r="E8" s="9" t="n">
+      <c r="E8" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="F8" s="10" t="inlineStr">
+      <c r="F8" s="11" t="inlineStr">
         <is>
           <t>按分機能（日割・翌月計上等）の要否・仕様が確定できず、算定エンジン要件が曖昧になり、ベンダー見積りに高値バッファが乗る。</t>
         </is>
       </c>
-      <c r="G8" s="10" t="inlineStr">
+      <c r="G8" s="11" t="inlineStr">
         <is>
           <t>算定ロジック要件・データモデル（期間属性）</t>
         </is>
       </c>
-      <c r="H8" s="13" t="inlineStr">
+      <c r="H8" s="14" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="I8" s="10" t="inlineStr">
+      <c r="I8" s="11" t="inlineStr">
         <is>
           <t>「拠点ごとに処理方法がバラバラ」とみなし、複数方式対応の按分機能を必須化（過剰スペック＝コスト増）。</t>
         </is>
       </c>
     </row>
     <row r="9" ht="52" customHeight="1">
-      <c r="A9" s="8" t="inlineStr">
+      <c r="A9" s="9" t="inlineStr">
         <is>
           <t>C-04</t>
         </is>
       </c>
-      <c r="B9" s="9" t="inlineStr">
+      <c r="B9" s="10" t="inlineStr">
         <is>
           <t>手順</t>
         </is>
       </c>
-      <c r="C9" s="10" t="inlineStr">
+      <c r="C9" s="11" t="inlineStr">
         <is>
           <t>報告後のデータ修正頻度</t>
         </is>
       </c>
-      <c r="D9" s="12" t="inlineStr">
+      <c r="D9" s="13" t="inlineStr">
         <is>
           <t>選択のみ</t>
         </is>
       </c>
-      <c r="E9" s="9" t="n">
+      <c r="E9" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="F9" s="10" t="inlineStr">
+      <c r="F9" s="11" t="inlineStr">
         <is>
           <t>修正申請ワークフロー・再承認・再計算の負荷設計（同時実行・性能）が決められない。</t>
         </is>
       </c>
-      <c r="G9" s="10" t="inlineStr">
+      <c r="G9" s="11" t="inlineStr">
         <is>
           <t>修正WF要件・性能要件</t>
         </is>
       </c>
-      <c r="H9" s="11" t="inlineStr">
+      <c r="H9" s="12" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="I9" s="10" t="inlineStr">
+      <c r="I9" s="11" t="inlineStr">
         <is>
           <t>「ほぼ毎月修正あり」とみなし修正WFをフル装備で設計。</t>
         </is>
       </c>
     </row>
     <row r="10" ht="52" customHeight="1">
-      <c r="A10" s="8" t="inlineStr">
+      <c r="A10" s="9" t="inlineStr">
         <is>
           <t>C-05</t>
         </is>
       </c>
-      <c r="B10" s="9" t="inlineStr">
+      <c r="B10" s="10" t="inlineStr">
         <is>
           <t>手順</t>
         </is>
       </c>
-      <c r="C10" s="10" t="inlineStr">
+      <c r="C10" s="11" t="inlineStr">
         <is>
           <t>主担当1ヶ月不在時の影響</t>
         </is>
       </c>
-      <c r="D10" s="12" t="inlineStr">
+      <c r="D10" s="13" t="inlineStr">
         <is>
           <t>選択のみ</t>
         </is>
       </c>
-      <c r="E10" s="9" t="n">
+      <c r="E10" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="F10" s="10" t="inlineStr">
+      <c r="F10" s="11" t="inlineStr">
         <is>
           <t>代行権限・委任機能の要否が決まらず、承認が止まるリスクを設計で防げない。</t>
         </is>
       </c>
-      <c r="G10" s="10" t="inlineStr">
+      <c r="G10" s="11" t="inlineStr">
         <is>
           <t>権限設計・代行承認機能</t>
         </is>
       </c>
-      <c r="H10" s="11" t="inlineStr">
+      <c r="H10" s="12" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="I10" s="10" t="inlineStr">
+      <c r="I10" s="11" t="inlineStr">
         <is>
           <t>「報告が止まる」とみなし代行承認・不在アラートを必須化。</t>
         </is>
       </c>
     </row>
     <row r="11" ht="52" customHeight="1">
-      <c r="A11" s="8" t="inlineStr">
+      <c r="A11" s="9" t="inlineStr">
         <is>
           <t>C-06</t>
         </is>
       </c>
-      <c r="B11" s="9" t="inlineStr">
+      <c r="B11" s="10" t="inlineStr">
         <is>
           <t>算定</t>
         </is>
       </c>
-      <c r="C11" s="10" t="inlineStr">
+      <c r="C11" s="11" t="inlineStr">
         <is>
           <t>排出量計算をどこまで拠点側で実施しているか</t>
         </is>
       </c>
-      <c r="D11" s="12" t="inlineStr">
+      <c r="D11" s="13" t="inlineStr">
         <is>
           <t>選択のみ</t>
         </is>
       </c>
-      <c r="E11" s="9" t="n">
+      <c r="E11" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="F11" s="10" t="inlineStr">
+      <c r="F11" s="11" t="inlineStr">
         <is>
           <t>算定エンジンの機能配置（中央集約か拠点計算容認か）というアーキテクチャの根幹が決められない。拠点独自計算が後から発覚すると数値の連続性が切れる。</t>
         </is>
       </c>
-      <c r="G11" s="10" t="inlineStr">
+      <c r="G11" s="11" t="inlineStr">
         <is>
           <t>算定エンジン・アーキテクチャ</t>
         </is>
       </c>
-      <c r="H11" s="13" t="inlineStr">
+      <c r="H11" s="14" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="I11" s="10" t="inlineStr">
+      <c r="I11" s="11" t="inlineStr">
         <is>
           <t>「拠点独自計算あり」とみなし、既存ロジックの棚卸し・移植検証を要件化（追加工数は当該拠点起因）。</t>
         </is>
       </c>
     </row>
     <row r="12" ht="52" customHeight="1">
-      <c r="A12" s="8" t="inlineStr">
+      <c r="A12" s="9" t="inlineStr">
         <is>
           <t>C-07</t>
         </is>
       </c>
-      <c r="B12" s="9" t="inlineStr">
+      <c r="B12" s="10" t="inlineStr">
         <is>
           <t>算定</t>
         </is>
       </c>
-      <c r="C12" s="10" t="inlineStr">
+      <c r="C12" s="11" t="inlineStr">
         <is>
           <t>本社標準と異なる独自係数・ルールの使用</t>
         </is>
       </c>
-      <c r="D12" s="12" t="inlineStr">
+      <c r="D12" s="13" t="inlineStr">
         <is>
           <t>選択のみ</t>
         </is>
       </c>
-      <c r="E12" s="9" t="n">
+      <c r="E12" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="F12" s="10" t="inlineStr">
+      <c r="F12" s="11" t="inlineStr">
         <is>
           <t>係数マスタの拠点別上書き管理の要否が不明。未申告の独自係数は移行後に数値差異として顕在化し、保証で説明不能になる。</t>
         </is>
       </c>
-      <c r="G12" s="10" t="inlineStr">
+      <c r="G12" s="11" t="inlineStr">
         <is>
           <t>係数マスタ設計・監査対応</t>
         </is>
       </c>
-      <c r="H12" s="13" t="inlineStr">
+      <c r="H12" s="14" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="I12" s="10" t="inlineStr">
+      <c r="I12" s="11" t="inlineStr">
         <is>
           <t>「独自係数あり」とみなし拠点別係数設定を実装。移行後に発覚した未申告係数による数値差異は当該拠点起因として記録。</t>
         </is>
       </c>
     </row>
     <row r="13" ht="52" customHeight="1">
-      <c r="A13" s="8" t="inlineStr">
+      <c r="A13" s="9" t="inlineStr">
         <is>
           <t>C-08</t>
         </is>
       </c>
-      <c r="B13" s="9" t="inlineStr">
+      <c r="B13" s="10" t="inlineStr">
         <is>
           <t>算定</t>
         </is>
       </c>
-      <c r="C13" s="10" t="inlineStr">
+      <c r="C13" s="11" t="inlineStr">
         <is>
           <t>計算Excel・マクロを説明・修正できる人数</t>
         </is>
       </c>
-      <c r="D13" s="12" t="inlineStr">
+      <c r="D13" s="13" t="inlineStr">
         <is>
           <t>選択のみ</t>
         </is>
       </c>
-      <c r="E13" s="9" t="n">
+      <c r="E13" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="F13" s="10" t="inlineStr">
+      <c r="F13" s="11" t="inlineStr">
         <is>
           <t>ロジック移植の可否・工数が見積れず、RFPでベンダーが高値バッファを乗せる。作成者退職済みなら再現不能＝過年度との連続性が切れる。</t>
         </is>
       </c>
-      <c r="G13" s="10" t="inlineStr">
+      <c r="G13" s="11" t="inlineStr">
         <is>
           <t>ロジック移植計画・RFP見積り前提</t>
         </is>
       </c>
-      <c r="H13" s="13" t="inlineStr">
+      <c r="H13" s="14" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="I13" s="10" t="inlineStr">
+      <c r="I13" s="11" t="inlineStr">
         <is>
           <t>「作成者頼み・ブラックボックス」とみなしリバースエンジニアリング工数を計上（費用増）。</t>
         </is>
       </c>
     </row>
     <row r="14" ht="52" customHeight="1">
-      <c r="A14" s="8" t="inlineStr">
+      <c r="A14" s="9" t="inlineStr">
         <is>
           <t>C-09</t>
         </is>
       </c>
-      <c r="B14" s="9" t="inlineStr">
+      <c r="B14" s="10" t="inlineStr">
         <is>
           <t>証憑</t>
         </is>
       </c>
-      <c r="C14" s="10" t="inlineStr">
+      <c r="C14" s="11" t="inlineStr">
         <is>
           <t>証憑の形式（紙／電子の比率）</t>
         </is>
       </c>
-      <c r="D14" s="12" t="inlineStr">
+      <c r="D14" s="13" t="inlineStr">
         <is>
           <t>選択のみ</t>
         </is>
       </c>
-      <c r="E14" s="9" t="n">
+      <c r="E14" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="F14" s="10" t="inlineStr">
+      <c r="F14" s="11" t="inlineStr">
         <is>
           <t>スキャン運用・ストレージ容量・アップロードUIの要件規模が決められない。</t>
         </is>
       </c>
-      <c r="G14" s="10" t="inlineStr">
+      <c r="G14" s="11" t="inlineStr">
         <is>
           <t>証憑管理機能・ストレージ設計</t>
         </is>
       </c>
-      <c r="H14" s="11" t="inlineStr">
+      <c r="H14" s="12" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="I14" s="10" t="inlineStr">
+      <c r="I14" s="11" t="inlineStr">
         <is>
           <t>「ほぼ紙」とみなしスキャン運用＋容量大きめで設計（費用増）。</t>
         </is>
       </c>
     </row>
     <row r="15" ht="52" customHeight="1">
-      <c r="A15" s="8" t="inlineStr">
+      <c r="A15" s="9" t="inlineStr">
         <is>
           <t>C-10</t>
         </is>
       </c>
-      <c r="B15" s="9" t="inlineStr">
+      <c r="B15" s="10" t="inlineStr">
         <is>
           <t>証憑</t>
         </is>
       </c>
-      <c r="C15" s="10" t="inlineStr">
+      <c r="C15" s="11" t="inlineStr">
         <is>
           <t>報告数値から証憑まで遡れるか</t>
         </is>
       </c>
-      <c r="D15" s="12" t="inlineStr">
+      <c r="D15" s="13" t="inlineStr">
         <is>
           <t>選択のみ</t>
         </is>
       </c>
-      <c r="E15" s="9" t="n">
+      <c r="E15" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="F15" s="10" t="inlineStr">
+      <c r="F15" s="11" t="inlineStr">
         <is>
           <t>数値⇔証憑の紐付けデータモデルと移行時の証憑再収集range が設計できない。保証対応の根幹要件が確定しない。</t>
         </is>
       </c>
-      <c r="G15" s="10" t="inlineStr">
+      <c r="G15" s="11" t="inlineStr">
         <is>
           <t>証憑紐付けデータモデル・移行計画</t>
         </is>
       </c>
-      <c r="H15" s="13" t="inlineStr">
+      <c r="H15" s="14" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="I15" s="10" t="inlineStr">
+      <c r="I15" s="11" t="inlineStr">
         <is>
           <t>「一部遡れない」とみなし移行時の証憑再収集タスクを計画化（工数は当該拠点負担）。</t>
         </is>
       </c>
     </row>
     <row r="16" ht="52" customHeight="1">
-      <c r="A16" s="8" t="inlineStr">
+      <c r="A16" s="9" t="inlineStr">
         <is>
           <t>C-11</t>
         </is>
       </c>
-      <c r="B16" s="9" t="inlineStr">
+      <c r="B16" s="10" t="inlineStr">
         <is>
           <t>証憑</t>
         </is>
       </c>
-      <c r="C16" s="10" t="inlineStr">
+      <c r="C16" s="11" t="inlineStr">
         <is>
           <t>証憑添付必須化への対応可否</t>
         </is>
       </c>
-      <c r="D16" s="12" t="inlineStr">
+      <c r="D16" s="13" t="inlineStr">
         <is>
           <t>選択のみ</t>
         </is>
       </c>
-      <c r="E16" s="9" t="n">
+      <c r="E16" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="F16" s="10" t="inlineStr">
+      <c r="F16" s="11" t="inlineStr">
         <is>
           <t>証憑必須制御の例外ルール（欠測時の代替手続き）が設計できず、稼働後に現場の入力が止まる。</t>
         </is>
       </c>
-      <c r="G16" s="10" t="inlineStr">
+      <c r="G16" s="11" t="inlineStr">
         <is>
           <t>入力制御・例外申請フロー</t>
         </is>
       </c>
-      <c r="H16" s="13" t="inlineStr">
+      <c r="H16" s="14" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="I16" s="10" t="inlineStr">
+      <c r="I16" s="11" t="inlineStr">
         <is>
           <t>「一部困難」とみなし例外申請フローを実装。稼働後の「添付できない」申告は当該拠点起因の運用課題として扱う。</t>
         </is>
       </c>
     </row>
     <row r="17" ht="52" customHeight="1">
-      <c r="A17" s="8" t="inlineStr">
+      <c r="A17" s="9" t="inlineStr">
         <is>
           <t>C-12</t>
         </is>
       </c>
-      <c r="B17" s="9" t="inlineStr">
+      <c r="B17" s="10" t="inlineStr">
         <is>
           <t>承認</t>
         </is>
       </c>
-      <c r="C17" s="10" t="inlineStr">
+      <c r="C17" s="11" t="inlineStr">
         <is>
           <t>データ報告への承認行為の有無</t>
         </is>
       </c>
-      <c r="D17" s="12" t="inlineStr">
+      <c r="D17" s="13" t="inlineStr">
         <is>
           <t>選択のみ</t>
         </is>
       </c>
-      <c r="E17" s="9" t="n">
+      <c r="E17" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="F17" s="10" t="inlineStr">
+      <c r="F17" s="11" t="inlineStr">
         <is>
           <t>承認階層の現状が不明だと多段階WFの段数・承認者マスタが設計できない。</t>
         </is>
       </c>
-      <c r="G17" s="10" t="inlineStr">
+      <c r="G17" s="11" t="inlineStr">
         <is>
           <t>承認ワークフロー設計</t>
         </is>
       </c>
-      <c r="H17" s="13" t="inlineStr">
+      <c r="H17" s="14" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="I17" s="10" t="inlineStr">
+      <c r="I17" s="11" t="inlineStr">
         <is>
           <t>「承認なし」とみなしゼロから承認体制を設計（当該拠点の業務変更負荷が最大化）。</t>
         </is>
       </c>
     </row>
     <row r="18" ht="52" customHeight="1">
-      <c r="A18" s="8" t="inlineStr">
+      <c r="A18" s="9" t="inlineStr">
         <is>
           <t>C-13</t>
         </is>
       </c>
-      <c r="B18" s="9" t="inlineStr">
+      <c r="B18" s="10" t="inlineStr">
         <is>
           <t>承認</t>
         </is>
       </c>
-      <c r="C18" s="10" t="inlineStr">
+      <c r="C18" s="11" t="inlineStr">
         <is>
           <t>データ変更履歴が残るか</t>
         </is>
       </c>
-      <c r="D18" s="12" t="inlineStr">
+      <c r="D18" s="13" t="inlineStr">
         <is>
           <t>選択のみ</t>
         </is>
       </c>
-      <c r="E18" s="9" t="n">
+      <c r="E18" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="F18" s="10" t="inlineStr">
+      <c r="F18" s="11" t="inlineStr">
         <is>
           <t>監査ログ要件（全項目履歴の要否）が決められない。保証の必須要件。</t>
         </is>
       </c>
-      <c r="G18" s="10" t="inlineStr">
+      <c r="G18" s="11" t="inlineStr">
         <is>
           <t>監査ログ・証跡要件</t>
         </is>
       </c>
-      <c r="H18" s="13" t="inlineStr">
+      <c r="H18" s="14" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="I18" s="10" t="inlineStr">
+      <c r="I18" s="11" t="inlineStr">
         <is>
           <t>「残らない（上書き）」とみなし全項目監査ログを必須化。</t>
         </is>
       </c>
     </row>
     <row r="19" ht="52" customHeight="1">
-      <c r="A19" s="8" t="inlineStr">
+      <c r="A19" s="9" t="inlineStr">
         <is>
           <t>C-14</t>
         </is>
       </c>
-      <c r="B19" s="9" t="inlineStr">
+      <c r="B19" s="10" t="inlineStr">
         <is>
           <t>IT</t>
         </is>
       </c>
-      <c r="C19" s="10" t="inlineStr">
+      <c r="C19" s="11" t="inlineStr">
         <is>
           <t>業務システムからのデータ出力（CSV/API）可否</t>
         </is>
       </c>
-      <c r="D19" s="12" t="inlineStr">
+      <c r="D19" s="13" t="inlineStr">
         <is>
           <t>選択のみ</t>
         </is>
       </c>
-      <c r="E19" s="9" t="n">
+      <c r="E19" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="F19" s="10" t="inlineStr">
+      <c r="F19" s="11" t="inlineStr">
         <is>
           <t>自動連携の対象範囲が確定できず、RFPの連携要件が「全件手入力」ベースになる。自動化によるROIも算定不能。</t>
         </is>
       </c>
-      <c r="G19" s="10" t="inlineStr">
+      <c r="G19" s="11" t="inlineStr">
         <is>
           <t>外部IF一覧・RFP連携要件・ROI</t>
         </is>
       </c>
-      <c r="H19" s="13" t="inlineStr">
+      <c r="H19" s="14" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="I19" s="10" t="inlineStr">
+      <c r="I19" s="11" t="inlineStr">
         <is>
           <t>「ほぼ不可」とみなし手入力ベースで設計。後日「出力可能」と判明した場合の連携追加費用は当該拠点起因。</t>
         </is>
       </c>
     </row>
     <row r="20" ht="52" customHeight="1">
-      <c r="A20" s="8" t="inlineStr">
+      <c r="A20" s="9" t="inlineStr">
         <is>
           <t>C-15</t>
         </is>
       </c>
-      <c r="B20" s="9" t="inlineStr">
+      <c r="B20" s="10" t="inlineStr">
         <is>
           <t>IT</t>
         </is>
       </c>
-      <c r="C20" s="10" t="inlineStr">
+      <c r="C20" s="11" t="inlineStr">
         <is>
           <t>電力・ガス会社のWeb明細サービス利用状況</t>
         </is>
       </c>
-      <c r="D20" s="12" t="inlineStr">
+      <c r="D20" s="13" t="inlineStr">
         <is>
           <t>選択のみ</t>
         </is>
       </c>
-      <c r="E20" s="9" t="n">
+      <c r="E20" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="F20" s="10" t="inlineStr">
+      <c r="F20" s="11" t="inlineStr">
         <is>
           <t>検針データ自動取込の対象から外れ、転記工数の削減効果を放棄することになる。</t>
         </is>
       </c>
-      <c r="G20" s="10" t="inlineStr">
+      <c r="G20" s="11" t="inlineStr">
         <is>
           <t>自動取込設計・ROI</t>
         </is>
       </c>
-      <c r="H20" s="11" t="inlineStr">
+      <c r="H20" s="12" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="I20" s="10" t="inlineStr">
+      <c r="I20" s="11" t="inlineStr">
         <is>
           <t>「利用不可」とみなす（自動化効果の逸失は当該拠点起因として記録）。</t>
         </is>
       </c>
     </row>
     <row r="21" ht="52" customHeight="1">
-      <c r="A21" s="8" t="inlineStr">
+      <c r="A21" s="9" t="inlineStr">
         <is>
           <t>C-16</t>
         </is>
       </c>
-      <c r="B21" s="9" t="inlineStr">
+      <c r="B21" s="10" t="inlineStr">
         <is>
           <t>IT</t>
         </is>
       </c>
-      <c r="C21" s="10" t="inlineStr">
+      <c r="C21" s="11" t="inlineStr">
         <is>
           <t>社外クラウド（SaaS）へのアクセス制限</t>
         </is>
       </c>
-      <c r="D21" s="12" t="inlineStr">
+      <c r="D21" s="13" t="inlineStr">
         <is>
           <t>選択のみ</t>
         </is>
       </c>
-      <c r="E21" s="9" t="n">
+      <c r="E21" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="F21" s="10" t="inlineStr">
+      <c r="F21" s="11" t="inlineStr">
         <is>
           <t>クラウドSaaS前提のアーキテクチャが成立するかという根本条件が未確認のままになる。稼働直前に「接続できない拠点」が発覚すると構成変更＝最大級の手戻り。</t>
         </is>
       </c>
-      <c r="G21" s="10" t="inlineStr">
+      <c r="G21" s="11" t="inlineStr">
         <is>
           <t>アーキテクチャ成立性・ネットワーク要件</t>
         </is>
       </c>
-      <c r="H21" s="13" t="inlineStr">
+      <c r="H21" s="14" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="I21" s="10" t="inlineStr">
+      <c r="I21" s="11" t="inlineStr">
         <is>
           <t>「原則不可の拠点あり」とみなしプロキシ/ホワイトリスト申請工程を計画化。稼働後の接続不可発覚は当該拠点起因。</t>
         </is>
       </c>
     </row>
     <row r="22" ht="52" customHeight="1">
-      <c r="A22" s="8" t="inlineStr">
+      <c r="A22" s="9" t="inlineStr">
         <is>
           <t>C-17</t>
         </is>
       </c>
-      <c r="B22" s="9" t="inlineStr">
+      <c r="B22" s="10" t="inlineStr">
         <is>
           <t>工数</t>
         </is>
       </c>
-      <c r="C22" s="10" t="inlineStr">
+      <c r="C22" s="11" t="inlineStr">
         <is>
           <t>非財務データ業務の月間工数</t>
         </is>
       </c>
-      <c r="D22" s="9" t="inlineStr">
+      <c r="D22" s="10" t="inlineStr">
         <is>
           <t>数値記入（工数集計）</t>
         </is>
       </c>
-      <c r="E22" s="9" t="n">
+      <c r="E22" s="10" t="n">
         <v>15</v>
       </c>
-      <c r="F22" s="10" t="inlineStr">
+      <c r="F22" s="11" t="inlineStr">
         <is>
           <t>ROI試算（工数削減効果）の分母が作れず、経営上申の定量根拠が失われる。投資判断が定性論に退化する。</t>
         </is>
       </c>
-      <c r="G22" s="10" t="inlineStr">
+      <c r="G22" s="11" t="inlineStr">
         <is>
           <t>ROI試算・経営上申資料</t>
         </is>
       </c>
-      <c r="H22" s="13" t="inlineStr">
+      <c r="H22" s="14" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="I22" s="10" t="inlineStr">
+      <c r="I22" s="11" t="inlineStr">
         <is>
           <t>当該拠点の工数削減効果をROIから除外（効果の過小計上は当該拠点起因として記録）。</t>
         </is>
       </c>
     </row>
     <row r="23" ht="52" customHeight="1">
-      <c r="A23" s="8" t="inlineStr">
+      <c r="A23" s="9" t="inlineStr">
         <is>
           <t>C-18</t>
         </is>
       </c>
-      <c r="B23" s="9" t="inlineStr">
+      <c r="B23" s="10" t="inlineStr">
         <is>
           <t>懸念</t>
         </is>
       </c>
-      <c r="C23" s="10" t="inlineStr">
+      <c r="C23" s="11" t="inlineStr">
         <is>
           <t>統制強化導入時の最大の懸念（任意）</t>
         </is>
       </c>
-      <c r="D23" s="9" t="inlineStr">
+      <c r="D23" s="10" t="inlineStr">
         <is>
           <t>短記述（任意）</t>
         </is>
       </c>
-      <c r="E23" s="9" t="n">
+      <c r="E23" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="F23" s="10" t="inlineStr">
+      <c r="F23" s="11" t="inlineStr">
         <is>
           <t>チェンジマネジメント設計の材料を失うが、要件の根幹には影響しない。</t>
         </is>
       </c>
-      <c r="G23" s="10" t="inlineStr">
+      <c r="G23" s="11" t="inlineStr">
         <is>
           <t>定着計画</t>
         </is>
       </c>
-      <c r="H23" s="14" t="inlineStr">
+      <c r="H23" s="15" t="inlineStr">
         <is>
           <t>低</t>
         </is>
       </c>
-      <c r="I23" s="10" t="inlineStr">
+      <c r="I23" s="11" t="inlineStr">
         <is>
           <t>「重大な懸念なし」とみなす。</t>
         </is>
       </c>
     </row>
     <row r="24" ht="52" customHeight="1">
-      <c r="A24" s="8" t="inlineStr">
+      <c r="A24" s="9" t="inlineStr">
         <is>
           <t>C-19</t>
         </is>
       </c>
-      <c r="B24" s="9" t="inlineStr">
+      <c r="B24" s="10" t="inlineStr">
         <is>
           <t>海外</t>
         </is>
       </c>
-      <c r="C24" s="10" t="inlineStr">
+      <c r="C24" s="11" t="inlineStr">
         <is>
           <t>現地語UI・現地サポートなしでの運用可否</t>
         </is>
       </c>
-      <c r="D24" s="12" t="inlineStr">
+      <c r="D24" s="13" t="inlineStr">
         <is>
           <t>選択のみ</t>
         </is>
       </c>
-      <c r="E24" s="9" t="n">
+      <c r="E24" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="F24" s="10" t="inlineStr">
+      <c r="F24" s="11" t="inlineStr">
         <is>
           <t>多言語要件の要否＝ベンダー選定の足切り条件が決められない。過剰なら対応ベンダーが絞られ価格上昇、過少なら現地が使えないシステムになる。</t>
         </is>
       </c>
-      <c r="G24" s="10" t="inlineStr">
+      <c r="G24" s="11" t="inlineStr">
         <is>
           <t>多言語要件・RFP必須要件</t>
         </is>
       </c>
-      <c r="H24" s="13" t="inlineStr">
+      <c r="H24" s="14" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="I24" s="10" t="inlineStr">
+      <c r="I24" s="11" t="inlineStr">
         <is>
           <t>「現地語UI必須」とみなしRFPに多言語要件を必須化（ベンダー絞り込み・価格上昇は未回答拠点起因）。</t>
         </is>
       </c>
     </row>
     <row r="25" ht="52" customHeight="1">
-      <c r="A25" s="8" t="inlineStr">
+      <c r="A25" s="9" t="inlineStr">
         <is>
           <t>C-20</t>
         </is>
       </c>
-      <c r="B25" s="9" t="inlineStr">
+      <c r="B25" s="10" t="inlineStr">
         <is>
           <t>手順</t>
         </is>
       </c>
-      <c r="C25" s="10" t="inlineStr">
+      <c r="C25" s="11" t="inlineStr">
         <is>
           <t>月次で最も時間がかかるステップ</t>
         </is>
       </c>
-      <c r="D25" s="12" t="inlineStr">
+      <c r="D25" s="13" t="inlineStr">
         <is>
           <t>選択のみ</t>
         </is>
       </c>
-      <c r="E25" s="9" t="n">
+      <c r="E25" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="F25" s="10" t="inlineStr">
+      <c r="F25" s="11" t="inlineStr">
         <is>
           <t>自動化投資の優先順位（Must/Should分類）が現場実態でなく推測ベースになる。</t>
         </is>
       </c>
-      <c r="G25" s="10" t="inlineStr">
+      <c r="G25" s="11" t="inlineStr">
         <is>
           <t>機能優先度・Must/Should分類</t>
         </is>
       </c>
-      <c r="H25" s="11" t="inlineStr">
+      <c r="H25" s="12" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="I25" s="10" t="inlineStr">
+      <c r="I25" s="11" t="inlineStr">
         <is>
           <t>全ステップ均等として設計（優先順位最適化を放棄）。</t>
         </is>
       </c>
     </row>
     <row r="26" ht="52" customHeight="1">
-      <c r="A26" s="8" t="inlineStr">
+      <c r="A26" s="9" t="inlineStr">
         <is>
           <t>C-21</t>
         </is>
       </c>
-      <c r="B26" s="9" t="inlineStr">
+      <c r="B26" s="10" t="inlineStr">
         <is>
           <t>手順</t>
         </is>
       </c>
-      <c r="C26" s="10" t="inlineStr">
+      <c r="C26" s="11" t="inlineStr">
         <is>
           <t>データ修正の方法（上書きか履歴付きか）</t>
         </is>
       </c>
-      <c r="D26" s="12" t="inlineStr">
+      <c r="D26" s="13" t="inlineStr">
         <is>
           <t>選択のみ</t>
         </is>
       </c>
-      <c r="E26" s="9" t="n">
+      <c r="E26" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="F26" s="10" t="inlineStr">
+      <c r="F26" s="11" t="inlineStr">
         <is>
           <t>上書き運用の拠点は過去データの信頼性に疑義。移行時のデータクレンジング要否が判断できない。</t>
         </is>
       </c>
-      <c r="G26" s="10" t="inlineStr">
+      <c r="G26" s="11" t="inlineStr">
         <is>
           <t>移行設計・修正WF</t>
         </is>
       </c>
-      <c r="H26" s="11" t="inlineStr">
+      <c r="H26" s="12" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="I26" s="10" t="inlineStr">
+      <c r="I26" s="11" t="inlineStr">
         <is>
           <t>「上書き（履歴なし）」とみなし移行データの検証タスクを追加。</t>
         </is>
       </c>
     </row>
     <row r="27" ht="52" customHeight="1">
-      <c r="A27" s="8" t="inlineStr">
+      <c r="A27" s="9" t="inlineStr">
         <is>
           <t>C-22</t>
         </is>
       </c>
-      <c r="B27" s="9" t="inlineStr">
+      <c r="B27" s="10" t="inlineStr">
         <is>
           <t>手順</t>
         </is>
       </c>
-      <c r="C27" s="10" t="inlineStr">
+      <c r="C27" s="11" t="inlineStr">
         <is>
           <t>年間で最も負荷が高い月</t>
         </is>
       </c>
-      <c r="D27" s="12" t="inlineStr">
+      <c r="D27" s="13" t="inlineStr">
         <is>
           <t>選択のみ</t>
         </is>
       </c>
-      <c r="E27" s="9" t="n">
+      <c r="E27" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="F27" s="10" t="inlineStr">
+      <c r="F27" s="11" t="inlineStr">
         <is>
           <t>ピーク時の同時アクセス・処理性能の要件根拠と、締切カレンダー設計ができない。</t>
         </is>
       </c>
-      <c r="G27" s="10" t="inlineStr">
+      <c r="G27" s="11" t="inlineStr">
         <is>
           <t>性能要件・年間スケジュール設計</t>
         </is>
       </c>
-      <c r="H27" s="11" t="inlineStr">
+      <c r="H27" s="12" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="I27" s="10" t="inlineStr">
+      <c r="I27" s="11" t="inlineStr">
         <is>
           <t>「1〜3月ピーク」とみなして設計。</t>
         </is>
       </c>
     </row>
     <row r="28" ht="52" customHeight="1">
-      <c r="A28" s="8" t="inlineStr">
+      <c r="A28" s="9" t="inlineStr">
         <is>
           <t>C-23</t>
         </is>
       </c>
-      <c r="B28" s="9" t="inlineStr">
+      <c r="B28" s="10" t="inlineStr">
         <is>
           <t>手順</t>
         </is>
       </c>
-      <c r="C28" s="10" t="inlineStr">
+      <c r="C28" s="11" t="inlineStr">
         <is>
           <t>抜け漏れ・遅延の主な原因</t>
         </is>
       </c>
-      <c r="D28" s="12" t="inlineStr">
+      <c r="D28" s="13" t="inlineStr">
         <is>
           <t>選択のみ</t>
         </is>
       </c>
-      <c r="E28" s="9" t="n">
+      <c r="E28" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="F28" s="10" t="inlineStr">
+      <c r="F28" s="11" t="inlineStr">
         <is>
           <t>督促・エスカレーション設計が原因に即さない汎用設計になる。</t>
         </is>
       </c>
-      <c r="G28" s="10" t="inlineStr">
+      <c r="G28" s="11" t="inlineStr">
         <is>
           <t>督促・エスカレーション設計</t>
         </is>
       </c>
-      <c r="H28" s="11" t="inlineStr">
+      <c r="H28" s="12" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="I28" s="10" t="inlineStr">
+      <c r="I28" s="11" t="inlineStr">
         <is>
           <t>「担当者不在＋請求書遅延」の複合とみなす。</t>
         </is>
       </c>
     </row>
     <row r="29" ht="52" customHeight="1">
-      <c r="A29" s="8" t="inlineStr">
+      <c r="A29" s="9" t="inlineStr">
         <is>
           <t>C-24</t>
         </is>
       </c>
-      <c r="B29" s="9" t="inlineStr">
+      <c r="B29" s="10" t="inlineStr">
         <is>
           <t>手順</t>
         </is>
       </c>
-      <c r="C29" s="10" t="inlineStr">
+      <c r="C29" s="11" t="inlineStr">
         <is>
           <t>過年度データの遡及修正経験</t>
         </is>
       </c>
-      <c r="D29" s="12" t="inlineStr">
+      <c r="D29" s="13" t="inlineStr">
         <is>
           <t>選択のみ</t>
         </is>
       </c>
-      <c r="E29" s="9" t="n">
+      <c r="E29" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="F29" s="10" t="inlineStr">
+      <c r="F29" s="11" t="inlineStr">
         <is>
           <t>遡及再計算機能（過年度ロック解除・再計算・再承認・訂正開示連携）の要否が決められない。</t>
         </is>
       </c>
-      <c r="G29" s="10" t="inlineStr">
+      <c r="G29" s="11" t="inlineStr">
         <is>
           <t>遡及再計算機能・訂正フロー</t>
         </is>
       </c>
-      <c r="H29" s="13" t="inlineStr">
+      <c r="H29" s="14" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="I29" s="10" t="inlineStr">
+      <c r="I29" s="11" t="inlineStr">
         <is>
           <t>「経験あり」とみなし遡及再計算を要件化（機能費用増）。</t>
         </is>
       </c>
     </row>
     <row r="30" ht="52" customHeight="1">
-      <c r="A30" s="8" t="inlineStr">
+      <c r="A30" s="9" t="inlineStr">
         <is>
           <t>C-25</t>
         </is>
       </c>
-      <c r="B30" s="9" t="inlineStr">
+      <c r="B30" s="10" t="inlineStr">
         <is>
           <t>算定</t>
         </is>
       </c>
-      <c r="C30" s="10" t="inlineStr">
+      <c r="C30" s="11" t="inlineStr">
         <is>
           <t>単位換算・按分計算の実施有無</t>
         </is>
       </c>
-      <c r="D30" s="12" t="inlineStr">
+      <c r="D30" s="13" t="inlineStr">
         <is>
           <t>選択のみ</t>
         </is>
       </c>
-      <c r="E30" s="9" t="n">
+      <c r="E30" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="F30" s="10" t="inlineStr">
+      <c r="F30" s="11" t="inlineStr">
         <is>
           <t>換算・按分エンジンの対象範囲が確定できない。</t>
         </is>
       </c>
-      <c r="G30" s="10" t="inlineStr">
+      <c r="G30" s="11" t="inlineStr">
         <is>
           <t>算定エンジン要件</t>
         </is>
       </c>
-      <c r="H30" s="13" t="inlineStr">
+      <c r="H30" s="14" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="I30" s="10" t="inlineStr">
+      <c r="I30" s="11" t="inlineStr">
         <is>
           <t>「両方実施」とみなしフル機能で設計（過剰なら費用増）。</t>
         </is>
       </c>
     </row>
     <row r="31" ht="52" customHeight="1">
-      <c r="A31" s="8" t="inlineStr">
+      <c r="A31" s="9" t="inlineStr">
         <is>
           <t>C-26</t>
         </is>
       </c>
-      <c r="B31" s="9" t="inlineStr">
+      <c r="B31" s="10" t="inlineStr">
         <is>
           <t>算定</t>
         </is>
       </c>
-      <c r="C31" s="10" t="inlineStr">
+      <c r="C31" s="11" t="inlineStr">
         <is>
           <t>推計・概算データの割合</t>
         </is>
       </c>
-      <c r="D31" s="12" t="inlineStr">
+      <c r="D31" s="13" t="inlineStr">
         <is>
           <t>選択のみ</t>
         </is>
       </c>
-      <c r="E31" s="9" t="n">
+      <c r="E31" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="F31" s="10" t="inlineStr">
+      <c r="F31" s="11" t="inlineStr">
         <is>
           <t>推計値管理機能（実測/推計フラグ・後日置換・遡及）の要否と、保証上の説明範囲が確定しない。推計割合が高いと保証で重点検証対象になる。</t>
         </is>
       </c>
-      <c r="G31" s="10" t="inlineStr">
+      <c r="G31" s="11" t="inlineStr">
         <is>
           <t>推計管理機能・保証対応</t>
         </is>
       </c>
-      <c r="H31" s="13" t="inlineStr">
+      <c r="H31" s="14" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="I31" s="10" t="inlineStr">
+      <c r="I31" s="11" t="inlineStr">
         <is>
           <t>「25%以上が推計」とみなし推計管理を必須化。保証時の指摘は当該拠点起因。</t>
         </is>
       </c>
     </row>
     <row r="32" ht="52" customHeight="1">
-      <c r="A32" s="8" t="inlineStr">
+      <c r="A32" s="9" t="inlineStr">
         <is>
           <t>C-27</t>
         </is>
       </c>
-      <c r="B32" s="9" t="inlineStr">
+      <c r="B32" s="10" t="inlineStr">
         <is>
           <t>算定</t>
         </is>
       </c>
-      <c r="C32" s="10" t="inlineStr">
+      <c r="C32" s="11" t="inlineStr">
         <is>
           <t>計算結果の妥当性チェック方法</t>
         </is>
       </c>
-      <c r="D32" s="12" t="inlineStr">
+      <c r="D32" s="13" t="inlineStr">
         <is>
           <t>選択のみ</t>
         </is>
       </c>
-      <c r="E32" s="9" t="n">
+      <c r="E32" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="F32" s="10" t="inlineStr">
+      <c r="F32" s="11" t="inlineStr">
         <is>
           <t>異常値検知ルール（前年比・原単位の閾値）の初期値が現場実態でなく机上設定になる。</t>
         </is>
       </c>
-      <c r="G32" s="10" t="inlineStr">
+      <c r="G32" s="11" t="inlineStr">
         <is>
           <t>異常値検知ルール</t>
         </is>
       </c>
-      <c r="H32" s="11" t="inlineStr">
+      <c r="H32" s="12" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="I32" s="10" t="inlineStr">
+      <c r="I32" s="11" t="inlineStr">
         <is>
           <t>「チェックなし」とみなし標準閾値から設計。</t>
         </is>
       </c>
     </row>
     <row r="33" ht="52" customHeight="1">
-      <c r="A33" s="8" t="inlineStr">
+      <c r="A33" s="9" t="inlineStr">
         <is>
           <t>C-28</t>
         </is>
       </c>
-      <c r="B33" s="9" t="inlineStr">
+      <c r="B33" s="10" t="inlineStr">
         <is>
           <t>証憑</t>
         </is>
       </c>
-      <c r="C33" s="10" t="inlineStr">
+      <c r="C33" s="11" t="inlineStr">
         <is>
           <t>個人PC・個人メールにしかない証憑の有無</t>
         </is>
       </c>
-      <c r="D33" s="12" t="inlineStr">
+      <c r="D33" s="13" t="inlineStr">
         <is>
           <t>選択のみ</t>
         </is>
       </c>
-      <c r="E33" s="9" t="n">
+      <c r="E33" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="F33" s="10" t="inlineStr">
+      <c r="F33" s="11" t="inlineStr">
         <is>
           <t>証憑消失リスクが放置される。移行前に退避しないと保証で証憑を提示できず、意見不能・重大指摘になり得る。</t>
         </is>
       </c>
-      <c r="G33" s="10" t="inlineStr">
+      <c r="G33" s="11" t="inlineStr">
         <is>
           <t>証憑救済・移行計画・保証対応</t>
         </is>
       </c>
-      <c r="H33" s="13" t="inlineStr">
+      <c r="H33" s="14" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="I33" s="10" t="inlineStr">
+      <c r="I33" s="11" t="inlineStr">
         <is>
           <t>「あり」とみなし移行前の証憑退避タスクを計画化。消失した証憑の責任は当該拠点起因。</t>
         </is>
       </c>
     </row>
     <row r="34" ht="52" customHeight="1">
-      <c r="A34" s="8" t="inlineStr">
+      <c r="A34" s="9" t="inlineStr">
         <is>
           <t>C-29</t>
         </is>
       </c>
-      <c r="B34" s="9" t="inlineStr">
+      <c r="B34" s="10" t="inlineStr">
         <is>
           <t>証憑</t>
         </is>
       </c>
-      <c r="C34" s="10" t="inlineStr">
+      <c r="C34" s="11" t="inlineStr">
         <is>
           <t>過去の監査・検証で証憑を探すのに要した時間</t>
         </is>
       </c>
-      <c r="D34" s="12" t="inlineStr">
+      <c r="D34" s="13" t="inlineStr">
         <is>
           <t>選択のみ</t>
         </is>
       </c>
-      <c r="E34" s="9" t="n">
+      <c r="E34" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="F34" s="10" t="inlineStr">
+      <c r="F34" s="11" t="inlineStr">
         <is>
           <t>検索性要件の根拠とROI（保証対応工数削減）の現状値が欠落する。</t>
         </is>
       </c>
-      <c r="G34" s="10" t="inlineStr">
+      <c r="G34" s="11" t="inlineStr">
         <is>
           <t>検索性要件・ROI</t>
         </is>
       </c>
-      <c r="H34" s="11" t="inlineStr">
+      <c r="H34" s="12" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="I34" s="10" t="inlineStr">
+      <c r="I34" s="11" t="inlineStr">
         <is>
           <t>「数日かかった」とみなす。</t>
         </is>
       </c>
     </row>
     <row r="35" ht="52" customHeight="1">
-      <c r="A35" s="8" t="inlineStr">
+      <c r="A35" s="9" t="inlineStr">
         <is>
           <t>C-30</t>
         </is>
       </c>
-      <c r="B35" s="9" t="inlineStr">
+      <c r="B35" s="10" t="inlineStr">
         <is>
           <t>承認</t>
         </is>
       </c>
-      <c r="C35" s="10" t="inlineStr">
+      <c r="C35" s="11" t="inlineStr">
         <is>
           <t>入力データのチェック実施者</t>
         </is>
       </c>
-      <c r="D35" s="12" t="inlineStr">
+      <c r="D35" s="13" t="inlineStr">
         <is>
           <t>選択のみ</t>
         </is>
       </c>
-      <c r="E35" s="9" t="n">
+      <c r="E35" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="F35" s="10" t="inlineStr">
+      <c r="F35" s="11" t="inlineStr">
         <is>
           <t>人的統制のどこをシステム統制に置換するかの設計根拠がない。統制過剰・過少の両リスク。</t>
         </is>
       </c>
-      <c r="G35" s="10" t="inlineStr">
+      <c r="G35" s="11" t="inlineStr">
         <is>
           <t>統制設計（キーコントロール配置）</t>
         </is>
       </c>
-      <c r="H35" s="13" t="inlineStr">
+      <c r="H35" s="14" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="I35" s="10" t="inlineStr">
+      <c r="I35" s="11" t="inlineStr">
         <is>
           <t>「自己チェックのみ」とみなし統制を厚めに設計（現場負荷増は当該拠点起因）。</t>
         </is>
       </c>
     </row>
     <row r="36" ht="52" customHeight="1">
-      <c r="A36" s="8" t="inlineStr">
+      <c r="A36" s="9" t="inlineStr">
         <is>
           <t>C-31</t>
         </is>
       </c>
-      <c r="B36" s="9" t="inlineStr">
+      <c r="B36" s="10" t="inlineStr">
         <is>
           <t>承認</t>
         </is>
       </c>
-      <c r="C36" s="10" t="inlineStr">
+      <c r="C36" s="11" t="inlineStr">
         <is>
           <t>確定・ロックの概念の有無</t>
         </is>
       </c>
-      <c r="D36" s="12" t="inlineStr">
+      <c r="D36" s="13" t="inlineStr">
         <is>
           <t>選択のみ</t>
         </is>
       </c>
-      <c r="E36" s="9" t="n">
+      <c r="E36" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="F36" s="10" t="inlineStr">
+      <c r="F36" s="11" t="inlineStr">
         <is>
           <t>ロック機能導入時の業務変更の大きさ（教育・移行負荷）が見積れない。</t>
         </is>
       </c>
-      <c r="G36" s="10" t="inlineStr">
+      <c r="G36" s="11" t="inlineStr">
         <is>
           <t>確定ロック機能・定着計画</t>
         </is>
       </c>
-      <c r="H36" s="11" t="inlineStr">
+      <c r="H36" s="12" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="I36" s="10" t="inlineStr">
+      <c r="I36" s="11" t="inlineStr">
         <is>
           <t>「概念なし」とみなし導入教育を計画化。</t>
         </is>
       </c>
     </row>
     <row r="37" ht="52" customHeight="1">
-      <c r="A37" s="8" t="inlineStr">
+      <c r="A37" s="9" t="inlineStr">
         <is>
           <t>C-32</t>
         </is>
       </c>
-      <c r="B37" s="9" t="inlineStr">
+      <c r="B37" s="10" t="inlineStr">
         <is>
           <t>承認</t>
         </is>
       </c>
-      <c r="C37" s="10" t="inlineStr">
+      <c r="C37" s="11" t="inlineStr">
         <is>
           <t>入力ファイル・システムのアクセス権</t>
         </is>
       </c>
-      <c r="D37" s="12" t="inlineStr">
+      <c r="D37" s="13" t="inlineStr">
         <is>
           <t>選択のみ</t>
         </is>
       </c>
-      <c r="E37" s="9" t="n">
+      <c r="E37" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="F37" s="10" t="inlineStr">
+      <c r="F37" s="11" t="inlineStr">
         <is>
           <t>権限マトリクスの現状が不明。「誰でも編集可」の拠点は改ざんリスクとして保証で指摘される。</t>
         </is>
       </c>
-      <c r="G37" s="10" t="inlineStr">
+      <c r="G37" s="11" t="inlineStr">
         <is>
           <t>権限設計・統制指摘リスク</t>
         </is>
       </c>
-      <c r="H37" s="13" t="inlineStr">
+      <c r="H37" s="14" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="I37" s="10" t="inlineStr">
+      <c r="I37" s="11" t="inlineStr">
         <is>
           <t>「誰でも編集可」とみなし統制上のリスク拠点として記録（指摘時の帰責明確化）。</t>
         </is>
       </c>
     </row>
     <row r="38" ht="52" customHeight="1">
-      <c r="A38" s="8" t="inlineStr">
+      <c r="A38" s="9" t="inlineStr">
         <is>
           <t>C-33</t>
         </is>
       </c>
-      <c r="B38" s="9" t="inlineStr">
+      <c r="B38" s="10" t="inlineStr">
         <is>
           <t>IT</t>
         </is>
       </c>
-      <c r="C38" s="10" t="inlineStr">
+      <c r="C38" s="11" t="inlineStr">
         <is>
           <t>拠点でのSAP利用状況</t>
         </is>
       </c>
-      <c r="D38" s="12" t="inlineStr">
+      <c r="D38" s="13" t="inlineStr">
         <is>
           <t>選択のみ</t>
         </is>
       </c>
-      <c r="E38" s="9" t="n">
+      <c r="E38" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="F38" s="10" t="inlineStr">
+      <c r="F38" s="11" t="inlineStr">
         <is>
           <t>SAP連携（直接連携の対象拠点range）が確定できず、連携設計から漏れる。後日判明時は連携追加＝追加費用。</t>
         </is>
       </c>
-      <c r="G38" s="10" t="inlineStr">
+      <c r="G38" s="11" t="inlineStr">
         <is>
           <t>SAP連携要件・外部IF設計</t>
         </is>
       </c>
-      <c r="H38" s="13" t="inlineStr">
+      <c r="H38" s="14" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="I38" s="10" t="inlineStr">
+      <c r="I38" s="11" t="inlineStr">
         <is>
           <t>「使っていない」とみなし連携対象外とする。後日の連携追加費用は当該拠点起因。</t>
         </is>
       </c>
     </row>
     <row r="39" ht="52" customHeight="1">
-      <c r="A39" s="8" t="inlineStr">
+      <c r="A39" s="9" t="inlineStr">
         <is>
           <t>C-34</t>
         </is>
       </c>
-      <c r="B39" s="9" t="inlineStr">
+      <c r="B39" s="10" t="inlineStr">
         <is>
           <t>IT</t>
         </is>
       </c>
-      <c r="C39" s="10" t="inlineStr">
+      <c r="C39" s="11" t="inlineStr">
         <is>
           <t>スマートメーター・BEMSの有無</t>
         </is>
       </c>
-      <c r="D39" s="12" t="inlineStr">
+      <c r="D39" s="13" t="inlineStr">
         <is>
           <t>選択のみ</t>
         </is>
       </c>
-      <c r="E39" s="9" t="n">
+      <c r="E39" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="F39" s="10" t="inlineStr">
+      <c r="F39" s="11" t="inlineStr">
         <is>
           <t>自動計測データ取込の対象から漏れ、手入力前提の設計になる。</t>
         </is>
       </c>
-      <c r="G39" s="10" t="inlineStr">
+      <c r="G39" s="11" t="inlineStr">
         <is>
           <t>自動取込設計</t>
         </is>
       </c>
-      <c r="H39" s="11" t="inlineStr">
+      <c r="H39" s="12" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="I39" s="10" t="inlineStr">
+      <c r="I39" s="11" t="inlineStr">
         <is>
           <t>「なし」とみなす（自動化機会の逸失は当該拠点起因）。</t>
         </is>
       </c>
     </row>
     <row r="40" ht="52" customHeight="1">
-      <c r="A40" s="8" t="inlineStr">
+      <c r="A40" s="9" t="inlineStr">
         <is>
           <t>C-35</t>
         </is>
       </c>
-      <c r="B40" s="9" t="inlineStr">
+      <c r="B40" s="10" t="inlineStr">
         <is>
           <t>IT</t>
         </is>
       </c>
-      <c r="C40" s="10" t="inlineStr">
+      <c r="C40" s="11" t="inlineStr">
         <is>
           <t>工場・現場のPC・ネットワーク環境</t>
         </is>
       </c>
-      <c r="D40" s="12" t="inlineStr">
+      <c r="D40" s="13" t="inlineStr">
         <is>
           <t>選択のみ</t>
         </is>
       </c>
-      <c r="E40" s="9" t="n">
+      <c r="E40" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="F40" s="10" t="inlineStr">
+      <c r="F40" s="11" t="inlineStr">
         <is>
           <t>入力UI要件（モバイル対応・オフライン入力）の要否が決められず、現場で使えないUIになるリスク。</t>
         </is>
       </c>
-      <c r="G40" s="10" t="inlineStr">
+      <c r="G40" s="11" t="inlineStr">
         <is>
           <t>入力UI要件・デバイス要件</t>
         </is>
       </c>
-      <c r="H40" s="11" t="inlineStr">
+      <c r="H40" s="12" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="I40" s="10" t="inlineStr">
+      <c r="I40" s="11" t="inlineStr">
         <is>
           <t>「PC利用可だがネットワーク制限あり」とみなす。</t>
         </is>
       </c>
     </row>
     <row r="41" ht="52" customHeight="1">
-      <c r="A41" s="8" t="inlineStr">
+      <c r="A41" s="9" t="inlineStr">
         <is>
           <t>C-36</t>
         </is>
       </c>
-      <c r="B41" s="9" t="inlineStr">
+      <c r="B41" s="10" t="inlineStr">
         <is>
           <t>IT</t>
         </is>
       </c>
-      <c r="C41" s="10" t="inlineStr">
+      <c r="C41" s="11" t="inlineStr">
         <is>
           <t>電子承認・ワークフローシステムの導入状況</t>
         </is>
       </c>
-      <c r="D41" s="12" t="inlineStr">
+      <c r="D41" s="13" t="inlineStr">
         <is>
           <t>選択のみ</t>
         </is>
       </c>
-      <c r="E41" s="9" t="n">
+      <c r="E41" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="F41" s="10" t="inlineStr">
+      <c r="F41" s="11" t="inlineStr">
         <is>
           <t>既存WFの流用可否が不明のまま新規実装し、二重投資になるリスク。</t>
         </is>
       </c>
-      <c r="G41" s="10" t="inlineStr">
+      <c r="G41" s="11" t="inlineStr">
         <is>
           <t>WF実装方式・投資効率</t>
         </is>
       </c>
-      <c r="H41" s="11" t="inlineStr">
+      <c r="H41" s="12" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="I41" s="10" t="inlineStr">
+      <c r="I41" s="11" t="inlineStr">
         <is>
           <t>「非財務には不向き」とみなし新規実装（二重投資リスクは未回答起因として記録）。</t>
         </is>
       </c>
     </row>
     <row r="42" ht="52" customHeight="1">
-      <c r="A42" s="8" t="inlineStr">
+      <c r="A42" s="9" t="inlineStr">
         <is>
           <t>C-37</t>
         </is>
       </c>
-      <c r="B42" s="9" t="inlineStr">
+      <c r="B42" s="10" t="inlineStr">
         <is>
           <t>工数</t>
         </is>
       </c>
-      <c r="C42" s="10" t="inlineStr">
+      <c r="C42" s="11" t="inlineStr">
         <is>
           <t>業務の属人化状況</t>
         </is>
       </c>
-      <c r="D42" s="12" t="inlineStr">
+      <c r="D42" s="13" t="inlineStr">
         <is>
           <t>選択のみ</t>
         </is>
       </c>
-      <c r="E42" s="9" t="n">
+      <c r="E42" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="F42" s="10" t="inlineStr">
+      <c r="F42" s="11" t="inlineStr">
         <is>
           <t>マニュアル・教育・機能化（フールプルーフ）の要件規模が決められない。</t>
         </is>
       </c>
-      <c r="G42" s="10" t="inlineStr">
+      <c r="G42" s="11" t="inlineStr">
         <is>
           <t>教育・マニュアル要件</t>
         </is>
       </c>
-      <c r="H42" s="11" t="inlineStr">
+      <c r="H42" s="12" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="I42" s="10" t="inlineStr">
+      <c r="I42" s="11" t="inlineStr">
         <is>
           <t>「一部属人化」とみなす。</t>
         </is>
       </c>
     </row>
     <row r="43" ht="17" customHeight="1">
-      <c r="A43" s="6" t="inlineStr">
+      <c r="A43" s="7" t="inlineStr">
         <is>
           <t>2. データ項目インベントリ（全拠点・最重要）</t>
         </is>
       </c>
-      <c r="B43" s="7" t="n"/>
-      <c r="C43" s="7" t="n"/>
-      <c r="D43" s="7" t="n"/>
-      <c r="E43" s="7" t="n"/>
-      <c r="F43" s="7" t="n"/>
-      <c r="G43" s="7" t="n"/>
-      <c r="H43" s="7" t="n"/>
-      <c r="I43" s="7" t="n"/>
+      <c r="B43" s="8" t="n"/>
+      <c r="C43" s="8" t="n"/>
+      <c r="D43" s="8" t="n"/>
+      <c r="E43" s="8" t="n"/>
+      <c r="F43" s="8" t="n"/>
+      <c r="G43" s="8" t="n"/>
+      <c r="H43" s="8" t="n"/>
+      <c r="I43" s="8" t="n"/>
     </row>
     <row r="44" ht="52" customHeight="1">
-      <c r="A44" s="8" t="inlineStr">
+      <c r="A44" s="9" t="inlineStr">
         <is>
           <t>INV-全行</t>
         </is>
       </c>
-      <c r="B44" s="9" t="inlineStr">
+      <c r="B44" s="10" t="inlineStr">
         <is>
           <t>インベントリ</t>
         </is>
       </c>
-      <c r="C44" s="10" t="inlineStr">
+      <c r="C44" s="11" t="inlineStr">
         <is>
           <t>報告データ項目の一覧（項目名・頻度・発生源・取得方法）</t>
         </is>
       </c>
-      <c r="D44" s="9" t="inlineStr">
+      <c r="D44" s="10" t="inlineStr">
         <is>
           <t>一覧記入（棚卸し）</t>
         </is>
       </c>
-      <c r="E44" s="9" t="n">
+      <c r="E44" s="10" t="n">
         <v>60</v>
       </c>
-      <c r="F44" s="10" t="inlineStr">
+      <c r="F44" s="11" t="inlineStr">
         <is>
           <t>収集項目マスタ・データモデル（項目・単位・頻度・発生源）が設計できず、RFPの規模前提（データ量・画面数・連携数）が示せない。ベンダー見積りが全面的に概算化し高値バッファが乗る。本調査の中で最も要件に直結するシート。</t>
         </is>
       </c>
-      <c r="G44" s="10" t="inlineStr">
+      <c r="G44" s="11" t="inlineStr">
         <is>
           <t>収集項目マスタ・データモデル・RFP規模前提</t>
         </is>
       </c>
-      <c r="H44" s="13" t="inlineStr">
+      <c r="H44" s="14" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="I44" s="10" t="inlineStr">
+      <c r="I44" s="11" t="inlineStr">
         <is>
           <t>事務局が既存報告様式（エコアシスト等）から項目を推定して確定する。拠点固有項目・ローカル報告項目の漏れが後日判明した場合の項目追加・改修費用は当該拠点起因。</t>
         </is>
       </c>
     </row>
     <row r="45" ht="17" customHeight="1">
-      <c r="A45" s="6" t="inlineStr">
+      <c r="A45" s="7" t="inlineStr">
         <is>
           <t>3. 手順とタイミング（選抜拠点ヒアリング・3-01〜3-18）</t>
         </is>
       </c>
-      <c r="B45" s="7" t="n"/>
-      <c r="C45" s="7" t="n"/>
-      <c r="D45" s="7" t="n"/>
-      <c r="E45" s="7" t="n"/>
-      <c r="F45" s="7" t="n"/>
-      <c r="G45" s="7" t="n"/>
-      <c r="H45" s="7" t="n"/>
-      <c r="I45" s="7" t="n"/>
+      <c r="B45" s="8" t="n"/>
+      <c r="C45" s="8" t="n"/>
+      <c r="D45" s="8" t="n"/>
+      <c r="E45" s="8" t="n"/>
+      <c r="F45" s="8" t="n"/>
+      <c r="G45" s="8" t="n"/>
+      <c r="H45" s="8" t="n"/>
+      <c r="I45" s="8" t="n"/>
     </row>
     <row r="46" ht="52" customHeight="1">
-      <c r="A46" s="8" t="inlineStr">
+      <c r="A46" s="9" t="inlineStr">
         <is>
           <t>3-01</t>
         </is>
       </c>
-      <c r="B46" s="9" t="inlineStr">
+      <c r="B46" s="10" t="inlineStr">
         <is>
           <t>手順書</t>
         </is>
       </c>
-      <c r="C46" s="10" t="inlineStr">
+      <c r="C46" s="11" t="inlineStr">
         <is>
           <t>手順書の形式・保管場所・更新時期</t>
         </is>
       </c>
-      <c r="D46" s="9" t="inlineStr">
+      <c r="D46" s="10" t="inlineStr">
         <is>
           <t>選択+補足〔ヒアリング〕</t>
         </is>
       </c>
-      <c r="E46" s="9" t="n">
+      <c r="E46" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="F46" s="10" t="inlineStr">
+      <c r="F46" s="11" t="inlineStr">
         <is>
           <t>C-01の詳細検証ができず、業務要件の文書化根拠が推測のままになる。</t>
         </is>
       </c>
-      <c r="G46" s="10" t="inlineStr">
+      <c r="G46" s="11" t="inlineStr">
         <is>
           <t>業務要件定義書</t>
         </is>
       </c>
-      <c r="H46" s="11" t="inlineStr">
+      <c r="H46" s="12" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="I46" s="10" t="inlineStr">
+      <c r="I46" s="11" t="inlineStr">
         <is>
           <t>「手順書なし」とみなす。</t>
         </is>
       </c>
     </row>
     <row r="47" ht="52" customHeight="1">
-      <c r="A47" s="8" t="inlineStr">
+      <c r="A47" s="9" t="inlineStr">
         <is>
           <t>3-02</t>
         </is>
       </c>
-      <c r="B47" s="9" t="inlineStr">
+      <c r="B47" s="10" t="inlineStr">
         <is>
           <t>手順書</t>
         </is>
       </c>
-      <c r="C47" s="10" t="inlineStr">
+      <c r="C47" s="11" t="inlineStr">
         <is>
           <t>手順書と実運用の乖離・独自の工夫</t>
         </is>
       </c>
-      <c r="D47" s="9" t="inlineStr">
+      <c r="D47" s="10" t="inlineStr">
         <is>
           <t>記述〔ヒアリング〕</t>
         </is>
       </c>
-      <c r="E47" s="9" t="n">
+      <c r="E47" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="F47" s="10" t="inlineStr">
+      <c r="F47" s="11" t="inlineStr">
         <is>
           <t>実運用に埋まった暗黙ルールを要件に反映できず、稼働後に「システムが実態と合わない」となる定着リスク。</t>
         </is>
       </c>
-      <c r="G47" s="10" t="inlineStr">
+      <c r="G47" s="11" t="inlineStr">
         <is>
           <t>To-Be業務フロー・定着計画</t>
         </is>
       </c>
-      <c r="H47" s="11" t="inlineStr">
+      <c r="H47" s="12" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="I47" s="10" t="inlineStr">
+      <c r="I47" s="11" t="inlineStr">
         <is>
           <t>「乖離あり」とみなし移行時の業務調査を追加。</t>
         </is>
       </c>
     </row>
     <row r="48" ht="52" customHeight="1">
-      <c r="A48" s="8" t="inlineStr">
+      <c r="A48" s="9" t="inlineStr">
         <is>
           <t>3-03</t>
         </is>
       </c>
-      <c r="B48" s="9" t="inlineStr">
+      <c r="B48" s="10" t="inlineStr">
         <is>
           <t>手順書</t>
         </is>
       </c>
-      <c r="C48" s="10" t="inlineStr">
+      <c r="C48" s="11" t="inlineStr">
         <is>
           <t>月次報告の作業ステップ（着手→完了）</t>
         </is>
       </c>
-      <c r="D48" s="9" t="inlineStr">
+      <c r="D48" s="10" t="inlineStr">
         <is>
           <t>記述〔ヒアリング〕</t>
         </is>
       </c>
-      <c r="E48" s="9" t="n">
+      <c r="E48" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="F48" s="10" t="inlineStr">
+      <c r="F48" s="11" t="inlineStr">
         <is>
           <t>To-Be業務フロー・画面遷移・入力ステップ設計の土台がなく、UI設計が机上になる。</t>
         </is>
       </c>
-      <c r="G48" s="10" t="inlineStr">
+      <c r="G48" s="11" t="inlineStr">
         <is>
           <t>To-Beフロー・画面設計</t>
         </is>
       </c>
-      <c r="H48" s="13" t="inlineStr">
+      <c r="H48" s="14" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="I48" s="10" t="inlineStr">
+      <c r="I48" s="11" t="inlineStr">
         <is>
           <t>標準テンプレートのフローを当該拠点に適用（適合しない場合の改修は当該拠点起因）。</t>
         </is>
       </c>
     </row>
     <row r="49" ht="52" customHeight="1">
-      <c r="A49" s="8" t="inlineStr">
+      <c r="A49" s="9" t="inlineStr">
         <is>
           <t>3-04</t>
         </is>
       </c>
-      <c r="B49" s="9" t="inlineStr">
+      <c r="B49" s="10" t="inlineStr">
         <is>
           <t>手順書</t>
         </is>
       </c>
-      <c r="C49" s="10" t="inlineStr">
+      <c r="C49" s="11" t="inlineStr">
         <is>
           <t>最も時間がかかる／神経を使うステップ</t>
         </is>
       </c>
-      <c r="D49" s="9" t="inlineStr">
+      <c r="D49" s="10" t="inlineStr">
         <is>
           <t>記述〔ヒアリング〕</t>
         </is>
       </c>
-      <c r="E49" s="9" t="n">
+      <c r="E49" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="F49" s="10" t="inlineStr">
+      <c r="F49" s="11" t="inlineStr">
         <is>
           <t>自動化・チェック機能の優先順位の根拠を失う。</t>
         </is>
       </c>
-      <c r="G49" s="10" t="inlineStr">
+      <c r="G49" s="11" t="inlineStr">
         <is>
           <t>機能優先度</t>
         </is>
       </c>
-      <c r="H49" s="11" t="inlineStr">
+      <c r="H49" s="12" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="I49" s="10" t="inlineStr">
+      <c r="I49" s="11" t="inlineStr">
         <is>
           <t>「転記・入力」が最重とみなす。</t>
         </is>
       </c>
     </row>
     <row r="50" ht="52" customHeight="1">
-      <c r="A50" s="8" t="inlineStr">
+      <c r="A50" s="9" t="inlineStr">
         <is>
           <t>3-05</t>
         </is>
       </c>
-      <c r="B50" s="9" t="inlineStr">
+      <c r="B50" s="10" t="inlineStr">
         <is>
           <t>タイミング</t>
         </is>
       </c>
-      <c r="C50" s="10" t="inlineStr">
+      <c r="C50" s="11" t="inlineStr">
         <is>
           <t>月次入力の実施タイミング</t>
         </is>
       </c>
-      <c r="D50" s="9" t="inlineStr">
+      <c r="D50" s="10" t="inlineStr">
         <is>
           <t>記述〔ヒアリング〕</t>
         </is>
       </c>
-      <c r="E50" s="9" t="n">
+      <c r="E50" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="F50" s="10" t="inlineStr">
+      <c r="F50" s="11" t="inlineStr">
         <is>
           <t>締め処理・リマインダーのカレンダー設計ができない。</t>
         </is>
       </c>
-      <c r="G50" s="10" t="inlineStr">
+      <c r="G50" s="11" t="inlineStr">
         <is>
           <t>締めスケジュール設計</t>
         </is>
       </c>
-      <c r="H50" s="11" t="inlineStr">
+      <c r="H50" s="12" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="I50" s="10" t="inlineStr">
+      <c r="I50" s="11" t="inlineStr">
         <is>
           <t>「月初5営業日以内」とみなす。</t>
         </is>
       </c>
     </row>
     <row r="51" ht="52" customHeight="1">
-      <c r="A51" s="8" t="inlineStr">
+      <c r="A51" s="9" t="inlineStr">
         <is>
           <t>3-06</t>
         </is>
       </c>
-      <c r="B51" s="9" t="inlineStr">
+      <c r="B51" s="10" t="inlineStr">
         <is>
           <t>タイミング</t>
         </is>
       </c>
-      <c r="C51" s="10" t="inlineStr">
+      <c r="C51" s="11" t="inlineStr">
         <is>
           <t>検針日・請求書到着と締切の時間差</t>
         </is>
       </c>
-      <c r="D51" s="9" t="inlineStr">
+      <c r="D51" s="10" t="inlineStr">
         <is>
           <t>記述〔ヒアリング〕</t>
         </is>
       </c>
-      <c r="E51" s="9" t="n">
+      <c r="E51" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="F51" s="10" t="inlineStr">
+      <c r="F51" s="11" t="inlineStr">
         <is>
           <t>締切設定が物理的に実現可能かが検証できず、実現不能な締切を要件化するリスク。</t>
         </is>
       </c>
-      <c r="G51" s="10" t="inlineStr">
+      <c r="G51" s="11" t="inlineStr">
         <is>
           <t>締切設計・推計値運用</t>
         </is>
       </c>
-      <c r="H51" s="13" t="inlineStr">
+      <c r="H51" s="14" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="I51" s="10" t="inlineStr">
+      <c r="I51" s="11" t="inlineStr">
         <is>
           <t>「間に合わない月あり」とみなし推計値入力→実績置換の機能を要件化。</t>
         </is>
       </c>
     </row>
     <row r="52" ht="52" customHeight="1">
-      <c r="A52" s="8" t="inlineStr">
+      <c r="A52" s="9" t="inlineStr">
         <is>
           <t>3-07</t>
         </is>
       </c>
-      <c r="B52" s="9" t="inlineStr">
+      <c r="B52" s="10" t="inlineStr">
         <is>
           <t>タイミング</t>
         </is>
       </c>
-      <c r="C52" s="10" t="inlineStr">
+      <c r="C52" s="11" t="inlineStr">
         <is>
           <t>期ズレの処理方法（詳細）</t>
         </is>
       </c>
-      <c r="D52" s="9" t="inlineStr">
+      <c r="D52" s="10" t="inlineStr">
         <is>
           <t>選択+補足〔ヒアリング〕</t>
         </is>
       </c>
-      <c r="E52" s="9" t="n">
+      <c r="E52" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="F52" s="10" t="inlineStr">
+      <c r="F52" s="11" t="inlineStr">
         <is>
           <t>C-03の詳細。按分エンジンの仕様（方式・端数処理）が確定できない。</t>
         </is>
       </c>
-      <c r="G52" s="10" t="inlineStr">
+      <c r="G52" s="11" t="inlineStr">
         <is>
           <t>算定エンジン仕様</t>
         </is>
       </c>
-      <c r="H52" s="13" t="inlineStr">
+      <c r="H52" s="14" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="I52" s="10" t="inlineStr">
+      <c r="I52" s="11" t="inlineStr">
         <is>
           <t>複数方式対応で設計（費用増）。</t>
         </is>
       </c>
     </row>
     <row r="53" ht="52" customHeight="1">
-      <c r="A53" s="8" t="inlineStr">
+      <c r="A53" s="9" t="inlineStr">
         <is>
           <t>3-08</t>
         </is>
       </c>
-      <c r="B53" s="9" t="inlineStr">
+      <c r="B53" s="10" t="inlineStr">
         <is>
           <t>タイミング</t>
         </is>
       </c>
-      <c r="C53" s="10" t="inlineStr">
+      <c r="C53" s="11" t="inlineStr">
         <is>
           <t>年間繁忙月と理由</t>
         </is>
       </c>
-      <c r="D53" s="9" t="inlineStr">
+      <c r="D53" s="10" t="inlineStr">
         <is>
           <t>記述〔ヒアリング〕</t>
         </is>
       </c>
-      <c r="E53" s="9" t="n">
+      <c r="E53" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="F53" s="10" t="inlineStr">
+      <c r="F53" s="11" t="inlineStr">
         <is>
           <t>C-22と同。性能・スケジュール設計の精度が下がる。</t>
         </is>
       </c>
-      <c r="G53" s="10" t="inlineStr">
+      <c r="G53" s="11" t="inlineStr">
         <is>
           <t>性能要件</t>
         </is>
       </c>
-      <c r="H53" s="14" t="inlineStr">
+      <c r="H53" s="15" t="inlineStr">
         <is>
           <t>低</t>
         </is>
       </c>
-      <c r="I53" s="10" t="inlineStr">
+      <c r="I53" s="11" t="inlineStr">
         <is>
           <t>「1〜3月」とみなす。</t>
         </is>
       </c>
     </row>
     <row r="54" ht="52" customHeight="1">
-      <c r="A54" s="8" t="inlineStr">
+      <c r="A54" s="9" t="inlineStr">
         <is>
           <t>3-09</t>
         </is>
       </c>
-      <c r="B54" s="9" t="inlineStr">
+      <c r="B54" s="10" t="inlineStr">
         <is>
           <t>修正</t>
         </is>
       </c>
-      <c r="C54" s="10" t="inlineStr">
+      <c r="C54" s="11" t="inlineStr">
         <is>
           <t>修正頻度と主な理由</t>
         </is>
       </c>
-      <c r="D54" s="9" t="inlineStr">
+      <c r="D54" s="10" t="inlineStr">
         <is>
           <t>選択+補足〔ヒアリング〕</t>
         </is>
       </c>
-      <c r="E54" s="9" t="n">
+      <c r="E54" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="F54" s="10" t="inlineStr">
+      <c r="F54" s="11" t="inlineStr">
         <is>
           <t>修正WFの分岐（理由別の承認レベル）が設計できない。</t>
         </is>
       </c>
-      <c r="G54" s="10" t="inlineStr">
+      <c r="G54" s="11" t="inlineStr">
         <is>
           <t>修正WF設計</t>
         </is>
       </c>
-      <c r="H54" s="11" t="inlineStr">
+      <c r="H54" s="12" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="I54" s="10" t="inlineStr">
+      <c r="I54" s="11" t="inlineStr">
         <is>
           <t>「毎月・理由多様」とみなす。</t>
         </is>
       </c>
     </row>
     <row r="55" ht="52" customHeight="1">
-      <c r="A55" s="8" t="inlineStr">
+      <c r="A55" s="9" t="inlineStr">
         <is>
           <t>3-10</t>
         </is>
       </c>
-      <c r="B55" s="9" t="inlineStr">
+      <c r="B55" s="10" t="inlineStr">
         <is>
           <t>修正</t>
         </is>
       </c>
-      <c r="C55" s="10" t="inlineStr">
+      <c r="C55" s="11" t="inlineStr">
         <is>
           <t>修正方法と連絡経路</t>
         </is>
       </c>
-      <c r="D55" s="9" t="inlineStr">
+      <c r="D55" s="10" t="inlineStr">
         <is>
           <t>記述〔ヒアリング〕</t>
         </is>
       </c>
-      <c r="E55" s="9" t="n">
+      <c r="E55" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="F55" s="10" t="inlineStr">
+      <c r="F55" s="11" t="inlineStr">
         <is>
           <t>差戻し・通知設計が実態と乖離するリスク。</t>
         </is>
       </c>
-      <c r="G55" s="10" t="inlineStr">
+      <c r="G55" s="11" t="inlineStr">
         <is>
           <t>差戻しフロー・通知設計</t>
         </is>
       </c>
-      <c r="H55" s="11" t="inlineStr">
+      <c r="H55" s="12" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="I55" s="10" t="inlineStr">
+      <c r="I55" s="11" t="inlineStr">
         <is>
           <t>「上書き・連絡なし」とみなす。</t>
         </is>
       </c>
     </row>
     <row r="56" ht="52" customHeight="1">
-      <c r="A56" s="8" t="inlineStr">
+      <c r="A56" s="9" t="inlineStr">
         <is>
           <t>3-11</t>
         </is>
       </c>
-      <c r="B56" s="9" t="inlineStr">
+      <c r="B56" s="10" t="inlineStr">
         <is>
           <t>修正</t>
         </is>
       </c>
-      <c r="C56" s="10" t="inlineStr">
+      <c r="C56" s="11" t="inlineStr">
         <is>
           <t>過年度遡及修正の作業実態</t>
         </is>
       </c>
-      <c r="D56" s="9" t="inlineStr">
+      <c r="D56" s="10" t="inlineStr">
         <is>
           <t>記述〔ヒアリング〕</t>
         </is>
       </c>
-      <c r="E56" s="9" t="n">
+      <c r="E56" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="F56" s="10" t="inlineStr">
+      <c r="F56" s="11" t="inlineStr">
         <is>
           <t>遡及再計算機能の深度（何年分・何を再計算するか）が決められない。</t>
         </is>
       </c>
-      <c r="G56" s="10" t="inlineStr">
+      <c r="G56" s="11" t="inlineStr">
         <is>
           <t>遡及再計算仕様</t>
         </is>
       </c>
-      <c r="H56" s="11" t="inlineStr">
+      <c r="H56" s="12" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="I56" s="10" t="inlineStr">
+      <c r="I56" s="11" t="inlineStr">
         <is>
           <t>「過去3年分の遡及が必要」とみなす。</t>
         </is>
       </c>
     </row>
     <row r="57" ht="52" customHeight="1">
-      <c r="A57" s="8" t="inlineStr">
+      <c r="A57" s="9" t="inlineStr">
         <is>
           <t>3-12</t>
         </is>
       </c>
-      <c r="B57" s="9" t="inlineStr">
+      <c r="B57" s="10" t="inlineStr">
         <is>
           <t>修正</t>
         </is>
       </c>
-      <c r="C57" s="10" t="inlineStr">
+      <c r="C57" s="11" t="inlineStr">
         <is>
           <t>欠測の典型パターンと穴埋め方法</t>
         </is>
       </c>
-      <c r="D57" s="9" t="inlineStr">
+      <c r="D57" s="10" t="inlineStr">
         <is>
           <t>記述〔ヒアリング〕</t>
         </is>
       </c>
-      <c r="E57" s="9" t="n">
+      <c r="E57" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="F57" s="10" t="inlineStr">
+      <c r="F57" s="11" t="inlineStr">
         <is>
           <t>欠測時の推計・代替ルール（例外設計）が現場実態と乖離し、稼働後に入力が止まる。</t>
         </is>
       </c>
-      <c r="G57" s="10" t="inlineStr">
+      <c r="G57" s="11" t="inlineStr">
         <is>
           <t>例外設計・推計ルール</t>
         </is>
       </c>
-      <c r="H57" s="13" t="inlineStr">
+      <c r="H57" s="14" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="I57" s="10" t="inlineStr">
+      <c r="I57" s="11" t="inlineStr">
         <is>
           <t>「メーター故障・請求遅延・担当不在の3パターンあり」とみなし例外フローを実装。</t>
         </is>
       </c>
     </row>
     <row r="58" ht="52" customHeight="1">
-      <c r="A58" s="8" t="inlineStr">
+      <c r="A58" s="9" t="inlineStr">
         <is>
           <t>3-13</t>
         </is>
       </c>
-      <c r="B58" s="9" t="inlineStr">
+      <c r="B58" s="10" t="inlineStr">
         <is>
           <t>修正</t>
         </is>
       </c>
-      <c r="C58" s="10" t="inlineStr">
+      <c r="C58" s="11" t="inlineStr">
         <is>
           <t>督促を受ける頻度と根本原因</t>
         </is>
       </c>
-      <c r="D58" s="9" t="inlineStr">
+      <c r="D58" s="10" t="inlineStr">
         <is>
           <t>記述〔ヒアリング〕</t>
         </is>
       </c>
-      <c r="E58" s="9" t="n">
+      <c r="E58" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="F58" s="10" t="inlineStr">
+      <c r="F58" s="11" t="inlineStr">
         <is>
           <t>督促自動化の設計根拠を失うが根幹には影響しない。</t>
         </is>
       </c>
-      <c r="G58" s="10" t="inlineStr">
+      <c r="G58" s="11" t="inlineStr">
         <is>
           <t>督促設計</t>
         </is>
       </c>
-      <c r="H58" s="14" t="inlineStr">
+      <c r="H58" s="15" t="inlineStr">
         <is>
           <t>低</t>
         </is>
       </c>
-      <c r="I58" s="10" t="inlineStr">
+      <c r="I58" s="11" t="inlineStr">
         <is>
           <t>「月1回以上」とみなす。</t>
         </is>
       </c>
     </row>
     <row r="59" ht="52" customHeight="1">
-      <c r="A59" s="8" t="inlineStr">
+      <c r="A59" s="9" t="inlineStr">
         <is>
           <t>3-14</t>
         </is>
       </c>
-      <c r="B59" s="9" t="inlineStr">
+      <c r="B59" s="10" t="inlineStr">
         <is>
           <t>特殊</t>
         </is>
       </c>
-      <c r="C59" s="10" t="inlineStr">
+      <c r="C59" s="11" t="inlineStr">
         <is>
           <t>メーター交換・契約変更時の処理手順</t>
         </is>
       </c>
-      <c r="D59" s="9" t="inlineStr">
+      <c r="D59" s="10" t="inlineStr">
         <is>
           <t>選択+補足〔ヒアリング〕</t>
         </is>
       </c>
-      <c r="E59" s="9" t="n">
+      <c r="E59" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="F59" s="10" t="inlineStr">
+      <c r="F59" s="11" t="inlineStr">
         <is>
           <t>設備・契約マスタの変更イベント処理（計測連続性の担保）が設計できない。</t>
         </is>
       </c>
-      <c r="G59" s="10" t="inlineStr">
+      <c r="G59" s="11" t="inlineStr">
         <is>
           <t>マスタ変更イベント処理</t>
         </is>
       </c>
-      <c r="H59" s="11" t="inlineStr">
+      <c r="H59" s="12" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="I59" s="10" t="inlineStr">
+      <c r="I59" s="11" t="inlineStr">
         <is>
           <t>「手順なし」とみなしシステム側でガイドを実装。</t>
         </is>
       </c>
     </row>
     <row r="60" ht="52" customHeight="1">
-      <c r="A60" s="8" t="inlineStr">
+      <c r="A60" s="9" t="inlineStr">
         <is>
           <t>3-15</t>
         </is>
       </c>
-      <c r="B60" s="9" t="inlineStr">
+      <c r="B60" s="10" t="inlineStr">
         <is>
           <t>特殊</t>
         </is>
       </c>
-      <c r="C60" s="10" t="inlineStr">
+      <c r="C60" s="11" t="inlineStr">
         <is>
           <t>組織変更・拠点統廃合時のデータ連続性</t>
         </is>
       </c>
-      <c r="D60" s="9" t="inlineStr">
+      <c r="D60" s="10" t="inlineStr">
         <is>
           <t>記述〔ヒアリング〕</t>
         </is>
       </c>
-      <c r="E60" s="9" t="n">
+      <c r="E60" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="F60" s="10" t="inlineStr">
+      <c r="F60" s="11" t="inlineStr">
         <is>
           <t>組織マスタの世代管理（比較可能性の担保）が設計できない。SSBJの過年度比較の根幹。</t>
         </is>
       </c>
-      <c r="G60" s="10" t="inlineStr">
+      <c r="G60" s="11" t="inlineStr">
         <is>
           <t>組織マスタ世代管理・比較可能性</t>
         </is>
       </c>
-      <c r="H60" s="13" t="inlineStr">
+      <c r="H60" s="14" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="I60" s="10" t="inlineStr">
+      <c r="I60" s="11" t="inlineStr">
         <is>
           <t>「連続性の担保なし」とみなし組織改編対応機能を必須化。</t>
         </is>
       </c>
     </row>
     <row r="61" ht="52" customHeight="1">
-      <c r="A61" s="8" t="inlineStr">
+      <c r="A61" s="9" t="inlineStr">
         <is>
           <t>3-16</t>
         </is>
       </c>
-      <c r="B61" s="9" t="inlineStr">
+      <c r="B61" s="10" t="inlineStr">
         <is>
           <t>特殊</t>
         </is>
       </c>
-      <c r="C61" s="10" t="inlineStr">
+      <c r="C61" s="11" t="inlineStr">
         <is>
           <t>複数報告間の数値不一致の有無と原因</t>
         </is>
       </c>
-      <c r="D61" s="9" t="inlineStr">
+      <c r="D61" s="10" t="inlineStr">
         <is>
           <t>選択+補足〔ヒアリング〕</t>
         </is>
       </c>
-      <c r="E61" s="9" t="n">
+      <c r="E61" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="F61" s="10" t="inlineStr">
+      <c r="F61" s="11" t="inlineStr">
         <is>
           <t>ワンソース・マルチユース要件の根拠を失い、開示数値の不整合リスク（最悪、訂正開示）が残置される。</t>
         </is>
       </c>
-      <c r="G61" s="10" t="inlineStr">
+      <c r="G61" s="11" t="inlineStr">
         <is>
           <t>一元データ管理・開示整合性</t>
         </is>
       </c>
-      <c r="H61" s="13" t="inlineStr">
+      <c r="H61" s="14" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="I61" s="10" t="inlineStr">
+      <c r="I61" s="11" t="inlineStr">
         <is>
           <t>「不一致あり」とみなし単一ソースからの多目的出力を必須要件化。</t>
         </is>
       </c>
     </row>
     <row r="62" ht="52" customHeight="1">
-      <c r="A62" s="8" t="inlineStr">
+      <c r="A62" s="9" t="inlineStr">
         <is>
           <t>3-17</t>
         </is>
       </c>
-      <c r="B62" s="9" t="inlineStr">
+      <c r="B62" s="10" t="inlineStr">
         <is>
           <t>特殊</t>
         </is>
       </c>
-      <c r="C62" s="10" t="inlineStr">
+      <c r="C62" s="11" t="inlineStr">
         <is>
           <t>担当者不在時の代替可否</t>
         </is>
       </c>
-      <c r="D62" s="9" t="inlineStr">
+      <c r="D62" s="10" t="inlineStr">
         <is>
           <t>選択+補足〔ヒアリング〕</t>
         </is>
       </c>
-      <c r="E62" s="9" t="n">
+      <c r="E62" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="F62" s="10" t="inlineStr">
+      <c r="F62" s="11" t="inlineStr">
         <is>
           <t>C-05と同。</t>
         </is>
       </c>
-      <c r="G62" s="10" t="inlineStr">
+      <c r="G62" s="11" t="inlineStr">
         <is>
           <t>代行設計</t>
         </is>
       </c>
-      <c r="H62" s="14" t="inlineStr">
+      <c r="H62" s="15" t="inlineStr">
         <is>
           <t>低</t>
         </is>
       </c>
-      <c r="I62" s="10" t="inlineStr">
+      <c r="I62" s="11" t="inlineStr">
         <is>
           <t>「止まる」とみなす。</t>
         </is>
       </c>
     </row>
     <row r="63" ht="52" customHeight="1">
-      <c r="A63" s="8" t="inlineStr">
+      <c r="A63" s="9" t="inlineStr">
         <is>
           <t>3-18</t>
         </is>
       </c>
-      <c r="B63" s="9" t="inlineStr">
+      <c r="B63" s="10" t="inlineStr">
         <is>
           <t>特殊</t>
         </is>
       </c>
-      <c r="C63" s="10" t="inlineStr">
+      <c r="C63" s="11" t="inlineStr">
         <is>
           <t>後任の独り立ちに要する期間</t>
         </is>
       </c>
-      <c r="D63" s="12" t="inlineStr">
+      <c r="D63" s="13" t="inlineStr">
         <is>
           <t>選択のみ〔ヒアリング〕</t>
         </is>
       </c>
-      <c r="E63" s="9" t="n">
+      <c r="E63" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="F63" s="10" t="inlineStr">
+      <c r="F63" s="11" t="inlineStr">
         <is>
           <t>教育・研修要件の規模が決められない。</t>
         </is>
       </c>
-      <c r="G63" s="10" t="inlineStr">
+      <c r="G63" s="11" t="inlineStr">
         <is>
           <t>教育要件</t>
         </is>
       </c>
-      <c r="H63" s="14" t="inlineStr">
+      <c r="H63" s="15" t="inlineStr">
         <is>
           <t>低</t>
         </is>
       </c>
-      <c r="I63" s="10" t="inlineStr">
+      <c r="I63" s="11" t="inlineStr">
         <is>
           <t>「3ヶ月」とみなす。</t>
         </is>
       </c>
     </row>
     <row r="64" ht="17" customHeight="1">
-      <c r="A64" s="6" t="inlineStr">
+      <c r="A64" s="7" t="inlineStr">
         <is>
           <t>4. 算定ロジックと係数（選抜拠点ヒアリング・4-01〜4-20）</t>
         </is>
       </c>
-      <c r="B64" s="7" t="n"/>
-      <c r="C64" s="7" t="n"/>
-      <c r="D64" s="7" t="n"/>
-      <c r="E64" s="7" t="n"/>
-      <c r="F64" s="7" t="n"/>
-      <c r="G64" s="7" t="n"/>
-      <c r="H64" s="7" t="n"/>
-      <c r="I64" s="7" t="n"/>
+      <c r="B64" s="8" t="n"/>
+      <c r="C64" s="8" t="n"/>
+      <c r="D64" s="8" t="n"/>
+      <c r="E64" s="8" t="n"/>
+      <c r="F64" s="8" t="n"/>
+      <c r="G64" s="8" t="n"/>
+      <c r="H64" s="8" t="n"/>
+      <c r="I64" s="8" t="n"/>
     </row>
     <row r="65" ht="52" customHeight="1">
-      <c r="A65" s="8" t="inlineStr">
+      <c r="A65" s="9" t="inlineStr">
         <is>
           <t>4-01</t>
         </is>
       </c>
-      <c r="B65" s="9" t="inlineStr">
+      <c r="B65" s="10" t="inlineStr">
         <is>
           <t>係数</t>
         </is>
       </c>
-      <c r="C65" s="10" t="inlineStr">
+      <c r="C65" s="11" t="inlineStr">
         <is>
           <t>拠点側の計算範囲（詳細）</t>
         </is>
       </c>
-      <c r="D65" s="9" t="inlineStr">
+      <c r="D65" s="10" t="inlineStr">
         <is>
           <t>選択+補足〔ヒアリング〕</t>
         </is>
       </c>
-      <c r="E65" s="9" t="n">
+      <c r="E65" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="F65" s="10" t="inlineStr">
+      <c r="F65" s="11" t="inlineStr">
         <is>
           <t>C-06の詳細。算定エンジンの機能配置が確定できない。</t>
         </is>
       </c>
-      <c r="G65" s="10" t="inlineStr">
+      <c r="G65" s="11" t="inlineStr">
         <is>
           <t>算定エンジン配置</t>
         </is>
       </c>
-      <c r="H65" s="13" t="inlineStr">
+      <c r="H65" s="14" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="I65" s="10" t="inlineStr">
+      <c r="I65" s="11" t="inlineStr">
         <is>
           <t>「拠点独自計算あり」とみなす。</t>
         </is>
       </c>
     </row>
     <row r="66" ht="52" customHeight="1">
-      <c r="A66" s="8" t="inlineStr">
+      <c r="A66" s="9" t="inlineStr">
         <is>
           <t>4-02</t>
         </is>
       </c>
-      <c r="B66" s="9" t="inlineStr">
+      <c r="B66" s="10" t="inlineStr">
         <is>
           <t>係数</t>
         </is>
       </c>
-      <c r="C66" s="10" t="inlineStr">
+      <c r="C66" s="11" t="inlineStr">
         <is>
           <t>使用係数の名称・出典・年度版の全量</t>
         </is>
       </c>
-      <c r="D66" s="9" t="inlineStr">
+      <c r="D66" s="10" t="inlineStr">
         <is>
           <t>記述〔ヒアリング〕</t>
         </is>
       </c>
-      <c r="E66" s="9" t="n">
+      <c r="E66" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="F66" s="10" t="inlineStr">
+      <c r="F66" s="11" t="inlineStr">
         <is>
           <t>係数マスタの初期データ（出典・版）が作れない。監査で「この数値の係数の出典は」と問われ回答不能＝保証の重大指摘。</t>
         </is>
       </c>
-      <c r="G66" s="10" t="inlineStr">
+      <c r="G66" s="11" t="inlineStr">
         <is>
           <t>係数マスタ初期整備・保証対応</t>
         </is>
       </c>
-      <c r="H66" s="13" t="inlineStr">
+      <c r="H66" s="14" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="I66" s="10" t="inlineStr">
+      <c r="I66" s="11" t="inlineStr">
         <is>
           <t>「出典不明の係数あり」とみなし、全係数を本社標準に強制置換（過年度との数値断絶は当該拠点起因）。</t>
         </is>
       </c>
     </row>
     <row r="67" ht="52" customHeight="1">
-      <c r="A67" s="8" t="inlineStr">
+      <c r="A67" s="9" t="inlineStr">
         <is>
           <t>4-03</t>
         </is>
       </c>
-      <c r="B67" s="9" t="inlineStr">
+      <c r="B67" s="10" t="inlineStr">
         <is>
           <t>係数</t>
         </is>
       </c>
-      <c r="C67" s="10" t="inlineStr">
+      <c r="C67" s="11" t="inlineStr">
         <is>
           <t>係数更新の連絡経路・適用時期・再計算有無</t>
         </is>
       </c>
-      <c r="D67" s="9" t="inlineStr">
+      <c r="D67" s="10" t="inlineStr">
         <is>
           <t>記述〔ヒアリング〕</t>
         </is>
       </c>
-      <c r="E67" s="9" t="n">
+      <c r="E67" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="F67" s="10" t="inlineStr">
+      <c r="F67" s="11" t="inlineStr">
         <is>
           <t>係数版管理・遡及再計算のトリガー設計ができず、係数改定のたびに手作業対応が残る。</t>
         </is>
       </c>
-      <c r="G67" s="10" t="inlineStr">
+      <c r="G67" s="11" t="inlineStr">
         <is>
           <t>係数版管理・自動再計算</t>
         </is>
       </c>
-      <c r="H67" s="13" t="inlineStr">
+      <c r="H67" s="14" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="I67" s="10" t="inlineStr">
+      <c r="I67" s="11" t="inlineStr">
         <is>
           <t>「連絡なし・再計算なし」とみなし自動再計算を必須化。</t>
         </is>
       </c>
     </row>
     <row r="68" ht="52" customHeight="1">
-      <c r="A68" s="8" t="inlineStr">
+      <c r="A68" s="9" t="inlineStr">
         <is>
           <t>4-04</t>
         </is>
       </c>
-      <c r="B68" s="9" t="inlineStr">
+      <c r="B68" s="10" t="inlineStr">
         <is>
           <t>係数</t>
         </is>
       </c>
-      <c r="C68" s="10" t="inlineStr">
+      <c r="C68" s="11" t="inlineStr">
         <is>
           <t>独自係数・独自ルールの内容と理由</t>
         </is>
       </c>
-      <c r="D68" s="9" t="inlineStr">
+      <c r="D68" s="10" t="inlineStr">
         <is>
           <t>選択+補足〔ヒアリング〕</t>
         </is>
       </c>
-      <c r="E68" s="9" t="n">
+      <c r="E68" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="F68" s="10" t="inlineStr">
+      <c r="F68" s="11" t="inlineStr">
         <is>
           <t>C-07の詳細。未申告の独自ルールは移行後の数値差異として顕在化。</t>
         </is>
       </c>
-      <c r="G68" s="10" t="inlineStr">
+      <c r="G68" s="11" t="inlineStr">
         <is>
           <t>係数マスタ・数値連続性</t>
         </is>
       </c>
-      <c r="H68" s="13" t="inlineStr">
+      <c r="H68" s="14" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="I68" s="10" t="inlineStr">
+      <c r="I68" s="11" t="inlineStr">
         <is>
           <t>「独自ルールあり・内容不明」とみなし本社標準に強制統一（差異発生は当該拠点起因）。</t>
         </is>
       </c>
     </row>
     <row r="69" ht="52" customHeight="1">
-      <c r="A69" s="8" t="inlineStr">
+      <c r="A69" s="9" t="inlineStr">
         <is>
           <t>4-05</t>
         </is>
       </c>
-      <c r="B69" s="9" t="inlineStr">
+      <c r="B69" s="10" t="inlineStr">
         <is>
           <t>換算</t>
         </is>
       </c>
-      <c r="C69" s="10" t="inlineStr">
+      <c r="C69" s="11" t="inlineStr">
         <is>
           <t>単位換算の場面と換算表の管理者</t>
         </is>
       </c>
-      <c r="D69" s="9" t="inlineStr">
+      <c r="D69" s="10" t="inlineStr">
         <is>
           <t>記述〔ヒアリング〕</t>
         </is>
       </c>
-      <c r="E69" s="9" t="n">
+      <c r="E69" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="F69" s="10" t="inlineStr">
+      <c r="F69" s="11" t="inlineStr">
         <is>
           <t>換算マスタ（換算係数・管理責任）が設計できない。</t>
         </is>
       </c>
-      <c r="G69" s="10" t="inlineStr">
+      <c r="G69" s="11" t="inlineStr">
         <is>
           <t>換算マスタ設計</t>
         </is>
       </c>
-      <c r="H69" s="11" t="inlineStr">
+      <c r="H69" s="12" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="I69" s="10" t="inlineStr">
+      <c r="I69" s="11" t="inlineStr">
         <is>
           <t>「管理者不在・Excel内に散在」とみなす。</t>
         </is>
       </c>
     </row>
     <row r="70" ht="52" customHeight="1">
-      <c r="A70" s="8" t="inlineStr">
+      <c r="A70" s="9" t="inlineStr">
         <is>
           <t>4-06</t>
         </is>
       </c>
-      <c r="B70" s="9" t="inlineStr">
+      <c r="B70" s="10" t="inlineStr">
         <is>
           <t>換算</t>
         </is>
       </c>
-      <c r="C70" s="10" t="inlineStr">
+      <c r="C70" s="11" t="inlineStr">
         <is>
           <t>按分計算の項目と按分基準の根拠</t>
         </is>
       </c>
-      <c r="D70" s="9" t="inlineStr">
+      <c r="D70" s="10" t="inlineStr">
         <is>
           <t>記述〔ヒアリング〕</t>
         </is>
       </c>
-      <c r="E70" s="9" t="n">
+      <c r="E70" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="F70" s="10" t="inlineStr">
+      <c r="F70" s="11" t="inlineStr">
         <is>
           <t>按分エンジンの仕様（基準マスタ）と、監査での按分根拠の説明可能性が確保できない。</t>
         </is>
       </c>
-      <c r="G70" s="10" t="inlineStr">
+      <c r="G70" s="11" t="inlineStr">
         <is>
           <t>按分エンジン・按分基準マスタ</t>
         </is>
       </c>
-      <c r="H70" s="13" t="inlineStr">
+      <c r="H70" s="14" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="I70" s="10" t="inlineStr">
+      <c r="I70" s="11" t="inlineStr">
         <is>
           <t>「根拠文書なし」とみなし按分基準の再整備タスクを計画化（工数は当該拠点負担）。</t>
         </is>
       </c>
     </row>
     <row r="71" ht="52" customHeight="1">
-      <c r="A71" s="8" t="inlineStr">
+      <c r="A71" s="9" t="inlineStr">
         <is>
           <t>4-07</t>
         </is>
       </c>
-      <c r="B71" s="9" t="inlineStr">
+      <c r="B71" s="10" t="inlineStr">
         <is>
           <t>換算</t>
         </is>
       </c>
-      <c r="C71" s="10" t="inlineStr">
+      <c r="C71" s="11" t="inlineStr">
         <is>
           <t>按分基準の見直し頻度・根拠資料</t>
         </is>
       </c>
-      <c r="D71" s="9" t="inlineStr">
+      <c r="D71" s="10" t="inlineStr">
         <is>
           <t>記述〔ヒアリング〕</t>
         </is>
       </c>
-      <c r="E71" s="9" t="n">
+      <c r="E71" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="F71" s="10" t="inlineStr">
+      <c r="F71" s="11" t="inlineStr">
         <is>
           <t>按分根拠の証跡化要件（版管理）が設計できない。</t>
         </is>
       </c>
-      <c r="G71" s="10" t="inlineStr">
+      <c r="G71" s="11" t="inlineStr">
         <is>
           <t>按分証跡要件</t>
         </is>
       </c>
-      <c r="H71" s="11" t="inlineStr">
+      <c r="H71" s="12" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="I71" s="10" t="inlineStr">
+      <c r="I71" s="11" t="inlineStr">
         <is>
           <t>「見直しなし・資料なし」とみなす。</t>
         </is>
       </c>
     </row>
     <row r="72" ht="52" customHeight="1">
-      <c r="A72" s="8" t="inlineStr">
+      <c r="A72" s="9" t="inlineStr">
         <is>
           <t>4-08</t>
         </is>
       </c>
-      <c r="B72" s="9" t="inlineStr">
+      <c r="B72" s="10" t="inlineStr">
         <is>
           <t>換算</t>
         </is>
       </c>
-      <c r="C72" s="10" t="inlineStr">
+      <c r="C72" s="11" t="inlineStr">
         <is>
           <t>推計項目・推計方法・割合</t>
         </is>
       </c>
-      <c r="D72" s="9" t="inlineStr">
+      <c r="D72" s="10" t="inlineStr">
         <is>
           <t>記述〔ヒアリング〕</t>
         </is>
       </c>
-      <c r="E72" s="9" t="n">
+      <c r="E72" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="F72" s="10" t="inlineStr">
+      <c r="F72" s="11" t="inlineStr">
         <is>
           <t>C-26の詳細。推計ロジックの標準化範囲が確定しない。</t>
         </is>
       </c>
-      <c r="G72" s="10" t="inlineStr">
+      <c r="G72" s="11" t="inlineStr">
         <is>
           <t>推計ロジック標準化</t>
         </is>
       </c>
-      <c r="H72" s="13" t="inlineStr">
+      <c r="H72" s="14" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="I72" s="10" t="inlineStr">
+      <c r="I72" s="11" t="inlineStr">
         <is>
           <t>「推計方法バラバラ」とみなし標準推計式を強制適用。</t>
         </is>
       </c>
     </row>
     <row r="73" ht="52" customHeight="1">
-      <c r="A73" s="8" t="inlineStr">
+      <c r="A73" s="9" t="inlineStr">
         <is>
           <t>4-09</t>
         </is>
       </c>
-      <c r="B73" s="9" t="inlineStr">
+      <c r="B73" s="10" t="inlineStr">
         <is>
           <t>ツール</t>
         </is>
       </c>
-      <c r="C73" s="10" t="inlineStr">
+      <c r="C73" s="11" t="inlineStr">
         <is>
           <t>計算Excelの作成者・在籍状況・説明可能者数</t>
         </is>
       </c>
-      <c r="D73" s="9" t="inlineStr">
+      <c r="D73" s="10" t="inlineStr">
         <is>
           <t>記述〔ヒアリング〕</t>
         </is>
       </c>
-      <c r="E73" s="9" t="n">
+      <c r="E73" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="F73" s="10" t="inlineStr">
+      <c r="F73" s="11" t="inlineStr">
         <is>
           <t>C-08の詳細。ロジック資産の仕分け（残す/移植/作り直す/捨てる）が不能になり、移植工数が確定しない。</t>
         </is>
       </c>
-      <c r="G73" s="10" t="inlineStr">
+      <c r="G73" s="11" t="inlineStr">
         <is>
           <t>ロジック移植計画</t>
         </is>
       </c>
-      <c r="H73" s="13" t="inlineStr">
+      <c r="H73" s="14" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="I73" s="10" t="inlineStr">
+      <c r="I73" s="11" t="inlineStr">
         <is>
           <t>「作成者退職・説明者ゼロ」とみなしロジック再構築（作り直し）費用を計上。</t>
         </is>
       </c>
     </row>
     <row r="74" ht="52" customHeight="1">
-      <c r="A74" s="8" t="inlineStr">
+      <c r="A74" s="9" t="inlineStr">
         <is>
           <t>4-10</t>
         </is>
       </c>
-      <c r="B74" s="9" t="inlineStr">
+      <c r="B74" s="10" t="inlineStr">
         <is>
           <t>ツール</t>
         </is>
       </c>
-      <c r="C74" s="10" t="inlineStr">
+      <c r="C74" s="11" t="inlineStr">
         <is>
           <t>計算Excelの修正対応可否</t>
         </is>
       </c>
-      <c r="D74" s="12" t="inlineStr">
+      <c r="D74" s="13" t="inlineStr">
         <is>
           <t>選択のみ〔ヒアリング〕</t>
         </is>
       </c>
-      <c r="E74" s="9" t="n">
+      <c r="E74" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="F74" s="10" t="inlineStr">
+      <c r="F74" s="11" t="inlineStr">
         <is>
           <t>同上の補完。要件定義中にロジック検証へ協力できる人がいるかの確認。</t>
         </is>
       </c>
-      <c r="G74" s="10" t="inlineStr">
+      <c r="G74" s="11" t="inlineStr">
         <is>
           <t>ロジック検証体制</t>
         </is>
       </c>
-      <c r="H74" s="11" t="inlineStr">
+      <c r="H74" s="12" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="I74" s="10" t="inlineStr">
+      <c r="I74" s="11" t="inlineStr">
         <is>
           <t>「できない」とみなす。</t>
         </is>
       </c>
     </row>
     <row r="75" ht="52" customHeight="1">
-      <c r="A75" s="8" t="inlineStr">
+      <c r="A75" s="9" t="inlineStr">
         <is>
           <t>4-11</t>
         </is>
       </c>
-      <c r="B75" s="9" t="inlineStr">
+      <c r="B75" s="10" t="inlineStr">
         <is>
           <t>ツール</t>
         </is>
       </c>
-      <c r="C75" s="10" t="inlineStr">
+      <c r="C75" s="11" t="inlineStr">
         <is>
           <t>計算結果の妥当性判断方法</t>
         </is>
       </c>
-      <c r="D75" s="9" t="inlineStr">
+      <c r="D75" s="10" t="inlineStr">
         <is>
           <t>記述〔ヒアリング〕</t>
         </is>
       </c>
-      <c r="E75" s="9" t="n">
+      <c r="E75" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="F75" s="10" t="inlineStr">
+      <c r="F75" s="11" t="inlineStr">
         <is>
           <t>異常値検知の閾値・確認手順の初期値が机上設定になる。</t>
         </is>
       </c>
-      <c r="G75" s="10" t="inlineStr">
+      <c r="G75" s="11" t="inlineStr">
         <is>
           <t>異常値検知設計</t>
         </is>
       </c>
-      <c r="H75" s="11" t="inlineStr">
+      <c r="H75" s="12" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="I75" s="10" t="inlineStr">
+      <c r="I75" s="11" t="inlineStr">
         <is>
           <t>「目視・感覚のみ」とみなす。</t>
         </is>
       </c>
     </row>
     <row r="76" ht="52" customHeight="1">
-      <c r="A76" s="8" t="inlineStr">
+      <c r="A76" s="9" t="inlineStr">
         <is>
           <t>4-12</t>
         </is>
       </c>
-      <c r="B76" s="9" t="inlineStr">
+      <c r="B76" s="10" t="inlineStr">
         <is>
           <t>ツール</t>
         </is>
       </c>
-      <c r="C76" s="10" t="inlineStr">
+      <c r="C76" s="11" t="inlineStr">
         <is>
           <t>計算ファイルのバージョン管理</t>
         </is>
       </c>
-      <c r="D76" s="9" t="inlineStr">
+      <c r="D76" s="10" t="inlineStr">
         <is>
           <t>記述〔ヒアリング〕</t>
         </is>
       </c>
-      <c r="E76" s="9" t="n">
+      <c r="E76" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="F76" s="10" t="inlineStr">
+      <c r="F76" s="11" t="inlineStr">
         <is>
           <t>移行時に「正版」を特定できず、誤った版のロジックをシステム化するリスク。過年度数値の再現もできない。</t>
         </is>
       </c>
-      <c r="G76" s="10" t="inlineStr">
+      <c r="G76" s="11" t="inlineStr">
         <is>
           <t>移行時の正版特定・数値再現性</t>
         </is>
       </c>
-      <c r="H76" s="13" t="inlineStr">
+      <c r="H76" s="14" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="I76" s="10" t="inlineStr">
+      <c r="I76" s="11" t="inlineStr">
         <is>
           <t>「版管理なし」とみなし移行時のロジック検証（正版特定）タスクを計画化。</t>
         </is>
       </c>
     </row>
     <row r="77" ht="52" customHeight="1">
-      <c r="A77" s="8" t="inlineStr">
+      <c r="A77" s="9" t="inlineStr">
         <is>
           <t>4-13</t>
         </is>
       </c>
-      <c r="B77" s="9" t="inlineStr">
+      <c r="B77" s="10" t="inlineStr">
         <is>
           <t>領域</t>
         </is>
       </c>
-      <c r="C77" s="10" t="inlineStr">
+      <c r="C77" s="11" t="inlineStr">
         <is>
           <t>小口排出源（社有車・非常用発電機等）の網羅状況</t>
         </is>
       </c>
-      <c r="D77" s="9" t="inlineStr">
+      <c r="D77" s="10" t="inlineStr">
         <is>
           <t>選択+補足〔ヒアリング〕</t>
         </is>
       </c>
-      <c r="E77" s="9" t="n">
+      <c r="E77" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="F77" s="10" t="inlineStr">
+      <c r="F77" s="11" t="inlineStr">
         <is>
           <t>排出源の網羅性＝保証の完全性要件が確認できない。バウンダリの漏れは保証の指摘対象。</t>
         </is>
       </c>
-      <c r="G77" s="10" t="inlineStr">
+      <c r="G77" s="11" t="inlineStr">
         <is>
           <t>バウンダリ設計・完全性</t>
         </is>
       </c>
-      <c r="H77" s="13" t="inlineStr">
+      <c r="H77" s="14" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="I77" s="10" t="inlineStr">
+      <c r="I77" s="11" t="inlineStr">
         <is>
           <t>「漏れあり」とみなし網羅性再調査タスクを計画化（工数は当該拠点負担）。</t>
         </is>
       </c>
     </row>
     <row r="78" ht="52" customHeight="1">
-      <c r="A78" s="8" t="inlineStr">
+      <c r="A78" s="9" t="inlineStr">
         <is>
           <t>4-14</t>
         </is>
       </c>
-      <c r="B78" s="9" t="inlineStr">
+      <c r="B78" s="10" t="inlineStr">
         <is>
           <t>領域</t>
         </is>
       </c>
-      <c r="C78" s="10" t="inlineStr">
+      <c r="C78" s="11" t="inlineStr">
         <is>
           <t>冷媒（フロン類）の把握方法</t>
         </is>
       </c>
-      <c r="D78" s="9" t="inlineStr">
+      <c r="D78" s="10" t="inlineStr">
         <is>
           <t>記述〔ヒアリング〕</t>
         </is>
       </c>
-      <c r="E78" s="9" t="n">
+      <c r="E78" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="F78" s="10" t="inlineStr">
+      <c r="F78" s="11" t="inlineStr">
         <is>
           <t>冷媒管理機能（充填・漏えい記録）の要否とデータ源が決められない。</t>
         </is>
       </c>
-      <c r="G78" s="10" t="inlineStr">
+      <c r="G78" s="11" t="inlineStr">
         <is>
           <t>冷媒管理機能</t>
         </is>
       </c>
-      <c r="H78" s="11" t="inlineStr">
+      <c r="H78" s="12" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="I78" s="10" t="inlineStr">
+      <c r="I78" s="11" t="inlineStr">
         <is>
           <t>「点検記録から手動転記」とみなす。</t>
         </is>
       </c>
     </row>
     <row r="79" ht="52" customHeight="1">
-      <c r="A79" s="8" t="inlineStr">
+      <c r="A79" s="9" t="inlineStr">
         <is>
           <t>4-15</t>
         </is>
       </c>
-      <c r="B79" s="9" t="inlineStr">
+      <c r="B79" s="10" t="inlineStr">
         <is>
           <t>領域</t>
         </is>
       </c>
-      <c r="C79" s="10" t="inlineStr">
+      <c r="C79" s="11" t="inlineStr">
         <is>
           <t>水の取水源別計測・排水把握</t>
         </is>
       </c>
-      <c r="D79" s="9" t="inlineStr">
+      <c r="D79" s="10" t="inlineStr">
         <is>
           <t>記述〔ヒアリング〕</t>
         </is>
       </c>
-      <c r="E79" s="9" t="n">
+      <c r="E79" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="F79" s="10" t="inlineStr">
+      <c r="F79" s="11" t="inlineStr">
         <is>
           <t>水関連のデータモデル（実測/推計区分）が設計できない。</t>
         </is>
       </c>
-      <c r="G79" s="10" t="inlineStr">
+      <c r="G79" s="11" t="inlineStr">
         <is>
           <t>水データモデル</t>
         </is>
       </c>
-      <c r="H79" s="11" t="inlineStr">
+      <c r="H79" s="12" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="I79" s="10" t="inlineStr">
+      <c r="I79" s="11" t="inlineStr">
         <is>
           <t>「上水以外は推計」とみなす。</t>
         </is>
       </c>
     </row>
     <row r="80" ht="52" customHeight="1">
-      <c r="A80" s="8" t="inlineStr">
+      <c r="A80" s="9" t="inlineStr">
         <is>
           <t>4-16</t>
         </is>
       </c>
-      <c r="B80" s="9" t="inlineStr">
+      <c r="B80" s="10" t="inlineStr">
         <is>
           <t>領域</t>
         </is>
       </c>
-      <c r="C80" s="10" t="inlineStr">
+      <c r="C80" s="11" t="inlineStr">
         <is>
           <t>廃棄物のマニフェスト照合有無</t>
         </is>
       </c>
-      <c r="D80" s="9" t="inlineStr">
+      <c r="D80" s="10" t="inlineStr">
         <is>
           <t>選択+補足〔ヒアリング〕</t>
         </is>
       </c>
-      <c r="E80" s="9" t="n">
+      <c r="E80" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="F80" s="10" t="inlineStr">
+      <c r="F80" s="11" t="inlineStr">
         <is>
           <t>マニフェスト連携・照合機能の要否が決められない。</t>
         </is>
       </c>
-      <c r="G80" s="10" t="inlineStr">
+      <c r="G80" s="11" t="inlineStr">
         <is>
           <t>廃棄物照合機能</t>
         </is>
       </c>
-      <c r="H80" s="11" t="inlineStr">
+      <c r="H80" s="12" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="I80" s="10" t="inlineStr">
+      <c r="I80" s="11" t="inlineStr">
         <is>
           <t>「照合なし」とみなす。</t>
         </is>
       </c>
     </row>
     <row r="81" ht="52" customHeight="1">
-      <c r="A81" s="8" t="inlineStr">
+      <c r="A81" s="9" t="inlineStr">
         <is>
           <t>4-17</t>
         </is>
       </c>
-      <c r="B81" s="9" t="inlineStr">
+      <c r="B81" s="10" t="inlineStr">
         <is>
           <t>領域</t>
         </is>
       </c>
-      <c r="C81" s="10" t="inlineStr">
+      <c r="C81" s="11" t="inlineStr">
         <is>
           <t>Scope3関連データの提供可能範囲</t>
         </is>
       </c>
-      <c r="D81" s="9" t="inlineStr">
+      <c r="D81" s="10" t="inlineStr">
         <is>
           <t>記述〔ヒアリング〕</t>
         </is>
       </c>
-      <c r="E81" s="9" t="n">
+      <c r="E81" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="F81" s="10" t="inlineStr">
+      <c r="F81" s="11" t="inlineStr">
         <is>
           <t>Scope3一次データ化（攻めの柱）の実現可能性が検証できず、拡張性要件が机上になる。</t>
         </is>
       </c>
-      <c r="G81" s="10" t="inlineStr">
+      <c r="G81" s="11" t="inlineStr">
         <is>
           <t>Scope3拡張要件（攻め）</t>
         </is>
       </c>
-      <c r="H81" s="13" t="inlineStr">
+      <c r="H81" s="14" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="I81" s="10" t="inlineStr">
+      <c r="I81" s="11" t="inlineStr">
         <is>
           <t>「提供不可」とみなしScope3拡張は将来要件へ後退（攻めの効果縮小は当該拠点起因として記録）。</t>
         </is>
       </c>
     </row>
     <row r="82" ht="52" customHeight="1">
-      <c r="A82" s="8" t="inlineStr">
+      <c r="A82" s="9" t="inlineStr">
         <is>
           <t>4-18</t>
         </is>
       </c>
-      <c r="B82" s="9" t="inlineStr">
+      <c r="B82" s="10" t="inlineStr">
         <is>
           <t>領域</t>
         </is>
       </c>
-      <c r="C82" s="10" t="inlineStr">
+      <c r="C82" s="11" t="inlineStr">
         <is>
           <t>製品LCA用データの関与・粒度</t>
         </is>
       </c>
-      <c r="D82" s="9" t="inlineStr">
+      <c r="D82" s="10" t="inlineStr">
         <is>
           <t>記述〔ヒアリング〕</t>
         </is>
       </c>
-      <c r="E82" s="9" t="n">
+      <c r="E82" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="F82" s="10" t="inlineStr">
+      <c r="F82" s="11" t="inlineStr">
         <is>
           <t>CFP即応（攻めユースケース第1候補）に必要な製品別データ構造（生産量×組成×包材）の実現可能性が確認できない。</t>
         </is>
       </c>
-      <c r="G82" s="10" t="inlineStr">
+      <c r="G82" s="11" t="inlineStr">
         <is>
           <t>CFP対応データ構造（攻め）</t>
         </is>
       </c>
-      <c r="H82" s="13" t="inlineStr">
+      <c r="H82" s="14" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="I82" s="10" t="inlineStr">
+      <c r="I82" s="11" t="inlineStr">
         <is>
           <t>「提供不可」とみなしCFP即応要件を縮小（受注対応力の逸失として記録）。</t>
         </is>
       </c>
     </row>
     <row r="83" ht="52" customHeight="1">
-      <c r="A83" s="8" t="inlineStr">
+      <c r="A83" s="9" t="inlineStr">
         <is>
           <t>4-19</t>
         </is>
       </c>
-      <c r="B83" s="9" t="inlineStr">
+      <c r="B83" s="10" t="inlineStr">
         <is>
           <t>領域</t>
         </is>
       </c>
-      <c r="C83" s="10" t="inlineStr">
+      <c r="C83" s="11" t="inlineStr">
         <is>
           <t>人事・労安データの定義の揺れ</t>
         </is>
       </c>
-      <c r="D83" s="9" t="inlineStr">
+      <c r="D83" s="10" t="inlineStr">
         <is>
           <t>記述〔ヒアリング〕</t>
         </is>
       </c>
-      <c r="E83" s="9" t="n">
+      <c r="E83" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="F83" s="10" t="inlineStr">
+      <c r="F83" s="11" t="inlineStr">
         <is>
           <t>S（社会）系データの定義標準化の対象が特定できず、拠点解釈のまま要件が固まる。</t>
         </is>
       </c>
-      <c r="G83" s="10" t="inlineStr">
+      <c r="G83" s="11" t="inlineStr">
         <is>
           <t>S系データ定義標準化</t>
         </is>
       </c>
-      <c r="H83" s="11" t="inlineStr">
+      <c r="H83" s="12" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="I83" s="10" t="inlineStr">
+      <c r="I83" s="11" t="inlineStr">
         <is>
           <t>「定義揺れあり」とみなし本社定義を強制適用。</t>
         </is>
       </c>
     </row>
     <row r="84" ht="52" customHeight="1">
-      <c r="A84" s="8" t="inlineStr">
+      <c r="A84" s="9" t="inlineStr">
         <is>
           <t>4-20</t>
         </is>
       </c>
-      <c r="B84" s="9" t="inlineStr">
+      <c r="B84" s="10" t="inlineStr">
         <is>
           <t>領域</t>
         </is>
       </c>
-      <c r="C84" s="10" t="inlineStr">
+      <c r="C84" s="11" t="inlineStr">
         <is>
           <t>本社算定ルールで曖昧・矛盾と感じる点</t>
         </is>
       </c>
-      <c r="D84" s="9" t="inlineStr">
+      <c r="D84" s="10" t="inlineStr">
         <is>
           <t>記述〔ヒアリング〕</t>
         </is>
       </c>
-      <c r="E84" s="9" t="n">
+      <c r="E84" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="F84" s="10" t="inlineStr">
+      <c r="F84" s="11" t="inlineStr">
         <is>
           <t>ルール標準化のバックログ（難所①の検討リスト）が作れず、曖昧なルールがそのままシステム要件に転写される。</t>
         </is>
       </c>
-      <c r="G84" s="10" t="inlineStr">
+      <c r="G84" s="11" t="inlineStr">
         <is>
           <t>算定ルール標準化・難所①</t>
         </is>
       </c>
-      <c r="H84" s="13" t="inlineStr">
+      <c r="H84" s="14" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="I84" s="10" t="inlineStr">
+      <c r="I84" s="11" t="inlineStr">
         <is>
           <t>「曖昧箇所なし」とみなしルールを現行のまま確定（後日の解釈揺れによる改修は未回答拠点起因）。</t>
         </is>
       </c>
     </row>
     <row r="85" ht="17" customHeight="1">
-      <c r="A85" s="6" t="inlineStr">
+      <c r="A85" s="7" t="inlineStr">
         <is>
           <t>5. 証憑と記録管理（選抜拠点ヒアリング・5-01〜5-14）</t>
         </is>
       </c>
-      <c r="B85" s="7" t="n"/>
-      <c r="C85" s="7" t="n"/>
-      <c r="D85" s="7" t="n"/>
-      <c r="E85" s="7" t="n"/>
-      <c r="F85" s="7" t="n"/>
-      <c r="G85" s="7" t="n"/>
-      <c r="H85" s="7" t="n"/>
-      <c r="I85" s="7" t="n"/>
+      <c r="B85" s="8" t="n"/>
+      <c r="C85" s="8" t="n"/>
+      <c r="D85" s="8" t="n"/>
+      <c r="E85" s="8" t="n"/>
+      <c r="F85" s="8" t="n"/>
+      <c r="G85" s="8" t="n"/>
+      <c r="H85" s="8" t="n"/>
+      <c r="I85" s="8" t="n"/>
     </row>
     <row r="86" ht="52" customHeight="1">
-      <c r="A86" s="8" t="inlineStr">
+      <c r="A86" s="9" t="inlineStr">
         <is>
           <t>5-01</t>
         </is>
       </c>
-      <c r="B86" s="9" t="inlineStr">
+      <c r="B86" s="10" t="inlineStr">
         <is>
           <t>所在</t>
         </is>
       </c>
-      <c r="C86" s="10" t="inlineStr">
+      <c r="C86" s="11" t="inlineStr">
         <is>
           <t>証憑の種類の全量</t>
         </is>
       </c>
-      <c r="D86" s="9" t="inlineStr">
+      <c r="D86" s="10" t="inlineStr">
         <is>
           <t>記述〔ヒアリング〕</t>
         </is>
       </c>
-      <c r="E86" s="9" t="n">
+      <c r="E86" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="F86" s="10" t="inlineStr">
+      <c r="F86" s="11" t="inlineStr">
         <is>
           <t>証憑管理機能の対象（添付形式・種類マスタ）が設計できない。</t>
         </is>
       </c>
-      <c r="G86" s="10" t="inlineStr">
+      <c r="G86" s="11" t="inlineStr">
         <is>
           <t>証憑種類マスタ</t>
         </is>
       </c>
-      <c r="H86" s="11" t="inlineStr">
+      <c r="H86" s="12" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="I86" s="10" t="inlineStr">
+      <c r="I86" s="11" t="inlineStr">
         <is>
           <t>「請求書・検針票・マニフェスト」の標準3種とみなす。</t>
         </is>
       </c>
     </row>
     <row r="87" ht="52" customHeight="1">
-      <c r="A87" s="8" t="inlineStr">
+      <c r="A87" s="9" t="inlineStr">
         <is>
           <t>5-02</t>
         </is>
       </c>
-      <c r="B87" s="9" t="inlineStr">
+      <c r="B87" s="10" t="inlineStr">
         <is>
           <t>所在</t>
         </is>
       </c>
-      <c r="C87" s="10" t="inlineStr">
+      <c r="C87" s="11" t="inlineStr">
         <is>
           <t>証憑形式の内訳（紙/PDF/システム内）</t>
         </is>
       </c>
-      <c r="D87" s="9" t="inlineStr">
+      <c r="D87" s="10" t="inlineStr">
         <is>
           <t>記述〔ヒアリング〕</t>
         </is>
       </c>
-      <c r="E87" s="9" t="n">
+      <c r="E87" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="F87" s="10" t="inlineStr">
+      <c r="F87" s="11" t="inlineStr">
         <is>
           <t>C-09の詳細。スキャン運用・容量設計の精度が下がる。</t>
         </is>
       </c>
-      <c r="G87" s="10" t="inlineStr">
+      <c r="G87" s="11" t="inlineStr">
         <is>
           <t>ストレージ・スキャン運用</t>
         </is>
       </c>
-      <c r="H87" s="11" t="inlineStr">
+      <c r="H87" s="12" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="I87" s="10" t="inlineStr">
+      <c r="I87" s="11" t="inlineStr">
         <is>
           <t>「紙半分」とみなす。</t>
         </is>
       </c>
     </row>
     <row r="88" ht="52" customHeight="1">
-      <c r="A88" s="8" t="inlineStr">
+      <c r="A88" s="9" t="inlineStr">
         <is>
           <t>5-03</t>
         </is>
       </c>
-      <c r="B88" s="9" t="inlineStr">
+      <c r="B88" s="10" t="inlineStr">
         <is>
           <t>所在</t>
         </is>
       </c>
-      <c r="C88" s="10" t="inlineStr">
+      <c r="C88" s="11" t="inlineStr">
         <is>
           <t>証憑の保管場所の全量</t>
         </is>
       </c>
-      <c r="D88" s="9" t="inlineStr">
+      <c r="D88" s="10" t="inlineStr">
         <is>
           <t>記述〔ヒアリング〕</t>
         </is>
       </c>
-      <c r="E88" s="9" t="n">
+      <c r="E88" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="F88" s="10" t="inlineStr">
+      <c r="F88" s="11" t="inlineStr">
         <is>
           <t>移行対象証憑の所在が特定できず、移行計画から漏れる。個人PC保管分は消失リスク。</t>
         </is>
       </c>
-      <c r="G88" s="10" t="inlineStr">
+      <c r="G88" s="11" t="inlineStr">
         <is>
           <t>証憑移行計画</t>
         </is>
       </c>
-      <c r="H88" s="13" t="inlineStr">
+      <c r="H88" s="14" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="I88" s="10" t="inlineStr">
+      <c r="I88" s="11" t="inlineStr">
         <is>
           <t>「個人PC・メール保管あり」とみなし全拠点に退避指示（未実施拠点の証憑消失は当該拠点起因）。</t>
         </is>
       </c>
     </row>
     <row r="89" ht="52" customHeight="1">
-      <c r="A89" s="8" t="inlineStr">
+      <c r="A89" s="9" t="inlineStr">
         <is>
           <t>5-04</t>
         </is>
       </c>
-      <c r="B89" s="9" t="inlineStr">
+      <c r="B89" s="10" t="inlineStr">
         <is>
           <t>所在</t>
         </is>
       </c>
-      <c r="C89" s="10" t="inlineStr">
+      <c r="C89" s="11" t="inlineStr">
         <is>
           <t>ファイル・フォルダの命名ルール</t>
         </is>
       </c>
-      <c r="D89" s="9" t="inlineStr">
+      <c r="D89" s="10" t="inlineStr">
         <is>
           <t>選択+補足〔ヒアリング〕</t>
         </is>
       </c>
-      <c r="E89" s="9" t="n">
+      <c r="E89" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="F89" s="10" t="inlineStr">
+      <c r="F89" s="11" t="inlineStr">
         <is>
           <t>証憑メタデータ（検索キー）設計の参考情報を失う。</t>
         </is>
       </c>
-      <c r="G89" s="10" t="inlineStr">
+      <c r="G89" s="11" t="inlineStr">
         <is>
           <t>検索性設計</t>
         </is>
       </c>
-      <c r="H89" s="14" t="inlineStr">
+      <c r="H89" s="15" t="inlineStr">
         <is>
           <t>低</t>
         </is>
       </c>
-      <c r="I89" s="10" t="inlineStr">
+      <c r="I89" s="11" t="inlineStr">
         <is>
           <t>「ルールなし」とみなす。</t>
         </is>
       </c>
     </row>
     <row r="90" ht="52" customHeight="1">
-      <c r="A90" s="8" t="inlineStr">
+      <c r="A90" s="9" t="inlineStr">
         <is>
           <t>5-05</t>
         </is>
       </c>
-      <c r="B90" s="9" t="inlineStr">
+      <c r="B90" s="10" t="inlineStr">
         <is>
           <t>所在</t>
         </is>
       </c>
-      <c r="C90" s="10" t="inlineStr">
+      <c r="C90" s="11" t="inlineStr">
         <is>
           <t>保存年限のルールと実態</t>
         </is>
       </c>
-      <c r="D90" s="9" t="inlineStr">
+      <c r="D90" s="10" t="inlineStr">
         <is>
           <t>記述〔ヒアリング〕</t>
         </is>
       </c>
-      <c r="E90" s="9" t="n">
+      <c r="E90" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="F90" s="10" t="inlineStr">
+      <c r="F90" s="11" t="inlineStr">
         <is>
           <t>保存期間要件（法定年数・保証対応年数）とストレージ容量が確定できない。</t>
         </is>
       </c>
-      <c r="G90" s="10" t="inlineStr">
+      <c r="G90" s="11" t="inlineStr">
         <is>
           <t>保存期間要件</t>
         </is>
       </c>
-      <c r="H90" s="11" t="inlineStr">
+      <c r="H90" s="12" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="I90" s="10" t="inlineStr">
+      <c r="I90" s="11" t="inlineStr">
         <is>
           <t>「実態は3年分のみ」とみなし過年度分の欠落リスクを記録。</t>
         </is>
       </c>
     </row>
     <row r="91" ht="52" customHeight="1">
-      <c r="A91" s="8" t="inlineStr">
+      <c r="A91" s="9" t="inlineStr">
         <is>
           <t>5-06</t>
         </is>
       </c>
-      <c r="B91" s="9" t="inlineStr">
+      <c r="B91" s="10" t="inlineStr">
         <is>
           <t>紐付け</t>
         </is>
       </c>
-      <c r="C91" s="10" t="inlineStr">
+      <c r="C91" s="11" t="inlineStr">
         <is>
           <t>数値→証憑のトレーサビリティ</t>
         </is>
       </c>
-      <c r="D91" s="9" t="inlineStr">
+      <c r="D91" s="10" t="inlineStr">
         <is>
           <t>選択+補足〔ヒアリング〕</t>
         </is>
       </c>
-      <c r="E91" s="9" t="n">
+      <c r="E91" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="F91" s="10" t="inlineStr">
+      <c r="F91" s="11" t="inlineStr">
         <is>
           <t>C-10の詳細。紐付けデータモデルと移行時の対応表整備範囲が確定しない。</t>
         </is>
       </c>
-      <c r="G91" s="10" t="inlineStr">
+      <c r="G91" s="11" t="inlineStr">
         <is>
           <t>紐付けモデル・移行対応表</t>
         </is>
       </c>
-      <c r="H91" s="13" t="inlineStr">
+      <c r="H91" s="14" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="I91" s="10" t="inlineStr">
+      <c r="I91" s="11" t="inlineStr">
         <is>
           <t>「対応表なし」とみなし移行時の紐付け再構築タスクを計画化。</t>
         </is>
       </c>
     </row>
     <row r="92" ht="52" customHeight="1">
-      <c r="A92" s="8" t="inlineStr">
+      <c r="A92" s="9" t="inlineStr">
         <is>
           <t>5-07</t>
         </is>
       </c>
-      <c r="B92" s="9" t="inlineStr">
+      <c r="B92" s="10" t="inlineStr">
         <is>
           <t>紐付け</t>
         </is>
       </c>
-      <c r="C92" s="10" t="inlineStr">
+      <c r="C92" s="11" t="inlineStr">
         <is>
           <t>監査時の証憑提示所要時間</t>
         </is>
       </c>
-      <c r="D92" s="9" t="inlineStr">
+      <c r="D92" s="10" t="inlineStr">
         <is>
           <t>記述〔ヒアリング〕</t>
         </is>
       </c>
-      <c r="E92" s="9" t="n">
+      <c r="E92" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="F92" s="10" t="inlineStr">
+      <c r="F92" s="11" t="inlineStr">
         <is>
           <t>検索性要件・ROIの根拠精度が下がる。</t>
         </is>
       </c>
-      <c r="G92" s="10" t="inlineStr">
+      <c r="G92" s="11" t="inlineStr">
         <is>
           <t>検索性・ROI</t>
         </is>
       </c>
-      <c r="H92" s="14" t="inlineStr">
+      <c r="H92" s="15" t="inlineStr">
         <is>
           <t>低</t>
         </is>
       </c>
-      <c r="I92" s="10" t="inlineStr">
+      <c r="I92" s="11" t="inlineStr">
         <is>
           <t>「半日/件」とみなす。</t>
         </is>
       </c>
     </row>
     <row r="93" ht="52" customHeight="1">
-      <c r="A93" s="8" t="inlineStr">
+      <c r="A93" s="9" t="inlineStr">
         <is>
           <t>5-08</t>
         </is>
       </c>
-      <c r="B93" s="9" t="inlineStr">
+      <c r="B93" s="10" t="inlineStr">
         <is>
           <t>紐付け</t>
         </is>
       </c>
-      <c r="C93" s="10" t="inlineStr">
+      <c r="C93" s="11" t="inlineStr">
         <is>
           <t>証憑が存在しない・再入手困難な項目</t>
         </is>
       </c>
-      <c r="D93" s="9" t="inlineStr">
+      <c r="D93" s="10" t="inlineStr">
         <is>
           <t>選択+補足〔ヒアリング〕</t>
         </is>
       </c>
-      <c r="E93" s="9" t="n">
+      <c r="E93" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="F93" s="10" t="inlineStr">
+      <c r="F93" s="11" t="inlineStr">
         <is>
           <t>保証で意見不能になり得る項目を事前に特定できず、検証本番で発覚する（最悪のタイミング）。代替証憑ルールも設計できない。</t>
         </is>
       </c>
-      <c r="G93" s="10" t="inlineStr">
+      <c r="G93" s="11" t="inlineStr">
         <is>
           <t>代替証憑ルール・保証リスク</t>
         </is>
       </c>
-      <c r="H93" s="13" t="inlineStr">
+      <c r="H93" s="14" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="I93" s="10" t="inlineStr">
+      <c r="I93" s="11" t="inlineStr">
         <is>
           <t>「存在しない項目あり」とみなし代替手続き（推計根拠文書化）を要件化。検証時の指摘は当該拠点起因。</t>
         </is>
       </c>
     </row>
     <row r="94" ht="52" customHeight="1">
-      <c r="A94" s="8" t="inlineStr">
+      <c r="A94" s="9" t="inlineStr">
         <is>
           <t>5-09</t>
         </is>
       </c>
-      <c r="B94" s="9" t="inlineStr">
+      <c r="B94" s="10" t="inlineStr">
         <is>
           <t>紐付け</t>
         </is>
       </c>
-      <c r="C94" s="10" t="inlineStr">
+      <c r="C94" s="11" t="inlineStr">
         <is>
           <t>第三者（ビル管理・テナント等）保有証憑の入手性</t>
         </is>
       </c>
-      <c r="D94" s="9" t="inlineStr">
+      <c r="D94" s="10" t="inlineStr">
         <is>
           <t>記述〔ヒアリング〕</t>
         </is>
       </c>
-      <c r="E94" s="9" t="n">
+      <c r="E94" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="F94" s="10" t="inlineStr">
+      <c r="F94" s="11" t="inlineStr">
         <is>
           <t>外部証憑の取得フロー（契約上の提供義務の有無）が設計できない。</t>
         </is>
       </c>
-      <c r="G94" s="10" t="inlineStr">
+      <c r="G94" s="11" t="inlineStr">
         <is>
           <t>外部証憑取得フロー</t>
         </is>
       </c>
-      <c r="H94" s="11" t="inlineStr">
+      <c r="H94" s="12" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="I94" s="10" t="inlineStr">
+      <c r="I94" s="11" t="inlineStr">
         <is>
           <t>「入手困難」とみなし契約整備タスクを追加。</t>
         </is>
       </c>
     </row>
     <row r="95" ht="52" customHeight="1">
-      <c r="A95" s="8" t="inlineStr">
+      <c r="A95" s="9" t="inlineStr">
         <is>
           <t>5-10</t>
         </is>
       </c>
-      <c r="B95" s="9" t="inlineStr">
+      <c r="B95" s="10" t="inlineStr">
         <is>
           <t>保全</t>
         </is>
       </c>
-      <c r="C95" s="10" t="inlineStr">
+      <c r="C95" s="11" t="inlineStr">
         <is>
           <t>担当交代時の記録引継ぎ・消失経験</t>
         </is>
       </c>
-      <c r="D95" s="9" t="inlineStr">
+      <c r="D95" s="10" t="inlineStr">
         <is>
           <t>記述〔ヒアリング〕</t>
         </is>
       </c>
-      <c r="E95" s="9" t="n">
+      <c r="E95" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="F95" s="10" t="inlineStr">
+      <c r="F95" s="11" t="inlineStr">
         <is>
           <t>記録保全の弱点が特定できず、システム化後も同じ消失が再発する。</t>
         </is>
       </c>
-      <c r="G95" s="10" t="inlineStr">
+      <c r="G95" s="11" t="inlineStr">
         <is>
           <t>記録保全設計</t>
         </is>
       </c>
-      <c r="H95" s="11" t="inlineStr">
+      <c r="H95" s="12" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="I95" s="10" t="inlineStr">
+      <c r="I95" s="11" t="inlineStr">
         <is>
           <t>「消失経験あり」とみなす。</t>
         </is>
       </c>
     </row>
     <row r="96" ht="52" customHeight="1">
-      <c r="A96" s="8" t="inlineStr">
+      <c r="A96" s="9" t="inlineStr">
         <is>
           <t>5-11</t>
         </is>
       </c>
-      <c r="B96" s="9" t="inlineStr">
+      <c r="B96" s="10" t="inlineStr">
         <is>
           <t>保全</t>
         </is>
       </c>
-      <c r="C96" s="10" t="inlineStr">
+      <c r="C96" s="11" t="inlineStr">
         <is>
           <t>個人メール・PCのみの重要記録</t>
         </is>
       </c>
-      <c r="D96" s="9" t="inlineStr">
+      <c r="D96" s="10" t="inlineStr">
         <is>
           <t>選択+補足〔ヒアリング〕</t>
         </is>
       </c>
-      <c r="E96" s="9" t="n">
+      <c r="E96" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="F96" s="10" t="inlineStr">
+      <c r="F96" s="11" t="inlineStr">
         <is>
           <t>C-28の詳細。</t>
         </is>
       </c>
-      <c r="G96" s="10" t="inlineStr">
+      <c r="G96" s="11" t="inlineStr">
         <is>
           <t>証憑退避</t>
         </is>
       </c>
-      <c r="H96" s="13" t="inlineStr">
+      <c r="H96" s="14" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="I96" s="10" t="inlineStr">
+      <c r="I96" s="11" t="inlineStr">
         <is>
           <t>「あり」とみなし退避タスクを計画化。</t>
         </is>
       </c>
     </row>
     <row r="97" ht="52" customHeight="1">
-      <c r="A97" s="8" t="inlineStr">
+      <c r="A97" s="9" t="inlineStr">
         <is>
           <t>5-12</t>
         </is>
       </c>
-      <c r="B97" s="9" t="inlineStr">
+      <c r="B97" s="10" t="inlineStr">
         <is>
           <t>保全</t>
         </is>
       </c>
-      <c r="C97" s="10" t="inlineStr">
+      <c r="C97" s="11" t="inlineStr">
         <is>
           <t>過去の検証指摘と対応の記録所在</t>
         </is>
       </c>
-      <c r="D97" s="9" t="inlineStr">
+      <c r="D97" s="10" t="inlineStr">
         <is>
           <t>記述〔ヒアリング〕</t>
         </is>
       </c>
-      <c r="E97" s="9" t="n">
+      <c r="E97" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="F97" s="10" t="inlineStr">
+      <c r="F97" s="11" t="inlineStr">
         <is>
           <t>過去指摘の要件反映（保証人協議のインプット）ができず、「後出しNG」予防の前提が崩れる。同じ指摘を再度受ける。</t>
         </is>
       </c>
-      <c r="G97" s="10" t="inlineStr">
+      <c r="G97" s="11" t="inlineStr">
         <is>
           <t>過去指摘反映・保証人協議</t>
         </is>
       </c>
-      <c r="H97" s="13" t="inlineStr">
+      <c r="H97" s="14" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="I97" s="10" t="inlineStr">
+      <c r="I97" s="11" t="inlineStr">
         <is>
           <t>「記録なし」とみなし保証人への指摘事項再照会を計画化（追加協議工数は当該部門起因）。</t>
         </is>
       </c>
     </row>
     <row r="98" ht="52" customHeight="1">
-      <c r="A98" s="8" t="inlineStr">
+      <c r="A98" s="9" t="inlineStr">
         <is>
           <t>5-13</t>
         </is>
       </c>
-      <c r="B98" s="9" t="inlineStr">
+      <c r="B98" s="10" t="inlineStr">
         <is>
           <t>保全</t>
         </is>
       </c>
-      <c r="C98" s="10" t="inlineStr">
+      <c r="C98" s="11" t="inlineStr">
         <is>
           <t>改ざん防止の仕組み</t>
         </is>
       </c>
-      <c r="D98" s="9" t="inlineStr">
+      <c r="D98" s="10" t="inlineStr">
         <is>
           <t>選択+補足〔ヒアリング〕</t>
         </is>
       </c>
-      <c r="E98" s="9" t="n">
+      <c r="E98" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="F98" s="10" t="inlineStr">
+      <c r="F98" s="11" t="inlineStr">
         <is>
           <t>統制設計の現状値が欠落し、改ざんリスク評価ができない。</t>
         </is>
       </c>
-      <c r="G98" s="10" t="inlineStr">
+      <c r="G98" s="11" t="inlineStr">
         <is>
           <t>改ざん防止要件</t>
         </is>
       </c>
-      <c r="H98" s="11" t="inlineStr">
+      <c r="H98" s="12" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="I98" s="10" t="inlineStr">
+      <c r="I98" s="11" t="inlineStr">
         <is>
           <t>「仕組みなし」とみなす。</t>
         </is>
       </c>
     </row>
     <row r="99" ht="52" customHeight="1">
-      <c r="A99" s="8" t="inlineStr">
+      <c r="A99" s="9" t="inlineStr">
         <is>
           <t>5-14</t>
         </is>
       </c>
-      <c r="B99" s="9" t="inlineStr">
+      <c r="B99" s="10" t="inlineStr">
         <is>
           <t>保全</t>
         </is>
       </c>
-      <c r="C99" s="10" t="inlineStr">
+      <c r="C99" s="11" t="inlineStr">
         <is>
           <t>証憑添付必須化の障害</t>
         </is>
       </c>
-      <c r="D99" s="9" t="inlineStr">
+      <c r="D99" s="10" t="inlineStr">
         <is>
           <t>記述〔ヒアリング〕</t>
         </is>
       </c>
-      <c r="E99" s="9" t="n">
+      <c r="E99" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="F99" s="10" t="inlineStr">
+      <c r="F99" s="11" t="inlineStr">
         <is>
           <t>C-11の詳細。例外設計が現場実態と乖離。</t>
         </is>
       </c>
-      <c r="G99" s="10" t="inlineStr">
+      <c r="G99" s="11" t="inlineStr">
         <is>
           <t>例外設計</t>
         </is>
       </c>
-      <c r="H99" s="13" t="inlineStr">
+      <c r="H99" s="14" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="I99" s="10" t="inlineStr">
+      <c r="I99" s="11" t="inlineStr">
         <is>
           <t>「障害あり」とみなし例外フロー実装。</t>
         </is>
       </c>
     </row>
     <row r="100" ht="17" customHeight="1">
-      <c r="A100" s="6" t="inlineStr">
+      <c r="A100" s="7" t="inlineStr">
         <is>
           <t>6. チェックと承認（選抜拠点ヒアリング・6-01〜6-14）</t>
         </is>
       </c>
-      <c r="B100" s="7" t="n"/>
-      <c r="C100" s="7" t="n"/>
-      <c r="D100" s="7" t="n"/>
-      <c r="E100" s="7" t="n"/>
-      <c r="F100" s="7" t="n"/>
-      <c r="G100" s="7" t="n"/>
-      <c r="H100" s="7" t="n"/>
-      <c r="I100" s="7" t="n"/>
+      <c r="B100" s="8" t="n"/>
+      <c r="C100" s="8" t="n"/>
+      <c r="D100" s="8" t="n"/>
+      <c r="E100" s="8" t="n"/>
+      <c r="F100" s="8" t="n"/>
+      <c r="G100" s="8" t="n"/>
+      <c r="H100" s="8" t="n"/>
+      <c r="I100" s="8" t="n"/>
     </row>
     <row r="101" ht="52" customHeight="1">
-      <c r="A101" s="8" t="inlineStr">
+      <c r="A101" s="9" t="inlineStr">
         <is>
           <t>6-01</t>
         </is>
       </c>
-      <c r="B101" s="9" t="inlineStr">
+      <c r="B101" s="10" t="inlineStr">
         <is>
           <t>チェック</t>
         </is>
       </c>
-      <c r="C101" s="10" t="inlineStr">
+      <c r="C101" s="11" t="inlineStr">
         <is>
           <t>チェックの実施者・方法</t>
         </is>
       </c>
-      <c r="D101" s="9" t="inlineStr">
+      <c r="D101" s="10" t="inlineStr">
         <is>
           <t>記述〔ヒアリング〕</t>
         </is>
       </c>
-      <c r="E101" s="9" t="n">
+      <c r="E101" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="F101" s="10" t="inlineStr">
+      <c r="F101" s="11" t="inlineStr">
         <is>
           <t>人的統制→システム統制の置換設計の根拠がない。統制の過剰／過少の両リスク。</t>
         </is>
       </c>
-      <c r="G101" s="10" t="inlineStr">
+      <c r="G101" s="11" t="inlineStr">
         <is>
           <t>キーコントロール配置</t>
         </is>
       </c>
-      <c r="H101" s="13" t="inlineStr">
+      <c r="H101" s="14" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="I101" s="10" t="inlineStr">
+      <c r="I101" s="11" t="inlineStr">
         <is>
           <t>「自己チェックのみ」とみなし統制を厚めに設計。</t>
         </is>
       </c>
     </row>
     <row r="102" ht="52" customHeight="1">
-      <c r="A102" s="8" t="inlineStr">
+      <c r="A102" s="9" t="inlineStr">
         <is>
           <t>6-02</t>
         </is>
       </c>
-      <c r="B102" s="9" t="inlineStr">
+      <c r="B102" s="10" t="inlineStr">
         <is>
           <t>チェック</t>
         </is>
       </c>
-      <c r="C102" s="10" t="inlineStr">
+      <c r="C102" s="11" t="inlineStr">
         <is>
           <t>チェック実施の記録有無</t>
         </is>
       </c>
-      <c r="D102" s="9" t="inlineStr">
+      <c r="D102" s="10" t="inlineStr">
         <is>
           <t>選択+補足〔ヒアリング〕</t>
         </is>
       </c>
-      <c r="E102" s="9" t="n">
+      <c r="E102" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="F102" s="10" t="inlineStr">
+      <c r="F102" s="11" t="inlineStr">
         <is>
           <t>統制の証跡化（チェック記録の保存）要件が決められない。保証で「チェックの証拠」を求められ提示不能。</t>
         </is>
       </c>
-      <c r="G102" s="10" t="inlineStr">
+      <c r="G102" s="11" t="inlineStr">
         <is>
           <t>統制証跡要件</t>
         </is>
       </c>
-      <c r="H102" s="11" t="inlineStr">
+      <c r="H102" s="12" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="I102" s="10" t="inlineStr">
+      <c r="I102" s="11" t="inlineStr">
         <is>
           <t>「残らない」とみなしシステムでのチェック記録を必須化。</t>
         </is>
       </c>
     </row>
     <row r="103" ht="52" customHeight="1">
-      <c r="A103" s="8" t="inlineStr">
+      <c r="A103" s="9" t="inlineStr">
         <is>
           <t>6-03</t>
         </is>
       </c>
-      <c r="B103" s="9" t="inlineStr">
+      <c r="B103" s="10" t="inlineStr">
         <is>
           <t>チェック</t>
         </is>
       </c>
-      <c r="C103" s="10" t="inlineStr">
+      <c r="C103" s="11" t="inlineStr">
         <is>
           <t>異常値の定義・閾値・対応者</t>
         </is>
       </c>
-      <c r="D103" s="9" t="inlineStr">
+      <c r="D103" s="10" t="inlineStr">
         <is>
           <t>選択+補足〔ヒアリング〕</t>
         </is>
       </c>
-      <c r="E103" s="9" t="n">
+      <c r="E103" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="F103" s="10" t="inlineStr">
+      <c r="F103" s="11" t="inlineStr">
         <is>
           <t>異常値検知ルールの初期値と対応フローが机上設定になる。</t>
         </is>
       </c>
-      <c r="G103" s="10" t="inlineStr">
+      <c r="G103" s="11" t="inlineStr">
         <is>
           <t>異常値検知・対応フロー</t>
         </is>
       </c>
-      <c r="H103" s="11" t="inlineStr">
+      <c r="H103" s="12" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="I103" s="10" t="inlineStr">
+      <c r="I103" s="11" t="inlineStr">
         <is>
           <t>「定義なし」とみなし標準閾値で設計。</t>
         </is>
       </c>
     </row>
     <row r="104" ht="52" customHeight="1">
-      <c r="A104" s="8" t="inlineStr">
+      <c r="A104" s="9" t="inlineStr">
         <is>
           <t>6-04</t>
         </is>
       </c>
-      <c r="B104" s="9" t="inlineStr">
+      <c r="B104" s="10" t="inlineStr">
         <is>
           <t>チェック</t>
         </is>
       </c>
-      <c r="C104" s="10" t="inlineStr">
+      <c r="C104" s="11" t="inlineStr">
         <is>
           <t>入力ミスが開示まで流れた経験</t>
         </is>
       </c>
-      <c r="D104" s="9" t="inlineStr">
+      <c r="D104" s="10" t="inlineStr">
         <is>
           <t>記述〔ヒアリング〕</t>
         </is>
       </c>
-      <c r="E104" s="9" t="n">
+      <c r="E104" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="F104" s="10" t="inlineStr">
+      <c r="F104" s="11" t="inlineStr">
         <is>
           <t>統制の穴の実例＝キーコントロール配置の最重要根拠を失う。同じ経路のミスが再発する。</t>
         </is>
       </c>
-      <c r="G104" s="10" t="inlineStr">
+      <c r="G104" s="11" t="inlineStr">
         <is>
           <t>キーコントロール設計</t>
         </is>
       </c>
-      <c r="H104" s="13" t="inlineStr">
+      <c r="H104" s="14" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="I104" s="10" t="inlineStr">
+      <c r="I104" s="11" t="inlineStr">
         <is>
           <t>「経験あり・経路不明」とみなし全経路に統制を配置（過剰統制コスト増）。</t>
         </is>
       </c>
     </row>
     <row r="105" ht="52" customHeight="1">
-      <c r="A105" s="8" t="inlineStr">
+      <c r="A105" s="9" t="inlineStr">
         <is>
           <t>6-05</t>
         </is>
       </c>
-      <c r="B105" s="9" t="inlineStr">
+      <c r="B105" s="10" t="inlineStr">
         <is>
           <t>承認</t>
         </is>
       </c>
-      <c r="C105" s="10" t="inlineStr">
+      <c r="C105" s="11" t="inlineStr">
         <is>
           <t>承認の実施者・形式</t>
         </is>
       </c>
-      <c r="D105" s="9" t="inlineStr">
+      <c r="D105" s="10" t="inlineStr">
         <is>
           <t>選択+補足〔ヒアリング〕</t>
         </is>
       </c>
-      <c r="E105" s="9" t="n">
+      <c r="E105" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="F105" s="10" t="inlineStr">
+      <c r="F105" s="11" t="inlineStr">
         <is>
           <t>C-12の詳細。承認者マスタ・承認形式が設計できない。</t>
         </is>
       </c>
-      <c r="G105" s="10" t="inlineStr">
+      <c r="G105" s="11" t="inlineStr">
         <is>
           <t>承認WF設計</t>
         </is>
       </c>
-      <c r="H105" s="13" t="inlineStr">
+      <c r="H105" s="14" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="I105" s="10" t="inlineStr">
+      <c r="I105" s="11" t="inlineStr">
         <is>
           <t>「承認なし」とみなす。</t>
         </is>
       </c>
     </row>
     <row r="106" ht="52" customHeight="1">
-      <c r="A106" s="8" t="inlineStr">
+      <c r="A106" s="9" t="inlineStr">
         <is>
           <t>6-06</t>
         </is>
       </c>
-      <c r="B106" s="9" t="inlineStr">
+      <c r="B106" s="10" t="inlineStr">
         <is>
           <t>承認</t>
         </is>
       </c>
-      <c r="C106" s="10" t="inlineStr">
+      <c r="C106" s="11" t="inlineStr">
         <is>
           <t>拠点長のデータ関与機会</t>
         </is>
       </c>
-      <c r="D106" s="9" t="inlineStr">
+      <c r="D106" s="10" t="inlineStr">
         <is>
           <t>選択+補足〔ヒアリング〕</t>
         </is>
       </c>
-      <c r="E106" s="9" t="n">
+      <c r="E106" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="F106" s="10" t="inlineStr">
+      <c r="F106" s="11" t="inlineStr">
         <is>
           <t>承認階層に拠点長を含めるかの判断材料を失う。</t>
         </is>
       </c>
-      <c r="G106" s="10" t="inlineStr">
+      <c r="G106" s="11" t="inlineStr">
         <is>
           <t>承認階層設計</t>
         </is>
       </c>
-      <c r="H106" s="11" t="inlineStr">
+      <c r="H106" s="12" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="I106" s="10" t="inlineStr">
+      <c r="I106" s="11" t="inlineStr">
         <is>
           <t>「関与なし」とみなし拠点長承認を新設（負荷増は当該拠点調整事項）。</t>
         </is>
       </c>
     </row>
     <row r="107" ht="52" customHeight="1">
-      <c r="A107" s="8" t="inlineStr">
+      <c r="A107" s="9" t="inlineStr">
         <is>
           <t>6-07</t>
         </is>
       </c>
-      <c r="B107" s="9" t="inlineStr">
+      <c r="B107" s="10" t="inlineStr">
         <is>
           <t>承認</t>
         </is>
       </c>
-      <c r="C107" s="10" t="inlineStr">
+      <c r="C107" s="11" t="inlineStr">
         <is>
           <t>承認者不在時の代行ルール</t>
         </is>
       </c>
-      <c r="D107" s="9" t="inlineStr">
+      <c r="D107" s="10" t="inlineStr">
         <is>
           <t>選択+補足〔ヒアリング〕</t>
         </is>
       </c>
-      <c r="E107" s="9" t="n">
+      <c r="E107" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="F107" s="10" t="inlineStr">
+      <c r="F107" s="11" t="inlineStr">
         <is>
           <t>代行承認・委任機能の仕様が決められない。</t>
         </is>
       </c>
-      <c r="G107" s="10" t="inlineStr">
+      <c r="G107" s="11" t="inlineStr">
         <is>
           <t>代行機能</t>
         </is>
       </c>
-      <c r="H107" s="11" t="inlineStr">
+      <c r="H107" s="12" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="I107" s="10" t="inlineStr">
+      <c r="I107" s="11" t="inlineStr">
         <is>
           <t>「ルールなし」とみなし代行機能を実装。</t>
         </is>
       </c>
     </row>
     <row r="108" ht="52" customHeight="1">
-      <c r="A108" s="8" t="inlineStr">
+      <c r="A108" s="9" t="inlineStr">
         <is>
           <t>6-08</t>
         </is>
       </c>
-      <c r="B108" s="9" t="inlineStr">
+      <c r="B108" s="10" t="inlineStr">
         <is>
           <t>承認</t>
         </is>
       </c>
-      <c r="C108" s="10" t="inlineStr">
+      <c r="C108" s="11" t="inlineStr">
         <is>
           <t>確定（ロック）の概念とタイミング・変更権限</t>
         </is>
       </c>
-      <c r="D108" s="9" t="inlineStr">
+      <c r="D108" s="10" t="inlineStr">
         <is>
           <t>記述〔ヒアリング〕</t>
         </is>
       </c>
-      <c r="E108" s="9" t="n">
+      <c r="E108" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="F108" s="10" t="inlineStr">
+      <c r="F108" s="11" t="inlineStr">
         <is>
           <t>確定ロック機能の仕様（誰がいつロック・解除権限）が設計できない。保証の前提となる「数値の確定」概念が定まらない。</t>
         </is>
       </c>
-      <c r="G108" s="10" t="inlineStr">
+      <c r="G108" s="11" t="inlineStr">
         <is>
           <t>確定ロック仕様</t>
         </is>
       </c>
-      <c r="H108" s="13" t="inlineStr">
+      <c r="H108" s="14" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="I108" s="10" t="inlineStr">
+      <c r="I108" s="11" t="inlineStr">
         <is>
           <t>「概念なし」とみなし本社一括ロック方式で設計。</t>
         </is>
       </c>
     </row>
     <row r="109" ht="52" customHeight="1">
-      <c r="A109" s="8" t="inlineStr">
+      <c r="A109" s="9" t="inlineStr">
         <is>
           <t>6-09</t>
         </is>
       </c>
-      <c r="B109" s="9" t="inlineStr">
+      <c r="B109" s="10" t="inlineStr">
         <is>
           <t>権限</t>
         </is>
       </c>
-      <c r="C109" s="10" t="inlineStr">
+      <c r="C109" s="11" t="inlineStr">
         <is>
           <t>ファイル・システムの編集権限</t>
         </is>
       </c>
-      <c r="D109" s="9" t="inlineStr">
+      <c r="D109" s="10" t="inlineStr">
         <is>
           <t>選択+補足〔ヒアリング〕</t>
         </is>
       </c>
-      <c r="E109" s="9" t="n">
+      <c r="E109" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="F109" s="10" t="inlineStr">
+      <c r="F109" s="11" t="inlineStr">
         <is>
           <t>C-32の詳細。</t>
         </is>
       </c>
-      <c r="G109" s="10" t="inlineStr">
+      <c r="G109" s="11" t="inlineStr">
         <is>
           <t>権限マトリクス</t>
         </is>
       </c>
-      <c r="H109" s="13" t="inlineStr">
+      <c r="H109" s="14" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="I109" s="10" t="inlineStr">
+      <c r="I109" s="11" t="inlineStr">
         <is>
           <t>「誰でも編集可」とみなす。</t>
         </is>
       </c>
     </row>
     <row r="110" ht="52" customHeight="1">
-      <c r="A110" s="8" t="inlineStr">
+      <c r="A110" s="9" t="inlineStr">
         <is>
           <t>6-10</t>
         </is>
       </c>
-      <c r="B110" s="9" t="inlineStr">
+      <c r="B110" s="10" t="inlineStr">
         <is>
           <t>権限</t>
         </is>
       </c>
-      <c r="C110" s="10" t="inlineStr">
+      <c r="C110" s="11" t="inlineStr">
         <is>
           <t>変更履歴の記録有無</t>
         </is>
       </c>
-      <c r="D110" s="9" t="inlineStr">
+      <c r="D110" s="10" t="inlineStr">
         <is>
           <t>選択+補足〔ヒアリング〕</t>
         </is>
       </c>
-      <c r="E110" s="9" t="n">
+      <c r="E110" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="F110" s="10" t="inlineStr">
+      <c r="F110" s="11" t="inlineStr">
         <is>
           <t>C-13の詳細。</t>
         </is>
       </c>
-      <c r="G110" s="10" t="inlineStr">
+      <c r="G110" s="11" t="inlineStr">
         <is>
           <t>監査ログ</t>
         </is>
       </c>
-      <c r="H110" s="13" t="inlineStr">
+      <c r="H110" s="14" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="I110" s="10" t="inlineStr">
+      <c r="I110" s="11" t="inlineStr">
         <is>
           <t>「残らない」とみなす。</t>
         </is>
       </c>
     </row>
     <row r="111" ht="52" customHeight="1">
-      <c r="A111" s="8" t="inlineStr">
+      <c r="A111" s="9" t="inlineStr">
         <is>
           <t>6-11</t>
         </is>
       </c>
-      <c r="B111" s="9" t="inlineStr">
+      <c r="B111" s="10" t="inlineStr">
         <is>
           <t>権限</t>
         </is>
       </c>
-      <c r="C111" s="10" t="inlineStr">
+      <c r="C111" s="11" t="inlineStr">
         <is>
           <t>共有ID・パスワードの使い回し</t>
         </is>
       </c>
-      <c r="D111" s="9" t="inlineStr">
+      <c r="D111" s="10" t="inlineStr">
         <is>
           <t>選択+補足〔ヒアリング〕</t>
         </is>
       </c>
-      <c r="E111" s="9" t="n">
+      <c r="E111" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="F111" s="10" t="inlineStr">
+      <c r="F111" s="11" t="inlineStr">
         <is>
           <t>個人ID必須化の移行負荷（アカウント発行数）が見積れない。共有IDは保証・監査で確実に指摘される。</t>
         </is>
       </c>
-      <c r="G111" s="10" t="inlineStr">
+      <c r="G111" s="11" t="inlineStr">
         <is>
           <t>認証設計・監査指摘リスク</t>
         </is>
       </c>
-      <c r="H111" s="13" t="inlineStr">
+      <c r="H111" s="14" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="I111" s="10" t="inlineStr">
+      <c r="I111" s="11" t="inlineStr">
         <is>
           <t>「共有IDあり」とみなし個人ID移行を必須化（移行負荷は当該拠点起因）。</t>
         </is>
       </c>
     </row>
     <row r="112" ht="52" customHeight="1">
-      <c r="A112" s="8" t="inlineStr">
+      <c r="A112" s="9" t="inlineStr">
         <is>
           <t>6-12</t>
         </is>
       </c>
-      <c r="B112" s="9" t="inlineStr">
+      <c r="B112" s="10" t="inlineStr">
         <is>
           <t>権限</t>
         </is>
       </c>
-      <c r="C112" s="10" t="inlineStr">
+      <c r="C112" s="11" t="inlineStr">
         <is>
           <t>内部監査・J-SOX・ISO審査の対象経験と指摘</t>
         </is>
       </c>
-      <c r="D112" s="9" t="inlineStr">
+      <c r="D112" s="10" t="inlineStr">
         <is>
           <t>選択+補足〔ヒアリング〕</t>
         </is>
       </c>
-      <c r="E112" s="9" t="n">
+      <c r="E112" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="F112" s="10" t="inlineStr">
+      <c r="F112" s="11" t="inlineStr">
         <is>
           <t>過去指摘を要件に反映できず、既知の弱点を放置した設計になる。</t>
         </is>
       </c>
-      <c r="G112" s="10" t="inlineStr">
+      <c r="G112" s="11" t="inlineStr">
         <is>
           <t>過去指摘反映</t>
         </is>
       </c>
-      <c r="H112" s="13" t="inlineStr">
+      <c r="H112" s="14" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="I112" s="10" t="inlineStr">
+      <c r="I112" s="11" t="inlineStr">
         <is>
           <t>「指摘あり・内容不明」とみなし内部監査室への照会を実施（回答遅延は当該部門起因）。</t>
         </is>
       </c>
     </row>
     <row r="113" ht="52" customHeight="1">
-      <c r="A113" s="8" t="inlineStr">
+      <c r="A113" s="9" t="inlineStr">
         <is>
           <t>6-13</t>
         </is>
       </c>
-      <c r="B113" s="9" t="inlineStr">
+      <c r="B113" s="10" t="inlineStr">
         <is>
           <t>備え</t>
         </is>
       </c>
-      <c r="C113" s="10" t="inlineStr">
+      <c r="C113" s="11" t="inlineStr">
         <is>
           <t>データ信頼性のヒヤリ経験</t>
         </is>
       </c>
-      <c r="D113" s="9" t="inlineStr">
+      <c r="D113" s="10" t="inlineStr">
         <is>
           <t>記述〔ヒアリング〕</t>
         </is>
       </c>
-      <c r="E113" s="9" t="n">
+      <c r="E113" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="F113" s="10" t="inlineStr">
+      <c r="F113" s="11" t="inlineStr">
         <is>
           <t>リスクシナリオの実例を失い、統制の優先順位が机上になる。</t>
         </is>
       </c>
-      <c r="G113" s="10" t="inlineStr">
+      <c r="G113" s="11" t="inlineStr">
         <is>
           <t>統制優先順位</t>
         </is>
       </c>
-      <c r="H113" s="11" t="inlineStr">
+      <c r="H113" s="12" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="I113" s="10" t="inlineStr">
+      <c r="I113" s="11" t="inlineStr">
         <is>
           <t>「ヒヤリ経験あり」とみなす。</t>
         </is>
       </c>
     </row>
     <row r="114" ht="52" customHeight="1">
-      <c r="A114" s="8" t="inlineStr">
+      <c r="A114" s="9" t="inlineStr">
         <is>
           <t>6-14</t>
         </is>
       </c>
-      <c r="B114" s="9" t="inlineStr">
+      <c r="B114" s="10" t="inlineStr">
         <is>
           <t>備え</t>
         </is>
       </c>
-      <c r="C114" s="10" t="inlineStr">
+      <c r="C114" s="11" t="inlineStr">
         <is>
           <t>統制強化で業務が回らなくなる懸念</t>
         </is>
       </c>
-      <c r="D114" s="9" t="inlineStr">
+      <c r="D114" s="10" t="inlineStr">
         <is>
           <t>記述〔ヒアリング〕</t>
         </is>
       </c>
-      <c r="E114" s="9" t="n">
+      <c r="E114" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="F114" s="10" t="inlineStr">
+      <c r="F114" s="11" t="inlineStr">
         <is>
           <t>例外設計・チェンジマネジメントの重点が特定できず、稼働後に現場が停止する統制を設計するリスク。</t>
         </is>
       </c>
-      <c r="G114" s="10" t="inlineStr">
+      <c r="G114" s="11" t="inlineStr">
         <is>
           <t>例外設計・定着計画</t>
         </is>
       </c>
-      <c r="H114" s="11" t="inlineStr">
+      <c r="H114" s="12" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="I114" s="10" t="inlineStr">
+      <c r="I114" s="11" t="inlineStr">
         <is>
           <t>「懸念あり・内容不明」とみなし統制は段階導入方式で設計。</t>
         </is>
       </c>
     </row>
     <row r="115" ht="17" customHeight="1">
-      <c r="A115" s="6" t="inlineStr">
+      <c r="A115" s="7" t="inlineStr">
         <is>
           <t>7. システムとIT環境（選抜拠点ヒアリング・7-01〜7-14）</t>
         </is>
       </c>
-      <c r="B115" s="7" t="n"/>
-      <c r="C115" s="7" t="n"/>
-      <c r="D115" s="7" t="n"/>
-      <c r="E115" s="7" t="n"/>
-      <c r="F115" s="7" t="n"/>
-      <c r="G115" s="7" t="n"/>
-      <c r="H115" s="7" t="n"/>
-      <c r="I115" s="7" t="n"/>
+      <c r="B115" s="8" t="n"/>
+      <c r="C115" s="8" t="n"/>
+      <c r="D115" s="8" t="n"/>
+      <c r="E115" s="8" t="n"/>
+      <c r="F115" s="8" t="n"/>
+      <c r="G115" s="8" t="n"/>
+      <c r="H115" s="8" t="n"/>
+      <c r="I115" s="8" t="n"/>
     </row>
     <row r="116" ht="52" customHeight="1">
-      <c r="A116" s="8" t="inlineStr">
+      <c r="A116" s="9" t="inlineStr">
         <is>
           <t>7-01</t>
         </is>
       </c>
-      <c r="B116" s="9" t="inlineStr">
+      <c r="B116" s="10" t="inlineStr">
         <is>
           <t>システム</t>
         </is>
       </c>
-      <c r="C116" s="10" t="inlineStr">
+      <c r="C116" s="11" t="inlineStr">
         <is>
           <t>拠点の業務システム全量</t>
         </is>
       </c>
-      <c r="D116" s="9" t="inlineStr">
+      <c r="D116" s="10" t="inlineStr">
         <is>
           <t>記述〔ヒアリング〕</t>
         </is>
       </c>
-      <c r="E116" s="9" t="n">
+      <c r="E116" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="F116" s="10" t="inlineStr">
+      <c r="F116" s="11" t="inlineStr">
         <is>
           <t>連携対象の全量が不明＝アーキテクチャ（外部IF一覧）が設計できず、RFPの連携要件が欠落。ベンダー見積りに高値バッファ。</t>
         </is>
       </c>
-      <c r="G116" s="10" t="inlineStr">
+      <c r="G116" s="11" t="inlineStr">
         <is>
           <t>外部IF一覧・アーキテクチャ</t>
         </is>
       </c>
-      <c r="H116" s="13" t="inlineStr">
+      <c r="H116" s="14" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="I116" s="10" t="inlineStr">
+      <c r="I116" s="11" t="inlineStr">
         <is>
           <t>「連携対象なし（全て手入力）」とみなす。後日の連携追加費用は当該拠点起因。</t>
         </is>
       </c>
     </row>
     <row r="117" ht="52" customHeight="1">
-      <c r="A117" s="8" t="inlineStr">
+      <c r="A117" s="9" t="inlineStr">
         <is>
           <t>7-02</t>
         </is>
       </c>
-      <c r="B117" s="9" t="inlineStr">
+      <c r="B117" s="10" t="inlineStr">
         <is>
           <t>システム</t>
         </is>
       </c>
-      <c r="C117" s="10" t="inlineStr">
+      <c r="C117" s="11" t="inlineStr">
         <is>
           <t>各システムのデータ出力可否</t>
         </is>
       </c>
-      <c r="D117" s="9" t="inlineStr">
+      <c r="D117" s="10" t="inlineStr">
         <is>
           <t>記述〔ヒアリング〕</t>
         </is>
       </c>
-      <c r="E117" s="9" t="n">
+      <c r="E117" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="F117" s="10" t="inlineStr">
+      <c r="F117" s="11" t="inlineStr">
         <is>
           <t>連携方式（API/CSV/手入力）が確定できない。</t>
         </is>
       </c>
-      <c r="G117" s="10" t="inlineStr">
+      <c r="G117" s="11" t="inlineStr">
         <is>
           <t>連携方式設計</t>
         </is>
       </c>
-      <c r="H117" s="13" t="inlineStr">
+      <c r="H117" s="14" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="I117" s="10" t="inlineStr">
+      <c r="I117" s="11" t="inlineStr">
         <is>
           <t>「出力不可」とみなす。</t>
         </is>
       </c>
     </row>
     <row r="118" ht="52" customHeight="1">
-      <c r="A118" s="8" t="inlineStr">
+      <c r="A118" s="9" t="inlineStr">
         <is>
           <t>7-03</t>
         </is>
       </c>
-      <c r="B118" s="9" t="inlineStr">
+      <c r="B118" s="10" t="inlineStr">
         <is>
           <t>システム</t>
         </is>
       </c>
-      <c r="C118" s="10" t="inlineStr">
+      <c r="C118" s="11" t="inlineStr">
         <is>
           <t>SAPとの関係・ユーティリティ費用の計上コード</t>
         </is>
       </c>
-      <c r="D118" s="9" t="inlineStr">
+      <c r="D118" s="10" t="inlineStr">
         <is>
           <t>記述〔ヒアリング〕</t>
         </is>
       </c>
-      <c r="E118" s="9" t="n">
+      <c r="E118" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="F118" s="10" t="inlineStr">
+      <c r="F118" s="11" t="inlineStr">
         <is>
           <t>SAP連携仕様（費用データからの活動量推計・勘定科目粒度）が設計できない。</t>
         </is>
       </c>
-      <c r="G118" s="10" t="inlineStr">
+      <c r="G118" s="11" t="inlineStr">
         <is>
           <t>SAP連携仕様</t>
         </is>
       </c>
-      <c r="H118" s="13" t="inlineStr">
+      <c r="H118" s="14" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="I118" s="10" t="inlineStr">
+      <c r="I118" s="11" t="inlineStr">
         <is>
           <t>「連携不可」とみなしSAP連携を対象外化。</t>
         </is>
       </c>
     </row>
     <row r="119" ht="52" customHeight="1">
-      <c r="A119" s="8" t="inlineStr">
+      <c r="A119" s="9" t="inlineStr">
         <is>
           <t>7-04</t>
         </is>
       </c>
-      <c r="B119" s="9" t="inlineStr">
+      <c r="B119" s="10" t="inlineStr">
         <is>
           <t>システム</t>
         </is>
       </c>
-      <c r="C119" s="10" t="inlineStr">
+      <c r="C119" s="11" t="inlineStr">
         <is>
           <t>会計システムからの費用データ抽出可否</t>
         </is>
       </c>
-      <c r="D119" s="9" t="inlineStr">
+      <c r="D119" s="10" t="inlineStr">
         <is>
           <t>選択+補足〔ヒアリング〕</t>
         </is>
       </c>
-      <c r="E119" s="9" t="n">
+      <c r="E119" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="F119" s="10" t="inlineStr">
+      <c r="F119" s="11" t="inlineStr">
         <is>
           <t>金額ベース推計（支出ベース算定）のフォールバック経路が使えるか不明。</t>
         </is>
       </c>
-      <c r="G119" s="10" t="inlineStr">
+      <c r="G119" s="11" t="inlineStr">
         <is>
           <t>支出ベース算定</t>
         </is>
       </c>
-      <c r="H119" s="11" t="inlineStr">
+      <c r="H119" s="12" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="I119" s="10" t="inlineStr">
+      <c r="I119" s="11" t="inlineStr">
         <is>
           <t>「抽出不可」とみなす。</t>
         </is>
       </c>
     </row>
     <row r="120" ht="52" customHeight="1">
-      <c r="A120" s="8" t="inlineStr">
+      <c r="A120" s="9" t="inlineStr">
         <is>
           <t>7-05</t>
         </is>
       </c>
-      <c r="B120" s="9" t="inlineStr">
+      <c r="B120" s="10" t="inlineStr">
         <is>
           <t>計測</t>
         </is>
       </c>
-      <c r="C120" s="10" t="inlineStr">
+      <c r="C120" s="11" t="inlineStr">
         <is>
           <t>BEMS/FEMS・スマートメーターの有無とデータ取出</t>
         </is>
       </c>
-      <c r="D120" s="9" t="inlineStr">
+      <c r="D120" s="10" t="inlineStr">
         <is>
           <t>選択+補足〔ヒアリング〕</t>
         </is>
       </c>
-      <c r="E120" s="9" t="n">
+      <c r="E120" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="F120" s="10" t="inlineStr">
+      <c r="F120" s="11" t="inlineStr">
         <is>
           <t>自動計測連携の対象が確定できない。</t>
         </is>
       </c>
-      <c r="G120" s="10" t="inlineStr">
+      <c r="G120" s="11" t="inlineStr">
         <is>
           <t>計測データ連携</t>
         </is>
       </c>
-      <c r="H120" s="11" t="inlineStr">
+      <c r="H120" s="12" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="I120" s="10" t="inlineStr">
+      <c r="I120" s="11" t="inlineStr">
         <is>
           <t>「なし」とみなす。</t>
         </is>
       </c>
     </row>
     <row r="121" ht="52" customHeight="1">
-      <c r="A121" s="8" t="inlineStr">
+      <c r="A121" s="9" t="inlineStr">
         <is>
           <t>7-06</t>
         </is>
       </c>
-      <c r="B121" s="9" t="inlineStr">
+      <c r="B121" s="10" t="inlineStr">
         <is>
           <t>計測</t>
         </is>
       </c>
-      <c r="C121" s="10" t="inlineStr">
+      <c r="C121" s="11" t="inlineStr">
         <is>
           <t>電力会社Web明細等の利用状況</t>
         </is>
       </c>
-      <c r="D121" s="9" t="inlineStr">
+      <c r="D121" s="10" t="inlineStr">
         <is>
           <t>選択+補足〔ヒアリング〕</t>
         </is>
       </c>
-      <c r="E121" s="9" t="n">
+      <c r="E121" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="F121" s="10" t="inlineStr">
+      <c r="F121" s="11" t="inlineStr">
         <is>
           <t>C-15の詳細。</t>
         </is>
       </c>
-      <c r="G121" s="10" t="inlineStr">
+      <c r="G121" s="11" t="inlineStr">
         <is>
           <t>自動取込</t>
         </is>
       </c>
-      <c r="H121" s="11" t="inlineStr">
+      <c r="H121" s="12" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="I121" s="10" t="inlineStr">
+      <c r="I121" s="11" t="inlineStr">
         <is>
           <t>「利用不可」とみなす。</t>
         </is>
       </c>
     </row>
     <row r="122" ht="52" customHeight="1">
-      <c r="A122" s="8" t="inlineStr">
+      <c r="A122" s="9" t="inlineStr">
         <is>
           <t>7-07</t>
         </is>
       </c>
-      <c r="B122" s="9" t="inlineStr">
+      <c r="B122" s="10" t="inlineStr">
         <is>
           <t>計測</t>
         </is>
       </c>
-      <c r="C122" s="10" t="inlineStr">
+      <c r="C122" s="11" t="inlineStr">
         <is>
           <t>子メーターの設置状況・検針方法</t>
         </is>
       </c>
-      <c r="D122" s="9" t="inlineStr">
+      <c r="D122" s="10" t="inlineStr">
         <is>
           <t>記述〔ヒアリング〕</t>
         </is>
       </c>
-      <c r="E122" s="9" t="n">
+      <c r="E122" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="F122" s="10" t="inlineStr">
+      <c r="F122" s="11" t="inlineStr">
         <is>
           <t>データ粒度（建屋別・部門別）の実現可能性が不明。細かい粒度の開示・按分要件が物理的に満たせない可能性。</t>
         </is>
       </c>
-      <c r="G122" s="10" t="inlineStr">
+      <c r="G122" s="11" t="inlineStr">
         <is>
           <t>データ粒度設計</t>
         </is>
       </c>
-      <c r="H122" s="11" t="inlineStr">
+      <c r="H122" s="12" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="I122" s="10" t="inlineStr">
+      <c r="I122" s="11" t="inlineStr">
         <is>
           <t>「拠点全体計のみ」とみなし細粒度要件を断念（粒度不足は当該拠点起因）。</t>
         </is>
       </c>
     </row>
     <row r="123" ht="52" customHeight="1">
-      <c r="A123" s="8" t="inlineStr">
+      <c r="A123" s="9" t="inlineStr">
         <is>
           <t>7-08</t>
         </is>
       </c>
-      <c r="B123" s="9" t="inlineStr">
+      <c r="B123" s="10" t="inlineStr">
         <is>
           <t>インフラ</t>
         </is>
       </c>
-      <c r="C123" s="10" t="inlineStr">
+      <c r="C123" s="11" t="inlineStr">
         <is>
           <t>SaaSアクセス制限の詳細</t>
         </is>
       </c>
-      <c r="D123" s="9" t="inlineStr">
+      <c r="D123" s="10" t="inlineStr">
         <is>
           <t>選択+補足〔ヒアリング〕</t>
         </is>
       </c>
-      <c r="E123" s="9" t="n">
+      <c r="E123" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="F123" s="10" t="inlineStr">
+      <c r="F123" s="11" t="inlineStr">
         <is>
           <t>C-16の詳細。アーキテクチャ成立性。</t>
         </is>
       </c>
-      <c r="G123" s="10" t="inlineStr">
+      <c r="G123" s="11" t="inlineStr">
         <is>
           <t>ネットワーク要件</t>
         </is>
       </c>
-      <c r="H123" s="13" t="inlineStr">
+      <c r="H123" s="14" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="I123" s="10" t="inlineStr">
+      <c r="I123" s="11" t="inlineStr">
         <is>
           <t>「制限あり」とみなす。</t>
         </is>
       </c>
     </row>
     <row r="124" ht="52" customHeight="1">
-      <c r="A124" s="8" t="inlineStr">
+      <c r="A124" s="9" t="inlineStr">
         <is>
           <t>7-09</t>
         </is>
       </c>
-      <c r="B124" s="9" t="inlineStr">
+      <c r="B124" s="10" t="inlineStr">
         <is>
           <t>インフラ</t>
         </is>
       </c>
-      <c r="C124" s="10" t="inlineStr">
+      <c r="C124" s="11" t="inlineStr">
         <is>
           <t>現場のネットワーク・デバイス環境</t>
         </is>
       </c>
-      <c r="D124" s="9" t="inlineStr">
+      <c r="D124" s="10" t="inlineStr">
         <is>
           <t>記述〔ヒアリング〕</t>
         </is>
       </c>
-      <c r="E124" s="9" t="n">
+      <c r="E124" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="F124" s="10" t="inlineStr">
+      <c r="F124" s="11" t="inlineStr">
         <is>
           <t>入力UI（モバイル・オフライン）要件が決められない。</t>
         </is>
       </c>
-      <c r="G124" s="10" t="inlineStr">
+      <c r="G124" s="11" t="inlineStr">
         <is>
           <t>デバイス・UI要件</t>
         </is>
       </c>
-      <c r="H124" s="11" t="inlineStr">
+      <c r="H124" s="12" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="I124" s="10" t="inlineStr">
+      <c r="I124" s="11" t="inlineStr">
         <is>
           <t>「制約あり」とみなす。</t>
         </is>
       </c>
     </row>
     <row r="125" ht="52" customHeight="1">
-      <c r="A125" s="8" t="inlineStr">
+      <c r="A125" s="9" t="inlineStr">
         <is>
           <t>7-10</t>
         </is>
       </c>
-      <c r="B125" s="9" t="inlineStr">
+      <c r="B125" s="10" t="inlineStr">
         <is>
           <t>インフラ</t>
         </is>
       </c>
-      <c r="C125" s="10" t="inlineStr">
+      <c r="C125" s="11" t="inlineStr">
         <is>
           <t>電子承認WFの導入状況（製品名）</t>
         </is>
       </c>
-      <c r="D125" s="9" t="inlineStr">
+      <c r="D125" s="10" t="inlineStr">
         <is>
           <t>選択+補足〔ヒアリング〕</t>
         </is>
       </c>
-      <c r="E125" s="9" t="n">
+      <c r="E125" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="F125" s="10" t="inlineStr">
+      <c r="F125" s="11" t="inlineStr">
         <is>
           <t>既存WF流用可否が不明のまま新規実装＝二重投資リスク。</t>
         </is>
       </c>
-      <c r="G125" s="10" t="inlineStr">
+      <c r="G125" s="11" t="inlineStr">
         <is>
           <t>WF実装方式</t>
         </is>
       </c>
-      <c r="H125" s="11" t="inlineStr">
+      <c r="H125" s="12" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="I125" s="10" t="inlineStr">
+      <c r="I125" s="11" t="inlineStr">
         <is>
           <t>「流用不可」とみなし新規実装。</t>
         </is>
       </c>
     </row>
     <row r="126" ht="52" customHeight="1">
-      <c r="A126" s="8" t="inlineStr">
+      <c r="A126" s="9" t="inlineStr">
         <is>
           <t>7-11</t>
         </is>
       </c>
-      <c r="B126" s="9" t="inlineStr">
+      <c r="B126" s="10" t="inlineStr">
         <is>
           <t>インフラ</t>
         </is>
       </c>
-      <c r="C126" s="10" t="inlineStr">
+      <c r="C126" s="11" t="inlineStr">
         <is>
           <t>OS・Office・マクロ実行可否</t>
         </is>
       </c>
-      <c r="D126" s="9" t="inlineStr">
+      <c r="D126" s="10" t="inlineStr">
         <is>
           <t>記述〔ヒアリング〕</t>
         </is>
       </c>
-      <c r="E126" s="9" t="n">
+      <c r="E126" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="F126" s="10" t="inlineStr">
+      <c r="F126" s="11" t="inlineStr">
         <is>
           <t>クライアント要件・移行制約の確認漏れ。</t>
         </is>
       </c>
-      <c r="G126" s="10" t="inlineStr">
+      <c r="G126" s="11" t="inlineStr">
         <is>
           <t>クライアント要件</t>
         </is>
       </c>
-      <c r="H126" s="14" t="inlineStr">
+      <c r="H126" s="15" t="inlineStr">
         <is>
           <t>低</t>
         </is>
       </c>
-      <c r="I126" s="10" t="inlineStr">
+      <c r="I126" s="11" t="inlineStr">
         <is>
           <t>「標準環境」とみなす。</t>
         </is>
       </c>
     </row>
     <row r="127" ht="52" customHeight="1">
-      <c r="A127" s="8" t="inlineStr">
+      <c r="A127" s="9" t="inlineStr">
         <is>
           <t>7-12</t>
         </is>
       </c>
-      <c r="B127" s="9" t="inlineStr">
+      <c r="B127" s="10" t="inlineStr">
         <is>
           <t>インフラ</t>
         </is>
       </c>
-      <c r="C127" s="10" t="inlineStr">
+      <c r="C127" s="11" t="inlineStr">
         <is>
           <t>ITサポート体制</t>
         </is>
       </c>
-      <c r="D127" s="9" t="inlineStr">
+      <c r="D127" s="10" t="inlineStr">
         <is>
           <t>記述〔ヒアリング〕</t>
         </is>
       </c>
-      <c r="E127" s="9" t="n">
+      <c r="E127" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="F127" s="10" t="inlineStr">
+      <c r="F127" s="11" t="inlineStr">
         <is>
           <t>導入・展開時の現地IT支援の有無が不明で、展開計画の実現性が検証できない。</t>
         </is>
       </c>
-      <c r="G127" s="10" t="inlineStr">
+      <c r="G127" s="11" t="inlineStr">
         <is>
           <t>展開計画</t>
         </is>
       </c>
-      <c r="H127" s="11" t="inlineStr">
+      <c r="H127" s="12" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="I127" s="10" t="inlineStr">
+      <c r="I127" s="11" t="inlineStr">
         <is>
           <t>「支援なし」とみなし本社リモート支援を計画化。</t>
         </is>
       </c>
     </row>
     <row r="128" ht="52" customHeight="1">
-      <c r="A128" s="8" t="inlineStr">
+      <c r="A128" s="9" t="inlineStr">
         <is>
           <t>7-13</t>
         </is>
       </c>
-      <c r="B128" s="9" t="inlineStr">
+      <c r="B128" s="10" t="inlineStr">
         <is>
           <t>教訓</t>
         </is>
       </c>
-      <c r="C128" s="10" t="inlineStr">
+      <c r="C128" s="11" t="inlineStr">
         <is>
           <t>定着しなかったシステムとその理由</t>
         </is>
       </c>
-      <c r="D128" s="9" t="inlineStr">
+      <c r="D128" s="10" t="inlineStr">
         <is>
           <t>記述〔ヒアリング〕</t>
         </is>
       </c>
-      <c r="E128" s="9" t="n">
+      <c r="E128" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="F128" s="10" t="inlineStr">
+      <c r="F128" s="11" t="inlineStr">
         <is>
           <t>失敗要因（操作性・言語・負荷）を要件に反映できず、同じ失敗を繰り返す。難所⑦（定着）の最重要インプット。</t>
         </is>
       </c>
-      <c r="G128" s="10" t="inlineStr">
+      <c r="G128" s="11" t="inlineStr">
         <is>
           <t>定着要件・難所⑦</t>
         </is>
       </c>
-      <c r="H128" s="13" t="inlineStr">
+      <c r="H128" s="14" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="I128" s="10" t="inlineStr">
+      <c r="I128" s="11" t="inlineStr">
         <is>
           <t>「失敗経験あり・要因不明」とみなしUI・研修要件を厚めに設計。</t>
         </is>
       </c>
     </row>
     <row r="129" ht="52" customHeight="1">
-      <c r="A129" s="8" t="inlineStr">
+      <c r="A129" s="9" t="inlineStr">
         <is>
           <t>7-14</t>
         </is>
       </c>
-      <c r="B129" s="9" t="inlineStr">
+      <c r="B129" s="10" t="inlineStr">
         <is>
           <t>教訓</t>
         </is>
       </c>
-      <c r="C129" s="10" t="inlineStr">
+      <c r="C129" s="11" t="inlineStr">
         <is>
           <t>エコアシスト等の改善要望</t>
         </is>
       </c>
-      <c r="D129" s="9" t="inlineStr">
+      <c r="D129" s="10" t="inlineStr">
         <is>
           <t>記述〔ヒアリング〕</t>
         </is>
       </c>
-      <c r="E129" s="9" t="n">
+      <c r="E129" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="F129" s="10" t="inlineStr">
+      <c r="F129" s="11" t="inlineStr">
         <is>
           <t>UI要件のバックログを失うが根幹には影響しない。</t>
         </is>
       </c>
-      <c r="G129" s="10" t="inlineStr">
+      <c r="G129" s="11" t="inlineStr">
         <is>
           <t>UI改善バックログ</t>
         </is>
       </c>
-      <c r="H129" s="14" t="inlineStr">
+      <c r="H129" s="15" t="inlineStr">
         <is>
           <t>低</t>
         </is>
       </c>
-      <c r="I129" s="10" t="inlineStr">
+      <c r="I129" s="11" t="inlineStr">
         <is>
           <t>「要望なし」とみなす。</t>
         </is>
       </c>
     </row>
     <row r="130" ht="17" customHeight="1">
-      <c r="A130" s="6" t="inlineStr">
+      <c r="A130" s="7" t="inlineStr">
         <is>
           <t>8. 体制と工数（選抜拠点ヒアリング・8-01〜8-11）</t>
         </is>
       </c>
-      <c r="B130" s="7" t="n"/>
-      <c r="C130" s="7" t="n"/>
-      <c r="D130" s="7" t="n"/>
-      <c r="E130" s="7" t="n"/>
-      <c r="F130" s="7" t="n"/>
-      <c r="G130" s="7" t="n"/>
-      <c r="H130" s="7" t="n"/>
-      <c r="I130" s="7" t="n"/>
+      <c r="B130" s="8" t="n"/>
+      <c r="C130" s="8" t="n"/>
+      <c r="D130" s="8" t="n"/>
+      <c r="E130" s="8" t="n"/>
+      <c r="F130" s="8" t="n"/>
+      <c r="G130" s="8" t="n"/>
+      <c r="H130" s="8" t="n"/>
+      <c r="I130" s="8" t="n"/>
     </row>
     <row r="131" ht="52" customHeight="1">
-      <c r="A131" s="8" t="inlineStr">
+      <c r="A131" s="9" t="inlineStr">
         <is>
           <t>8-01</t>
         </is>
       </c>
-      <c r="B131" s="9" t="inlineStr">
+      <c r="B131" s="10" t="inlineStr">
         <is>
           <t>工数</t>
         </is>
       </c>
-      <c r="C131" s="10" t="inlineStr">
+      <c r="C131" s="11" t="inlineStr">
         <is>
           <t>月間工数の作業別内訳</t>
         </is>
       </c>
-      <c r="D131" s="9" t="inlineStr">
+      <c r="D131" s="10" t="inlineStr">
         <is>
           <t>記述〔ヒアリング〕</t>
         </is>
       </c>
-      <c r="E131" s="9" t="n">
+      <c r="E131" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="F131" s="10" t="inlineStr">
+      <c r="F131" s="11" t="inlineStr">
         <is>
           <t>C-17の詳細。ROI試算の分母が作れず投資対効果の定量説明が不能。</t>
         </is>
       </c>
-      <c r="G131" s="10" t="inlineStr">
+      <c r="G131" s="11" t="inlineStr">
         <is>
           <t>ROI試算</t>
         </is>
       </c>
-      <c r="H131" s="13" t="inlineStr">
+      <c r="H131" s="14" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="I131" s="10" t="inlineStr">
+      <c r="I131" s="11" t="inlineStr">
         <is>
           <t>当該拠点をROI算定から除外。</t>
         </is>
       </c>
     </row>
     <row r="132" ht="52" customHeight="1">
-      <c r="A132" s="8" t="inlineStr">
+      <c r="A132" s="9" t="inlineStr">
         <is>
           <t>8-02</t>
         </is>
       </c>
-      <c r="B132" s="9" t="inlineStr">
+      <c r="B132" s="10" t="inlineStr">
         <is>
           <t>工数</t>
         </is>
       </c>
-      <c r="C132" s="10" t="inlineStr">
+      <c r="C132" s="11" t="inlineStr">
         <is>
           <t>年次イベントの追加工数</t>
         </is>
       </c>
-      <c r="D132" s="9" t="inlineStr">
+      <c r="D132" s="10" t="inlineStr">
         <is>
           <t>記述〔ヒアリング〕</t>
         </is>
       </c>
-      <c r="E132" s="9" t="n">
+      <c r="E132" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="F132" s="10" t="inlineStr">
+      <c r="F132" s="11" t="inlineStr">
         <is>
           <t>繁忙期のピーク設計とROIの年次効果が欠落。</t>
         </is>
       </c>
-      <c r="G132" s="10" t="inlineStr">
+      <c r="G132" s="11" t="inlineStr">
         <is>
           <t>性能設計・ROI</t>
         </is>
       </c>
-      <c r="H132" s="11" t="inlineStr">
+      <c r="H132" s="12" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="I132" s="10" t="inlineStr">
+      <c r="I132" s="11" t="inlineStr">
         <is>
           <t>「年200時間」とみなす。</t>
         </is>
       </c>
     </row>
     <row r="133" ht="52" customHeight="1">
-      <c r="A133" s="8" t="inlineStr">
+      <c r="A133" s="9" t="inlineStr">
         <is>
           <t>8-03</t>
         </is>
       </c>
-      <c r="B133" s="9" t="inlineStr">
+      <c r="B133" s="10" t="inlineStr">
         <is>
           <t>工数</t>
         </is>
       </c>
-      <c r="C133" s="10" t="inlineStr">
+      <c r="C133" s="11" t="inlineStr">
         <is>
           <t>本社照会・差し戻しの件数・時間</t>
         </is>
       </c>
-      <c r="D133" s="9" t="inlineStr">
+      <c r="D133" s="10" t="inlineStr">
         <is>
           <t>記述〔ヒアリング〕</t>
         </is>
       </c>
-      <c r="E133" s="9" t="n">
+      <c r="E133" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="F133" s="10" t="inlineStr">
+      <c r="F133" s="11" t="inlineStr">
         <is>
           <t>データ品質の現状値（差戻し率）が不明で、品質改善効果が測定できない。</t>
         </is>
       </c>
-      <c r="G133" s="10" t="inlineStr">
+      <c r="G133" s="11" t="inlineStr">
         <is>
           <t>品質KPI・差戻しフロー</t>
         </is>
       </c>
-      <c r="H133" s="11" t="inlineStr">
+      <c r="H133" s="12" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="I133" s="10" t="inlineStr">
+      <c r="I133" s="11" t="inlineStr">
         <is>
           <t>「月5件・10時間」とみなす。</t>
         </is>
       </c>
     </row>
     <row r="134" ht="52" customHeight="1">
-      <c r="A134" s="8" t="inlineStr">
+      <c r="A134" s="9" t="inlineStr">
         <is>
           <t>8-04</t>
         </is>
       </c>
-      <c r="B134" s="9" t="inlineStr">
+      <c r="B134" s="10" t="inlineStr">
         <is>
           <t>体制</t>
         </is>
       </c>
-      <c r="C134" s="10" t="inlineStr">
+      <c r="C134" s="11" t="inlineStr">
         <is>
           <t>関与人数（主担当・副担当・承認者）と兼務状況</t>
         </is>
       </c>
-      <c r="D134" s="9" t="inlineStr">
+      <c r="D134" s="10" t="inlineStr">
         <is>
           <t>記述〔ヒアリング〕</t>
         </is>
       </c>
-      <c r="E134" s="9" t="n">
+      <c r="E134" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="F134" s="10" t="inlineStr">
+      <c r="F134" s="11" t="inlineStr">
         <is>
           <t>ユーザー数＝ライセンス数・アカウント数が見積れず、RFPのコスト前提が狂う。ベンダー見積りの重要変数。</t>
         </is>
       </c>
-      <c r="G134" s="10" t="inlineStr">
+      <c r="G134" s="11" t="inlineStr">
         <is>
           <t>ライセンス数・RFPコスト前提</t>
         </is>
       </c>
-      <c r="H134" s="13" t="inlineStr">
+      <c r="H134" s="14" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="I134" s="10" t="inlineStr">
+      <c r="I134" s="11" t="inlineStr">
         <is>
           <t>「1拠点3ユーザー」とみなす。超過分のライセンス追加費用は当該拠点起因。</t>
         </is>
       </c>
     </row>
     <row r="135" ht="52" customHeight="1">
-      <c r="A135" s="8" t="inlineStr">
+      <c r="A135" s="9" t="inlineStr">
         <is>
           <t>8-05</t>
         </is>
       </c>
-      <c r="B135" s="9" t="inlineStr">
+      <c r="B135" s="10" t="inlineStr">
         <is>
           <t>体制</t>
         </is>
       </c>
-      <c r="C135" s="10" t="inlineStr">
+      <c r="C135" s="11" t="inlineStr">
         <is>
           <t>主担当の在籍年数・交代回数</t>
         </is>
       </c>
-      <c r="D135" s="9" t="inlineStr">
+      <c r="D135" s="10" t="inlineStr">
         <is>
           <t>記述〔ヒアリング〕</t>
         </is>
       </c>
-      <c r="E135" s="9" t="n">
+      <c r="E135" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="F135" s="10" t="inlineStr">
+      <c r="F135" s="11" t="inlineStr">
         <is>
           <t>教育要件の規模感が不明。</t>
         </is>
       </c>
-      <c r="G135" s="10" t="inlineStr">
+      <c r="G135" s="11" t="inlineStr">
         <is>
           <t>教育要件</t>
         </is>
       </c>
-      <c r="H135" s="14" t="inlineStr">
+      <c r="H135" s="15" t="inlineStr">
         <is>
           <t>低</t>
         </is>
       </c>
-      <c r="I135" s="10" t="inlineStr">
+      <c r="I135" s="11" t="inlineStr">
         <is>
           <t>「交代頻繁」とみなす。</t>
         </is>
       </c>
     </row>
     <row r="136" ht="52" customHeight="1">
-      <c r="A136" s="8" t="inlineStr">
+      <c r="A136" s="9" t="inlineStr">
         <is>
           <t>8-06</t>
         </is>
       </c>
-      <c r="B136" s="9" t="inlineStr">
+      <c r="B136" s="10" t="inlineStr">
         <is>
           <t>体制</t>
         </is>
       </c>
-      <c r="C136" s="10" t="inlineStr">
+      <c r="C136" s="11" t="inlineStr">
         <is>
           <t>「この人がいないと回らない」業務・知識</t>
         </is>
       </c>
-      <c r="D136" s="9" t="inlineStr">
+      <c r="D136" s="10" t="inlineStr">
         <is>
           <t>記述〔ヒアリング〕</t>
         </is>
       </c>
-      <c r="E136" s="9" t="n">
+      <c r="E136" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="F136" s="10" t="inlineStr">
+      <c r="F136" s="11" t="inlineStr">
         <is>
           <t>属人知識の機能化（システムに埋め込むべきガイド・チェック）対象が特定できない。</t>
         </is>
       </c>
-      <c r="G136" s="10" t="inlineStr">
+      <c r="G136" s="11" t="inlineStr">
         <is>
           <t>フールプルーフ設計</t>
         </is>
       </c>
-      <c r="H136" s="11" t="inlineStr">
+      <c r="H136" s="12" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="I136" s="10" t="inlineStr">
+      <c r="I136" s="11" t="inlineStr">
         <is>
           <t>「属人知識あり・内容不明」とみなす。</t>
         </is>
       </c>
     </row>
     <row r="137" ht="52" customHeight="1">
-      <c r="A137" s="8" t="inlineStr">
+      <c r="A137" s="9" t="inlineStr">
         <is>
           <t>8-07</t>
         </is>
       </c>
-      <c r="B137" s="9" t="inlineStr">
+      <c r="B137" s="10" t="inlineStr">
         <is>
           <t>体制</t>
         </is>
       </c>
-      <c r="C137" s="10" t="inlineStr">
+      <c r="C137" s="11" t="inlineStr">
         <is>
           <t>引継ぎ資料の有無と質</t>
         </is>
       </c>
-      <c r="D137" s="9" t="inlineStr">
+      <c r="D137" s="10" t="inlineStr">
         <is>
           <t>選択+補足〔ヒアリング〕</t>
         </is>
       </c>
-      <c r="E137" s="9" t="n">
+      <c r="E137" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="F137" s="10" t="inlineStr">
+      <c r="F137" s="11" t="inlineStr">
         <is>
           <t>同上。</t>
         </is>
       </c>
-      <c r="G137" s="10" t="inlineStr">
+      <c r="G137" s="11" t="inlineStr">
         <is>
           <t>教育・マニュアル要件</t>
         </is>
       </c>
-      <c r="H137" s="14" t="inlineStr">
+      <c r="H137" s="15" t="inlineStr">
         <is>
           <t>低</t>
         </is>
       </c>
-      <c r="I137" s="10" t="inlineStr">
+      <c r="I137" s="11" t="inlineStr">
         <is>
           <t>「実質なし」とみなす。</t>
         </is>
       </c>
     </row>
     <row r="138" ht="52" customHeight="1">
-      <c r="A138" s="8" t="inlineStr">
+      <c r="A138" s="9" t="inlineStr">
         <is>
           <t>8-08</t>
         </is>
       </c>
-      <c r="B138" s="9" t="inlineStr">
+      <c r="B138" s="10" t="inlineStr">
         <is>
           <t>スキル</t>
         </is>
       </c>
-      <c r="C138" s="10" t="inlineStr">
+      <c r="C138" s="11" t="inlineStr">
         <is>
           <t>担当者のスキル自己評価</t>
         </is>
       </c>
-      <c r="D138" s="9" t="inlineStr">
+      <c r="D138" s="10" t="inlineStr">
         <is>
           <t>記述〔ヒアリング〕</t>
         </is>
       </c>
-      <c r="E138" s="9" t="n">
+      <c r="E138" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="F138" s="10" t="inlineStr">
+      <c r="F138" s="11" t="inlineStr">
         <is>
           <t>UI複雑度・研修設計の前提が不明。高機能UIを設計しても使いこなせないリスク。</t>
         </is>
       </c>
-      <c r="G138" s="10" t="inlineStr">
+      <c r="G138" s="11" t="inlineStr">
         <is>
           <t>UI要件・研修設計</t>
         </is>
       </c>
-      <c r="H138" s="11" t="inlineStr">
+      <c r="H138" s="12" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="I138" s="10" t="inlineStr">
+      <c r="I138" s="11" t="inlineStr">
         <is>
           <t>「Excel基本操作レベル」とみなしシンプルUI必須。</t>
         </is>
       </c>
     </row>
     <row r="139" ht="52" customHeight="1">
-      <c r="A139" s="8" t="inlineStr">
+      <c r="A139" s="9" t="inlineStr">
         <is>
           <t>8-09</t>
         </is>
       </c>
-      <c r="B139" s="9" t="inlineStr">
+      <c r="B139" s="10" t="inlineStr">
         <is>
           <t>スキル</t>
         </is>
       </c>
-      <c r="C139" s="10" t="inlineStr">
+      <c r="C139" s="11" t="inlineStr">
         <is>
           <t>新システムへの期待と不安</t>
         </is>
       </c>
-      <c r="D139" s="9" t="inlineStr">
+      <c r="D139" s="10" t="inlineStr">
         <is>
           <t>記述〔ヒアリング〕</t>
         </is>
       </c>
-      <c r="E139" s="9" t="n">
+      <c r="E139" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="F139" s="10" t="inlineStr">
+      <c r="F139" s="11" t="inlineStr">
         <is>
           <t>チェンジマネジメントの材料。</t>
         </is>
       </c>
-      <c r="G139" s="10" t="inlineStr">
+      <c r="G139" s="11" t="inlineStr">
         <is>
           <t>定着計画</t>
         </is>
       </c>
-      <c r="H139" s="14" t="inlineStr">
+      <c r="H139" s="15" t="inlineStr">
         <is>
           <t>低</t>
         </is>
       </c>
-      <c r="I139" s="10" t="inlineStr">
+      <c r="I139" s="11" t="inlineStr">
         <is>
           <t>「不安あり」とみなす。</t>
         </is>
       </c>
     </row>
     <row r="140" ht="52" customHeight="1">
-      <c r="A140" s="8" t="inlineStr">
+      <c r="A140" s="9" t="inlineStr">
         <is>
           <t>8-10</t>
         </is>
       </c>
-      <c r="B140" s="9" t="inlineStr">
+      <c r="B140" s="10" t="inlineStr">
         <is>
           <t>スキル</t>
         </is>
       </c>
-      <c r="C140" s="10" t="inlineStr">
+      <c r="C140" s="11" t="inlineStr">
         <is>
           <t>業務の拠点内での位置づけ</t>
         </is>
       </c>
-      <c r="D140" s="9" t="inlineStr">
+      <c r="D140" s="10" t="inlineStr">
         <is>
           <t>記述〔ヒアリング〕</t>
         </is>
       </c>
-      <c r="E140" s="9" t="n">
+      <c r="E140" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="F140" s="10" t="inlineStr">
+      <c r="F140" s="11" t="inlineStr">
         <is>
           <t>「片手間仕事」扱いの拠点は入力遅延の高リスク拠点。督促設計・経営巻き込みの対象特定ができない。</t>
         </is>
       </c>
-      <c r="G140" s="10" t="inlineStr">
+      <c r="G140" s="11" t="inlineStr">
         <is>
           <t>定着リスク評価</t>
         </is>
       </c>
-      <c r="H140" s="11" t="inlineStr">
+      <c r="H140" s="12" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="I140" s="10" t="inlineStr">
+      <c r="I140" s="11" t="inlineStr">
         <is>
           <t>「片手間扱い」とみなし高リスク拠点として督促を強化。</t>
         </is>
       </c>
     </row>
     <row r="141" ht="52" customHeight="1">
-      <c r="A141" s="8" t="inlineStr">
+      <c r="A141" s="9" t="inlineStr">
         <is>
           <t>8-11</t>
         </is>
       </c>
-      <c r="B141" s="9" t="inlineStr">
+      <c r="B141" s="10" t="inlineStr">
         <is>
           <t>スキル</t>
         </is>
       </c>
-      <c r="C141" s="10" t="inlineStr">
+      <c r="C141" s="11" t="inlineStr">
         <is>
           <t>自動化で浮いた時間でやりたい業務</t>
         </is>
       </c>
-      <c r="D141" s="9" t="inlineStr">
+      <c r="D141" s="10" t="inlineStr">
         <is>
           <t>記述〔ヒアリング〕</t>
         </is>
       </c>
-      <c r="E141" s="9" t="n">
+      <c r="E141" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="F141" s="10" t="inlineStr">
+      <c r="F141" s="11" t="inlineStr">
         <is>
           <t>効果の定性ストーリー（攻めの説明材料）を失うが根幹には影響しない。</t>
         </is>
       </c>
-      <c r="G141" s="10" t="inlineStr">
+      <c r="G141" s="11" t="inlineStr">
         <is>
           <t>効果ストーリー</t>
         </is>
       </c>
-      <c r="H141" s="14" t="inlineStr">
+      <c r="H141" s="15" t="inlineStr">
         <is>
           <t>低</t>
         </is>
       </c>
-      <c r="I141" s="10" t="inlineStr">
+      <c r="I141" s="11" t="inlineStr">
         <is>
           <t>記載なしで進める。</t>
         </is>
       </c>
     </row>
     <row r="142" ht="17" customHeight="1">
-      <c r="A142" s="6" t="inlineStr">
+      <c r="A142" s="7" t="inlineStr">
         <is>
           <t>9. 海外拠点固有（選抜拠点ヒアリング・9-01〜9-14）</t>
         </is>
       </c>
-      <c r="B142" s="7" t="n"/>
-      <c r="C142" s="7" t="n"/>
-      <c r="D142" s="7" t="n"/>
-      <c r="E142" s="7" t="n"/>
-      <c r="F142" s="7" t="n"/>
-      <c r="G142" s="7" t="n"/>
-      <c r="H142" s="7" t="n"/>
-      <c r="I142" s="7" t="n"/>
+      <c r="B142" s="8" t="n"/>
+      <c r="C142" s="8" t="n"/>
+      <c r="D142" s="8" t="n"/>
+      <c r="E142" s="8" t="n"/>
+      <c r="F142" s="8" t="n"/>
+      <c r="G142" s="8" t="n"/>
+      <c r="H142" s="8" t="n"/>
+      <c r="I142" s="8" t="n"/>
     </row>
     <row r="143" ht="52" customHeight="1">
-      <c r="A143" s="8" t="inlineStr">
+      <c r="A143" s="9" t="inlineStr">
         <is>
           <t>9-01</t>
         </is>
       </c>
-      <c r="B143" s="9" t="inlineStr">
+      <c r="B143" s="10" t="inlineStr">
         <is>
           <t>言語</t>
         </is>
       </c>
-      <c r="C143" s="10" t="inlineStr">
+      <c r="C143" s="11" t="inlineStr">
         <is>
           <t>業務・帳票・システムの言語と翻訳体制</t>
         </is>
       </c>
-      <c r="D143" s="9" t="inlineStr">
+      <c r="D143" s="10" t="inlineStr">
         <is>
           <t>記述〔ヒアリング〕</t>
         </is>
       </c>
-      <c r="E143" s="9" t="n">
+      <c r="E143" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="F143" s="10" t="inlineStr">
+      <c r="F143" s="11" t="inlineStr">
         <is>
           <t>多言語UI・翻訳運用の要件（対象言語・翻訳責任）が決められない。RFPの必須要件が確定しない。</t>
         </is>
       </c>
-      <c r="G143" s="10" t="inlineStr">
+      <c r="G143" s="11" t="inlineStr">
         <is>
           <t>多言語要件・RFP必須要件</t>
         </is>
       </c>
-      <c r="H143" s="13" t="inlineStr">
+      <c r="H143" s="14" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="I143" s="10" t="inlineStr">
+      <c r="I143" s="11" t="inlineStr">
         <is>
           <t>「現地語のみ・翻訳者なし」とみなし多言語UI＋翻訳運用を必須化（費用増）。</t>
         </is>
       </c>
     </row>
     <row r="144" ht="52" customHeight="1">
-      <c r="A144" s="8" t="inlineStr">
+      <c r="A144" s="9" t="inlineStr">
         <is>
           <t>9-02</t>
         </is>
       </c>
-      <c r="B144" s="9" t="inlineStr">
+      <c r="B144" s="10" t="inlineStr">
         <is>
           <t>言語</t>
         </is>
       </c>
-      <c r="C144" s="10" t="inlineStr">
+      <c r="C144" s="11" t="inlineStr">
         <is>
           <t>使用単位系（ガロン・ポンド等）</t>
         </is>
       </c>
-      <c r="D144" s="9" t="inlineStr">
+      <c r="D144" s="10" t="inlineStr">
         <is>
           <t>記述〔ヒアリング〕</t>
         </is>
       </c>
-      <c r="E144" s="9" t="n">
+      <c r="E144" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="F144" s="10" t="inlineStr">
+      <c r="F144" s="11" t="inlineStr">
         <is>
           <t>単位換算エンジンの対象（ヤードポンド法対応）が漏れる。換算ミス＝数値誤りの温床。</t>
         </is>
       </c>
-      <c r="G144" s="10" t="inlineStr">
+      <c r="G144" s="11" t="inlineStr">
         <is>
           <t>単位換算エンジン</t>
         </is>
       </c>
-      <c r="H144" s="11" t="inlineStr">
+      <c r="H144" s="12" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="I144" s="10" t="inlineStr">
+      <c r="I144" s="11" t="inlineStr">
         <is>
           <t>「非メートル法あり」とみなし換算機能を実装。</t>
         </is>
       </c>
     </row>
     <row r="145" ht="52" customHeight="1">
-      <c r="A145" s="8" t="inlineStr">
+      <c r="A145" s="9" t="inlineStr">
         <is>
           <t>9-03</t>
         </is>
       </c>
-      <c r="B145" s="9" t="inlineStr">
+      <c r="B145" s="10" t="inlineStr">
         <is>
           <t>言語</t>
         </is>
       </c>
-      <c r="C145" s="10" t="inlineStr">
+      <c r="C145" s="11" t="inlineStr">
         <is>
           <t>現地会計年度と暦年報告のズレ</t>
         </is>
       </c>
-      <c r="D145" s="9" t="inlineStr">
+      <c r="D145" s="10" t="inlineStr">
         <is>
           <t>記述〔ヒアリング〕</t>
         </is>
       </c>
-      <c r="E145" s="9" t="n">
+      <c r="E145" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="F145" s="10" t="inlineStr">
+      <c r="F145" s="11" t="inlineStr">
         <is>
           <t>レポーティング期間変換（FY/CY変換）機能の要否が決められない。</t>
         </is>
       </c>
-      <c r="G145" s="10" t="inlineStr">
+      <c r="G145" s="11" t="inlineStr">
         <is>
           <t>期間変換機能</t>
         </is>
       </c>
-      <c r="H145" s="11" t="inlineStr">
+      <c r="H145" s="12" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="I145" s="10" t="inlineStr">
+      <c r="I145" s="11" t="inlineStr">
         <is>
           <t>「ズレあり」とみなし変換機能を実装。</t>
         </is>
       </c>
     </row>
     <row r="146" ht="52" customHeight="1">
-      <c r="A146" s="8" t="inlineStr">
+      <c r="A146" s="9" t="inlineStr">
         <is>
           <t>9-04</t>
         </is>
       </c>
-      <c r="B146" s="9" t="inlineStr">
+      <c r="B146" s="10" t="inlineStr">
         <is>
           <t>言語</t>
         </is>
       </c>
-      <c r="C146" s="10" t="inlineStr">
+      <c r="C146" s="11" t="inlineStr">
         <is>
           <t>通貨換算のレートと実施者</t>
         </is>
       </c>
-      <c r="D146" s="9" t="inlineStr">
+      <c r="D146" s="10" t="inlineStr">
         <is>
           <t>記述〔ヒアリング〕</t>
         </is>
       </c>
-      <c r="E146" s="9" t="n">
+      <c r="E146" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="F146" s="10" t="inlineStr">
+      <c r="F146" s="11" t="inlineStr">
         <is>
           <t>為替レートマスタ（レート種別・時点・責任者）が設計できない。</t>
         </is>
       </c>
-      <c r="G146" s="10" t="inlineStr">
+      <c r="G146" s="11" t="inlineStr">
         <is>
           <t>為替レートマスタ</t>
         </is>
       </c>
-      <c r="H146" s="11" t="inlineStr">
+      <c r="H146" s="12" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="I146" s="10" t="inlineStr">
+      <c r="I146" s="11" t="inlineStr">
         <is>
           <t>「レート不統一」とみなし本社一元管理で設計。</t>
         </is>
       </c>
     </row>
     <row r="147" ht="52" customHeight="1">
-      <c r="A147" s="8" t="inlineStr">
+      <c r="A147" s="9" t="inlineStr">
         <is>
           <t>9-05</t>
         </is>
       </c>
-      <c r="B147" s="9" t="inlineStr">
+      <c r="B147" s="10" t="inlineStr">
         <is>
           <t>制度</t>
         </is>
       </c>
-      <c r="C147" s="10" t="inlineStr">
+      <c r="C147" s="11" t="inlineStr">
         <is>
           <t>現地排出係数の種類と入手元</t>
         </is>
       </c>
-      <c r="D147" s="9" t="inlineStr">
+      <c r="D147" s="10" t="inlineStr">
         <is>
           <t>記述〔ヒアリング〕</t>
         </is>
       </c>
-      <c r="E147" s="9" t="n">
+      <c r="E147" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="F147" s="10" t="inlineStr">
+      <c r="F147" s="11" t="inlineStr">
         <is>
           <t>係数マスタの国別整備（出典・更新経路）ができず、海外分の算定が保証で説明不能。</t>
         </is>
       </c>
-      <c r="G147" s="10" t="inlineStr">
+      <c r="G147" s="11" t="inlineStr">
         <is>
           <t>国別係数マスタ</t>
         </is>
       </c>
-      <c r="H147" s="13" t="inlineStr">
+      <c r="H147" s="14" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="I147" s="10" t="inlineStr">
+      <c r="I147" s="11" t="inlineStr">
         <is>
           <t>「出典不明」とみなしIEA標準係数へ強制統一（現地当局報告との不整合リスクは当該拠点起因）。</t>
         </is>
       </c>
     </row>
     <row r="148" ht="52" customHeight="1">
-      <c r="A148" s="8" t="inlineStr">
+      <c r="A148" s="9" t="inlineStr">
         <is>
           <t>9-06</t>
         </is>
       </c>
-      <c r="B148" s="9" t="inlineStr">
+      <c r="B148" s="10" t="inlineStr">
         <is>
           <t>制度</t>
         </is>
       </c>
-      <c r="C148" s="10" t="inlineStr">
+      <c r="C148" s="11" t="inlineStr">
         <is>
           <t>現地の報告義務と本社報告との重複</t>
         </is>
       </c>
-      <c r="D148" s="9" t="inlineStr">
+      <c r="D148" s="10" t="inlineStr">
         <is>
           <t>記述〔ヒアリング〕</t>
         </is>
       </c>
-      <c r="E148" s="9" t="n">
+      <c r="E148" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="F148" s="10" t="inlineStr">
+      <c r="F148" s="11" t="inlineStr">
         <is>
           <t>ワンソース・マルチユースの対象（現地当局レポート）が漏れ、二重入力が温存される。</t>
         </is>
       </c>
-      <c r="G148" s="10" t="inlineStr">
+      <c r="G148" s="11" t="inlineStr">
         <is>
           <t>マルチユース出力設計</t>
         </is>
       </c>
-      <c r="H148" s="11" t="inlineStr">
+      <c r="H148" s="12" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="I148" s="10" t="inlineStr">
+      <c r="I148" s="11" t="inlineStr">
         <is>
           <t>「重複なし」とみなし現地レポート出力を対象外化。</t>
         </is>
       </c>
     </row>
     <row r="149" ht="52" customHeight="1">
-      <c r="A149" s="8" t="inlineStr">
+      <c r="A149" s="9" t="inlineStr">
         <is>
           <t>9-07</t>
         </is>
       </c>
-      <c r="B149" s="9" t="inlineStr">
+      <c r="B149" s="10" t="inlineStr">
         <is>
           <t>制度</t>
         </is>
       </c>
-      <c r="C149" s="10" t="inlineStr">
+      <c r="C149" s="11" t="inlineStr">
         <is>
           <t>CSRD・現地開示・顧客ESG要請の有無</t>
         </is>
       </c>
-      <c r="D149" s="9" t="inlineStr">
+      <c r="D149" s="10" t="inlineStr">
         <is>
           <t>選択+補足〔ヒアリング〕</t>
         </is>
       </c>
-      <c r="E149" s="9" t="n">
+      <c r="E149" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="F149" s="10" t="inlineStr">
+      <c r="F149" s="11" t="inlineStr">
         <is>
           <t>マルチ基準対応（CSRD等）の拡張性要件が漏れ、将来の追加開発費用が増大。</t>
         </is>
       </c>
-      <c r="G149" s="10" t="inlineStr">
+      <c r="G149" s="11" t="inlineStr">
         <is>
           <t>拡張性要件</t>
         </is>
       </c>
-      <c r="H149" s="11" t="inlineStr">
+      <c r="H149" s="12" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="I149" s="10" t="inlineStr">
+      <c r="I149" s="11" t="inlineStr">
         <is>
           <t>「追加要求なし」とみなす（後日判明時の追加開発は当該拠点起因）。</t>
         </is>
       </c>
     </row>
     <row r="150" ht="52" customHeight="1">
-      <c r="A150" s="8" t="inlineStr">
+      <c r="A150" s="9" t="inlineStr">
         <is>
           <t>9-08</t>
         </is>
       </c>
-      <c r="B150" s="9" t="inlineStr">
+      <c r="B150" s="10" t="inlineStr">
         <is>
           <t>制度</t>
         </is>
       </c>
-      <c r="C150" s="10" t="inlineStr">
+      <c r="C150" s="11" t="inlineStr">
         <is>
           <t>データ越境移転の制約（中国データ安全法等）</t>
         </is>
       </c>
-      <c r="D150" s="9" t="inlineStr">
+      <c r="D150" s="10" t="inlineStr">
         <is>
           <t>選択+補足〔ヒアリング〕</t>
         </is>
       </c>
-      <c r="E150" s="9" t="n">
+      <c r="E150" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="F150" s="10" t="inlineStr">
+      <c r="F150" s="11" t="inlineStr">
         <is>
           <t>アーキテクチャの根幹（リージョン設計・データ保管場所）とベンダー足切り条件が確定できない。稼働後に発覚すると構成変更＝最大級の手戻り＋法令違反リスク。</t>
         </is>
       </c>
-      <c r="G150" s="10" t="inlineStr">
+      <c r="G150" s="11" t="inlineStr">
         <is>
           <t>リージョン設計・法令対応・ベンダー要件</t>
         </is>
       </c>
-      <c r="H150" s="13" t="inlineStr">
+      <c r="H150" s="14" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="I150" s="10" t="inlineStr">
+      <c r="I150" s="11" t="inlineStr">
         <is>
           <t>「制約あり」とみなしリージョン分離可能な構成を必須化（費用増）。法令違反リスクの帰責は明確化必須。</t>
         </is>
       </c>
     </row>
     <row r="151" ht="52" customHeight="1">
-      <c r="A151" s="8" t="inlineStr">
+      <c r="A151" s="9" t="inlineStr">
         <is>
           <t>9-09</t>
         </is>
       </c>
-      <c r="B151" s="9" t="inlineStr">
+      <c r="B151" s="10" t="inlineStr">
         <is>
           <t>運用</t>
         </is>
       </c>
-      <c r="C151" s="10" t="inlineStr">
+      <c r="C151" s="11" t="inlineStr">
         <is>
           <t>現地事情による欠測・遅延の頻度</t>
         </is>
       </c>
-      <c r="D151" s="9" t="inlineStr">
+      <c r="D151" s="10" t="inlineStr">
         <is>
           <t>記述〔ヒアリング〕</t>
         </is>
       </c>
-      <c r="E151" s="9" t="n">
+      <c r="E151" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="F151" s="10" t="inlineStr">
+      <c r="F151" s="11" t="inlineStr">
         <is>
           <t>欠測例外設計（現地固有パターン）が漏れる。</t>
         </is>
       </c>
-      <c r="G151" s="10" t="inlineStr">
+      <c r="G151" s="11" t="inlineStr">
         <is>
           <t>例外設計</t>
         </is>
       </c>
-      <c r="H151" s="11" t="inlineStr">
+      <c r="H151" s="12" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="I151" s="10" t="inlineStr">
+      <c r="I151" s="11" t="inlineStr">
         <is>
           <t>「頻発」とみなす。</t>
         </is>
       </c>
     </row>
     <row r="152" ht="52" customHeight="1">
-      <c r="A152" s="8" t="inlineStr">
+      <c r="A152" s="9" t="inlineStr">
         <is>
           <t>9-10</t>
         </is>
       </c>
-      <c r="B152" s="9" t="inlineStr">
+      <c r="B152" s="10" t="inlineStr">
         <is>
           <t>運用</t>
         </is>
       </c>
-      <c r="C152" s="10" t="inlineStr">
+      <c r="C152" s="11" t="inlineStr">
         <is>
           <t>現地委託先からのデータ・証憑の入手性</t>
         </is>
       </c>
-      <c r="D152" s="9" t="inlineStr">
+      <c r="D152" s="10" t="inlineStr">
         <is>
           <t>記述〔ヒアリング〕</t>
         </is>
       </c>
-      <c r="E152" s="9" t="n">
+      <c r="E152" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="F152" s="10" t="inlineStr">
+      <c r="F152" s="11" t="inlineStr">
         <is>
           <t>第三者データの取得可能性と契約整備の要否が不明。</t>
         </is>
       </c>
-      <c r="G152" s="10" t="inlineStr">
+      <c r="G152" s="11" t="inlineStr">
         <is>
           <t>外部データ取得・契約整備</t>
         </is>
       </c>
-      <c r="H152" s="11" t="inlineStr">
+      <c r="H152" s="12" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="I152" s="10" t="inlineStr">
+      <c r="I152" s="11" t="inlineStr">
         <is>
           <t>「入手困難」とみなし契約整備タスクを追加。</t>
         </is>
       </c>
     </row>
     <row r="153" ht="52" customHeight="1">
-      <c r="A153" s="8" t="inlineStr">
+      <c r="A153" s="9" t="inlineStr">
         <is>
           <t>9-11</t>
         </is>
       </c>
-      <c r="B153" s="9" t="inlineStr">
+      <c r="B153" s="10" t="inlineStr">
         <is>
           <t>運用</t>
         </is>
       </c>
-      <c r="C153" s="10" t="inlineStr">
+      <c r="C153" s="11" t="inlineStr">
         <is>
           <t>現地経営層の関与度と承認の実現性</t>
         </is>
       </c>
-      <c r="D153" s="9" t="inlineStr">
+      <c r="D153" s="10" t="inlineStr">
         <is>
           <t>記述〔ヒアリング〕</t>
         </is>
       </c>
-      <c r="E153" s="9" t="n">
+      <c r="E153" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="F153" s="10" t="inlineStr">
+      <c r="F153" s="11" t="inlineStr">
         <is>
           <t>承認階層に現地社長を組み込めるかが不明で、グローバル統制設計が机上になる。</t>
         </is>
       </c>
-      <c r="G153" s="10" t="inlineStr">
+      <c r="G153" s="11" t="inlineStr">
         <is>
           <t>グローバル承認設計</t>
         </is>
       </c>
-      <c r="H153" s="11" t="inlineStr">
+      <c r="H153" s="12" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="I153" s="10" t="inlineStr">
+      <c r="I153" s="11" t="inlineStr">
         <is>
           <t>「関与なし」とみなし本社側承認で代替。</t>
         </is>
       </c>
     </row>
     <row r="154" ht="52" customHeight="1">
-      <c r="A154" s="8" t="inlineStr">
+      <c r="A154" s="9" t="inlineStr">
         <is>
           <t>9-12</t>
         </is>
       </c>
-      <c r="B154" s="9" t="inlineStr">
+      <c r="B154" s="10" t="inlineStr">
         <is>
           <t>運用</t>
         </is>
       </c>
-      <c r="C154" s="10" t="inlineStr">
+      <c r="C154" s="11" t="inlineStr">
         <is>
           <t>時差・現地祝日の締切影響</t>
         </is>
       </c>
-      <c r="D154" s="9" t="inlineStr">
+      <c r="D154" s="10" t="inlineStr">
         <is>
           <t>記述〔ヒアリング〕</t>
         </is>
       </c>
-      <c r="E154" s="9" t="n">
+      <c r="E154" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="F154" s="10" t="inlineStr">
+      <c r="F154" s="11" t="inlineStr">
         <is>
           <t>締切カレンダー（タイムゾーン・祝日）設計の精度が下がる。</t>
         </is>
       </c>
-      <c r="G154" s="10" t="inlineStr">
+      <c r="G154" s="11" t="inlineStr">
         <is>
           <t>締切カレンダー</t>
         </is>
       </c>
-      <c r="H154" s="14" t="inlineStr">
+      <c r="H154" s="15" t="inlineStr">
         <is>
           <t>低</t>
         </is>
       </c>
-      <c r="I154" s="10" t="inlineStr">
+      <c r="I154" s="11" t="inlineStr">
         <is>
           <t>「影響あり」とみなし現地優先で設計。</t>
         </is>
       </c>
     </row>
     <row r="155" ht="52" customHeight="1">
-      <c r="A155" s="8" t="inlineStr">
+      <c r="A155" s="9" t="inlineStr">
         <is>
           <t>9-13</t>
         </is>
       </c>
-      <c r="B155" s="9" t="inlineStr">
+      <c r="B155" s="10" t="inlineStr">
         <is>
           <t>運用</t>
         </is>
       </c>
-      <c r="C155" s="10" t="inlineStr">
+      <c r="C155" s="11" t="inlineStr">
         <is>
           <t>本社未報告の現地環境・安全データ</t>
         </is>
       </c>
-      <c r="D155" s="9" t="inlineStr">
+      <c r="D155" s="10" t="inlineStr">
         <is>
           <t>選択+補足〔ヒアリング〕</t>
         </is>
       </c>
-      <c r="E155" s="9" t="n">
+      <c r="E155" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="F155" s="10" t="inlineStr">
+      <c r="F155" s="11" t="inlineStr">
         <is>
           <t>バウンダリ漏れ＝保証の完全性違反の火種が残る。後日発覚すると開示訂正リスク。</t>
         </is>
       </c>
-      <c r="G155" s="10" t="inlineStr">
+      <c r="G155" s="11" t="inlineStr">
         <is>
           <t>バウンダリ完全性</t>
         </is>
       </c>
-      <c r="H155" s="13" t="inlineStr">
+      <c r="H155" s="14" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="I155" s="10" t="inlineStr">
+      <c r="I155" s="11" t="inlineStr">
         <is>
           <t>「未報告データあり」とみなし全量調査を指示（未申告分の後日発覚は当該拠点起因）。</t>
         </is>
       </c>
     </row>
     <row r="156" ht="52" customHeight="1">
-      <c r="A156" s="8" t="inlineStr">
+      <c r="A156" s="9" t="inlineStr">
         <is>
           <t>9-14</t>
         </is>
       </c>
-      <c r="B156" s="9" t="inlineStr">
+      <c r="B156" s="10" t="inlineStr">
         <is>
           <t>運用</t>
         </is>
       </c>
-      <c r="C156" s="10" t="inlineStr">
+      <c r="C156" s="11" t="inlineStr">
         <is>
           <t>現地語UI・サポートなしでの運用可否</t>
         </is>
       </c>
-      <c r="D156" s="9" t="inlineStr">
+      <c r="D156" s="10" t="inlineStr">
         <is>
           <t>選択+補足〔ヒアリング〕</t>
         </is>
       </c>
-      <c r="E156" s="9" t="n">
+      <c r="E156" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="F156" s="10" t="inlineStr">
+      <c r="F156" s="11" t="inlineStr">
         <is>
           <t>C-19の詳細。</t>
         </is>
       </c>
-      <c r="G156" s="10" t="inlineStr">
+      <c r="G156" s="11" t="inlineStr">
         <is>
           <t>多言語要件</t>
         </is>
       </c>
-      <c r="H156" s="13" t="inlineStr">
+      <c r="H156" s="14" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="I156" s="10" t="inlineStr">
+      <c r="I156" s="11" t="inlineStr">
         <is>
           <t>「困難」とみなし多言語要件を必須化。</t>
         </is>
       </c>
     </row>
     <row r="157" ht="17" customHeight="1">
-      <c r="A157" s="6" t="inlineStr">
+      <c r="A157" s="7" t="inlineStr">
         <is>
           <t>10. 難所チェック（全拠点・10-01〜10-14, F1〜F3）</t>
         </is>
       </c>
-      <c r="B157" s="7" t="n"/>
-      <c r="C157" s="7" t="n"/>
-      <c r="D157" s="7" t="n"/>
-      <c r="E157" s="7" t="n"/>
-      <c r="F157" s="7" t="n"/>
-      <c r="G157" s="7" t="n"/>
-      <c r="H157" s="7" t="n"/>
-      <c r="I157" s="7" t="n"/>
+      <c r="B157" s="8" t="n"/>
+      <c r="C157" s="8" t="n"/>
+      <c r="D157" s="8" t="n"/>
+      <c r="E157" s="8" t="n"/>
+      <c r="F157" s="8" t="n"/>
+      <c r="G157" s="8" t="n"/>
+      <c r="H157" s="8" t="n"/>
+      <c r="I157" s="8" t="n"/>
     </row>
     <row r="158" ht="52" customHeight="1">
-      <c r="A158" s="8" t="inlineStr">
+      <c r="A158" s="9" t="inlineStr">
         <is>
           <t>10-01〜14</t>
         </is>
       </c>
-      <c r="B158" s="9" t="inlineStr">
+      <c r="B158" s="10" t="inlineStr">
         <is>
           <t>難所症状</t>
         </is>
       </c>
-      <c r="C158" s="10" t="inlineStr">
+      <c r="C158" s="11" t="inlineStr">
         <is>
           <t>5つの難所への当てはまり度（14症状）</t>
         </is>
       </c>
-      <c r="D158" s="12" t="inlineStr">
+      <c r="D158" s="13" t="inlineStr">
         <is>
           <t>選択のみ（14問合計）</t>
         </is>
       </c>
-      <c r="E158" s="9" t="n">
+      <c r="E158" s="10" t="n">
         <v>15</v>
       </c>
-      <c r="F158" s="10" t="inlineStr">
+      <c r="F158" s="11" t="inlineStr">
         <is>
           <t>難所別の症状マップ（どの拠点がどの難所で苦しんでいるか）が作れず、機能要件の優先順位・拠点Tier設計・重点統制拠点の選定がすべて推測になる。</t>
         </is>
       </c>
-      <c r="G158" s="10" t="inlineStr">
+      <c r="G158" s="11" t="inlineStr">
         <is>
           <t>機能優先度・拠点Tier設計・統制重点化</t>
         </is>
       </c>
-      <c r="H158" s="11" t="inlineStr">
+      <c r="H158" s="12" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="I158" s="10" t="inlineStr">
+      <c r="I158" s="11" t="inlineStr">
         <is>
           <t>全症状「3（中程度）」とみなし平均的な設計とする（当該拠点の実態が重い場合の対応漏れは当該拠点起因）。</t>
         </is>
       </c>
     </row>
     <row r="159" ht="52" customHeight="1">
-      <c r="A159" s="8" t="inlineStr">
+      <c r="A159" s="9" t="inlineStr">
         <is>
           <t>10-F1〜F3</t>
         </is>
       </c>
-      <c r="B159" s="9" t="inlineStr">
+      <c r="B159" s="10" t="inlineStr">
         <is>
           <t>自由記述</t>
         </is>
       </c>
-      <c r="C159" s="10" t="inlineStr">
+      <c r="C159" s="11" t="inlineStr">
         <is>
           <t>最大のペイン・要望トップ3・残してほしい点</t>
         </is>
       </c>
-      <c r="D159" s="9" t="inlineStr">
+      <c r="D159" s="10" t="inlineStr">
         <is>
           <t>自由記述（3問合計）</t>
         </is>
       </c>
-      <c r="E159" s="9" t="n">
+      <c r="E159" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="F159" s="10" t="inlineStr">
+      <c r="F159" s="11" t="inlineStr">
         <is>
           <t>現場の受容性設計（何を残し何を変えるか）の材料を失い、定着リスクが高まる。</t>
         </is>
       </c>
-      <c r="G159" s="10" t="inlineStr">
+      <c r="G159" s="11" t="inlineStr">
         <is>
           <t>定着計画・UI設計</t>
         </is>
       </c>
-      <c r="H159" s="14" t="inlineStr">
+      <c r="H159" s="15" t="inlineStr">
         <is>
           <t>低</t>
         </is>
       </c>
-      <c r="I159" s="10" t="inlineStr">
+      <c r="I159" s="11" t="inlineStr">
         <is>
           <t>「特記なし」とみなす。</t>
         </is>
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="6" t="inlineStr">
+      <c r="A161" s="7" t="inlineStr">
         <is>
           <t>【所要時間の集計（適正目安）】</t>
         </is>
       </c>
-      <c r="B161" s="7" t="n"/>
-      <c r="C161" s="7" t="n"/>
-      <c r="D161" s="7" t="n"/>
-      <c r="E161" s="7" t="n"/>
-      <c r="F161" s="7" t="n"/>
-      <c r="G161" s="7" t="n"/>
-      <c r="H161" s="7" t="n"/>
-      <c r="I161" s="7" t="n"/>
+      <c r="B161" s="8" t="n"/>
+      <c r="C161" s="8" t="n"/>
+      <c r="D161" s="8" t="n"/>
+      <c r="E161" s="8" t="n"/>
+      <c r="F161" s="8" t="n"/>
+      <c r="G161" s="8" t="n"/>
+      <c r="H161" s="8" t="n"/>
+      <c r="I161" s="8" t="n"/>
     </row>
     <row r="162" ht="46" customHeight="1">
       <c r="A162" s="2" t="inlineStr">
@@ -7533,20 +7543,28 @@
     <row r="163" ht="46" customHeight="1">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>■ 選抜拠点ヒアリング（シート3〜9・拠点での記入不要）: 台本全量で約449分 ≒ 約7.5時間。ただし実際は該当領域のみに絞って実施するため、1拠点あたり2時間×1〜2回を想定。事務局が聞き取り・記録するため拠点側の事前準備は原則不要。</t>
+          <t>■ 選抜拠点ヒアリング（シート3〜9・拠点での記入不要）: 台本の101問すべてを実施すると約449分 ≒ 約7.5時間かかる。これは全拠点記入分（約2.4時間）と別建てで発生するため、選抜拠点が台本を全問実施すると合計は約590分 ≒ **約9.8時間**に達する（記入分と単純に別枠と考えると、まさに約10時間規模になる）。</t>
         </is>
       </c>
     </row>
     <row r="164" ht="46" customHeight="1">
       <c r="A164" s="2" t="inlineStr">
         <is>
+          <t>■ したがって選抜拠点ヒアリングは101問の全量実施を前提にせず、事前に重点セクションへ絞り込むことが必須。優先順位の目安: ①本シートで影響度「高」の設問（4-02係数出典、4-09計算Excelの属人化、5-08証憑不存在、6-08確定ロック、9-08データ越境制約等）を最優先で聞く、②C-01〜C-37（コア設問）の回答で「一部ある・古い／わからない／困難」等の要注意回答があったカテゴリのみ深掘りする、③言語・組織固有の設問（海外拠点のみ対象の9番シート等）は該当拠点のみに限定する。この絞り込みにより、実施時間は1拠点あたり2時間×1〜2回（計2〜4時間）に収まる想定。全拠点記入分（約2.4時間）と合わせて選抜拠点の総所要は約4.4〜6.4時間となる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="165" ht="46" customHeight="1">
+      <c r="A165" s="2" t="inlineStr">
+        <is>
           <t>■ 適正見積りの前提: 選択のみ=1分／選択+補足=3分／記述=5分／工数集計=15分／インベントリ=60分。標準的な回答速度での想定（インベントリは既存報告様式を参照しながらの転記を前提）。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="16">
+  <mergeCells count="17">
     <mergeCell ref="A64:I64"/>
+    <mergeCell ref="A165:I165"/>
     <mergeCell ref="A43:I43"/>
     <mergeCell ref="A142:I142"/>
     <mergeCell ref="A1:G1"/>
